--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -57,13 +57,13 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-17T15:32:01+00:00</t>
+    <t>2023-10-31T15:37:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>JPSys</t>
+    <t>VA</t>
   </si>
   <si>
     <t>Contact</t>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-31T15:37:13+00:00</t>
+    <t>2023-11-01T18:52:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for Use Case Practitioner</t>
+    <t>This StructureDefinition contains the maps for VistA NEW PERSON (file 200) to FHIR Practitioner</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2888" uniqueCount="543">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2887" uniqueCount="544">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-01T18:52:48+00:00</t>
+    <t>2023-11-08T21:21:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1364,6 +1364,9 @@
   </si>
   <si>
     <t>ISO 3166 3 letter codes can be used in place of a human readable country name.</t>
+  </si>
+  <si>
+    <t>http://va.gov/fhir/ValueSet/VFPractitionerCountry</t>
   </si>
   <si>
     <t>Address.country</t>
@@ -8492,13 +8495,11 @@
         <v>38</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="Y54" t="s" s="2">
-        <v>38</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="Y54" s="2"/>
       <c r="Z54" t="s" s="2">
-        <v>38</v>
+        <v>433</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>38</v>
@@ -8516,7 +8517,7 @@
         <v>38</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>36</v>
@@ -8531,13 +8532,13 @@
         <v>59</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>38</v>
@@ -8546,15 +8547,15 @@
         <v>416</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8580,14 +8581,14 @@
         <v>170</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>38</v>
@@ -8600,7 +8601,7 @@
         <v>38</v>
       </c>
       <c r="T55" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="U55" t="s" s="2">
         <v>38</v>
@@ -8636,7 +8637,7 @@
         <v>38</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>36</v>
@@ -8651,7 +8652,7 @@
         <v>59</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>286</v>
@@ -8671,10 +8672,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8789,10 +8790,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8909,10 +8910,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9021,18 +9022,18 @@
         <v>38</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9143,18 +9144,18 @@
         <v>38</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9180,14 +9181,14 @@
         <v>67</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>38</v>
@@ -9215,10 +9216,10 @@
         <v>132</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>38</v>
@@ -9236,7 +9237,7 @@
         <v>38</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>36</v>
@@ -9251,13 +9252,13 @@
         <v>59</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>38</v>
@@ -9271,10 +9272,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9297,17 +9298,17 @@
         <v>48</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>38</v>
@@ -9356,7 +9357,7 @@
         <v>38</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>36</v>
@@ -9371,30 +9372,30 @@
         <v>59</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9417,17 +9418,17 @@
         <v>38</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>38</v>
@@ -9476,7 +9477,7 @@
         <v>38</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>36</v>
@@ -9494,10 +9495,10 @@
         <v>38</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>38</v>
@@ -9511,10 +9512,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9537,13 +9538,13 @@
         <v>38</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9594,7 +9595,7 @@
         <v>38</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>36</v>
@@ -9609,13 +9610,13 @@
         <v>59</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>38</v>
@@ -9629,10 +9630,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9747,10 +9748,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9867,14 +9868,14 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -9896,10 +9897,10 @@
         <v>93</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="N66" t="s" s="2">
         <v>96</v>
@@ -9954,7 +9955,7 @@
         <v>38</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>36</v>
@@ -9989,10 +9990,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10018,14 +10019,14 @@
         <v>105</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>38</v>
@@ -10074,7 +10075,7 @@
         <v>38</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>36</v>
@@ -10092,7 +10093,7 @@
         <v>38</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>38</v>
@@ -10109,10 +10110,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10138,10 +10139,10 @@
         <v>138</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10168,13 +10169,13 @@
         <v>38</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>38</v>
@@ -10192,7 +10193,7 @@
         <v>38</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>47</v>
@@ -10210,10 +10211,10 @@
         <v>38</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>38</v>
@@ -10227,10 +10228,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10345,10 +10346,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10465,10 +10466,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10491,19 +10492,19 @@
         <v>48</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>38</v>
@@ -10552,7 +10553,7 @@
         <v>38</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>36</v>
@@ -10567,10 +10568,10 @@
         <v>59</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>38</v>
@@ -10587,10 +10588,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10616,16 +10617,16 @@
         <v>117</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>38</v>
@@ -10674,7 +10675,7 @@
         <v>38</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>36</v>
@@ -10689,10 +10690,10 @@
         <v>59</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>38</v>
@@ -10704,15 +10705,15 @@
         <v>38</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10738,14 +10739,14 @@
         <v>170</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>38</v>
@@ -10794,7 +10795,7 @@
         <v>38</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>36</v>
@@ -10812,10 +10813,10 @@
         <v>38</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>38</v>
@@ -10829,10 +10830,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10858,10 +10859,10 @@
         <v>198</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -10912,7 +10913,7 @@
         <v>38</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>36</v>
@@ -10930,7 +10931,7 @@
         <v>38</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>38</v>
@@ -10947,10 +10948,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10976,16 +10977,16 @@
         <v>138</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>38</v>
@@ -11034,7 +11035,7 @@
         <v>38</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>36</v>
@@ -11049,13 +11050,13 @@
         <v>59</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>38</v>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-08T21:21:15+00:00</t>
+    <t>2023-11-08T21:56:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-09T22:38:39+00:00</t>
+    <t>2023-11-14T14:54:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-14T14:54:31+00:00</t>
+    <t>2023-11-14T17:25:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$76</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$92</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2929" uniqueCount="586">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3532" uniqueCount="628">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.0</t>
+    <t>0.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-14T17:25:19+00:00</t>
+    <t>2023-11-15T12:04:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -243,10 +243,10 @@
     <t>Mapping: FiveWs Pattern Mapping</t>
   </si>
   <si>
+    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
+  </si>
+  <si>
     <t>Mapping: Clinical Data Warehouse (CDW)</t>
-  </si>
-  <si>
-    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
   </si>
   <si>
     <t xml:space="preserve">Provider
@@ -666,10 +666,10 @@
     <t>./Value</t>
   </si>
   <si>
+    <t>415: source value from NEW PERSON - IEN (#200-.001)</t>
+  </si>
+  <si>
     <t>SStaff.PrescribingProvider.VPID</t>
-  </si>
-  <si>
-    <t>415: source value from NEW PERSON - IEN (#200-.001)</t>
   </si>
   <si>
     <t>Practitioner.identifier.period</t>
@@ -695,68 +695,6 @@
   </si>
   <si>
     <t>./StartDate and ./EndDate</t>
-  </si>
-  <si>
-    <t>Practitioner.identifier.period.id</t>
-  </si>
-  <si>
-    <t>Practitioner.identifier.period.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.identifier.period.start</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dateTime
-</t>
-  </si>
-  <si>
-    <t>Starting time with inclusive boundary</t>
-  </si>
-  <si>
-    <t>The start of the period. The boundary is inclusive.</t>
-  </si>
-  <si>
-    <t>If the low element is missing, the meaning is that the low boundary is not known.</t>
-  </si>
-  <si>
-    <t>Period.start</t>
-  </si>
-  <si>
-    <t xml:space="preserve">per-1
-</t>
-  </si>
-  <si>
-    <t>DR.1</t>
-  </si>
-  <si>
-    <t>./low</t>
-  </si>
-  <si>
-    <t>380: source value from NEW PERSON - EFFECTIVE DATE/TIME (#200-42) case For NPI only</t>
-  </si>
-  <si>
-    <t>Practitioner.identifier.period.end</t>
-  </si>
-  <si>
-    <t>End time with inclusive boundary, if not ongoing</t>
-  </si>
-  <si>
-    <t>The end of the period. If the end of the period is missing, it means no end was known or planned at the time the instance was created. The start may be in the past, and the end date in the future, which means that period is expected/planned to end at that time.</t>
-  </si>
-  <si>
-    <t>The high value includes any matching date/time. i.e. 2012-02-03T10:00:00 is in a period that has an end value of 2012-02-03.</t>
-  </si>
-  <si>
-    <t>If the end of the period is missing, it means that the period is ongoing</t>
-  </si>
-  <si>
-    <t>Period.end</t>
-  </si>
-  <si>
-    <t>DR.2</t>
-  </si>
-  <si>
-    <t>./high</t>
   </si>
   <si>
     <t>Practitioner.identifier.assigner</t>
@@ -796,6 +734,111 @@
     <t>&lt;valueIdentifier xmlns="http://hl7.org/fhir"&gt;
   &lt;system value="http://hl7.org/fhir/sid/us-npi"/&gt;
 &lt;/valueIdentifier&gt;</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:NPI.id</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:NPI.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:NPI.use</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:NPI.type</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:NPI.system</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:NPI.value</t>
+  </si>
+  <si>
+    <t>376: source value from NEW PERSON - NPI (#200-41.99)</t>
+  </si>
+  <si>
+    <t>SStaff.PrescribingProvider.NPI
+SStaff.SStaff.NPI</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:NPI.period</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:NPI.period.id</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier.period.id</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:NPI.period.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier.period.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:NPI.period.start</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier.period.start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dateTime
+</t>
+  </si>
+  <si>
+    <t>Starting time with inclusive boundary</t>
+  </si>
+  <si>
+    <t>The start of the period. The boundary is inclusive.</t>
+  </si>
+  <si>
+    <t>If the low element is missing, the meaning is that the low boundary is not known.</t>
+  </si>
+  <si>
+    <t>Period.start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">per-1
+</t>
+  </si>
+  <si>
+    <t>DR.1</t>
+  </si>
+  <si>
+    <t>./low</t>
+  </si>
+  <si>
+    <t>380: source value from NEW PERSON - EFFECTIVE DATE/TIME (#200-42) case For NPI only</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:NPI.period.end</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier.period.end</t>
+  </si>
+  <si>
+    <t>End time with inclusive boundary, if not ongoing</t>
+  </si>
+  <si>
+    <t>The end of the period. If the end of the period is missing, it means no end was known or planned at the time the instance was created. The start may be in the past, and the end date in the future, which means that period is expected/planned to end at that time.</t>
+  </si>
+  <si>
+    <t>The high value includes any matching date/time. i.e. 2012-02-03T10:00:00 is in a period that has an end value of 2012-02-03.</t>
+  </si>
+  <si>
+    <t>If the end of the period is missing, it means that the period is ongoing</t>
+  </si>
+  <si>
+    <t>Period.end</t>
+  </si>
+  <si>
+    <t>DR.2</t>
+  </si>
+  <si>
+    <t>./high</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:NPI.assigner</t>
   </si>
   <si>
     <t>Practitioner.active</t>
@@ -1133,13 +1176,13 @@
     <t>./url</t>
   </si>
   <si>
+    <t>383: source value from NEW PERSON - PHONE (HOME) (#200-.131)</t>
+  </si>
+  <si>
     <t>SStaff.PrescribingProvider.HomePhone
 SStaff.SStaff.HomePhone</t>
   </si>
   <si>
-    <t>383: source value from NEW PERSON - PHONE (HOME) (#200-.131)</t>
-  </si>
-  <si>
     <t>Practitioner.telecom.use</t>
   </si>
   <si>
@@ -1341,10 +1384,10 @@
     <t>./StreetAddress (newline delimitted)</t>
   </si>
   <si>
+    <t>404: source value from NEW PERSON - TEMPORARY ADDRESS 3 (#200-.1213)</t>
+  </si>
+  <si>
     <t>SStaff.SStaff.TemporaryAddress3</t>
-  </si>
-  <si>
-    <t>404: source value from NEW PERSON - TEMPORARY ADDRESS 3 (#200-.1213)</t>
   </si>
   <si>
     <t>Practitioner.address.city</t>
@@ -1375,10 +1418,10 @@
     <t>./Jurisdiction</t>
   </si>
   <si>
+    <t>405: source value from NEW PERSON - TEMPORARY CITY (#200-.1214)</t>
+  </si>
+  <si>
     <t>SStaff.SStaff.TemporaryCity</t>
-  </si>
-  <si>
-    <t>405: source value from NEW PERSON - TEMPORARY CITY (#200-.1214)</t>
   </si>
   <si>
     <t>Practitioner.address.district</t>
@@ -1440,10 +1483,10 @@
     <t>./Sites</t>
   </si>
   <si>
+    <t>406: source value from NEW PERSON - TEMPORARY STATE (#200-.1215)</t>
+  </si>
+  <si>
     <t>SStaff.SStaff.TemporaryStateName</t>
-  </si>
-  <si>
-    <t>406: source value from NEW PERSON - TEMPORARY STATE (#200-.1215)</t>
   </si>
   <si>
     <t>Practitioner.address.postalCode</t>
@@ -1474,12 +1517,12 @@
     <t>./PostalIdentificationCode</t>
   </si>
   <si>
+    <t>407: source value from NEW PERSON - TEMPORARY ZIP CODE (#200-.1216)</t>
+  </si>
+  <si>
     <t>SStaff.SStaff.TemporaryZipCode</t>
   </si>
   <si>
-    <t>407: source value from NEW PERSON - TEMPORARY ZIP CODE (#200-.1216)</t>
-  </si>
-  <si>
     <t>Practitioner.address.country</t>
   </si>
   <si>
@@ -1507,7 +1550,93 @@
     <t>./Country</t>
   </si>
   <si>
-    <t>1533: fixed value without value? if NEW PERSON - STATE (#200-.1215) case NULL</t>
+    <t>1532: terminologyMaps using VF_PractitionerCountry on NEW PERSON - STATE (#200-.1215) case not NULL</t>
+  </si>
+  <si>
+    <t>Practitioner.address.country.id</t>
+  </si>
+  <si>
+    <t>xml:id (or equivalent in JSON)</t>
+  </si>
+  <si>
+    <t>unique id for the element within a resource (for internal references)</t>
+  </si>
+  <si>
+    <t>Practitioner.address.country.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.address.country.extension.id</t>
+  </si>
+  <si>
+    <t>Practitioner.address.country.extension.extension</t>
+  </si>
+  <si>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
+  </si>
+  <si>
+    <t>Practitioner.address.country.extension.url</t>
+  </si>
+  <si>
+    <t>identifies the meaning of the extension</t>
+  </si>
+  <si>
+    <t>Source of the definition for the extension code - a logical name or a URL.</t>
+  </si>
+  <si>
+    <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
+  </si>
+  <si>
+    <t>Extension.url</t>
+  </si>
+  <si>
+    <t>Practitioner.address.country.extension.value[x]</t>
+  </si>
+  <si>
+    <t>Value of extension</t>
+  </si>
+  <si>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">type:$this}
+</t>
+  </si>
+  <si>
+    <t>closed</t>
+  </si>
+  <si>
+    <t>Extension.value[x]</t>
+  </si>
+  <si>
+    <t>Practitioner.address.country.extension.value[x]:valueCode</t>
+  </si>
+  <si>
+    <t>valueCode</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+inv-21:1531: fixed value "unknown" {null}inv-22:1533: fixed value "unknown" {null}</t>
+  </si>
+  <si>
+    <t>1533: fixed value = unknown if NEW PERSON - STATE (#200-.1215) case NULL</t>
+  </si>
+  <si>
+    <t>Practitioner.address.country.value</t>
+  </si>
+  <si>
+    <t>Primitive value for string</t>
+  </si>
+  <si>
+    <t>The actual value</t>
+  </si>
+  <si>
+    <t>1048576</t>
+  </si>
+  <si>
+    <t>string.value</t>
   </si>
   <si>
     <t>Practitioner.address.period</t>
@@ -1543,19 +1672,19 @@
     <t>Practitioner.address.period.start</t>
   </si>
   <si>
+    <t>408: source value from NEW PERSON - START DATE OF TEMP ADDRES (#200-.1217)</t>
+  </si>
+  <si>
     <t>SStaff.SStaff.TemporaryAddressStartDate</t>
   </si>
   <si>
-    <t>408: source value from NEW PERSON - START DATE OF TEMP ADDRES (#200-.1217)</t>
-  </si>
-  <si>
     <t>Practitioner.address.period.end</t>
   </si>
   <si>
+    <t>409: source value from NEW PERSON - END DATE OF TEMP ADDRESS (#200-.1218)</t>
+  </si>
+  <si>
     <t>SStaff.SStaff.TemporaryAddressEndDate</t>
-  </si>
-  <si>
-    <t>409: source value from NEW PERSON - END DATE OF TEMP ADDRESS (#200-.1218)</t>
   </si>
   <si>
     <t>Practitioner.gender</t>
@@ -1610,11 +1739,11 @@
     <t>(not represented in ServD)</t>
   </si>
   <si>
+    <t>394: source value from NEW PERSON - DOB (#200-5)</t>
+  </si>
+  <si>
     <t>SStaff.SStaff.DateOfBirth
 Staff.Staff.DateofBirth</t>
-  </si>
-  <si>
-    <t>394: source value from NEW PERSON - DOB (#200-5)</t>
   </si>
   <si>
     <t>Practitioner.photo</t>
@@ -2149,11 +2278,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP76"/>
+  <dimension ref="A1:AP92"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="40.70703125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="40.70703125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="55.0546875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="46.1796875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
@@ -2191,8 +2320,8 @@
     <col min="38" max="38" width="102.6171875" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="52.3828125" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="43.94140625" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="96.609375" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="100.24609375" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="43.94140625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4390,18 +4519,20 @@
         <v>80</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>159</v>
+        <v>220</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>160</v>
+        <v>221</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="N19" s="2"/>
+        <v>222</v>
+      </c>
+      <c r="N19" t="s" s="2">
+        <v>223</v>
+      </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>80</v>
@@ -4450,7 +4581,7 @@
         <v>80</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>162</v>
+        <v>224</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -4462,16 +4593,16 @@
         <v>80</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>80</v>
+        <v>225</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>163</v>
+        <v>226</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>80</v>
+        <v>227</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>80</v>
@@ -4485,44 +4616,46 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="C20" s="2"/>
+        <v>146</v>
+      </c>
+      <c r="C20" t="s" s="2">
+        <v>229</v>
+      </c>
       <c r="D20" t="s" s="2">
-        <v>134</v>
+        <v>80</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O20" s="2"/>
+        <v>149</v>
+      </c>
+      <c r="N20" s="2"/>
+      <c r="O20" t="s" s="2">
+        <v>151</v>
+      </c>
       <c r="P20" t="s" s="2">
         <v>80</v>
       </c>
@@ -4531,7 +4664,7 @@
         <v>80</v>
       </c>
       <c r="S20" t="s" s="2">
-        <v>80</v>
+        <v>230</v>
       </c>
       <c r="T20" t="s" s="2">
         <v>80</v>
@@ -4558,19 +4691,19 @@
         <v>80</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>166</v>
+        <v>80</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>167</v>
+        <v>80</v>
       </c>
       <c r="AD20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>153</v>
+        <v>80</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>168</v>
+        <v>146</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -4582,19 +4715,19 @@
         <v>80</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>80</v>
+        <v>154</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>80</v>
+        <v>156</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>80</v>
+        <v>157</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>80</v>
@@ -4605,10 +4738,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>221</v>
+        <v>158</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4628,20 +4761,18 @@
         <v>80</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>222</v>
+        <v>159</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>223</v>
+        <v>160</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>225</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>80</v>
@@ -4690,7 +4821,7 @@
         <v>80</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>226</v>
+        <v>162</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -4699,16 +4830,16 @@
         <v>89</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>227</v>
+        <v>80</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>228</v>
+        <v>80</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>229</v>
+        <v>163</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>80</v>
@@ -4720,26 +4851,26 @@
         <v>80</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>230</v>
+        <v>80</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>231</v>
+        <v>164</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>80</v>
+        <v>134</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>80</v>
@@ -4748,27 +4879,25 @@
         <v>80</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>222</v>
+        <v>135</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>232</v>
+        <v>136</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>233</v>
+        <v>165</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>234</v>
+        <v>138</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="Q22" t="s" s="2">
-        <v>235</v>
-      </c>
+      <c r="Q22" s="2"/>
       <c r="R22" t="s" s="2">
         <v>80</v>
       </c>
@@ -4800,37 +4929,37 @@
         <v>80</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>80</v>
+        <v>166</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>80</v>
+        <v>167</v>
       </c>
       <c r="AD22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>80</v>
+        <v>153</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>236</v>
+        <v>168</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>227</v>
+        <v>80</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>237</v>
+        <v>80</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>238</v>
+        <v>163</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>80</v>
@@ -4847,10 +4976,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>239</v>
+        <v>169</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4867,24 +4996,26 @@
         <v>80</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="J23" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>240</v>
+        <v>109</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>241</v>
+        <v>170</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>242</v>
+        <v>171</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="O23" s="2"/>
+        <v>172</v>
+      </c>
+      <c r="O23" t="s" s="2">
+        <v>173</v>
+      </c>
       <c r="P23" t="s" s="2">
         <v>80</v>
       </c>
@@ -4908,13 +5039,13 @@
         <v>80</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>80</v>
+        <v>174</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>80</v>
+        <v>175</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>80</v>
+        <v>176</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>80</v>
@@ -4932,7 +5063,7 @@
         <v>80</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>244</v>
+        <v>177</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4947,13 +5078,13 @@
         <v>101</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>245</v>
+        <v>132</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>246</v>
+        <v>178</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>247</v>
+        <v>80</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>80</v>
@@ -4967,14 +5098,12 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="C24" t="s" s="2">
-        <v>249</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
         <v>80</v>
       </c>
@@ -4986,7 +5115,7 @@
         <v>89</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>80</v>
@@ -4995,17 +5124,19 @@
         <v>90</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>147</v>
+        <v>180</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>148</v>
+        <v>181</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="N24" s="2"/>
+        <v>182</v>
+      </c>
+      <c r="N24" t="s" s="2">
+        <v>183</v>
+      </c>
       <c r="O24" t="s" s="2">
-        <v>151</v>
+        <v>184</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>80</v>
@@ -5015,7 +5146,7 @@
         <v>80</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>250</v>
+        <v>80</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>80</v>
@@ -5030,13 +5161,13 @@
         <v>80</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>80</v>
+        <v>185</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>80</v>
+        <v>186</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>80</v>
+        <v>187</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>80</v>
@@ -5054,13 +5185,13 @@
         <v>80</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>146</v>
+        <v>188</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>80</v>
@@ -5069,16 +5200,16 @@
         <v>101</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>154</v>
+        <v>189</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>156</v>
+        <v>80</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>157</v>
+        <v>80</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>80</v>
@@ -5089,10 +5220,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>251</v>
+        <v>235</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>251</v>
+        <v>190</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5115,26 +5246,24 @@
         <v>90</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>252</v>
+        <v>103</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>253</v>
+        <v>191</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>254</v>
+        <v>192</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>255</v>
+        <v>193</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>256</v>
+        <v>194</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="Q25" t="s" s="2">
-        <v>257</v>
-      </c>
+      <c r="Q25" s="2"/>
       <c r="R25" t="s" s="2">
         <v>80</v>
       </c>
@@ -5142,7 +5271,7 @@
         <v>80</v>
       </c>
       <c r="T25" t="s" s="2">
-        <v>80</v>
+        <v>195</v>
       </c>
       <c r="U25" t="s" s="2">
         <v>80</v>
@@ -5178,7 +5307,7 @@
         <v>80</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>251</v>
+        <v>196</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -5193,16 +5322,16 @@
         <v>101</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>80</v>
+        <v>197</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>258</v>
+        <v>198</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>80</v>
+        <v>199</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>259</v>
+        <v>80</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>80</v>
@@ -5213,10 +5342,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>260</v>
+        <v>236</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>260</v>
+        <v>200</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5224,13 +5353,13 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G26" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="G26" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="H26" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>80</v>
@@ -5239,20 +5368,18 @@
         <v>90</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>261</v>
+        <v>159</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>262</v>
+        <v>201</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>263</v>
+        <v>202</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>265</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>80</v>
       </c>
@@ -5264,7 +5391,7 @@
         <v>80</v>
       </c>
       <c r="T26" t="s" s="2">
-        <v>80</v>
+        <v>204</v>
       </c>
       <c r="U26" t="s" s="2">
         <v>80</v>
@@ -5300,13 +5427,13 @@
         <v>80</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>260</v>
+        <v>205</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>80</v>
@@ -5315,30 +5442,30 @@
         <v>101</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>266</v>
+        <v>206</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>267</v>
+        <v>207</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>268</v>
+        <v>208</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>80</v>
+        <v>237</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>80</v>
+        <v>238</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>269</v>
+        <v>239</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>269</v>
+        <v>211</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5358,16 +5485,16 @@
         <v>80</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>159</v>
+        <v>212</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>160</v>
+        <v>213</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>161</v>
+        <v>214</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -5418,7 +5545,7 @@
         <v>80</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>162</v>
+        <v>215</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -5430,16 +5557,16 @@
         <v>80</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>80</v>
+        <v>216</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>163</v>
+        <v>217</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>80</v>
+        <v>218</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>80</v>
@@ -5453,21 +5580,21 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>270</v>
+        <v>240</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>270</v>
+        <v>241</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>134</v>
+        <v>80</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>80</v>
@@ -5479,17 +5606,15 @@
         <v>80</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>136</v>
+        <v>160</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>138</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>80</v>
@@ -5526,31 +5651,31 @@
         <v>80</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>166</v>
+        <v>80</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>167</v>
+        <v>80</v>
       </c>
       <c r="AD28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>153</v>
+        <v>80</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>140</v>
+        <v>80</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>80</v>
@@ -5573,46 +5698,44 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>271</v>
+        <v>242</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>271</v>
+        <v>243</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>80</v>
+        <v>134</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I29" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>109</v>
+        <v>135</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>272</v>
+        <v>136</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>273</v>
+        <v>165</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>275</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>80</v>
       </c>
@@ -5636,52 +5759,52 @@
         <v>80</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>174</v>
+        <v>80</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>276</v>
+        <v>80</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>277</v>
+        <v>80</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>80</v>
+        <v>166</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>80</v>
+        <v>167</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>80</v>
+        <v>153</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>278</v>
+        <v>168</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>279</v>
+        <v>80</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>280</v>
+        <v>163</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>281</v>
+        <v>80</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>80</v>
@@ -5695,10 +5818,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>282</v>
+        <v>244</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>282</v>
+        <v>245</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5721,20 +5844,18 @@
         <v>90</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>159</v>
+        <v>246</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>283</v>
+        <v>247</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>284</v>
+        <v>248</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>286</v>
-      </c>
+        <v>249</v>
+      </c>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>80</v>
       </c>
@@ -5782,7 +5903,7 @@
         <v>80</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>287</v>
+        <v>250</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -5791,16 +5912,16 @@
         <v>89</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>80</v>
+        <v>251</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>288</v>
+        <v>252</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>289</v>
+        <v>253</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>80</v>
@@ -5809,32 +5930,32 @@
         <v>80</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>80</v>
+        <v>254</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>290</v>
+        <v>80</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>291</v>
+        <v>255</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>291</v>
+        <v>256</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>292</v>
+        <v>80</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>80</v>
@@ -5843,22 +5964,24 @@
         <v>90</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>159</v>
+        <v>246</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>293</v>
+        <v>257</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>294</v>
+        <v>258</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>295</v>
+        <v>259</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="Q31" s="2"/>
+      <c r="Q31" t="s" s="2">
+        <v>260</v>
+      </c>
       <c r="R31" t="s" s="2">
         <v>80</v>
       </c>
@@ -5902,7 +6025,7 @@
         <v>80</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>296</v>
+        <v>261</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5911,19 +6034,19 @@
         <v>89</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>80</v>
+        <v>251</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>297</v>
+        <v>262</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>298</v>
+        <v>263</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>299</v>
+        <v>80</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>80</v>
@@ -5937,21 +6060,21 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>300</v>
+        <v>264</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>300</v>
+        <v>219</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>301</v>
+        <v>80</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>80</v>
@@ -5963,16 +6086,16 @@
         <v>90</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>159</v>
+        <v>220</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>302</v>
+        <v>221</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>303</v>
+        <v>222</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>304</v>
+        <v>223</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -6022,13 +6145,13 @@
         <v>80</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>305</v>
+        <v>224</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>80</v>
@@ -6037,13 +6160,13 @@
         <v>101</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>306</v>
+        <v>225</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>307</v>
+        <v>226</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>308</v>
+        <v>227</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>80</v>
@@ -6057,10 +6180,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>309</v>
+        <v>265</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>309</v>
+        <v>265</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6071,7 +6194,7 @@
         <v>78</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>80</v>
@@ -6083,20 +6206,26 @@
         <v>90</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>159</v>
+        <v>266</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>310</v>
+        <v>267</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="N33" s="2"/>
-      <c r="O33" s="2"/>
+        <v>268</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="O33" t="s" s="2">
+        <v>270</v>
+      </c>
       <c r="P33" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="Q33" s="2"/>
+      <c r="Q33" t="s" s="2">
+        <v>271</v>
+      </c>
       <c r="R33" t="s" s="2">
         <v>80</v>
       </c>
@@ -6140,13 +6269,13 @@
         <v>80</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>312</v>
+        <v>265</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>80</v>
@@ -6155,16 +6284,16 @@
         <v>101</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>313</v>
+        <v>80</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>314</v>
+        <v>272</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>315</v>
+        <v>80</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>80</v>
+        <v>273</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>80</v>
@@ -6175,10 +6304,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>316</v>
+        <v>274</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>316</v>
+        <v>274</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6186,13 +6315,13 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>80</v>
@@ -6201,16 +6330,20 @@
         <v>90</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>159</v>
+        <v>275</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>317</v>
+        <v>276</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="N34" s="2"/>
-      <c r="O34" s="2"/>
+        <v>277</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="O34" t="s" s="2">
+        <v>279</v>
+      </c>
       <c r="P34" t="s" s="2">
         <v>80</v>
       </c>
@@ -6258,7 +6391,7 @@
         <v>80</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>319</v>
+        <v>274</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -6273,13 +6406,13 @@
         <v>101</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>320</v>
+        <v>280</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>321</v>
+        <v>281</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>80</v>
+        <v>282</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>80</v>
@@ -6293,10 +6426,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>322</v>
+        <v>283</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>322</v>
+        <v>283</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6316,21 +6449,19 @@
         <v>80</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>212</v>
+        <v>159</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>323</v>
+        <v>160</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>324</v>
+        <v>161</v>
       </c>
       <c r="N35" s="2"/>
-      <c r="O35" t="s" s="2">
-        <v>325</v>
-      </c>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>80</v>
       </c>
@@ -6378,7 +6509,7 @@
         <v>80</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>326</v>
+        <v>162</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -6390,16 +6521,16 @@
         <v>80</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>327</v>
+        <v>80</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>328</v>
+        <v>163</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>218</v>
+        <v>80</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>80</v>
@@ -6413,14 +6544,14 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>329</v>
+        <v>284</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>329</v>
+        <v>284</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>80</v>
+        <v>134</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -6430,29 +6561,27 @@
         <v>79</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>330</v>
+        <v>135</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>331</v>
+        <v>136</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>332</v>
+        <v>165</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>334</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>80</v>
       </c>
@@ -6488,19 +6617,19 @@
         <v>80</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>80</v>
+        <v>166</v>
       </c>
       <c r="AC36" t="s" s="2">
-        <v>80</v>
+        <v>167</v>
       </c>
       <c r="AD36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>80</v>
+        <v>153</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>329</v>
+        <v>168</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -6512,16 +6641,16 @@
         <v>80</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>335</v>
+        <v>80</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>336</v>
+        <v>163</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>337</v>
+        <v>80</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>80</v>
@@ -6535,10 +6664,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>338</v>
+        <v>285</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>338</v>
+        <v>285</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6555,22 +6684,26 @@
         <v>80</v>
       </c>
       <c r="I37" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>159</v>
+        <v>109</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>160</v>
+        <v>286</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="N37" s="2"/>
-      <c r="O37" s="2"/>
+        <v>287</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="O37" t="s" s="2">
+        <v>289</v>
+      </c>
       <c r="P37" t="s" s="2">
         <v>80</v>
       </c>
@@ -6594,13 +6727,13 @@
         <v>80</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>80</v>
+        <v>174</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>80</v>
+        <v>290</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>80</v>
+        <v>291</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>80</v>
@@ -6618,7 +6751,7 @@
         <v>80</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>162</v>
+        <v>292</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -6630,16 +6763,16 @@
         <v>80</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>80</v>
+        <v>293</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>163</v>
+        <v>294</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>80</v>
+        <v>295</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>80</v>
@@ -6653,21 +6786,21 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>339</v>
+        <v>296</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>339</v>
+        <v>296</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>134</v>
+        <v>80</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>80</v>
@@ -6676,21 +6809,23 @@
         <v>80</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>136</v>
+        <v>297</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>165</v>
+        <v>298</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O38" s="2"/>
+        <v>299</v>
+      </c>
+      <c r="O38" t="s" s="2">
+        <v>300</v>
+      </c>
       <c r="P38" t="s" s="2">
         <v>80</v>
       </c>
@@ -6726,37 +6861,37 @@
         <v>80</v>
       </c>
       <c r="AB38" t="s" s="2">
-        <v>166</v>
+        <v>80</v>
       </c>
       <c r="AC38" t="s" s="2">
-        <v>167</v>
+        <v>80</v>
       </c>
       <c r="AD38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>153</v>
+        <v>80</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>168</v>
+        <v>301</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>80</v>
+        <v>302</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>163</v>
+        <v>303</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>80</v>
@@ -6765,7 +6900,7 @@
         <v>80</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>80</v>
+        <v>304</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>80</v>
@@ -6773,18 +6908,18 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>340</v>
+        <v>305</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>340</v>
+        <v>305</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>80</v>
+        <v>306</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G39" t="s" s="2">
         <v>89</v>
@@ -6799,15 +6934,17 @@
         <v>90</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>109</v>
+        <v>159</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>341</v>
+        <v>307</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="N39" s="2"/>
+        <v>308</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>309</v>
+      </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>80</v>
@@ -6832,13 +6969,13 @@
         <v>80</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>174</v>
+        <v>80</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>343</v>
+        <v>80</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>344</v>
+        <v>80</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>80</v>
@@ -6856,7 +6993,7 @@
         <v>80</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>345</v>
+        <v>310</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6865,19 +7002,19 @@
         <v>89</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>346</v>
+        <v>80</v>
       </c>
       <c r="AJ39" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>347</v>
+        <v>311</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>348</v>
+        <v>312</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>349</v>
+        <v>313</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>80</v>
@@ -6891,24 +7028,24 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>350</v>
+        <v>314</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>350</v>
+        <v>314</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>80</v>
+        <v>315</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>80</v>
@@ -6920,17 +7057,15 @@
         <v>159</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>351</v>
+        <v>316</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>352</v>
+        <v>317</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>354</v>
-      </c>
+        <v>318</v>
+      </c>
+      <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>80</v>
       </c>
@@ -6978,13 +7113,13 @@
         <v>80</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>355</v>
+        <v>319</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>80</v>
@@ -6993,30 +7128,30 @@
         <v>101</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>356</v>
+        <v>320</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>357</v>
+        <v>321</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>208</v>
+        <v>322</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>358</v>
+        <v>80</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>359</v>
+        <v>80</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>360</v>
+        <v>323</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>360</v>
+        <v>323</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7027,32 +7162,28 @@
         <v>78</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I41" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="J41" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>109</v>
+        <v>159</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>361</v>
+        <v>324</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>364</v>
-      </c>
+        <v>325</v>
+      </c>
+      <c r="N41" s="2"/>
+      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>80</v>
       </c>
@@ -7076,13 +7207,13 @@
         <v>80</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>174</v>
+        <v>80</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>365</v>
+        <v>80</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>366</v>
+        <v>80</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>80</v>
@@ -7100,13 +7231,13 @@
         <v>80</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>367</v>
+        <v>326</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>80</v>
@@ -7115,13 +7246,13 @@
         <v>101</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>368</v>
+        <v>327</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>280</v>
+        <v>328</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>369</v>
+        <v>329</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>80</v>
@@ -7135,10 +7266,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>370</v>
+        <v>330</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>370</v>
+        <v>330</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7149,7 +7280,7 @@
         <v>78</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>80</v>
@@ -7161,17 +7292,15 @@
         <v>90</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>371</v>
+        <v>159</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>372</v>
+        <v>331</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>374</v>
-      </c>
+        <v>332</v>
+      </c>
+      <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>80</v>
@@ -7220,13 +7349,13 @@
         <v>80</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>375</v>
+        <v>333</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>80</v>
@@ -7235,10 +7364,10 @@
         <v>101</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>163</v>
+        <v>334</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>163</v>
+        <v>335</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>80</v>
@@ -7255,10 +7384,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>376</v>
+        <v>336</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>376</v>
+        <v>336</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7284,13 +7413,15 @@
         <v>212</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>377</v>
+        <v>337</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>378</v>
+        <v>338</v>
       </c>
       <c r="N43" s="2"/>
-      <c r="O43" s="2"/>
+      <c r="O43" t="s" s="2">
+        <v>339</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>80</v>
       </c>
@@ -7338,7 +7469,7 @@
         <v>80</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>379</v>
+        <v>340</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -7353,10 +7484,10 @@
         <v>101</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>132</v>
+        <v>341</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>328</v>
+        <v>342</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>218</v>
@@ -7373,10 +7504,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>380</v>
+        <v>343</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>380</v>
+        <v>343</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7399,19 +7530,19 @@
         <v>90</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>381</v>
+        <v>344</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>382</v>
+        <v>345</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>383</v>
+        <v>346</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>384</v>
+        <v>347</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>385</v>
+        <v>348</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>80</v>
@@ -7460,7 +7591,7 @@
         <v>80</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>380</v>
+        <v>343</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -7475,13 +7606,13 @@
         <v>101</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>386</v>
+        <v>349</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>387</v>
+        <v>350</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>163</v>
+        <v>351</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>80</v>
@@ -7495,10 +7626,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>388</v>
+        <v>352</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>388</v>
+        <v>352</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7613,10 +7744,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>389</v>
+        <v>353</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>389</v>
+        <v>353</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7733,10 +7864,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>390</v>
+        <v>354</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>390</v>
+        <v>354</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7750,10 +7881,10 @@
         <v>89</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="J47" t="s" s="2">
         <v>90</v>
@@ -7762,17 +7893,13 @@
         <v>109</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>391</v>
+        <v>355</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>394</v>
-      </c>
+        <v>356</v>
+      </c>
+      <c r="N47" s="2"/>
+      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>80</v>
       </c>
@@ -7784,7 +7911,7 @@
         <v>80</v>
       </c>
       <c r="T47" t="s" s="2">
-        <v>395</v>
+        <v>80</v>
       </c>
       <c r="U47" t="s" s="2">
         <v>80</v>
@@ -7799,10 +7926,10 @@
         <v>174</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>396</v>
+        <v>357</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>397</v>
+        <v>358</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>80</v>
@@ -7820,7 +7947,7 @@
         <v>80</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>398</v>
+        <v>359</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7829,19 +7956,19 @@
         <v>89</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>80</v>
+        <v>360</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>399</v>
+        <v>361</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>280</v>
+        <v>362</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>400</v>
+        <v>363</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>80</v>
@@ -7855,10 +7982,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>401</v>
+        <v>364</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>401</v>
+        <v>364</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7872,7 +7999,7 @@
         <v>89</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>80</v>
@@ -7881,18 +8008,20 @@
         <v>90</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>109</v>
+        <v>159</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>402</v>
+        <v>365</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>403</v>
+        <v>366</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="O48" s="2"/>
+        <v>367</v>
+      </c>
+      <c r="O48" t="s" s="2">
+        <v>368</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>80</v>
       </c>
@@ -7904,7 +8033,7 @@
         <v>80</v>
       </c>
       <c r="T48" t="s" s="2">
-        <v>405</v>
+        <v>80</v>
       </c>
       <c r="U48" t="s" s="2">
         <v>80</v>
@@ -7916,13 +8045,13 @@
         <v>80</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>174</v>
+        <v>80</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>406</v>
+        <v>80</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>407</v>
+        <v>80</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>80</v>
@@ -7940,7 +8069,7 @@
         <v>80</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>408</v>
+        <v>369</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7955,30 +8084,30 @@
         <v>101</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>409</v>
+        <v>370</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>280</v>
+        <v>371</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>80</v>
+        <v>208</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>80</v>
+        <v>372</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>80</v>
+        <v>373</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>410</v>
+        <v>374</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>410</v>
+        <v>374</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7995,25 +8124,25 @@
         <v>80</v>
       </c>
       <c r="I49" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="J49" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>159</v>
+        <v>109</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>411</v>
+        <v>375</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>412</v>
+        <v>376</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>413</v>
+        <v>377</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>286</v>
+        <v>378</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>80</v>
@@ -8026,7 +8155,7 @@
         <v>80</v>
       </c>
       <c r="T49" t="s" s="2">
-        <v>414</v>
+        <v>80</v>
       </c>
       <c r="U49" t="s" s="2">
         <v>80</v>
@@ -8038,13 +8167,13 @@
         <v>80</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>80</v>
+        <v>174</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>80</v>
+        <v>379</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>80</v>
+        <v>380</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>80</v>
@@ -8062,7 +8191,7 @@
         <v>80</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>415</v>
+        <v>381</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -8077,13 +8206,13 @@
         <v>101</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>416</v>
+        <v>382</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>80</v>
+        <v>383</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>80</v>
@@ -8097,10 +8226,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>417</v>
+        <v>384</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>417</v>
+        <v>384</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8111,10 +8240,10 @@
         <v>78</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>418</v>
+        <v>89</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>80</v>
@@ -8123,15 +8252,17 @@
         <v>90</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>159</v>
+        <v>385</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>419</v>
+        <v>386</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="N50" s="2"/>
+        <v>387</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>388</v>
+      </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>80</v>
@@ -8144,7 +8275,7 @@
         <v>80</v>
       </c>
       <c r="T50" t="s" s="2">
-        <v>421</v>
+        <v>80</v>
       </c>
       <c r="U50" t="s" s="2">
         <v>80</v>
@@ -8180,13 +8311,13 @@
         <v>80</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>422</v>
+        <v>389</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>80</v>
@@ -8195,34 +8326,34 @@
         <v>101</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>423</v>
+        <v>163</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>424</v>
+        <v>163</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>425</v>
+        <v>80</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>426</v>
+        <v>80</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>427</v>
+        <v>80</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>428</v>
+        <v>390</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>428</v>
+        <v>390</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>429</v>
+        <v>80</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -8232,7 +8363,7 @@
         <v>89</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>80</v>
@@ -8241,13 +8372,13 @@
         <v>90</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>159</v>
+        <v>212</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>430</v>
+        <v>391</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>431</v>
+        <v>392</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8262,7 +8393,7 @@
         <v>80</v>
       </c>
       <c r="T51" t="s" s="2">
-        <v>432</v>
+        <v>80</v>
       </c>
       <c r="U51" t="s" s="2">
         <v>80</v>
@@ -8298,7 +8429,7 @@
         <v>80</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>433</v>
+        <v>393</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -8313,44 +8444,44 @@
         <v>101</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>434</v>
+        <v>132</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>435</v>
+        <v>342</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>436</v>
+        <v>218</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>437</v>
+        <v>80</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>438</v>
+        <v>80</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>439</v>
+        <v>394</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>439</v>
+        <v>394</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>440</v>
+        <v>80</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>80</v>
@@ -8359,18 +8490,20 @@
         <v>90</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>159</v>
+        <v>395</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>441</v>
+        <v>396</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>442</v>
+        <v>397</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="O52" s="2"/>
+        <v>398</v>
+      </c>
+      <c r="O52" t="s" s="2">
+        <v>399</v>
+      </c>
       <c r="P52" t="s" s="2">
         <v>80</v>
       </c>
@@ -8382,7 +8515,7 @@
         <v>80</v>
       </c>
       <c r="T52" t="s" s="2">
-        <v>444</v>
+        <v>80</v>
       </c>
       <c r="U52" t="s" s="2">
         <v>80</v>
@@ -8418,13 +8551,13 @@
         <v>80</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>445</v>
+        <v>394</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>80</v>
@@ -8433,13 +8566,13 @@
         <v>101</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>446</v>
+        <v>400</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>447</v>
+        <v>401</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>80</v>
+        <v>163</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>80</v>
@@ -8453,14 +8586,14 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>448</v>
+        <v>402</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>448</v>
+        <v>402</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>449</v>
+        <v>80</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -8470,22 +8603,22 @@
         <v>89</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K53" t="s" s="2">
         <v>159</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>450</v>
+        <v>160</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>451</v>
+        <v>161</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8512,13 +8645,13 @@
         <v>80</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>185</v>
+        <v>80</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>452</v>
+        <v>80</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>453</v>
+        <v>80</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>80</v>
@@ -8536,7 +8669,7 @@
         <v>80</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>454</v>
+        <v>162</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -8548,64 +8681,66 @@
         <v>80</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>455</v>
+        <v>80</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>456</v>
+        <v>163</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>457</v>
+        <v>80</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>458</v>
+        <v>80</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>459</v>
+        <v>80</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>460</v>
+        <v>403</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>460</v>
+        <v>403</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>461</v>
+        <v>134</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>159</v>
+        <v>135</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>462</v>
+        <v>136</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="N54" s="2"/>
+        <v>165</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>138</v>
+      </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>80</v>
@@ -8618,7 +8753,7 @@
         <v>80</v>
       </c>
       <c r="T54" t="s" s="2">
-        <v>464</v>
+        <v>80</v>
       </c>
       <c r="U54" t="s" s="2">
         <v>80</v>
@@ -8642,57 +8777,57 @@
         <v>80</v>
       </c>
       <c r="AB54" t="s" s="2">
-        <v>80</v>
+        <v>166</v>
       </c>
       <c r="AC54" t="s" s="2">
-        <v>80</v>
+        <v>167</v>
       </c>
       <c r="AD54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE54" t="s" s="2">
-        <v>80</v>
+        <v>153</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>465</v>
+        <v>168</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>466</v>
+        <v>80</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>467</v>
+        <v>163</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>468</v>
+        <v>80</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>469</v>
+        <v>80</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>470</v>
+        <v>80</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>471</v>
+        <v>404</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>471</v>
+        <v>404</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8706,27 +8841,29 @@
         <v>89</v>
       </c>
       <c r="H55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I55" t="s" s="2">
         <v>90</v>
-      </c>
-      <c r="I55" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="J55" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>159</v>
+        <v>109</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>472</v>
+        <v>405</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>473</v>
+        <v>406</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="O55" s="2"/>
+        <v>407</v>
+      </c>
+      <c r="O55" t="s" s="2">
+        <v>408</v>
+      </c>
       <c r="P55" t="s" s="2">
         <v>80</v>
       </c>
@@ -8738,7 +8875,7 @@
         <v>80</v>
       </c>
       <c r="T55" t="s" s="2">
-        <v>80</v>
+        <v>409</v>
       </c>
       <c r="U55" t="s" s="2">
         <v>80</v>
@@ -8752,9 +8889,11 @@
       <c r="X55" t="s" s="2">
         <v>174</v>
       </c>
-      <c r="Y55" s="2"/>
+      <c r="Y55" t="s" s="2">
+        <v>410</v>
+      </c>
       <c r="Z55" t="s" s="2">
-        <v>475</v>
+        <v>411</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>80</v>
@@ -8772,7 +8911,7 @@
         <v>80</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>476</v>
+        <v>412</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -8787,30 +8926,30 @@
         <v>101</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>477</v>
+        <v>413</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>478</v>
+        <v>294</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>479</v>
+        <v>414</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>458</v>
+        <v>80</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>480</v>
+        <v>80</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>481</v>
+        <v>415</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>481</v>
+        <v>415</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8833,18 +8972,18 @@
         <v>90</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>212</v>
+        <v>109</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>482</v>
+        <v>416</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="N56" s="2"/>
-      <c r="O56" t="s" s="2">
-        <v>484</v>
-      </c>
+        <v>417</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>80</v>
       </c>
@@ -8856,7 +8995,7 @@
         <v>80</v>
       </c>
       <c r="T56" t="s" s="2">
-        <v>485</v>
+        <v>419</v>
       </c>
       <c r="U56" t="s" s="2">
         <v>80</v>
@@ -8868,13 +9007,13 @@
         <v>80</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>80</v>
+        <v>174</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>80</v>
+        <v>420</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>80</v>
+        <v>421</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>80</v>
@@ -8892,7 +9031,7 @@
         <v>80</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>486</v>
+        <v>422</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -8907,13 +9046,13 @@
         <v>101</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>487</v>
+        <v>423</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>328</v>
+        <v>294</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>218</v>
+        <v>80</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>80</v>
@@ -8927,10 +9066,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>488</v>
+        <v>424</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>488</v>
+        <v>424</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8950,19 +9089,23 @@
         <v>80</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K57" t="s" s="2">
         <v>159</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>160</v>
+        <v>425</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="N57" s="2"/>
-      <c r="O57" s="2"/>
+        <v>426</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="O57" t="s" s="2">
+        <v>300</v>
+      </c>
       <c r="P57" t="s" s="2">
         <v>80</v>
       </c>
@@ -8974,7 +9117,7 @@
         <v>80</v>
       </c>
       <c r="T57" t="s" s="2">
-        <v>80</v>
+        <v>428</v>
       </c>
       <c r="U57" t="s" s="2">
         <v>80</v>
@@ -9010,7 +9153,7 @@
         <v>80</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>162</v>
+        <v>429</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -9022,13 +9165,13 @@
         <v>80</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>80</v>
+        <v>430</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>163</v>
+        <v>303</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>80</v>
@@ -9045,43 +9188,41 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>489</v>
+        <v>431</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>489</v>
+        <v>431</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>134</v>
+        <v>80</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>79</v>
+        <v>432</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>136</v>
+        <v>433</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>138</v>
-      </c>
+        <v>434</v>
+      </c>
+      <c r="N58" s="2"/>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>80</v>
@@ -9094,7 +9235,7 @@
         <v>80</v>
       </c>
       <c r="T58" t="s" s="2">
-        <v>80</v>
+        <v>435</v>
       </c>
       <c r="U58" t="s" s="2">
         <v>80</v>
@@ -9118,19 +9259,19 @@
         <v>80</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>166</v>
+        <v>80</v>
       </c>
       <c r="AC58" t="s" s="2">
-        <v>167</v>
+        <v>80</v>
       </c>
       <c r="AD58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>153</v>
+        <v>80</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>168</v>
+        <v>436</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -9142,37 +9283,37 @@
         <v>80</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>80</v>
+        <v>437</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>163</v>
+        <v>438</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>80</v>
+        <v>439</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>80</v>
+        <v>440</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>80</v>
+        <v>441</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>490</v>
+        <v>442</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>490</v>
+        <v>442</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>80</v>
+        <v>443</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -9182,7 +9323,7 @@
         <v>89</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="I59" t="s" s="2">
         <v>80</v>
@@ -9191,17 +9332,15 @@
         <v>90</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>222</v>
+        <v>159</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>223</v>
+        <v>444</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>225</v>
-      </c>
+        <v>445</v>
+      </c>
+      <c r="N59" s="2"/>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>80</v>
@@ -9214,7 +9353,7 @@
         <v>80</v>
       </c>
       <c r="T59" t="s" s="2">
-        <v>80</v>
+        <v>446</v>
       </c>
       <c r="U59" t="s" s="2">
         <v>80</v>
@@ -9250,7 +9389,7 @@
         <v>80</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>226</v>
+        <v>447</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -9259,40 +9398,40 @@
         <v>89</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>227</v>
+        <v>80</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>228</v>
+        <v>448</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>229</v>
+        <v>449</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>80</v>
+        <v>450</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>491</v>
+        <v>451</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>492</v>
+        <v>452</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>493</v>
+        <v>453</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>493</v>
+        <v>453</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>80</v>
+        <v>454</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -9311,24 +9450,22 @@
         <v>90</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>222</v>
+        <v>159</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>232</v>
+        <v>455</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>233</v>
+        <v>456</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>234</v>
+        <v>457</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="Q60" t="s" s="2">
-        <v>235</v>
-      </c>
+      <c r="Q60" s="2"/>
       <c r="R60" t="s" s="2">
         <v>80</v>
       </c>
@@ -9336,7 +9473,7 @@
         <v>80</v>
       </c>
       <c r="T60" t="s" s="2">
-        <v>80</v>
+        <v>458</v>
       </c>
       <c r="U60" t="s" s="2">
         <v>80</v>
@@ -9372,7 +9509,7 @@
         <v>80</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>236</v>
+        <v>459</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -9381,16 +9518,16 @@
         <v>89</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>227</v>
+        <v>80</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>237</v>
+        <v>460</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>238</v>
+        <v>461</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>80</v>
@@ -9399,22 +9536,22 @@
         <v>80</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>494</v>
+        <v>80</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>495</v>
+        <v>80</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>496</v>
+        <v>462</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>496</v>
+        <v>462</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>80</v>
+        <v>463</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -9424,7 +9561,7 @@
         <v>89</v>
       </c>
       <c r="H61" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="I61" t="s" s="2">
         <v>80</v>
@@ -9433,18 +9570,16 @@
         <v>90</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>109</v>
+        <v>159</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>497</v>
+        <v>464</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>498</v>
+        <v>465</v>
       </c>
       <c r="N61" s="2"/>
-      <c r="O61" t="s" s="2">
-        <v>499</v>
-      </c>
+      <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>80</v>
       </c>
@@ -9468,13 +9603,13 @@
         <v>80</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>500</v>
+        <v>466</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>501</v>
+        <v>467</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>80</v>
@@ -9492,7 +9627,7 @@
         <v>80</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>496</v>
+        <v>468</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -9507,34 +9642,34 @@
         <v>101</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>502</v>
+        <v>469</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>503</v>
+        <v>470</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>504</v>
+        <v>471</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>80</v>
+        <v>472</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>80</v>
+        <v>473</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>505</v>
+        <v>474</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>505</v>
+        <v>474</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>80</v>
+        <v>475</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
@@ -9544,7 +9679,7 @@
         <v>89</v>
       </c>
       <c r="H62" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="I62" t="s" s="2">
         <v>80</v>
@@ -9553,18 +9688,16 @@
         <v>90</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>506</v>
+        <v>159</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>507</v>
+        <v>476</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>508</v>
+        <v>477</v>
       </c>
       <c r="N62" s="2"/>
-      <c r="O62" t="s" s="2">
-        <v>509</v>
-      </c>
+      <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>80</v>
       </c>
@@ -9576,7 +9709,7 @@
         <v>80</v>
       </c>
       <c r="T62" t="s" s="2">
-        <v>80</v>
+        <v>478</v>
       </c>
       <c r="U62" t="s" s="2">
         <v>80</v>
@@ -9612,7 +9745,7 @@
         <v>80</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>505</v>
+        <v>479</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -9627,30 +9760,30 @@
         <v>101</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>510</v>
+        <v>480</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>511</v>
+        <v>481</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>512</v>
+        <v>482</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>513</v>
+        <v>483</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>514</v>
+        <v>484</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>515</v>
+        <v>485</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>515</v>
+        <v>485</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9661,30 +9794,30 @@
         <v>78</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="I63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>516</v>
+        <v>159</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>517</v>
+        <v>486</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>518</v>
-      </c>
-      <c r="N63" s="2"/>
-      <c r="O63" t="s" s="2">
-        <v>519</v>
-      </c>
+        <v>487</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>80</v>
       </c>
@@ -9708,13 +9841,11 @@
         <v>80</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y63" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="Y63" s="2"/>
       <c r="Z63" t="s" s="2">
-        <v>80</v>
+        <v>489</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>80</v>
@@ -9732,13 +9863,13 @@
         <v>80</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>515</v>
+        <v>490</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>80</v>
@@ -9747,30 +9878,30 @@
         <v>101</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>80</v>
+        <v>491</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>520</v>
+        <v>492</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>521</v>
+        <v>493</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>80</v>
+        <v>494</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>80</v>
+        <v>473</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>522</v>
+        <v>495</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>522</v>
+        <v>495</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9781,7 +9912,7 @@
         <v>78</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>80</v>
@@ -9793,13 +9924,13 @@
         <v>80</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>523</v>
+        <v>159</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>524</v>
+        <v>496</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>525</v>
+        <v>497</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9850,28 +9981,28 @@
         <v>80</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>522</v>
+        <v>162</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>526</v>
+        <v>80</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>527</v>
+        <v>80</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>528</v>
+        <v>80</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>80</v>
@@ -9885,21 +10016,21 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>529</v>
+        <v>498</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>529</v>
+        <v>498</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>80</v>
+        <v>134</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>80</v>
@@ -9911,15 +10042,17 @@
         <v>80</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>159</v>
+        <v>135</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>160</v>
+        <v>136</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="N65" s="2"/>
+        <v>137</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>138</v>
+      </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>80</v>
@@ -9968,25 +10101,25 @@
         <v>80</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>80</v>
+        <v>140</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>163</v>
+        <v>80</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>80</v>
@@ -10003,21 +10136,21 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>530</v>
+        <v>499</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>530</v>
+        <v>499</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>134</v>
+        <v>80</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>80</v>
@@ -10029,17 +10162,15 @@
         <v>80</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>136</v>
+        <v>160</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>138</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="N66" s="2"/>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>80</v>
@@ -10088,19 +10219,19 @@
         <v>80</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>140</v>
+        <v>80</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>80</v>
@@ -10123,46 +10254,42 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>531</v>
+        <v>500</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>531</v>
+        <v>500</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>532</v>
+        <v>80</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I67" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K67" t="s" s="2">
         <v>135</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>533</v>
+        <v>501</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>534</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>144</v>
-      </c>
+        <v>502</v>
+      </c>
+      <c r="N67" s="2"/>
+      <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>80</v>
       </c>
@@ -10198,19 +10325,19 @@
         <v>80</v>
       </c>
       <c r="AB67" t="s" s="2">
-        <v>80</v>
+        <v>166</v>
       </c>
       <c r="AC67" t="s" s="2">
-        <v>80</v>
+        <v>167</v>
       </c>
       <c r="AD67" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE67" t="s" s="2">
-        <v>80</v>
+        <v>153</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>535</v>
+        <v>168</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
@@ -10228,7 +10355,7 @@
         <v>80</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>132</v>
+        <v>80</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>80</v>
@@ -10245,10 +10372,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>536</v>
+        <v>503</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>536</v>
+        <v>503</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10256,10 +10383,10 @@
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>80</v>
@@ -10271,18 +10398,18 @@
         <v>80</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>147</v>
+        <v>103</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>537</v>
+        <v>504</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>538</v>
-      </c>
-      <c r="N68" s="2"/>
-      <c r="O68" t="s" s="2">
-        <v>539</v>
-      </c>
+        <v>505</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>80</v>
       </c>
@@ -10330,25 +10457,25 @@
         <v>80</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>536</v>
+        <v>507</v>
       </c>
       <c r="AG68" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>540</v>
+        <v>132</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>80</v>
@@ -10365,10 +10492,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>541</v>
+        <v>508</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>541</v>
+        <v>508</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10376,7 +10503,7 @@
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G69" t="s" s="2">
         <v>89</v>
@@ -10391,13 +10518,13 @@
         <v>80</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>180</v>
+        <v>109</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>542</v>
+        <v>509</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>543</v>
+        <v>510</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10424,34 +10551,32 @@
         <v>80</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>544</v>
+        <v>80</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>545</v>
+        <v>80</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>546</v>
+        <v>80</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AB69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC69" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>511</v>
+      </c>
+      <c r="AC69" s="2"/>
       <c r="AD69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE69" t="s" s="2">
-        <v>80</v>
+        <v>512</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>541</v>
+        <v>513</v>
       </c>
       <c r="AG69" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AH69" t="s" s="2">
         <v>89</v>
@@ -10466,10 +10591,10 @@
         <v>80</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>527</v>
+        <v>132</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>547</v>
+        <v>80</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>80</v>
@@ -10483,12 +10608,14 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>548</v>
+        <v>514</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>548</v>
-      </c>
-      <c r="C70" s="2"/>
+        <v>508</v>
+      </c>
+      <c r="C70" t="s" s="2">
+        <v>515</v>
+      </c>
       <c r="D70" t="s" s="2">
         <v>80</v>
       </c>
@@ -10509,13 +10636,13 @@
         <v>80</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>159</v>
+        <v>109</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>160</v>
+        <v>509</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>161</v>
+        <v>510</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10566,7 +10693,7 @@
         <v>80</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>162</v>
+        <v>513</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -10578,13 +10705,13 @@
         <v>80</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>80</v>
+        <v>516</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>163</v>
+        <v>132</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>80</v>
@@ -10593,29 +10720,29 @@
         <v>80</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>80</v>
+        <v>517</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>80</v>
+        <v>473</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>549</v>
+        <v>518</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>549</v>
+        <v>518</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>134</v>
+        <v>80</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>80</v>
@@ -10627,17 +10754,15 @@
         <v>80</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>136</v>
+        <v>519</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>138</v>
-      </c>
+        <v>520</v>
+      </c>
+      <c r="N71" s="2"/>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>80</v>
@@ -10659,7 +10784,7 @@
         <v>80</v>
       </c>
       <c r="W71" t="s" s="2">
-        <v>80</v>
+        <v>521</v>
       </c>
       <c r="X71" t="s" s="2">
         <v>80</v>
@@ -10674,37 +10799,37 @@
         <v>80</v>
       </c>
       <c r="AB71" t="s" s="2">
-        <v>166</v>
+        <v>80</v>
       </c>
       <c r="AC71" t="s" s="2">
-        <v>167</v>
+        <v>80</v>
       </c>
       <c r="AD71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE71" t="s" s="2">
-        <v>153</v>
+        <v>80</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>168</v>
+        <v>522</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>140</v>
+        <v>80</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>163</v>
+        <v>80</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>80</v>
@@ -10721,10 +10846,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>550</v>
+        <v>523</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>550</v>
+        <v>523</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10735,7 +10860,7 @@
         <v>78</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>80</v>
@@ -10747,19 +10872,17 @@
         <v>90</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>551</v>
+        <v>212</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>552</v>
+        <v>524</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>554</v>
-      </c>
+        <v>525</v>
+      </c>
+      <c r="N72" s="2"/>
       <c r="O72" t="s" s="2">
-        <v>555</v>
+        <v>526</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>80</v>
@@ -10772,7 +10895,7 @@
         <v>80</v>
       </c>
       <c r="T72" t="s" s="2">
-        <v>80</v>
+        <v>527</v>
       </c>
       <c r="U72" t="s" s="2">
         <v>80</v>
@@ -10808,13 +10931,13 @@
         <v>80</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>556</v>
+        <v>528</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>80</v>
@@ -10823,13 +10946,13 @@
         <v>101</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>557</v>
+        <v>529</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>558</v>
+        <v>342</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>80</v>
+        <v>218</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>80</v>
@@ -10843,10 +10966,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>559</v>
+        <v>530</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>559</v>
+        <v>530</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10866,23 +10989,19 @@
         <v>80</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K73" t="s" s="2">
         <v>159</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>560</v>
+        <v>160</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>561</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>562</v>
-      </c>
-      <c r="O73" t="s" s="2">
-        <v>563</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="N73" s="2"/>
+      <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>80</v>
       </c>
@@ -10930,7 +11049,7 @@
         <v>80</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>564</v>
+        <v>162</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
@@ -10942,13 +11061,13 @@
         <v>80</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>565</v>
+        <v>80</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>566</v>
+        <v>163</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>80</v>
@@ -10960,26 +11079,26 @@
         <v>80</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>567</v>
+        <v>80</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>568</v>
+        <v>531</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>568</v>
+        <v>531</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>80</v>
+        <v>134</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>80</v>
@@ -10991,18 +11110,18 @@
         <v>80</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>212</v>
+        <v>135</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>569</v>
+        <v>136</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="N74" s="2"/>
-      <c r="O74" t="s" s="2">
-        <v>571</v>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>80</v>
       </c>
@@ -11038,40 +11157,40 @@
         <v>80</v>
       </c>
       <c r="AB74" t="s" s="2">
-        <v>80</v>
+        <v>166</v>
       </c>
       <c r="AC74" t="s" s="2">
-        <v>80</v>
+        <v>167</v>
       </c>
       <c r="AD74" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE74" t="s" s="2">
-        <v>80</v>
+        <v>153</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>568</v>
+        <v>168</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>572</v>
+        <v>163</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>573</v>
+        <v>80</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>80</v>
@@ -11085,10 +11204,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>574</v>
+        <v>532</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>574</v>
+        <v>532</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11108,18 +11227,20 @@
         <v>80</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>575</v>
+        <v>247</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>576</v>
-      </c>
-      <c r="N75" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>249</v>
+      </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>80</v>
@@ -11168,7 +11289,7 @@
         <v>80</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>574</v>
+        <v>250</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
@@ -11177,16 +11298,16 @@
         <v>89</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>80</v>
+        <v>251</v>
       </c>
       <c r="AJ75" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>80</v>
+        <v>252</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>577</v>
+        <v>253</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>80</v>
@@ -11195,18 +11316,18 @@
         <v>80</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>80</v>
+        <v>533</v>
       </c>
       <c r="AP75" t="s" s="2">
-        <v>80</v>
+        <v>534</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>578</v>
+        <v>535</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>578</v>
+        <v>535</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11217,7 +11338,7 @@
         <v>78</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>80</v>
@@ -11226,27 +11347,27 @@
         <v>80</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>180</v>
+        <v>246</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>579</v>
+        <v>257</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>580</v>
+        <v>258</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>581</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>582</v>
-      </c>
+        <v>259</v>
+      </c>
+      <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="Q76" s="2"/>
+      <c r="Q76" t="s" s="2">
+        <v>260</v>
+      </c>
       <c r="R76" t="s" s="2">
         <v>80</v>
       </c>
@@ -11266,13 +11387,13 @@
         <v>80</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>113</v>
+        <v>80</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>115</v>
+        <v>80</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>80</v>
@@ -11290,41 +11411,1959 @@
         <v>80</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>578</v>
+        <v>261</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>80</v>
+        <v>251</v>
       </c>
       <c r="AJ76" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK76" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="AL76" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="AM76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO76" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="AP76" t="s" s="2">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="77" hidden="true">
+      <c r="A77" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="C77" s="2"/>
+      <c r="D77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E77" s="2"/>
+      <c r="F77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G77" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J77" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K77" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="L77" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="M77" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="N77" s="2"/>
+      <c r="O77" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="P77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q77" s="2"/>
+      <c r="R77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X77" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="Y77" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="Z77" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="AA77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF77" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="AG77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH77" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ77" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK77" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="AL77" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="AM77" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="AN77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP77" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="78" hidden="true">
+      <c r="A78" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="B78" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="C78" s="2"/>
+      <c r="D78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E78" s="2"/>
+      <c r="F78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G78" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J78" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K78" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="L78" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="M78" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="N78" s="2"/>
+      <c r="O78" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="P78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q78" s="2"/>
+      <c r="R78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF78" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="AG78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH78" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ78" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK78" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="AL78" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="AM78" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="AN78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO78" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="AP78" t="s" s="2">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="79" hidden="true">
+      <c r="A79" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="B79" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="C79" s="2"/>
+      <c r="D79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E79" s="2"/>
+      <c r="F79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G79" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K79" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="L79" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="M79" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="N79" s="2"/>
+      <c r="O79" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="P79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q79" s="2"/>
+      <c r="R79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF79" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="AG79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH79" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ79" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL79" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="AM79" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="AN79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP79" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="80" hidden="true">
+      <c r="A80" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="B80" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="C80" s="2"/>
+      <c r="D80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E80" s="2"/>
+      <c r="F80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G80" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K80" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="L80" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="M80" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="N80" s="2"/>
+      <c r="O80" s="2"/>
+      <c r="P80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q80" s="2"/>
+      <c r="R80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF80" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="AG80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH80" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ80" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK80" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="AL80" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="AM80" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="AN80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP80" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="81" hidden="true">
+      <c r="A81" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="B81" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="C81" s="2"/>
+      <c r="D81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E81" s="2"/>
+      <c r="F81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G81" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K81" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="L81" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="M81" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="N81" s="2"/>
+      <c r="O81" s="2"/>
+      <c r="P81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q81" s="2"/>
+      <c r="R81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF81" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AG81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH81" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL81" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="AM81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP81" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="82" hidden="true">
+      <c r="A82" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="B82" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="C82" s="2"/>
+      <c r="D82" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="E82" s="2"/>
+      <c r="F82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K82" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L82" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="M82" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="N82" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="O82" s="2"/>
+      <c r="P82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q82" s="2"/>
+      <c r="R82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF82" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="AG82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ82" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL82" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="AM82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP82" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="83" hidden="true">
+      <c r="A83" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="B83" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="C83" s="2"/>
+      <c r="D83" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="E83" s="2"/>
+      <c r="F83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G83" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I83" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="J83" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K83" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L83" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="M83" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="N83" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="O83" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="P83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q83" s="2"/>
+      <c r="R83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF83" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="AG83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH83" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ83" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL83" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AM83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP83" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="84" hidden="true">
+      <c r="A84" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="B84" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="C84" s="2"/>
+      <c r="D84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E84" s="2"/>
+      <c r="F84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K84" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="L84" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="M84" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="N84" s="2"/>
+      <c r="O84" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="P84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q84" s="2"/>
+      <c r="R84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF84" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="AG84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ84" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL84" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="AM84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP84" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="85" hidden="true">
+      <c r="A85" t="s" s="2">
         <v>583</v>
       </c>
-      <c r="AL76" t="s" s="2">
+      <c r="B85" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="C85" s="2"/>
+      <c r="D85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E85" s="2"/>
+      <c r="F85" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G85" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K85" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="L85" t="s" s="2">
         <v>584</v>
       </c>
-      <c r="AM76" t="s" s="2">
+      <c r="M85" t="s" s="2">
         <v>585</v>
       </c>
-      <c r="AN76" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO76" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP76" t="s" s="2">
+      <c r="N85" s="2"/>
+      <c r="O85" s="2"/>
+      <c r="P85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q85" s="2"/>
+      <c r="R85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X85" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="Y85" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="Z85" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="AA85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF85" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="AG85" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AH85" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ85" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL85" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="AM85" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="AN85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP85" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="86" hidden="true">
+      <c r="A86" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="B86" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="C86" s="2"/>
+      <c r="D86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E86" s="2"/>
+      <c r="F86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G86" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K86" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="L86" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="M86" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="N86" s="2"/>
+      <c r="O86" s="2"/>
+      <c r="P86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q86" s="2"/>
+      <c r="R86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF86" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AG86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH86" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL86" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="AM86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP86" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="87" hidden="true">
+      <c r="A87" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="B87" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="C87" s="2"/>
+      <c r="D87" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="E87" s="2"/>
+      <c r="F87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G87" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K87" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L87" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="M87" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="N87" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="O87" s="2"/>
+      <c r="P87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q87" s="2"/>
+      <c r="R87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB87" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="AC87" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AD87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE87" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AF87" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="AG87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH87" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ87" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL87" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="AM87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP87" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="88" hidden="true">
+      <c r="A88" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="B88" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="C88" s="2"/>
+      <c r="D88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E88" s="2"/>
+      <c r="F88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G88" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J88" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K88" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="L88" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="M88" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="N88" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="O88" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="P88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q88" s="2"/>
+      <c r="R88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF88" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="AG88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH88" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ88" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK88" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="AL88" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="AM88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP88" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="89" hidden="true">
+      <c r="A89" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="B89" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="C89" s="2"/>
+      <c r="D89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E89" s="2"/>
+      <c r="F89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G89" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J89" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K89" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="L89" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="M89" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="N89" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="O89" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="P89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q89" s="2"/>
+      <c r="R89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF89" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="AG89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH89" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ89" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK89" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="AL89" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="AM89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO89" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="AP89" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="90" hidden="true">
+      <c r="A90" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="B90" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="C90" s="2"/>
+      <c r="D90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E90" s="2"/>
+      <c r="F90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G90" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K90" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="L90" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="M90" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="N90" s="2"/>
+      <c r="O90" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="P90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q90" s="2"/>
+      <c r="R90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF90" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="AG90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH90" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ90" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL90" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="AM90" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="AN90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP90" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="91" hidden="true">
+      <c r="A91" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="B91" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="C91" s="2"/>
+      <c r="D91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E91" s="2"/>
+      <c r="F91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G91" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K91" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="L91" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="M91" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="N91" s="2"/>
+      <c r="O91" s="2"/>
+      <c r="P91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q91" s="2"/>
+      <c r="R91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF91" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="AG91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH91" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ91" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL91" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="AM91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP91" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="92" hidden="true">
+      <c r="A92" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="B92" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="C92" s="2"/>
+      <c r="D92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E92" s="2"/>
+      <c r="F92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G92" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K92" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="L92" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="M92" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="N92" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="O92" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="P92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q92" s="2"/>
+      <c r="R92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X92" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="Y92" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="Z92" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AA92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF92" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="AG92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH92" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ92" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK92" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="AL92" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="AM92" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="AN92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP92" t="s" s="2">
         <v>80</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP76">
+  <autoFilter ref="A1:AP92">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -11334,7 +13373,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI75">
+  <conditionalFormatting sqref="A2:AI91">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.4.0</t>
+    <t>0.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T12:04:59+00:00</t>
+    <t>2023-11-15T19:14:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1618,7 +1618,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-21:1531: fixed value "unknown" {null}inv-22:1533: fixed value "unknown" {null}</t>
+inv-27:1531: fixed value = unknown if NEW PERSON - STATE (#200-.115) case NULL {null}inv-28:1533: fixed value = unknown if NEW PERSON - STATE (#200-.1215) case NULL {null}</t>
   </si>
   <si>
     <t>1533: fixed value = unknown if NEW PERSON - STATE (#200-.1215) case NULL</t>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$92</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$110</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3532" uniqueCount="628">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4218" uniqueCount="641">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T19:14:31+00:00</t>
+    <t>2023-11-15T20:37:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1264,6 +1264,10 @@
     <t>The home/mailing address of the practitioner is often required for employee administration purposes, and also for some rostering services where the start point (practitioners home) can be used in calculations.</t>
   </si>
   <si>
+    <t xml:space="preserve">value:use}
+</t>
+  </si>
+  <si>
     <t>ORC-24, STF-11, ROL-11, PRT-14</t>
   </si>
   <si>
@@ -1382,12 +1386,6 @@
   </si>
   <si>
     <t>./StreetAddress (newline delimitted)</t>
-  </si>
-  <si>
-    <t>404: source value from NEW PERSON - TEMPORARY ADDRESS 3 (#200-.1213)</t>
-  </si>
-  <si>
-    <t>SStaff.SStaff.TemporaryAddress3</t>
   </si>
   <si>
     <t>Practitioner.address.city</t>
@@ -1418,12 +1416,6 @@
     <t>./Jurisdiction</t>
   </si>
   <si>
-    <t>405: source value from NEW PERSON - TEMPORARY CITY (#200-.1214)</t>
-  </si>
-  <si>
-    <t>SStaff.SStaff.TemporaryCity</t>
-  </si>
-  <si>
     <t>Practitioner.address.district</t>
   </si>
   <si>
@@ -1483,12 +1475,6 @@
     <t>./Sites</t>
   </si>
   <si>
-    <t>406: source value from NEW PERSON - TEMPORARY STATE (#200-.1215)</t>
-  </si>
-  <si>
-    <t>SStaff.SStaff.TemporaryStateName</t>
-  </si>
-  <si>
     <t>Practitioner.address.postalCode</t>
   </si>
   <si>
@@ -1517,12 +1503,6 @@
     <t>./PostalIdentificationCode</t>
   </si>
   <si>
-    <t>407: source value from NEW PERSON - TEMPORARY ZIP CODE (#200-.1216)</t>
-  </si>
-  <si>
-    <t>SStaff.SStaff.TemporaryZipCode</t>
-  </si>
-  <si>
     <t>Practitioner.address.country</t>
   </si>
   <si>
@@ -1535,9 +1515,6 @@
     <t>ISO 3166 3 letter codes can be used in place of a human readable country name.</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFPractitionerCountry</t>
-  </si>
-  <si>
     <t>Address.country</t>
   </si>
   <si>
@@ -1548,95 +1525,6 @@
   </si>
   <si>
     <t>./Country</t>
-  </si>
-  <si>
-    <t>1532: terminologyMaps using VF_PractitionerCountry on NEW PERSON - STATE (#200-.1215) case not NULL</t>
-  </si>
-  <si>
-    <t>Practitioner.address.country.id</t>
-  </si>
-  <si>
-    <t>xml:id (or equivalent in JSON)</t>
-  </si>
-  <si>
-    <t>unique id for the element within a resource (for internal references)</t>
-  </si>
-  <si>
-    <t>Practitioner.address.country.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.address.country.extension.id</t>
-  </si>
-  <si>
-    <t>Practitioner.address.country.extension.extension</t>
-  </si>
-  <si>
-    <t>Extension</t>
-  </si>
-  <si>
-    <t>An Extension</t>
-  </si>
-  <si>
-    <t>Practitioner.address.country.extension.url</t>
-  </si>
-  <si>
-    <t>identifies the meaning of the extension</t>
-  </si>
-  <si>
-    <t>Source of the definition for the extension code - a logical name or a URL.</t>
-  </si>
-  <si>
-    <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
-  </si>
-  <si>
-    <t>Extension.url</t>
-  </si>
-  <si>
-    <t>Practitioner.address.country.extension.value[x]</t>
-  </si>
-  <si>
-    <t>Value of extension</t>
-  </si>
-  <si>
-    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">type:$this}
-</t>
-  </si>
-  <si>
-    <t>closed</t>
-  </si>
-  <si>
-    <t>Extension.value[x]</t>
-  </si>
-  <si>
-    <t>Practitioner.address.country.extension.value[x]:valueCode</t>
-  </si>
-  <si>
-    <t>valueCode</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-27:1531: fixed value = unknown if NEW PERSON - STATE (#200-.115) case NULL {null}inv-28:1533: fixed value = unknown if NEW PERSON - STATE (#200-.1215) case NULL {null}</t>
-  </si>
-  <si>
-    <t>1533: fixed value = unknown if NEW PERSON - STATE (#200-.1215) case NULL</t>
-  </si>
-  <si>
-    <t>Practitioner.address.country.value</t>
-  </si>
-  <si>
-    <t>Primitive value for string</t>
-  </si>
-  <si>
-    <t>The actual value</t>
-  </si>
-  <si>
-    <t>1048576</t>
-  </si>
-  <si>
-    <t>string.value</t>
   </si>
   <si>
     <t>Practitioner.address.period</t>
@@ -1663,12 +1551,163 @@
     <t>XAD.12 / XAD.13 + XAD.14</t>
   </si>
   <si>
+    <t>Practitioner.address:home</t>
+  </si>
+  <si>
+    <t>Practitioner.address:home.id</t>
+  </si>
+  <si>
+    <t>Practitioner.address:home.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.address:home.use</t>
+  </si>
+  <si>
+    <t>Practitioner.address:home.type</t>
+  </si>
+  <si>
+    <t>Practitioner.address:home.text</t>
+  </si>
+  <si>
+    <t>Practitioner.address:home.line</t>
+  </si>
+  <si>
+    <t>398: source value from NEW PERSON - STREET ADDRESS 3 (#200-.113)</t>
+  </si>
+  <si>
+    <t>SStaff.PrescribingProvider.StreetAddress3
+SStaff.SStaff.StreetAddress3</t>
+  </si>
+  <si>
+    <t>Practitioner.address:home.city</t>
+  </si>
+  <si>
+    <t>399: source value from NEW PERSON - CITY (#200-.114)</t>
+  </si>
+  <si>
+    <t>SStaff.PrescribingProvider.City
+SStaff.SStaff.City</t>
+  </si>
+  <si>
+    <t>Practitioner.address:home.district</t>
+  </si>
+  <si>
+    <t>Practitioner.address:home.state</t>
+  </si>
+  <si>
+    <t>400: source value from NEW PERSON - STATE (#200-.115)</t>
+  </si>
+  <si>
+    <t>SStaff.PrescribingProvider.StateIEN
+SStaff.SStaff.StateName</t>
+  </si>
+  <si>
+    <t>Practitioner.address:home.postalCode</t>
+  </si>
+  <si>
+    <t>401: source value from NEW PERSON - ZIP CODE (#200-.116)</t>
+  </si>
+  <si>
+    <t>SStaff.PrescribingProvider.ZipCode
+SStaff.SStaff.ZipCode</t>
+  </si>
+  <si>
+    <t>Practitioner.address:home.country</t>
+  </si>
+  <si>
+    <t>http://va.gov/fhir/ValueSet/VSVFPractitionerCountry</t>
+  </si>
+  <si>
+    <t>1530: terminologyMaps using VF_PractitionerCountry on NEW PERSON - STATE (#200-.115) case not NULL</t>
+  </si>
+  <si>
+    <t>Practitioner.address:home.period</t>
+  </si>
+  <si>
+    <t>Practitioner.address:temp</t>
+  </si>
+  <si>
+    <t>temp</t>
+  </si>
+  <si>
+    <t>Practitioner.address:temp.id</t>
+  </si>
+  <si>
+    <t>Practitioner.address:temp.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.address:temp.use</t>
+  </si>
+  <si>
+    <t>Practitioner.address:temp.type</t>
+  </si>
+  <si>
+    <t>Practitioner.address:temp.text</t>
+  </si>
+  <si>
+    <t>Practitioner.address:temp.line</t>
+  </si>
+  <si>
+    <t>404: source value from NEW PERSON - TEMPORARY ADDRESS 3 (#200-.1213)</t>
+  </si>
+  <si>
+    <t>SStaff.SStaff.TemporaryAddress3</t>
+  </si>
+  <si>
+    <t>Practitioner.address:temp.city</t>
+  </si>
+  <si>
+    <t>405: source value from NEW PERSON - TEMPORARY CITY (#200-.1214)</t>
+  </si>
+  <si>
+    <t>SStaff.SStaff.TemporaryCity</t>
+  </si>
+  <si>
+    <t>Practitioner.address:temp.district</t>
+  </si>
+  <si>
+    <t>Practitioner.address:temp.state</t>
+  </si>
+  <si>
+    <t>406: source value from NEW PERSON - TEMPORARY STATE (#200-.1215)</t>
+  </si>
+  <si>
+    <t>SStaff.SStaff.TemporaryStateName</t>
+  </si>
+  <si>
+    <t>Practitioner.address:temp.postalCode</t>
+  </si>
+  <si>
+    <t>407: source value from NEW PERSON - TEMPORARY ZIP CODE (#200-.1216)</t>
+  </si>
+  <si>
+    <t>SStaff.SStaff.TemporaryZipCode</t>
+  </si>
+  <si>
+    <t>Practitioner.address:temp.country</t>
+  </si>
+  <si>
+    <t>1532: terminologyMaps using VF_PractitionerCountry on NEW PERSON - STATE (#200-.1215) case not NULL</t>
+  </si>
+  <si>
+    <t>Practitioner.address:temp.period</t>
+  </si>
+  <si>
+    <t>Practitioner.address:temp.period.id</t>
+  </si>
+  <si>
     <t>Practitioner.address.period.id</t>
   </si>
   <si>
+    <t>Practitioner.address:temp.period.extension</t>
+  </si>
+  <si>
     <t>Practitioner.address.period.extension</t>
   </si>
   <si>
+    <t>Practitioner.address:temp.period.start</t>
+  </si>
+  <si>
     <t>Practitioner.address.period.start</t>
   </si>
   <si>
@@ -1676,6 +1715,9 @@
   </si>
   <si>
     <t>SStaff.SStaff.TemporaryAddressStartDate</t>
+  </si>
+  <si>
+    <t>Practitioner.address:temp.period.end</t>
   </si>
   <si>
     <t>Practitioner.address.period.end</t>
@@ -2278,11 +2320,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP92"/>
+  <dimension ref="A1:AP110"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="55.0546875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="46.1796875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="40.87109375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="40.70703125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
@@ -8539,16 +8581,14 @@
         <v>80</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC52" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>400</v>
+      </c>
+      <c r="AC52" s="2"/>
       <c r="AD52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>80</v>
+        <v>153</v>
       </c>
       <c r="AF52" t="s" s="2">
         <v>394</v>
@@ -8566,10 +8606,10 @@
         <v>101</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>163</v>
@@ -8586,10 +8626,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8704,10 +8744,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8824,10 +8864,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8853,16 +8893,16 @@
         <v>109</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>80</v>
@@ -8875,7 +8915,7 @@
         <v>80</v>
       </c>
       <c r="T55" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="U55" t="s" s="2">
         <v>80</v>
@@ -8890,10 +8930,10 @@
         <v>174</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>80</v>
@@ -8911,7 +8951,7 @@
         <v>80</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -8926,13 +8966,13 @@
         <v>101</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>294</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>80</v>
@@ -8946,10 +8986,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8975,13 +9015,13 @@
         <v>109</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8995,7 +9035,7 @@
         <v>80</v>
       </c>
       <c r="T56" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="U56" t="s" s="2">
         <v>80</v>
@@ -9010,10 +9050,10 @@
         <v>174</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>80</v>
@@ -9031,7 +9071,7 @@
         <v>80</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -9046,7 +9086,7 @@
         <v>101</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>294</v>
@@ -9066,10 +9106,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9095,13 +9135,13 @@
         <v>159</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="O57" t="s" s="2">
         <v>300</v>
@@ -9117,7 +9157,7 @@
         <v>80</v>
       </c>
       <c r="T57" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="U57" t="s" s="2">
         <v>80</v>
@@ -9153,7 +9193,7 @@
         <v>80</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -9168,7 +9208,7 @@
         <v>101</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>303</v>
@@ -9188,10 +9228,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9202,7 +9242,7 @@
         <v>78</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>90</v>
@@ -9217,10 +9257,10 @@
         <v>159</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -9235,7 +9275,7 @@
         <v>80</v>
       </c>
       <c r="T58" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="U58" t="s" s="2">
         <v>80</v>
@@ -9271,7 +9311,7 @@
         <v>80</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -9286,34 +9326,34 @@
         <v>101</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>440</v>
+        <v>80</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>441</v>
+        <v>80</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -9335,10 +9375,10 @@
         <v>159</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>444</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>445</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9353,43 +9393,43 @@
         <v>80</v>
       </c>
       <c r="T59" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="U59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF59" t="s" s="2">
         <v>446</v>
-      </c>
-      <c r="U59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF59" t="s" s="2">
-        <v>447</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -9404,34 +9444,34 @@
         <v>101</v>
       </c>
       <c r="AK59" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="AL59" t="s" s="2">
         <v>448</v>
       </c>
-      <c r="AL59" t="s" s="2">
+      <c r="AM59" t="s" s="2">
         <v>449</v>
       </c>
-      <c r="AM59" t="s" s="2">
-        <v>450</v>
-      </c>
       <c r="AN59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>451</v>
+        <v>80</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>452</v>
+        <v>80</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -9453,13 +9493,13 @@
         <v>159</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9473,7 +9513,7 @@
         <v>80</v>
       </c>
       <c r="T60" t="s" s="2">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="U60" t="s" s="2">
         <v>80</v>
@@ -9509,7 +9549,7 @@
         <v>80</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -9524,10 +9564,10 @@
         <v>101</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>80</v>
@@ -9544,14 +9584,14 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -9573,10 +9613,10 @@
         <v>159</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9606,10 +9646,10 @@
         <v>185</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>80</v>
@@ -9627,7 +9667,7 @@
         <v>80</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -9642,34 +9682,34 @@
         <v>101</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>472</v>
+        <v>80</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>473</v>
+        <v>80</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
@@ -9691,10 +9731,10 @@
         <v>159</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9709,7 +9749,7 @@
         <v>80</v>
       </c>
       <c r="T62" t="s" s="2">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="U62" t="s" s="2">
         <v>80</v>
@@ -9745,7 +9785,7 @@
         <v>80</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -9760,30 +9800,30 @@
         <v>101</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>483</v>
+        <v>80</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>484</v>
+        <v>80</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>485</v>
+        <v>478</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>485</v>
+        <v>478</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9809,13 +9849,13 @@
         <v>159</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>486</v>
+        <v>479</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>487</v>
+        <v>480</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>488</v>
+        <v>481</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9841,11 +9881,13 @@
         <v>80</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="Y63" s="2"/>
+        <v>80</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="Z63" t="s" s="2">
-        <v>489</v>
+        <v>80</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>80</v>
@@ -9863,7 +9905,7 @@
         <v>80</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>490</v>
+        <v>482</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -9878,30 +9920,30 @@
         <v>101</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>492</v>
+        <v>484</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>493</v>
+        <v>485</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>494</v>
+        <v>80</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>473</v>
+        <v>80</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>495</v>
+        <v>486</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>495</v>
+        <v>486</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9921,19 +9963,21 @@
         <v>80</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>159</v>
+        <v>212</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>496</v>
+        <v>487</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>497</v>
+        <v>488</v>
       </c>
       <c r="N64" s="2"/>
-      <c r="O64" s="2"/>
+      <c r="O64" t="s" s="2">
+        <v>489</v>
+      </c>
       <c r="P64" t="s" s="2">
         <v>80</v>
       </c>
@@ -9945,7 +9989,7 @@
         <v>80</v>
       </c>
       <c r="T64" t="s" s="2">
-        <v>80</v>
+        <v>490</v>
       </c>
       <c r="U64" t="s" s="2">
         <v>80</v>
@@ -9981,7 +10025,7 @@
         <v>80</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>162</v>
+        <v>491</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -9993,16 +10037,16 @@
         <v>80</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>80</v>
+        <v>492</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>80</v>
+        <v>342</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>80</v>
+        <v>218</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>80</v>
@@ -10016,44 +10060,48 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="C65" s="2"/>
+        <v>394</v>
+      </c>
+      <c r="C65" t="s" s="2">
+        <v>410</v>
+      </c>
       <c r="D65" t="s" s="2">
-        <v>134</v>
+        <v>80</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="I65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>135</v>
+        <v>395</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>136</v>
+        <v>396</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>137</v>
+        <v>397</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O65" s="2"/>
+        <v>398</v>
+      </c>
+      <c r="O65" t="s" s="2">
+        <v>399</v>
+      </c>
       <c r="P65" t="s" s="2">
         <v>80</v>
       </c>
@@ -10101,7 +10149,7 @@
         <v>80</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>168</v>
+        <v>394</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
@@ -10113,16 +10161,16 @@
         <v>80</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>80</v>
+        <v>401</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>80</v>
+        <v>402</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>80</v>
+        <v>163</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>80</v>
@@ -10136,10 +10184,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>499</v>
+        <v>494</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>499</v>
+        <v>403</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10254,21 +10302,21 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>500</v>
+        <v>404</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>80</v>
+        <v>134</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>80</v>
@@ -10283,12 +10331,14 @@
         <v>135</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>501</v>
+        <v>136</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="N67" s="2"/>
+        <v>165</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>138</v>
+      </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>80</v>
@@ -10355,7 +10405,7 @@
         <v>80</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>80</v>
+        <v>163</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>80</v>
@@ -10372,10 +10422,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>503</v>
+        <v>496</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>503</v>
+        <v>405</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10383,7 +10433,7 @@
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G68" t="s" s="2">
         <v>89</v>
@@ -10392,24 +10442,26 @@
         <v>80</v>
       </c>
       <c r="I68" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>504</v>
+        <v>406</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>505</v>
+        <v>407</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>506</v>
-      </c>
-      <c r="O68" s="2"/>
+        <v>408</v>
+      </c>
+      <c r="O68" t="s" s="2">
+        <v>409</v>
+      </c>
       <c r="P68" t="s" s="2">
         <v>80</v>
       </c>
@@ -10421,7 +10473,7 @@
         <v>80</v>
       </c>
       <c r="T68" t="s" s="2">
-        <v>80</v>
+        <v>410</v>
       </c>
       <c r="U68" t="s" s="2">
         <v>80</v>
@@ -10433,13 +10485,13 @@
         <v>80</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>80</v>
+        <v>174</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>80</v>
+        <v>411</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>80</v>
+        <v>412</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>80</v>
@@ -10457,10 +10509,10 @@
         <v>80</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>507</v>
+        <v>413</v>
       </c>
       <c r="AG68" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AH68" t="s" s="2">
         <v>89</v>
@@ -10469,16 +10521,16 @@
         <v>80</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>80</v>
+        <v>414</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>132</v>
+        <v>294</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>80</v>
+        <v>415</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>80</v>
@@ -10492,10 +10544,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>508</v>
+        <v>497</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>508</v>
+        <v>416</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10515,18 +10567,20 @@
         <v>80</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K69" t="s" s="2">
         <v>109</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>509</v>
+        <v>417</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>510</v>
-      </c>
-      <c r="N69" s="2"/>
+        <v>418</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>419</v>
+      </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>80</v>
@@ -10539,7 +10593,7 @@
         <v>80</v>
       </c>
       <c r="T69" t="s" s="2">
-        <v>80</v>
+        <v>420</v>
       </c>
       <c r="U69" t="s" s="2">
         <v>80</v>
@@ -10551,29 +10605,31 @@
         <v>80</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>80</v>
+        <v>174</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>80</v>
+        <v>421</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>80</v>
+        <v>422</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AB69" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="AC69" s="2"/>
+        <v>80</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="AD69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE69" t="s" s="2">
-        <v>512</v>
+        <v>80</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>513</v>
+        <v>423</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -10588,10 +10644,10 @@
         <v>101</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>80</v>
+        <v>424</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>132</v>
+        <v>294</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>80</v>
@@ -10608,14 +10664,12 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>514</v>
+        <v>498</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>508</v>
-      </c>
-      <c r="C70" t="s" s="2">
-        <v>515</v>
-      </c>
+        <v>425</v>
+      </c>
+      <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
         <v>80</v>
       </c>
@@ -10633,19 +10687,23 @@
         <v>80</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>109</v>
+        <v>159</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>509</v>
+        <v>426</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>510</v>
-      </c>
-      <c r="N70" s="2"/>
-      <c r="O70" s="2"/>
+        <v>427</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="O70" t="s" s="2">
+        <v>300</v>
+      </c>
       <c r="P70" t="s" s="2">
         <v>80</v>
       </c>
@@ -10657,7 +10715,7 @@
         <v>80</v>
       </c>
       <c r="T70" t="s" s="2">
-        <v>80</v>
+        <v>429</v>
       </c>
       <c r="U70" t="s" s="2">
         <v>80</v>
@@ -10693,7 +10751,7 @@
         <v>80</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>513</v>
+        <v>430</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -10705,13 +10763,13 @@
         <v>80</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>516</v>
+        <v>101</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>80</v>
+        <v>431</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>132</v>
+        <v>303</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>80</v>
@@ -10720,18 +10778,18 @@
         <v>80</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>517</v>
+        <v>80</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>473</v>
+        <v>80</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>518</v>
+        <v>499</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>518</v>
+        <v>432</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10742,25 +10800,25 @@
         <v>78</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>89</v>
+        <v>433</v>
       </c>
       <c r="H71" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="I71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K71" t="s" s="2">
         <v>159</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>519</v>
+        <v>434</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>520</v>
+        <v>435</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -10775,7 +10833,7 @@
         <v>80</v>
       </c>
       <c r="T71" t="s" s="2">
-        <v>80</v>
+        <v>436</v>
       </c>
       <c r="U71" t="s" s="2">
         <v>80</v>
@@ -10784,7 +10842,7 @@
         <v>80</v>
       </c>
       <c r="W71" t="s" s="2">
-        <v>521</v>
+        <v>80</v>
       </c>
       <c r="X71" t="s" s="2">
         <v>80</v>
@@ -10811,49 +10869,49 @@
         <v>80</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>522</v>
+        <v>437</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>80</v>
+        <v>438</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>80</v>
+        <v>439</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>80</v>
+        <v>440</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>80</v>
+        <v>501</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>523</v>
+        <v>502</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>523</v>
+        <v>441</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>80</v>
+        <v>442</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -10863,7 +10921,7 @@
         <v>89</v>
       </c>
       <c r="H72" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="I72" t="s" s="2">
         <v>80</v>
@@ -10872,18 +10930,16 @@
         <v>90</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>212</v>
+        <v>159</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>524</v>
+        <v>443</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>525</v>
+        <v>444</v>
       </c>
       <c r="N72" s="2"/>
-      <c r="O72" t="s" s="2">
-        <v>526</v>
-      </c>
+      <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>80</v>
       </c>
@@ -10895,7 +10951,7 @@
         <v>80</v>
       </c>
       <c r="T72" t="s" s="2">
-        <v>527</v>
+        <v>445</v>
       </c>
       <c r="U72" t="s" s="2">
         <v>80</v>
@@ -10931,7 +10987,7 @@
         <v>80</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>528</v>
+        <v>446</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
@@ -10946,34 +11002,34 @@
         <v>101</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>529</v>
+        <v>447</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>342</v>
+        <v>448</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>218</v>
+        <v>449</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>80</v>
+        <v>503</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>80</v>
+        <v>504</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>530</v>
+        <v>505</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>530</v>
+        <v>450</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>80</v>
+        <v>451</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
@@ -10989,18 +11045,20 @@
         <v>80</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K73" t="s" s="2">
         <v>159</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>160</v>
+        <v>452</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="N73" s="2"/>
+        <v>453</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>454</v>
+      </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>80</v>
@@ -11013,7 +11071,7 @@
         <v>80</v>
       </c>
       <c r="T73" t="s" s="2">
-        <v>80</v>
+        <v>455</v>
       </c>
       <c r="U73" t="s" s="2">
         <v>80</v>
@@ -11049,7 +11107,7 @@
         <v>80</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>162</v>
+        <v>456</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
@@ -11061,13 +11119,13 @@
         <v>80</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>80</v>
+        <v>457</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>163</v>
+        <v>458</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>80</v>
@@ -11084,43 +11142,41 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>531</v>
+        <v>506</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>531</v>
+        <v>459</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>134</v>
+        <v>460</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H74" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="I74" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>136</v>
+        <v>461</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>138</v>
-      </c>
+        <v>462</v>
+      </c>
+      <c r="N74" s="2"/>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>80</v>
@@ -11145,73 +11201,73 @@
         <v>80</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>80</v>
+        <v>185</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>80</v>
+        <v>463</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>80</v>
+        <v>464</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AB74" t="s" s="2">
-        <v>166</v>
+        <v>80</v>
       </c>
       <c r="AC74" t="s" s="2">
-        <v>167</v>
+        <v>80</v>
       </c>
       <c r="AD74" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE74" t="s" s="2">
-        <v>153</v>
+        <v>80</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>168</v>
+        <v>465</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>80</v>
+        <v>466</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>163</v>
+        <v>467</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>80</v>
+        <v>468</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>80</v>
+        <v>507</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>80</v>
+        <v>508</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>532</v>
+        <v>509</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>532</v>
+        <v>469</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>80</v>
+        <v>470</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
@@ -11221,7 +11277,7 @@
         <v>89</v>
       </c>
       <c r="H75" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="I75" t="s" s="2">
         <v>80</v>
@@ -11230,17 +11286,15 @@
         <v>90</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>246</v>
+        <v>159</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>247</v>
+        <v>471</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>249</v>
-      </c>
+        <v>472</v>
+      </c>
+      <c r="N75" s="2"/>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>80</v>
@@ -11253,7 +11307,7 @@
         <v>80</v>
       </c>
       <c r="T75" t="s" s="2">
-        <v>80</v>
+        <v>473</v>
       </c>
       <c r="U75" t="s" s="2">
         <v>80</v>
@@ -11289,7 +11343,7 @@
         <v>80</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>250</v>
+        <v>474</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
@@ -11298,36 +11352,36 @@
         <v>89</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>251</v>
+        <v>80</v>
       </c>
       <c r="AJ75" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>252</v>
+        <v>475</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>253</v>
+        <v>476</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>80</v>
+        <v>477</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>533</v>
+        <v>510</v>
       </c>
       <c r="AP75" t="s" s="2">
-        <v>534</v>
+        <v>511</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>535</v>
+        <v>512</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>535</v>
+        <v>478</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11341,7 +11395,7 @@
         <v>89</v>
       </c>
       <c r="H76" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="I76" t="s" s="2">
         <v>80</v>
@@ -11350,24 +11404,22 @@
         <v>90</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>246</v>
+        <v>159</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>257</v>
+        <v>479</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>258</v>
+        <v>480</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>259</v>
+        <v>481</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="Q76" t="s" s="2">
-        <v>260</v>
-      </c>
+      <c r="Q76" s="2"/>
       <c r="R76" t="s" s="2">
         <v>80</v>
       </c>
@@ -11387,13 +11439,11 @@
         <v>80</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y76" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="Y76" s="2"/>
       <c r="Z76" t="s" s="2">
-        <v>80</v>
+        <v>513</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>80</v>
@@ -11411,7 +11461,7 @@
         <v>80</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>261</v>
+        <v>482</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>78</v>
@@ -11420,36 +11470,36 @@
         <v>89</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>251</v>
+        <v>80</v>
       </c>
       <c r="AJ76" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>262</v>
+        <v>483</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>263</v>
+        <v>484</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>80</v>
+        <v>485</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>536</v>
+        <v>514</v>
       </c>
       <c r="AP76" t="s" s="2">
-        <v>537</v>
+        <v>508</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>538</v>
+        <v>515</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>538</v>
+        <v>486</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11472,17 +11522,17 @@
         <v>90</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>109</v>
+        <v>212</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>539</v>
+        <v>487</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>540</v>
+        <v>488</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" t="s" s="2">
-        <v>541</v>
+        <v>489</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>80</v>
@@ -11495,7 +11545,7 @@
         <v>80</v>
       </c>
       <c r="T77" t="s" s="2">
-        <v>80</v>
+        <v>490</v>
       </c>
       <c r="U77" t="s" s="2">
         <v>80</v>
@@ -11507,13 +11557,13 @@
         <v>80</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>174</v>
+        <v>80</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>542</v>
+        <v>80</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>543</v>
+        <v>80</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>80</v>
@@ -11531,7 +11581,7 @@
         <v>80</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>538</v>
+        <v>491</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
@@ -11546,13 +11596,13 @@
         <v>101</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>544</v>
+        <v>492</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>545</v>
+        <v>342</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>546</v>
+        <v>218</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>80</v>
@@ -11566,12 +11616,14 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>547</v>
+        <v>516</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="C78" s="2"/>
+        <v>394</v>
+      </c>
+      <c r="C78" t="s" s="2">
+        <v>517</v>
+      </c>
       <c r="D78" t="s" s="2">
         <v>80</v>
       </c>
@@ -11583,7 +11635,7 @@
         <v>89</v>
       </c>
       <c r="H78" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="I78" t="s" s="2">
         <v>80</v>
@@ -11592,17 +11644,19 @@
         <v>90</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>548</v>
+        <v>395</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>549</v>
+        <v>396</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>550</v>
-      </c>
-      <c r="N78" s="2"/>
+        <v>397</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>398</v>
+      </c>
       <c r="O78" t="s" s="2">
-        <v>551</v>
+        <v>399</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>80</v>
@@ -11651,13 +11705,13 @@
         <v>80</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>547</v>
+        <v>394</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>80</v>
@@ -11666,30 +11720,30 @@
         <v>101</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>552</v>
+        <v>401</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>553</v>
+        <v>402</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>554</v>
+        <v>163</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>555</v>
+        <v>80</v>
       </c>
       <c r="AP78" t="s" s="2">
-        <v>556</v>
+        <v>80</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>557</v>
+        <v>518</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>557</v>
+        <v>403</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11700,7 +11754,7 @@
         <v>78</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>80</v>
@@ -11712,18 +11766,16 @@
         <v>80</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>558</v>
+        <v>159</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>559</v>
+        <v>160</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>560</v>
+        <v>161</v>
       </c>
       <c r="N79" s="2"/>
-      <c r="O79" t="s" s="2">
-        <v>561</v>
-      </c>
+      <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>80</v>
       </c>
@@ -11771,28 +11823,28 @@
         <v>80</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>557</v>
+        <v>162</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>562</v>
+        <v>163</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>563</v>
+        <v>80</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>80</v>
@@ -11806,14 +11858,14 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>564</v>
+        <v>519</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>564</v>
+        <v>404</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>80</v>
+        <v>134</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
@@ -11832,15 +11884,17 @@
         <v>80</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>565</v>
+        <v>135</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>566</v>
+        <v>136</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>567</v>
-      </c>
-      <c r="N80" s="2"/>
+        <v>165</v>
+      </c>
+      <c r="N80" t="s" s="2">
+        <v>138</v>
+      </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>80</v>
@@ -11877,19 +11931,19 @@
         <v>80</v>
       </c>
       <c r="AB80" t="s" s="2">
-        <v>80</v>
+        <v>166</v>
       </c>
       <c r="AC80" t="s" s="2">
-        <v>80</v>
+        <v>167</v>
       </c>
       <c r="AD80" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE80" t="s" s="2">
-        <v>80</v>
+        <v>153</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>564</v>
+        <v>168</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>78</v>
@@ -11901,16 +11955,16 @@
         <v>80</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>568</v>
+        <v>80</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>569</v>
+        <v>163</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>570</v>
+        <v>80</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>80</v>
@@ -11924,10 +11978,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>571</v>
+        <v>520</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>571</v>
+        <v>405</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11944,22 +11998,26 @@
         <v>80</v>
       </c>
       <c r="I81" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>159</v>
+        <v>109</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>160</v>
+        <v>406</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="N81" s="2"/>
-      <c r="O81" s="2"/>
+        <v>407</v>
+      </c>
+      <c r="N81" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="O81" t="s" s="2">
+        <v>409</v>
+      </c>
       <c r="P81" t="s" s="2">
         <v>80</v>
       </c>
@@ -11971,7 +12029,7 @@
         <v>80</v>
       </c>
       <c r="T81" t="s" s="2">
-        <v>80</v>
+        <v>410</v>
       </c>
       <c r="U81" t="s" s="2">
         <v>80</v>
@@ -11983,13 +12041,13 @@
         <v>80</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>80</v>
+        <v>174</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>80</v>
+        <v>411</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>80</v>
+        <v>412</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>80</v>
@@ -12007,7 +12065,7 @@
         <v>80</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>162</v>
+        <v>413</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>78</v>
@@ -12019,16 +12077,16 @@
         <v>80</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>80</v>
+        <v>414</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>163</v>
+        <v>294</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>80</v>
+        <v>415</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>80</v>
@@ -12042,21 +12100,21 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>572</v>
+        <v>521</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>572</v>
+        <v>416</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>134</v>
+        <v>80</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>80</v>
@@ -12065,19 +12123,19 @@
         <v>80</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>135</v>
+        <v>109</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>136</v>
+        <v>417</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>165</v>
+        <v>418</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>138</v>
+        <v>419</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -12091,7 +12149,7 @@
         <v>80</v>
       </c>
       <c r="T82" t="s" s="2">
-        <v>80</v>
+        <v>420</v>
       </c>
       <c r="U82" t="s" s="2">
         <v>80</v>
@@ -12103,13 +12161,13 @@
         <v>80</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>80</v>
+        <v>174</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>80</v>
+        <v>421</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>80</v>
+        <v>422</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>80</v>
@@ -12127,25 +12185,25 @@
         <v>80</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>168</v>
+        <v>423</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>80</v>
+        <v>424</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>163</v>
+        <v>294</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>80</v>
@@ -12162,45 +12220,45 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>573</v>
+        <v>522</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>573</v>
+        <v>425</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>574</v>
+        <v>80</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I83" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="J83" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>575</v>
+        <v>426</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>576</v>
+        <v>427</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>138</v>
+        <v>428</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>144</v>
+        <v>300</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>80</v>
@@ -12213,7 +12271,7 @@
         <v>80</v>
       </c>
       <c r="T83" t="s" s="2">
-        <v>80</v>
+        <v>429</v>
       </c>
       <c r="U83" t="s" s="2">
         <v>80</v>
@@ -12249,25 +12307,25 @@
         <v>80</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>577</v>
+        <v>430</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>80</v>
+        <v>431</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>132</v>
+        <v>303</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>80</v>
@@ -12284,10 +12342,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>578</v>
+        <v>523</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>578</v>
+        <v>432</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12298,30 +12356,28 @@
         <v>78</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>79</v>
+        <v>433</v>
       </c>
       <c r="H84" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="I84" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>579</v>
+        <v>434</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>580</v>
+        <v>435</v>
       </c>
       <c r="N84" s="2"/>
-      <c r="O84" t="s" s="2">
-        <v>581</v>
-      </c>
+      <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>80</v>
       </c>
@@ -12333,7 +12389,7 @@
         <v>80</v>
       </c>
       <c r="T84" t="s" s="2">
-        <v>80</v>
+        <v>436</v>
       </c>
       <c r="U84" t="s" s="2">
         <v>80</v>
@@ -12369,7 +12425,7 @@
         <v>80</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>578</v>
+        <v>437</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>78</v>
@@ -12384,59 +12440,59 @@
         <v>101</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>80</v>
+        <v>438</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>582</v>
+        <v>439</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>80</v>
+        <v>440</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>80</v>
+        <v>524</v>
       </c>
       <c r="AP84" t="s" s="2">
-        <v>80</v>
+        <v>525</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>583</v>
+        <v>526</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>583</v>
+        <v>441</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>80</v>
+        <v>442</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G85" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H85" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="I85" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>180</v>
+        <v>159</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>584</v>
+        <v>443</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>585</v>
+        <v>444</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -12451,7 +12507,7 @@
         <v>80</v>
       </c>
       <c r="T85" t="s" s="2">
-        <v>80</v>
+        <v>445</v>
       </c>
       <c r="U85" t="s" s="2">
         <v>80</v>
@@ -12463,13 +12519,13 @@
         <v>80</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>586</v>
+        <v>80</v>
       </c>
       <c r="Y85" t="s" s="2">
-        <v>587</v>
+        <v>80</v>
       </c>
       <c r="Z85" t="s" s="2">
-        <v>588</v>
+        <v>80</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>80</v>
@@ -12487,10 +12543,10 @@
         <v>80</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>583</v>
+        <v>446</v>
       </c>
       <c r="AG85" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AH85" t="s" s="2">
         <v>89</v>
@@ -12502,34 +12558,34 @@
         <v>101</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>80</v>
+        <v>447</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>569</v>
+        <v>448</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>589</v>
+        <v>449</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO85" t="s" s="2">
-        <v>80</v>
+        <v>527</v>
       </c>
       <c r="AP85" t="s" s="2">
-        <v>80</v>
+        <v>528</v>
       </c>
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>590</v>
+        <v>529</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>590</v>
+        <v>450</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>80</v>
+        <v>451</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
@@ -12545,18 +12601,20 @@
         <v>80</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K86" t="s" s="2">
         <v>159</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>160</v>
+        <v>452</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="N86" s="2"/>
+        <v>453</v>
+      </c>
+      <c r="N86" t="s" s="2">
+        <v>454</v>
+      </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>80</v>
@@ -12569,7 +12627,7 @@
         <v>80</v>
       </c>
       <c r="T86" t="s" s="2">
-        <v>80</v>
+        <v>455</v>
       </c>
       <c r="U86" t="s" s="2">
         <v>80</v>
@@ -12605,7 +12663,7 @@
         <v>80</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>162</v>
+        <v>456</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>78</v>
@@ -12617,13 +12675,13 @@
         <v>80</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>80</v>
+        <v>457</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>163</v>
+        <v>458</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>80</v>
@@ -12640,43 +12698,41 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>591</v>
+        <v>530</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>591</v>
+        <v>459</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>134</v>
+        <v>460</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H87" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="I87" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>136</v>
+        <v>461</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>138</v>
-      </c>
+        <v>462</v>
+      </c>
+      <c r="N87" s="2"/>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
         <v>80</v>
@@ -12701,83 +12757,83 @@
         <v>80</v>
       </c>
       <c r="X87" t="s" s="2">
-        <v>80</v>
+        <v>185</v>
       </c>
       <c r="Y87" t="s" s="2">
-        <v>80</v>
+        <v>463</v>
       </c>
       <c r="Z87" t="s" s="2">
-        <v>80</v>
+        <v>464</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AB87" t="s" s="2">
-        <v>166</v>
+        <v>80</v>
       </c>
       <c r="AC87" t="s" s="2">
-        <v>167</v>
+        <v>80</v>
       </c>
       <c r="AD87" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE87" t="s" s="2">
-        <v>153</v>
+        <v>80</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>168</v>
+        <v>465</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI87" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>80</v>
+        <v>466</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>163</v>
+        <v>467</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>80</v>
+        <v>468</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO87" t="s" s="2">
-        <v>80</v>
+        <v>531</v>
       </c>
       <c r="AP87" t="s" s="2">
-        <v>80</v>
+        <v>532</v>
       </c>
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>592</v>
+        <v>533</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>592</v>
+        <v>469</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>80</v>
+        <v>470</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H88" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="I88" t="s" s="2">
         <v>80</v>
@@ -12786,20 +12842,16 @@
         <v>90</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>593</v>
+        <v>159</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>594</v>
+        <v>471</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>595</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>596</v>
-      </c>
-      <c r="O88" t="s" s="2">
-        <v>597</v>
-      </c>
+        <v>472</v>
+      </c>
+      <c r="N88" s="2"/>
+      <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
         <v>80</v>
       </c>
@@ -12811,7 +12863,7 @@
         <v>80</v>
       </c>
       <c r="T88" t="s" s="2">
-        <v>80</v>
+        <v>473</v>
       </c>
       <c r="U88" t="s" s="2">
         <v>80</v>
@@ -12847,13 +12899,13 @@
         <v>80</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>598</v>
+        <v>474</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>80</v>
@@ -12862,30 +12914,30 @@
         <v>101</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>599</v>
+        <v>475</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>600</v>
+        <v>476</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>80</v>
+        <v>477</v>
       </c>
       <c r="AN88" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>80</v>
+        <v>534</v>
       </c>
       <c r="AP88" t="s" s="2">
-        <v>80</v>
+        <v>535</v>
       </c>
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>601</v>
+        <v>536</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>601</v>
+        <v>478</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12899,7 +12951,7 @@
         <v>89</v>
       </c>
       <c r="H89" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="I89" t="s" s="2">
         <v>80</v>
@@ -12911,17 +12963,15 @@
         <v>159</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>602</v>
+        <v>479</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>603</v>
+        <v>480</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>604</v>
-      </c>
-      <c r="O89" t="s" s="2">
-        <v>605</v>
-      </c>
+        <v>481</v>
+      </c>
+      <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>80</v>
       </c>
@@ -12945,13 +12995,11 @@
         <v>80</v>
       </c>
       <c r="X89" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y89" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="Y89" s="2"/>
       <c r="Z89" t="s" s="2">
-        <v>80</v>
+        <v>513</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>80</v>
@@ -12969,7 +13017,7 @@
         <v>80</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>606</v>
+        <v>482</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>78</v>
@@ -12984,30 +13032,30 @@
         <v>101</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>607</v>
+        <v>483</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>608</v>
+        <v>484</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>80</v>
+        <v>485</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>609</v>
+        <v>537</v>
       </c>
       <c r="AP89" t="s" s="2">
-        <v>80</v>
+        <v>532</v>
       </c>
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>610</v>
+        <v>538</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>610</v>
+        <v>486</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13027,20 +13075,20 @@
         <v>80</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K90" t="s" s="2">
         <v>212</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>611</v>
+        <v>487</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>612</v>
+        <v>488</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" t="s" s="2">
-        <v>613</v>
+        <v>489</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>80</v>
@@ -13053,7 +13101,7 @@
         <v>80</v>
       </c>
       <c r="T90" t="s" s="2">
-        <v>80</v>
+        <v>490</v>
       </c>
       <c r="U90" t="s" s="2">
         <v>80</v>
@@ -13089,7 +13137,7 @@
         <v>80</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>610</v>
+        <v>491</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>78</v>
@@ -13104,13 +13152,13 @@
         <v>101</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>80</v>
+        <v>492</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>614</v>
+        <v>342</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>615</v>
+        <v>218</v>
       </c>
       <c r="AN90" t="s" s="2">
         <v>80</v>
@@ -13124,10 +13172,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>616</v>
+        <v>539</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>616</v>
+        <v>540</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13150,13 +13198,13 @@
         <v>80</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>220</v>
+        <v>159</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>617</v>
+        <v>160</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>618</v>
+        <v>161</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -13207,7 +13255,7 @@
         <v>80</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>616</v>
+        <v>162</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>78</v>
@@ -13219,13 +13267,13 @@
         <v>80</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>619</v>
+        <v>163</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>80</v>
@@ -13242,14 +13290,14 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>620</v>
+        <v>541</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>620</v>
+        <v>542</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>80</v>
+        <v>134</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
@@ -13268,20 +13316,18 @@
         <v>80</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>180</v>
+        <v>135</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>621</v>
+        <v>136</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>622</v>
+        <v>165</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>623</v>
-      </c>
-      <c r="O92" t="s" s="2">
-        <v>624</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
         <v>80</v>
       </c>
@@ -13305,31 +13351,31 @@
         <v>80</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>113</v>
+        <v>80</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>115</v>
+        <v>80</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AB92" t="s" s="2">
-        <v>80</v>
+        <v>166</v>
       </c>
       <c r="AC92" t="s" s="2">
-        <v>80</v>
+        <v>167</v>
       </c>
       <c r="AD92" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE92" t="s" s="2">
-        <v>80</v>
+        <v>153</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>620</v>
+        <v>168</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>78</v>
@@ -13341,29 +13387,2189 @@
         <v>80</v>
       </c>
       <c r="AJ92" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL92" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="AM92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP92" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="93" hidden="true">
+      <c r="A93" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="B93" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="C93" s="2"/>
+      <c r="D93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E93" s="2"/>
+      <c r="F93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G93" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J93" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K93" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="L93" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="M93" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="N93" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="O93" s="2"/>
+      <c r="P93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q93" s="2"/>
+      <c r="R93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF93" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="AG93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH93" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI93" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="AJ93" t="s" s="2">
         <v>101</v>
       </c>
-      <c r="AK92" t="s" s="2">
+      <c r="AK93" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="AL93" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="AM93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO93" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="AP93" t="s" s="2">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="94" hidden="true">
+      <c r="A94" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="B94" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="C94" s="2"/>
+      <c r="D94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E94" s="2"/>
+      <c r="F94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G94" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J94" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K94" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="L94" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="M94" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="N94" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="O94" s="2"/>
+      <c r="P94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q94" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="R94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF94" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="AG94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH94" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI94" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="AJ94" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK94" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="AL94" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="AM94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO94" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="AP94" t="s" s="2">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="95" hidden="true">
+      <c r="A95" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="B95" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="C95" s="2"/>
+      <c r="D95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E95" s="2"/>
+      <c r="F95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G95" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J95" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K95" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="L95" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="M95" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="N95" s="2"/>
+      <c r="O95" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="P95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q95" s="2"/>
+      <c r="R95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X95" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="Y95" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="Z95" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="AA95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF95" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="AG95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH95" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ95" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK95" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="AL95" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="AM95" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="AN95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP95" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="96" hidden="true">
+      <c r="A96" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="B96" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="C96" s="2"/>
+      <c r="D96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E96" s="2"/>
+      <c r="F96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G96" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J96" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K96" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="L96" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="M96" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="N96" s="2"/>
+      <c r="O96" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="P96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q96" s="2"/>
+      <c r="R96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF96" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="AG96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH96" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ96" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK96" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="AL96" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="AM96" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="AN96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO96" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="AP96" t="s" s="2">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="97" hidden="true">
+      <c r="A97" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="B97" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="C97" s="2"/>
+      <c r="D97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E97" s="2"/>
+      <c r="F97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G97" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K97" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="L97" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="M97" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="N97" s="2"/>
+      <c r="O97" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="P97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q97" s="2"/>
+      <c r="R97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF97" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="AG97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH97" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ97" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL97" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="AM97" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="AN97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP97" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="98" hidden="true">
+      <c r="A98" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="B98" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="C98" s="2"/>
+      <c r="D98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E98" s="2"/>
+      <c r="F98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G98" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K98" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="L98" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="M98" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="N98" s="2"/>
+      <c r="O98" s="2"/>
+      <c r="P98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q98" s="2"/>
+      <c r="R98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF98" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="AG98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH98" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ98" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK98" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="AL98" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="AM98" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="AN98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP98" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="99" hidden="true">
+      <c r="A99" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="B99" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="C99" s="2"/>
+      <c r="D99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E99" s="2"/>
+      <c r="F99" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G99" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K99" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="L99" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="M99" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="N99" s="2"/>
+      <c r="O99" s="2"/>
+      <c r="P99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q99" s="2"/>
+      <c r="R99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF99" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AG99" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH99" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL99" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="AM99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP99" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="100" hidden="true">
+      <c r="A100" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="B100" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="C100" s="2"/>
+      <c r="D100" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="E100" s="2"/>
+      <c r="F100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G100" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K100" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L100" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="M100" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="N100" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="O100" s="2"/>
+      <c r="P100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q100" s="2"/>
+      <c r="R100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF100" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="AG100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH100" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ100" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL100" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="AM100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP100" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="101" hidden="true">
+      <c r="A101" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="B101" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="C101" s="2"/>
+      <c r="D101" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="E101" s="2"/>
+      <c r="F101" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G101" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I101" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="J101" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K101" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L101" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="M101" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="N101" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="O101" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="P101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q101" s="2"/>
+      <c r="R101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF101" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="AG101" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH101" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ101" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL101" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AM101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP101" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="102" hidden="true">
+      <c r="A102" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="B102" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="C102" s="2"/>
+      <c r="D102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E102" s="2"/>
+      <c r="F102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G102" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K102" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="L102" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="M102" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="N102" s="2"/>
+      <c r="O102" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="P102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q102" s="2"/>
+      <c r="R102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF102" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="AG102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH102" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ102" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL102" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="AM102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP102" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="103" hidden="true">
+      <c r="A103" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="B103" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="C103" s="2"/>
+      <c r="D103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E103" s="2"/>
+      <c r="F103" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G103" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K103" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="L103" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="M103" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="N103" s="2"/>
+      <c r="O103" s="2"/>
+      <c r="P103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q103" s="2"/>
+      <c r="R103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X103" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="Y103" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="Z103" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="AA103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF103" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="AG103" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AH103" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ103" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL103" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="AM103" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="AN103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP103" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="104" hidden="true">
+      <c r="A104" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="B104" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="C104" s="2"/>
+      <c r="D104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E104" s="2"/>
+      <c r="F104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G104" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K104" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="L104" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="M104" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="N104" s="2"/>
+      <c r="O104" s="2"/>
+      <c r="P104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q104" s="2"/>
+      <c r="R104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF104" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AG104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH104" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL104" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="AM104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP104" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="105" hidden="true">
+      <c r="A105" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="B105" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="C105" s="2"/>
+      <c r="D105" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="E105" s="2"/>
+      <c r="F105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G105" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K105" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L105" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="M105" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="N105" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="O105" s="2"/>
+      <c r="P105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q105" s="2"/>
+      <c r="R105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB105" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="AC105" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AD105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE105" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AF105" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="AG105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH105" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ105" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL105" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="AM105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP105" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="106" hidden="true">
+      <c r="A106" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="B106" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="C106" s="2"/>
+      <c r="D106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E106" s="2"/>
+      <c r="F106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J106" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K106" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="L106" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="M106" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="N106" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="O106" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="P106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q106" s="2"/>
+      <c r="R106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF106" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="AG106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ106" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK106" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="AL106" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="AM106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP106" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="107" hidden="true">
+      <c r="A107" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="B107" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="C107" s="2"/>
+      <c r="D107" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E107" s="2"/>
+      <c r="F107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G107" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H107" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I107" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J107" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K107" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="L107" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="M107" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="N107" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="O107" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="P107" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q107" s="2"/>
+      <c r="R107" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S107" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T107" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U107" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V107" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W107" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X107" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y107" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z107" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA107" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB107" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC107" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD107" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE107" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF107" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="AG107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH107" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI107" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ107" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK107" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="AL107" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="AM107" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN107" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO107" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="AP107" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="108" hidden="true">
+      <c r="A108" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="B108" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="C108" s="2"/>
+      <c r="D108" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E108" s="2"/>
+      <c r="F108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G108" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H108" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I108" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J108" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K108" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="L108" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="M108" t="s" s="2">
         <v>625</v>
       </c>
-      <c r="AL92" t="s" s="2">
+      <c r="N108" s="2"/>
+      <c r="O108" t="s" s="2">
         <v>626</v>
       </c>
-      <c r="AM92" t="s" s="2">
+      <c r="P108" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q108" s="2"/>
+      <c r="R108" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S108" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T108" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U108" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V108" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W108" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X108" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y108" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z108" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA108" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB108" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC108" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD108" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE108" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF108" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="AG108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH108" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI108" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ108" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK108" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL108" t="s" s="2">
         <v>627</v>
       </c>
-      <c r="AN92" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO92" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP92" t="s" s="2">
+      <c r="AM108" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="AN108" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO108" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP108" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="109" hidden="true">
+      <c r="A109" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="B109" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="C109" s="2"/>
+      <c r="D109" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E109" s="2"/>
+      <c r="F109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G109" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H109" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I109" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J109" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K109" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="L109" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="M109" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="N109" s="2"/>
+      <c r="O109" s="2"/>
+      <c r="P109" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q109" s="2"/>
+      <c r="R109" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S109" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T109" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U109" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V109" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W109" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X109" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y109" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z109" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA109" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB109" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC109" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD109" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE109" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF109" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="AG109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH109" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI109" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ109" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK109" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL109" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="AM109" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN109" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO109" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP109" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="110" hidden="true">
+      <c r="A110" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="B110" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="C110" s="2"/>
+      <c r="D110" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E110" s="2"/>
+      <c r="F110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G110" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H110" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I110" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J110" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K110" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="L110" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="M110" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="N110" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="O110" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="P110" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q110" s="2"/>
+      <c r="R110" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S110" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T110" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U110" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V110" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W110" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X110" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="Y110" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="Z110" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AA110" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB110" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC110" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD110" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE110" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF110" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="AG110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH110" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI110" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ110" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK110" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="AL110" t="s" s="2">
+        <v>639</v>
+      </c>
+      <c r="AM110" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="AN110" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO110" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP110" t="s" s="2">
         <v>80</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP92">
+  <autoFilter ref="A1:AP110">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -13373,7 +15579,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI91">
+  <conditionalFormatting sqref="A2:AI109">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$110</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$136</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4218" uniqueCount="641">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5204" uniqueCount="669">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T20:37:43+00:00</t>
+    <t>2023-11-29T20:32:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1727,6 +1727,90 @@
   </si>
   <si>
     <t>SStaff.SStaff.TemporaryAddressEndDate</t>
+  </si>
+  <si>
+    <t>Practitioner.address:physical</t>
+  </si>
+  <si>
+    <t>physical</t>
+  </si>
+  <si>
+    <t>Practitioner.address:physical.id</t>
+  </si>
+  <si>
+    <t>Practitioner.address:physical.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.address:physical.use</t>
+  </si>
+  <si>
+    <t>Practitioner.address:physical.type</t>
+  </si>
+  <si>
+    <t>Practitioner.address:physical.text</t>
+  </si>
+  <si>
+    <t>Practitioner.address:physical.line</t>
+  </si>
+  <si>
+    <t>Practitioner.address:physical.city</t>
+  </si>
+  <si>
+    <t>Practitioner.address:physical.district</t>
+  </si>
+  <si>
+    <t>Practitioner.address:physical.state</t>
+  </si>
+  <si>
+    <t>Practitioner.address:physical.postalCode</t>
+  </si>
+  <si>
+    <t>Practitioner.address:physical.country</t>
+  </si>
+  <si>
+    <t>Practitioner.address:physical.period</t>
+  </si>
+  <si>
+    <t>Practitioner.address:postal</t>
+  </si>
+  <si>
+    <t>postal</t>
+  </si>
+  <si>
+    <t>Practitioner.address:postal.id</t>
+  </si>
+  <si>
+    <t>Practitioner.address:postal.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.address:postal.use</t>
+  </si>
+  <si>
+    <t>Practitioner.address:postal.type</t>
+  </si>
+  <si>
+    <t>Practitioner.address:postal.text</t>
+  </si>
+  <si>
+    <t>Practitioner.address:postal.line</t>
+  </si>
+  <si>
+    <t>Practitioner.address:postal.city</t>
+  </si>
+  <si>
+    <t>Practitioner.address:postal.district</t>
+  </si>
+  <si>
+    <t>Practitioner.address:postal.state</t>
+  </si>
+  <si>
+    <t>Practitioner.address:postal.postalCode</t>
+  </si>
+  <si>
+    <t>Practitioner.address:postal.country</t>
+  </si>
+  <si>
+    <t>Practitioner.address:postal.period</t>
   </si>
   <si>
     <t>Practitioner.gender</t>
@@ -2320,7 +2404,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP110"/>
+  <dimension ref="A1:AP136"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="40.87109375" customWidth="true" bestFit="true"/>
@@ -13655,9 +13739,11 @@
         <v>551</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>551</v>
-      </c>
-      <c r="C95" s="2"/>
+        <v>394</v>
+      </c>
+      <c r="C95" t="s" s="2">
+        <v>552</v>
+      </c>
       <c r="D95" t="s" s="2">
         <v>80</v>
       </c>
@@ -13669,7 +13755,7 @@
         <v>89</v>
       </c>
       <c r="H95" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="I95" t="s" s="2">
         <v>80</v>
@@ -13678,17 +13764,19 @@
         <v>90</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>109</v>
+        <v>395</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>552</v>
+        <v>396</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="N95" s="2"/>
+        <v>397</v>
+      </c>
+      <c r="N95" t="s" s="2">
+        <v>398</v>
+      </c>
       <c r="O95" t="s" s="2">
-        <v>554</v>
+        <v>399</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>80</v>
@@ -13713,13 +13801,13 @@
         <v>80</v>
       </c>
       <c r="X95" t="s" s="2">
-        <v>174</v>
+        <v>80</v>
       </c>
       <c r="Y95" t="s" s="2">
-        <v>555</v>
+        <v>80</v>
       </c>
       <c r="Z95" t="s" s="2">
-        <v>556</v>
+        <v>80</v>
       </c>
       <c r="AA95" t="s" s="2">
         <v>80</v>
@@ -13737,13 +13825,13 @@
         <v>80</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>551</v>
+        <v>394</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH95" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI95" t="s" s="2">
         <v>80</v>
@@ -13752,13 +13840,13 @@
         <v>101</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>557</v>
+        <v>401</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>558</v>
+        <v>402</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>559</v>
+        <v>163</v>
       </c>
       <c r="AN95" t="s" s="2">
         <v>80</v>
@@ -13772,10 +13860,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>560</v>
+        <v>553</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>560</v>
+        <v>403</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13795,21 +13883,19 @@
         <v>80</v>
       </c>
       <c r="J96" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>561</v>
+        <v>159</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>562</v>
+        <v>160</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>563</v>
+        <v>161</v>
       </c>
       <c r="N96" s="2"/>
-      <c r="O96" t="s" s="2">
-        <v>564</v>
-      </c>
+      <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
         <v>80</v>
       </c>
@@ -13857,7 +13943,7 @@
         <v>80</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>560</v>
+        <v>162</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>78</v>
@@ -13869,37 +13955,37 @@
         <v>80</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>565</v>
+        <v>80</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>566</v>
+        <v>163</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>567</v>
+        <v>80</v>
       </c>
       <c r="AN96" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO96" t="s" s="2">
-        <v>568</v>
+        <v>80</v>
       </c>
       <c r="AP96" t="s" s="2">
-        <v>569</v>
+        <v>80</v>
       </c>
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>570</v>
+        <v>554</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>570</v>
+        <v>404</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>80</v>
+        <v>134</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
@@ -13918,18 +14004,18 @@
         <v>80</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>571</v>
+        <v>135</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>572</v>
+        <v>136</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="N97" s="2"/>
-      <c r="O97" t="s" s="2">
-        <v>574</v>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="N97" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
         <v>80</v>
       </c>
@@ -13965,19 +14051,19 @@
         <v>80</v>
       </c>
       <c r="AB97" t="s" s="2">
-        <v>80</v>
+        <v>166</v>
       </c>
       <c r="AC97" t="s" s="2">
-        <v>80</v>
+        <v>167</v>
       </c>
       <c r="AD97" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE97" t="s" s="2">
-        <v>80</v>
+        <v>153</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>570</v>
+        <v>168</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>78</v>
@@ -13989,16 +14075,16 @@
         <v>80</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>575</v>
+        <v>163</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>576</v>
+        <v>80</v>
       </c>
       <c r="AN97" t="s" s="2">
         <v>80</v>
@@ -14012,10 +14098,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>577</v>
+        <v>555</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>577</v>
+        <v>405</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14026,28 +14112,32 @@
         <v>78</v>
       </c>
       <c r="G98" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H98" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I98" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="J98" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>578</v>
+        <v>109</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>579</v>
+        <v>406</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>580</v>
-      </c>
-      <c r="N98" s="2"/>
-      <c r="O98" s="2"/>
+        <v>407</v>
+      </c>
+      <c r="N98" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="O98" t="s" s="2">
+        <v>409</v>
+      </c>
       <c r="P98" t="s" s="2">
         <v>80</v>
       </c>
@@ -14059,7 +14149,7 @@
         <v>80</v>
       </c>
       <c r="T98" t="s" s="2">
-        <v>80</v>
+        <v>410</v>
       </c>
       <c r="U98" t="s" s="2">
         <v>80</v>
@@ -14071,13 +14161,13 @@
         <v>80</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>80</v>
+        <v>174</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>80</v>
+        <v>411</v>
       </c>
       <c r="Z98" t="s" s="2">
-        <v>80</v>
+        <v>412</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>80</v>
@@ -14095,13 +14185,13 @@
         <v>80</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>577</v>
+        <v>413</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH98" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI98" t="s" s="2">
         <v>80</v>
@@ -14110,13 +14200,13 @@
         <v>101</v>
       </c>
       <c r="AK98" t="s" s="2">
-        <v>581</v>
+        <v>414</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>582</v>
+        <v>294</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>583</v>
+        <v>415</v>
       </c>
       <c r="AN98" t="s" s="2">
         <v>80</v>
@@ -14130,10 +14220,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>584</v>
+        <v>556</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>584</v>
+        <v>416</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14153,18 +14243,20 @@
         <v>80</v>
       </c>
       <c r="J99" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>159</v>
+        <v>109</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>160</v>
+        <v>417</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="N99" s="2"/>
+        <v>418</v>
+      </c>
+      <c r="N99" t="s" s="2">
+        <v>419</v>
+      </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
         <v>80</v>
@@ -14177,7 +14269,7 @@
         <v>80</v>
       </c>
       <c r="T99" t="s" s="2">
-        <v>80</v>
+        <v>420</v>
       </c>
       <c r="U99" t="s" s="2">
         <v>80</v>
@@ -14189,13 +14281,13 @@
         <v>80</v>
       </c>
       <c r="X99" t="s" s="2">
-        <v>80</v>
+        <v>174</v>
       </c>
       <c r="Y99" t="s" s="2">
-        <v>80</v>
+        <v>421</v>
       </c>
       <c r="Z99" t="s" s="2">
-        <v>80</v>
+        <v>422</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>80</v>
@@ -14213,7 +14305,7 @@
         <v>80</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>162</v>
+        <v>423</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>78</v>
@@ -14225,13 +14317,13 @@
         <v>80</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="AK99" t="s" s="2">
-        <v>80</v>
+        <v>424</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>163</v>
+        <v>294</v>
       </c>
       <c r="AM99" t="s" s="2">
         <v>80</v>
@@ -14248,21 +14340,21 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>585</v>
+        <v>557</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>585</v>
+        <v>425</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
-        <v>134</v>
+        <v>80</v>
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G100" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H100" t="s" s="2">
         <v>80</v>
@@ -14271,21 +14363,23 @@
         <v>80</v>
       </c>
       <c r="J100" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>136</v>
+        <v>426</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>165</v>
+        <v>427</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O100" s="2"/>
+        <v>428</v>
+      </c>
+      <c r="O100" t="s" s="2">
+        <v>300</v>
+      </c>
       <c r="P100" t="s" s="2">
         <v>80</v>
       </c>
@@ -14297,7 +14391,7 @@
         <v>80</v>
       </c>
       <c r="T100" t="s" s="2">
-        <v>80</v>
+        <v>429</v>
       </c>
       <c r="U100" t="s" s="2">
         <v>80</v>
@@ -14333,25 +14427,25 @@
         <v>80</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>168</v>
+        <v>430</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH100" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI100" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>80</v>
+        <v>431</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>163</v>
+        <v>303</v>
       </c>
       <c r="AM100" t="s" s="2">
         <v>80</v>
@@ -14368,46 +14462,42 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>586</v>
+        <v>558</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>586</v>
+        <v>432</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>587</v>
+        <v>80</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>79</v>
+        <v>433</v>
       </c>
       <c r="H101" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="I101" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="J101" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>588</v>
+        <v>434</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>589</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O101" t="s" s="2">
-        <v>144</v>
-      </c>
+        <v>435</v>
+      </c>
+      <c r="N101" s="2"/>
+      <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
         <v>80</v>
       </c>
@@ -14419,7 +14509,7 @@
         <v>80</v>
       </c>
       <c r="T101" t="s" s="2">
-        <v>80</v>
+        <v>436</v>
       </c>
       <c r="U101" t="s" s="2">
         <v>80</v>
@@ -14455,7 +14545,7 @@
         <v>80</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>590</v>
+        <v>437</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>78</v>
@@ -14467,16 +14557,16 @@
         <v>80</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK101" t="s" s="2">
-        <v>80</v>
+        <v>438</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>132</v>
+        <v>439</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>80</v>
+        <v>440</v>
       </c>
       <c r="AN101" t="s" s="2">
         <v>80</v>
@@ -14490,44 +14580,42 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>591</v>
+        <v>559</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>591</v>
+        <v>441</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
-        <v>80</v>
+        <v>442</v>
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G102" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H102" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="I102" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J102" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>592</v>
+        <v>443</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>593</v>
+        <v>444</v>
       </c>
       <c r="N102" s="2"/>
-      <c r="O102" t="s" s="2">
-        <v>594</v>
-      </c>
+      <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
         <v>80</v>
       </c>
@@ -14539,7 +14627,7 @@
         <v>80</v>
       </c>
       <c r="T102" t="s" s="2">
-        <v>80</v>
+        <v>445</v>
       </c>
       <c r="U102" t="s" s="2">
         <v>80</v>
@@ -14575,13 +14663,13 @@
         <v>80</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>591</v>
+        <v>446</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH102" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI102" t="s" s="2">
         <v>80</v>
@@ -14590,13 +14678,13 @@
         <v>101</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>80</v>
+        <v>447</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>595</v>
+        <v>448</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>80</v>
+        <v>449</v>
       </c>
       <c r="AN102" t="s" s="2">
         <v>80</v>
@@ -14610,18 +14698,18 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>596</v>
+        <v>560</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>596</v>
+        <v>450</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
-        <v>80</v>
+        <v>451</v>
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G103" t="s" s="2">
         <v>89</v>
@@ -14633,18 +14721,20 @@
         <v>80</v>
       </c>
       <c r="J103" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>180</v>
+        <v>159</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>597</v>
+        <v>452</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>598</v>
-      </c>
-      <c r="N103" s="2"/>
+        <v>453</v>
+      </c>
+      <c r="N103" t="s" s="2">
+        <v>454</v>
+      </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
         <v>80</v>
@@ -14657,7 +14747,7 @@
         <v>80</v>
       </c>
       <c r="T103" t="s" s="2">
-        <v>80</v>
+        <v>455</v>
       </c>
       <c r="U103" t="s" s="2">
         <v>80</v>
@@ -14669,13 +14759,13 @@
         <v>80</v>
       </c>
       <c r="X103" t="s" s="2">
-        <v>599</v>
+        <v>80</v>
       </c>
       <c r="Y103" t="s" s="2">
-        <v>600</v>
+        <v>80</v>
       </c>
       <c r="Z103" t="s" s="2">
-        <v>601</v>
+        <v>80</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>80</v>
@@ -14693,10 +14783,10 @@
         <v>80</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>596</v>
+        <v>456</v>
       </c>
       <c r="AG103" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AH103" t="s" s="2">
         <v>89</v>
@@ -14708,13 +14798,13 @@
         <v>101</v>
       </c>
       <c r="AK103" t="s" s="2">
-        <v>80</v>
+        <v>457</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>582</v>
+        <v>458</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>602</v>
+        <v>80</v>
       </c>
       <c r="AN103" t="s" s="2">
         <v>80</v>
@@ -14728,14 +14818,14 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>603</v>
+        <v>561</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>603</v>
+        <v>459</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
-        <v>80</v>
+        <v>460</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
@@ -14745,22 +14835,22 @@
         <v>89</v>
       </c>
       <c r="H104" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="I104" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J104" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K104" t="s" s="2">
         <v>159</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>160</v>
+        <v>461</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>161</v>
+        <v>462</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -14787,13 +14877,13 @@
         <v>80</v>
       </c>
       <c r="X104" t="s" s="2">
-        <v>80</v>
+        <v>185</v>
       </c>
       <c r="Y104" t="s" s="2">
-        <v>80</v>
+        <v>463</v>
       </c>
       <c r="Z104" t="s" s="2">
-        <v>80</v>
+        <v>464</v>
       </c>
       <c r="AA104" t="s" s="2">
         <v>80</v>
@@ -14811,7 +14901,7 @@
         <v>80</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>162</v>
+        <v>465</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>78</v>
@@ -14823,16 +14913,16 @@
         <v>80</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="AK104" t="s" s="2">
-        <v>80</v>
+        <v>466</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>163</v>
+        <v>467</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>80</v>
+        <v>468</v>
       </c>
       <c r="AN104" t="s" s="2">
         <v>80</v>
@@ -14846,43 +14936,41 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>604</v>
+        <v>562</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>604</v>
+        <v>469</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
-        <v>134</v>
+        <v>470</v>
       </c>
       <c r="E105" s="2"/>
       <c r="F105" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G105" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H105" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="I105" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J105" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>136</v>
+        <v>471</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="N105" t="s" s="2">
-        <v>138</v>
-      </c>
+        <v>472</v>
+      </c>
+      <c r="N105" s="2"/>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
         <v>80</v>
@@ -14895,7 +14983,7 @@
         <v>80</v>
       </c>
       <c r="T105" t="s" s="2">
-        <v>80</v>
+        <v>473</v>
       </c>
       <c r="U105" t="s" s="2">
         <v>80</v>
@@ -14919,40 +15007,40 @@
         <v>80</v>
       </c>
       <c r="AB105" t="s" s="2">
-        <v>166</v>
+        <v>80</v>
       </c>
       <c r="AC105" t="s" s="2">
-        <v>167</v>
+        <v>80</v>
       </c>
       <c r="AD105" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE105" t="s" s="2">
-        <v>153</v>
+        <v>80</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>168</v>
+        <v>474</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH105" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI105" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK105" t="s" s="2">
-        <v>80</v>
+        <v>475</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>163</v>
+        <v>476</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>80</v>
+        <v>477</v>
       </c>
       <c r="AN105" t="s" s="2">
         <v>80</v>
@@ -14966,10 +15054,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>605</v>
+        <v>563</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>605</v>
+        <v>478</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14980,10 +15068,10 @@
         <v>78</v>
       </c>
       <c r="G106" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H106" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="I106" t="s" s="2">
         <v>80</v>
@@ -14992,20 +15080,18 @@
         <v>90</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>606</v>
+        <v>159</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>607</v>
+        <v>479</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>608</v>
+        <v>480</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>609</v>
-      </c>
-      <c r="O106" t="s" s="2">
-        <v>610</v>
-      </c>
+        <v>481</v>
+      </c>
+      <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
         <v>80</v>
       </c>
@@ -15053,13 +15139,13 @@
         <v>80</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>611</v>
+        <v>482</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH106" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI106" t="s" s="2">
         <v>80</v>
@@ -15068,13 +15154,13 @@
         <v>101</v>
       </c>
       <c r="AK106" t="s" s="2">
-        <v>612</v>
+        <v>483</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>613</v>
+        <v>484</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>80</v>
+        <v>485</v>
       </c>
       <c r="AN106" t="s" s="2">
         <v>80</v>
@@ -15088,10 +15174,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>614</v>
+        <v>564</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>614</v>
+        <v>486</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15114,19 +15200,17 @@
         <v>90</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>159</v>
+        <v>212</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>615</v>
+        <v>487</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>616</v>
-      </c>
-      <c r="N107" t="s" s="2">
-        <v>617</v>
-      </c>
+        <v>488</v>
+      </c>
+      <c r="N107" s="2"/>
       <c r="O107" t="s" s="2">
-        <v>618</v>
+        <v>489</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>80</v>
@@ -15139,7 +15223,7 @@
         <v>80</v>
       </c>
       <c r="T107" t="s" s="2">
-        <v>80</v>
+        <v>490</v>
       </c>
       <c r="U107" t="s" s="2">
         <v>80</v>
@@ -15175,7 +15259,7 @@
         <v>80</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>619</v>
+        <v>491</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>78</v>
@@ -15190,19 +15274,19 @@
         <v>101</v>
       </c>
       <c r="AK107" t="s" s="2">
-        <v>620</v>
+        <v>492</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>621</v>
+        <v>342</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>80</v>
+        <v>218</v>
       </c>
       <c r="AN107" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO107" t="s" s="2">
-        <v>622</v>
+        <v>80</v>
       </c>
       <c r="AP107" t="s" s="2">
         <v>80</v>
@@ -15210,12 +15294,14 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>623</v>
+        <v>565</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>623</v>
-      </c>
-      <c r="C108" s="2"/>
+        <v>394</v>
+      </c>
+      <c r="C108" t="s" s="2">
+        <v>566</v>
+      </c>
       <c r="D108" t="s" s="2">
         <v>80</v>
       </c>
@@ -15227,26 +15313,28 @@
         <v>89</v>
       </c>
       <c r="H108" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="I108" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J108" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>212</v>
+        <v>395</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>624</v>
+        <v>396</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>625</v>
-      </c>
-      <c r="N108" s="2"/>
+        <v>397</v>
+      </c>
+      <c r="N108" t="s" s="2">
+        <v>398</v>
+      </c>
       <c r="O108" t="s" s="2">
-        <v>626</v>
+        <v>399</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>80</v>
@@ -15295,13 +15383,13 @@
         <v>80</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>623</v>
+        <v>394</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH108" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI108" t="s" s="2">
         <v>80</v>
@@ -15310,13 +15398,13 @@
         <v>101</v>
       </c>
       <c r="AK108" t="s" s="2">
-        <v>80</v>
+        <v>401</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>627</v>
+        <v>402</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>628</v>
+        <v>163</v>
       </c>
       <c r="AN108" t="s" s="2">
         <v>80</v>
@@ -15330,10 +15418,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>629</v>
+        <v>567</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>629</v>
+        <v>403</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15356,13 +15444,13 @@
         <v>80</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>220</v>
+        <v>159</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>630</v>
+        <v>160</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>631</v>
+        <v>161</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" s="2"/>
@@ -15413,7 +15501,7 @@
         <v>80</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>629</v>
+        <v>162</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>78</v>
@@ -15425,13 +15513,13 @@
         <v>80</v>
       </c>
       <c r="AJ109" t="s" s="2">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="AK109" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>632</v>
+        <v>163</v>
       </c>
       <c r="AM109" t="s" s="2">
         <v>80</v>
@@ -15448,14 +15536,14 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>633</v>
+        <v>568</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>633</v>
+        <v>404</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
-        <v>80</v>
+        <v>134</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
@@ -15474,20 +15562,18 @@
         <v>80</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>180</v>
+        <v>135</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>634</v>
+        <v>136</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>635</v>
+        <v>165</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>636</v>
-      </c>
-      <c r="O110" t="s" s="2">
-        <v>637</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
         <v>80</v>
       </c>
@@ -15511,31 +15597,31 @@
         <v>80</v>
       </c>
       <c r="X110" t="s" s="2">
-        <v>113</v>
+        <v>80</v>
       </c>
       <c r="Y110" t="s" s="2">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="Z110" t="s" s="2">
-        <v>115</v>
+        <v>80</v>
       </c>
       <c r="AA110" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AB110" t="s" s="2">
-        <v>80</v>
+        <v>166</v>
       </c>
       <c r="AC110" t="s" s="2">
-        <v>80</v>
+        <v>167</v>
       </c>
       <c r="AD110" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE110" t="s" s="2">
-        <v>80</v>
+        <v>153</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>633</v>
+        <v>168</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>78</v>
@@ -15547,29 +15633,3143 @@
         <v>80</v>
       </c>
       <c r="AJ110" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK110" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL110" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="AM110" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN110" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO110" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP110" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="111" hidden="true">
+      <c r="A111" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="B111" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="C111" s="2"/>
+      <c r="D111" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E111" s="2"/>
+      <c r="F111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G111" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H111" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I111" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="J111" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K111" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="L111" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="M111" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="N111" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="O111" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="P111" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q111" s="2"/>
+      <c r="R111" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S111" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T111" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="U111" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V111" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W111" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X111" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="Y111" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="Z111" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="AA111" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB111" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC111" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD111" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE111" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF111" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="AG111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH111" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI111" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ111" t="s" s="2">
         <v>101</v>
       </c>
-      <c r="AK110" t="s" s="2">
+      <c r="AK111" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="AL111" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="AM111" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="AN111" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO111" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP111" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="112" hidden="true">
+      <c r="A112" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="B112" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="C112" s="2"/>
+      <c r="D112" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E112" s="2"/>
+      <c r="F112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G112" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H112" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I112" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J112" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K112" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="L112" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="M112" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="N112" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="O112" s="2"/>
+      <c r="P112" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q112" s="2"/>
+      <c r="R112" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S112" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T112" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="U112" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V112" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W112" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X112" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="Y112" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="Z112" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="AA112" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB112" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC112" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD112" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE112" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF112" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="AG112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH112" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI112" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ112" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK112" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="AL112" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="AM112" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN112" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO112" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP112" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="113" hidden="true">
+      <c r="A113" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="B113" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="C113" s="2"/>
+      <c r="D113" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E113" s="2"/>
+      <c r="F113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G113" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H113" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I113" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J113" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K113" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="L113" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="M113" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="N113" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="O113" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="P113" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q113" s="2"/>
+      <c r="R113" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S113" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T113" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="U113" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V113" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W113" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X113" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y113" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z113" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA113" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB113" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC113" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD113" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE113" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF113" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="AG113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH113" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI113" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ113" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK113" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="AL113" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="AM113" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN113" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO113" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP113" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="114" hidden="true">
+      <c r="A114" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="B114" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="C114" s="2"/>
+      <c r="D114" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E114" s="2"/>
+      <c r="F114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G114" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="H114" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="I114" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J114" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K114" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="L114" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="M114" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="N114" s="2"/>
+      <c r="O114" s="2"/>
+      <c r="P114" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q114" s="2"/>
+      <c r="R114" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S114" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T114" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="U114" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V114" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W114" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X114" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y114" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z114" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA114" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB114" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC114" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD114" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE114" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF114" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="AG114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH114" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI114" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ114" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK114" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="AL114" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="AM114" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="AN114" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO114" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP114" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="115" hidden="true">
+      <c r="A115" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="B115" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="C115" s="2"/>
+      <c r="D115" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="E115" s="2"/>
+      <c r="F115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G115" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H115" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="I115" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J115" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K115" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="L115" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="M115" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="N115" s="2"/>
+      <c r="O115" s="2"/>
+      <c r="P115" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q115" s="2"/>
+      <c r="R115" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S115" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T115" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="U115" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V115" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W115" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X115" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y115" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z115" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA115" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB115" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC115" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD115" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE115" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF115" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="AG115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH115" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI115" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ115" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK115" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="AL115" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="AM115" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="AN115" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO115" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP115" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="116" hidden="true">
+      <c r="A116" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="B116" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="C116" s="2"/>
+      <c r="D116" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="E116" s="2"/>
+      <c r="F116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G116" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H116" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I116" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J116" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K116" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="L116" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="M116" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="N116" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="O116" s="2"/>
+      <c r="P116" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q116" s="2"/>
+      <c r="R116" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S116" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T116" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="U116" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V116" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W116" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X116" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y116" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z116" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA116" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB116" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC116" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD116" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE116" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF116" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="AG116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH116" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI116" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ116" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK116" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="AL116" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="AM116" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN116" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO116" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP116" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="117" hidden="true">
+      <c r="A117" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="B117" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="C117" s="2"/>
+      <c r="D117" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="E117" s="2"/>
+      <c r="F117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G117" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H117" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="I117" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J117" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K117" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="L117" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="M117" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="N117" s="2"/>
+      <c r="O117" s="2"/>
+      <c r="P117" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q117" s="2"/>
+      <c r="R117" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S117" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T117" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U117" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V117" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W117" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X117" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="Y117" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="Z117" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="AA117" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB117" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC117" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD117" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE117" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF117" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="AG117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH117" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI117" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ117" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK117" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="AL117" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="AM117" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="AN117" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO117" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP117" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="118" hidden="true">
+      <c r="A118" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="B118" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="C118" s="2"/>
+      <c r="D118" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="E118" s="2"/>
+      <c r="F118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G118" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H118" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="I118" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J118" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K118" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="L118" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="M118" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="N118" s="2"/>
+      <c r="O118" s="2"/>
+      <c r="P118" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q118" s="2"/>
+      <c r="R118" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S118" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T118" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="U118" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V118" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W118" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X118" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y118" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z118" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA118" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB118" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC118" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD118" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE118" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF118" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="AG118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH118" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI118" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ118" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK118" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="AL118" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="AM118" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="AN118" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO118" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP118" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="119" hidden="true">
+      <c r="A119" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="B119" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="C119" s="2"/>
+      <c r="D119" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E119" s="2"/>
+      <c r="F119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G119" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H119" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="I119" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J119" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K119" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="L119" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="M119" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="N119" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="O119" s="2"/>
+      <c r="P119" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q119" s="2"/>
+      <c r="R119" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S119" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T119" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U119" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V119" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W119" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X119" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y119" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z119" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA119" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB119" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC119" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD119" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE119" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF119" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="AG119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH119" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI119" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ119" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK119" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="AL119" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="AM119" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="AN119" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO119" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP119" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="120" hidden="true">
+      <c r="A120" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="B120" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="C120" s="2"/>
+      <c r="D120" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E120" s="2"/>
+      <c r="F120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G120" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H120" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I120" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J120" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K120" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="L120" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="M120" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="N120" s="2"/>
+      <c r="O120" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="P120" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q120" s="2"/>
+      <c r="R120" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S120" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T120" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="U120" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V120" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W120" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X120" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y120" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z120" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA120" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB120" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC120" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD120" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE120" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF120" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="AG120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH120" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI120" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ120" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK120" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="AL120" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="AM120" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="AN120" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO120" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP120" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="121" hidden="true">
+      <c r="A121" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="B121" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="C121" s="2"/>
+      <c r="D121" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E121" s="2"/>
+      <c r="F121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G121" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H121" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I121" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J121" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K121" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="L121" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="M121" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="N121" s="2"/>
+      <c r="O121" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="P121" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q121" s="2"/>
+      <c r="R121" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S121" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T121" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U121" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V121" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W121" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X121" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="Y121" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="Z121" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="AA121" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB121" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC121" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD121" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE121" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF121" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="AG121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH121" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI121" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ121" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK121" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="AL121" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="AM121" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="AN121" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO121" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP121" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="122" hidden="true">
+      <c r="A122" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="B122" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="C122" s="2"/>
+      <c r="D122" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E122" s="2"/>
+      <c r="F122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G122" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H122" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I122" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J122" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K122" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="L122" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="M122" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="N122" s="2"/>
+      <c r="O122" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="P122" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q122" s="2"/>
+      <c r="R122" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S122" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T122" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U122" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V122" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W122" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X122" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y122" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z122" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA122" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB122" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC122" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD122" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE122" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF122" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="AG122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH122" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI122" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ122" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK122" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="AL122" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="AM122" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="AN122" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO122" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="AP122" t="s" s="2">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="123" hidden="true">
+      <c r="A123" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="B123" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="C123" s="2"/>
+      <c r="D123" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E123" s="2"/>
+      <c r="F123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G123" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H123" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I123" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J123" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K123" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="L123" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="M123" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="N123" s="2"/>
+      <c r="O123" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="P123" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q123" s="2"/>
+      <c r="R123" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S123" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T123" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U123" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V123" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W123" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X123" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y123" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z123" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA123" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB123" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC123" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD123" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE123" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF123" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="AG123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH123" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI123" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ123" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK123" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL123" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="AM123" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="AN123" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO123" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP123" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="124" hidden="true">
+      <c r="A124" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="B124" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="C124" s="2"/>
+      <c r="D124" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E124" s="2"/>
+      <c r="F124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G124" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H124" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I124" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J124" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K124" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="L124" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="M124" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="N124" s="2"/>
+      <c r="O124" s="2"/>
+      <c r="P124" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q124" s="2"/>
+      <c r="R124" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S124" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T124" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U124" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V124" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W124" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X124" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y124" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z124" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA124" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB124" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC124" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD124" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE124" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF124" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="AG124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH124" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI124" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ124" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK124" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="AL124" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="AM124" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="AN124" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO124" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP124" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="125" hidden="true">
+      <c r="A125" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="B125" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="C125" s="2"/>
+      <c r="D125" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E125" s="2"/>
+      <c r="F125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G125" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H125" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I125" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J125" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K125" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="L125" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="M125" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="N125" s="2"/>
+      <c r="O125" s="2"/>
+      <c r="P125" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q125" s="2"/>
+      <c r="R125" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S125" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T125" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U125" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V125" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W125" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X125" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y125" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z125" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA125" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB125" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC125" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD125" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE125" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF125" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AG125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH125" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI125" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ125" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK125" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL125" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="AM125" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN125" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO125" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP125" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="126" hidden="true">
+      <c r="A126" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="B126" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="C126" s="2"/>
+      <c r="D126" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="E126" s="2"/>
+      <c r="F126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G126" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H126" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I126" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J126" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K126" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L126" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="M126" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="N126" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="O126" s="2"/>
+      <c r="P126" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q126" s="2"/>
+      <c r="R126" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S126" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T126" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U126" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V126" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W126" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X126" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y126" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z126" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA126" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB126" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC126" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD126" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE126" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF126" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="AG126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH126" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI126" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ126" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK126" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL126" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="AM126" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN126" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO126" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP126" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="127" hidden="true">
+      <c r="A127" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="B127" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="C127" s="2"/>
+      <c r="D127" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="E127" s="2"/>
+      <c r="F127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G127" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H127" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I127" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="J127" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K127" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L127" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="M127" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="N127" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="O127" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="P127" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q127" s="2"/>
+      <c r="R127" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S127" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T127" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U127" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V127" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W127" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X127" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y127" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z127" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA127" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB127" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC127" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD127" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE127" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF127" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="AG127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH127" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI127" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ127" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK127" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL127" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AM127" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN127" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO127" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP127" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="128" hidden="true">
+      <c r="A128" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="B128" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="C128" s="2"/>
+      <c r="D128" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E128" s="2"/>
+      <c r="F128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G128" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H128" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I128" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J128" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K128" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="L128" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="M128" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="N128" s="2"/>
+      <c r="O128" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="P128" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q128" s="2"/>
+      <c r="R128" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S128" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T128" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U128" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V128" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W128" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X128" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y128" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z128" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA128" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB128" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC128" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD128" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE128" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF128" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="AG128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH128" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI128" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ128" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK128" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL128" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="AM128" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN128" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO128" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP128" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="129" hidden="true">
+      <c r="A129" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="B129" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="C129" s="2"/>
+      <c r="D129" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E129" s="2"/>
+      <c r="F129" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G129" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H129" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I129" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J129" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K129" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="L129" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="M129" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="N129" s="2"/>
+      <c r="O129" s="2"/>
+      <c r="P129" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q129" s="2"/>
+      <c r="R129" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S129" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T129" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U129" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V129" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W129" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X129" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="Y129" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="Z129" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="AA129" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB129" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC129" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD129" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE129" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF129" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="AG129" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AH129" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI129" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ129" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK129" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL129" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="AM129" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="AN129" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO129" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP129" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="130" hidden="true">
+      <c r="A130" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="B130" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="C130" s="2"/>
+      <c r="D130" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E130" s="2"/>
+      <c r="F130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G130" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H130" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I130" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J130" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K130" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="L130" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="M130" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="N130" s="2"/>
+      <c r="O130" s="2"/>
+      <c r="P130" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q130" s="2"/>
+      <c r="R130" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S130" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T130" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U130" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V130" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W130" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X130" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y130" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z130" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA130" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB130" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC130" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD130" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE130" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF130" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AG130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH130" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI130" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ130" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK130" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL130" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="AM130" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN130" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO130" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP130" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="131" hidden="true">
+      <c r="A131" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="B131" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="C131" s="2"/>
+      <c r="D131" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="E131" s="2"/>
+      <c r="F131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G131" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H131" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I131" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J131" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K131" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L131" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="M131" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="N131" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="O131" s="2"/>
+      <c r="P131" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q131" s="2"/>
+      <c r="R131" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S131" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T131" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U131" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V131" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W131" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X131" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y131" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z131" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA131" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB131" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="AC131" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AD131" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE131" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AF131" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="AG131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH131" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI131" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ131" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK131" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL131" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="AM131" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN131" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO131" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP131" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="132" hidden="true">
+      <c r="A132" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="B132" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="C132" s="2"/>
+      <c r="D132" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E132" s="2"/>
+      <c r="F132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G132" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H132" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I132" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J132" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K132" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="L132" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="M132" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="N132" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="O132" t="s" s="2">
         <v>638</v>
       </c>
-      <c r="AL110" t="s" s="2">
+      <c r="P132" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q132" s="2"/>
+      <c r="R132" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S132" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T132" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U132" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V132" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W132" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X132" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y132" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z132" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA132" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB132" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC132" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD132" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE132" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF132" t="s" s="2">
         <v>639</v>
       </c>
-      <c r="AM110" t="s" s="2">
+      <c r="AG132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH132" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI132" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ132" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK132" t="s" s="2">
         <v>640</v>
       </c>
-      <c r="AN110" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO110" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP110" t="s" s="2">
+      <c r="AL132" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="AM132" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN132" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO132" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP132" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="133" hidden="true">
+      <c r="A133" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="B133" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="C133" s="2"/>
+      <c r="D133" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E133" s="2"/>
+      <c r="F133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G133" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H133" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I133" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J133" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K133" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="L133" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="M133" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="N133" t="s" s="2">
+        <v>645</v>
+      </c>
+      <c r="O133" t="s" s="2">
+        <v>646</v>
+      </c>
+      <c r="P133" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q133" s="2"/>
+      <c r="R133" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S133" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T133" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U133" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V133" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W133" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X133" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y133" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z133" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA133" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB133" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC133" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD133" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE133" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF133" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="AG133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH133" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI133" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ133" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK133" t="s" s="2">
+        <v>648</v>
+      </c>
+      <c r="AL133" t="s" s="2">
+        <v>649</v>
+      </c>
+      <c r="AM133" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN133" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO133" t="s" s="2">
+        <v>650</v>
+      </c>
+      <c r="AP133" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="134" hidden="true">
+      <c r="A134" t="s" s="2">
+        <v>651</v>
+      </c>
+      <c r="B134" t="s" s="2">
+        <v>651</v>
+      </c>
+      <c r="C134" s="2"/>
+      <c r="D134" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E134" s="2"/>
+      <c r="F134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G134" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H134" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I134" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J134" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K134" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="L134" t="s" s="2">
+        <v>652</v>
+      </c>
+      <c r="M134" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="N134" s="2"/>
+      <c r="O134" t="s" s="2">
+        <v>654</v>
+      </c>
+      <c r="P134" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q134" s="2"/>
+      <c r="R134" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S134" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T134" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U134" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V134" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W134" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X134" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y134" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z134" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA134" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB134" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC134" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD134" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE134" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF134" t="s" s="2">
+        <v>651</v>
+      </c>
+      <c r="AG134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH134" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI134" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ134" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK134" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL134" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="AM134" t="s" s="2">
+        <v>656</v>
+      </c>
+      <c r="AN134" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO134" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP134" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="135" hidden="true">
+      <c r="A135" t="s" s="2">
+        <v>657</v>
+      </c>
+      <c r="B135" t="s" s="2">
+        <v>657</v>
+      </c>
+      <c r="C135" s="2"/>
+      <c r="D135" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E135" s="2"/>
+      <c r="F135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G135" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H135" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I135" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J135" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K135" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="L135" t="s" s="2">
+        <v>658</v>
+      </c>
+      <c r="M135" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="N135" s="2"/>
+      <c r="O135" s="2"/>
+      <c r="P135" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q135" s="2"/>
+      <c r="R135" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S135" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T135" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U135" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V135" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W135" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X135" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y135" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z135" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA135" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB135" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC135" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD135" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE135" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF135" t="s" s="2">
+        <v>657</v>
+      </c>
+      <c r="AG135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH135" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI135" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ135" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK135" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL135" t="s" s="2">
+        <v>660</v>
+      </c>
+      <c r="AM135" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN135" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO135" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP135" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="136" hidden="true">
+      <c r="A136" t="s" s="2">
+        <v>661</v>
+      </c>
+      <c r="B136" t="s" s="2">
+        <v>661</v>
+      </c>
+      <c r="C136" s="2"/>
+      <c r="D136" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E136" s="2"/>
+      <c r="F136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G136" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H136" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I136" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J136" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K136" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="L136" t="s" s="2">
+        <v>662</v>
+      </c>
+      <c r="M136" t="s" s="2">
+        <v>663</v>
+      </c>
+      <c r="N136" t="s" s="2">
+        <v>664</v>
+      </c>
+      <c r="O136" t="s" s="2">
+        <v>665</v>
+      </c>
+      <c r="P136" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q136" s="2"/>
+      <c r="R136" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S136" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T136" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U136" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V136" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W136" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X136" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="Y136" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="Z136" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AA136" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB136" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC136" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD136" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE136" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF136" t="s" s="2">
+        <v>661</v>
+      </c>
+      <c r="AG136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH136" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI136" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ136" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK136" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="AL136" t="s" s="2">
+        <v>667</v>
+      </c>
+      <c r="AM136" t="s" s="2">
+        <v>668</v>
+      </c>
+      <c r="AN136" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO136" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP136" t="s" s="2">
         <v>80</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP110">
+  <autoFilter ref="A1:AP136">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -15579,7 +18779,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI109">
+  <conditionalFormatting sqref="A2:AI135">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$136</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$152</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5204" uniqueCount="669">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5798" uniqueCount="720">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.0</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-29T20:32:59+00:00</t>
+    <t>2023-11-29T21:08:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1621,6 +1621,132 @@
     <t>1530: terminologyMaps using VF_PractitionerCountry on NEW PERSON - STATE (#200-.115) case not NULL</t>
   </si>
   <si>
+    <t>Practitioner.address:home.country.id</t>
+  </si>
+  <si>
+    <t>Practitioner.address.country.id</t>
+  </si>
+  <si>
+    <t>xml:id (or equivalent in JSON)</t>
+  </si>
+  <si>
+    <t>unique id for the element within a resource (for internal references)</t>
+  </si>
+  <si>
+    <t>Practitioner.address:home.country.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.address.country.extension</t>
+  </si>
+  <si>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
+  </si>
+  <si>
+    <t>Practitioner.address:home.country.extension:data-absent-reason</t>
+  </si>
+  <si>
+    <t>data-absent-reason</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {data-absent-reason}
+</t>
+  </si>
+  <si>
+    <t>unknown | asked | temp | notasked | masked | unsupported | astext | error</t>
+  </si>
+  <si>
+    <t>Provides a reason why the expected value or elements in the element that is extended are missing.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t>ANY.nullFlavor</t>
+  </si>
+  <si>
+    <t>Practitioner.address:home.country.extension:data-absent-reason.id</t>
+  </si>
+  <si>
+    <t>Practitioner.address.country.extension.id</t>
+  </si>
+  <si>
+    <t>Practitioner.address:home.country.extension:data-absent-reason.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.address.country.extension.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.address:home.country.extension:data-absent-reason.url</t>
+  </si>
+  <si>
+    <t>Practitioner.address.country.extension.url</t>
+  </si>
+  <si>
+    <t>identifies the meaning of the extension</t>
+  </si>
+  <si>
+    <t>Source of the definition for the extension code - a logical name or a URL.</t>
+  </si>
+  <si>
+    <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/StructureDefinition/data-absent-reason</t>
+  </si>
+  <si>
+    <t>Extension.url</t>
+  </si>
+  <si>
+    <t>Practitioner.address:home.country.extension:data-absent-reason.value[x]</t>
+  </si>
+  <si>
+    <t>Practitioner.address.country.extension.value[x]</t>
+  </si>
+  <si>
+    <t>Value of extension</t>
+  </si>
+  <si>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/extensibility.html) for a list).</t>
+  </si>
+  <si>
+    <t>Used to specify why the normally expected content of the data element is missing.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/data-absent-reason|4.0.1</t>
+  </si>
+  <si>
+    <t>Extension.value[x]</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+inv-27:1531: fixed value = unknown if NEW PERSON - STATE (#200-.115) case NULL {null}</t>
+  </si>
+  <si>
+    <t>1531: fixed value = unknown if NEW PERSON - STATE (#200-.115) case NULL</t>
+  </si>
+  <si>
+    <t>Practitioner.address:home.country.value</t>
+  </si>
+  <si>
+    <t>Practitioner.address.country.value</t>
+  </si>
+  <si>
+    <t>Primitive value for string</t>
+  </si>
+  <si>
+    <t>The actual value</t>
+  </si>
+  <si>
+    <t>1048576</t>
+  </si>
+  <si>
+    <t>string.value</t>
+  </si>
+  <si>
     <t>Practitioner.address:home.period</t>
   </si>
   <si>
@@ -1688,6 +1814,37 @@
   </si>
   <si>
     <t>1532: terminologyMaps using VF_PractitionerCountry on NEW PERSON - STATE (#200-.1215) case not NULL</t>
+  </si>
+  <si>
+    <t>Practitioner.address:temp.country.id</t>
+  </si>
+  <si>
+    <t>Practitioner.address:temp.country.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.address:temp.country.extension:data-absent-reason</t>
+  </si>
+  <si>
+    <t>Practitioner.address:temp.country.extension:data-absent-reason.id</t>
+  </si>
+  <si>
+    <t>Practitioner.address:temp.country.extension:data-absent-reason.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.address:temp.country.extension:data-absent-reason.url</t>
+  </si>
+  <si>
+    <t>Practitioner.address:temp.country.extension:data-absent-reason.value[x]</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+inv-28:1533: fixed value = unknown if NEW PERSON - STATE (#200-.1215) case NULL {null}</t>
+  </si>
+  <si>
+    <t>1533: fixed value = unknown if NEW PERSON - STATE (#200-.1215) case NULL</t>
+  </si>
+  <si>
+    <t>Practitioner.address:temp.country.value</t>
   </si>
   <si>
     <t>Practitioner.address:temp.period</t>
@@ -2404,12 +2561,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP136"/>
+  <dimension ref="A1:AP152"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="40.87109375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="40.70703125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="1" max="1" width="70.5625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="46.1796875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="18.9921875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -2417,7 +2574,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="23.58203125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="30.90625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -11583,7 +11740,7 @@
         <v>515</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>486</v>
+        <v>516</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11603,21 +11760,19 @@
         <v>80</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>212</v>
+        <v>159</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>487</v>
+        <v>517</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>488</v>
+        <v>518</v>
       </c>
       <c r="N77" s="2"/>
-      <c r="O77" t="s" s="2">
-        <v>489</v>
-      </c>
+      <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>80</v>
       </c>
@@ -11629,7 +11784,7 @@
         <v>80</v>
       </c>
       <c r="T77" t="s" s="2">
-        <v>490</v>
+        <v>80</v>
       </c>
       <c r="U77" t="s" s="2">
         <v>80</v>
@@ -11665,7 +11820,7 @@
         <v>80</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>491</v>
+        <v>162</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
@@ -11677,16 +11832,16 @@
         <v>80</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>492</v>
+        <v>80</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>342</v>
+        <v>80</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>218</v>
+        <v>80</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>80</v>
@@ -11700,14 +11855,12 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="C78" t="s" s="2">
-        <v>517</v>
-      </c>
+        <v>520</v>
+      </c>
+      <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
         <v>80</v>
       </c>
@@ -11716,32 +11869,28 @@
         <v>78</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H78" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="I78" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>395</v>
+        <v>135</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>396</v>
+        <v>521</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="O78" t="s" s="2">
-        <v>399</v>
-      </c>
+        <v>522</v>
+      </c>
+      <c r="N78" s="2"/>
+      <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>80</v>
       </c>
@@ -11777,19 +11926,17 @@
         <v>80</v>
       </c>
       <c r="AB78" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC78" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="AC78" s="2"/>
       <c r="AD78" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE78" t="s" s="2">
-        <v>80</v>
+        <v>153</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>394</v>
+        <v>168</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
@@ -11801,16 +11948,16 @@
         <v>80</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>401</v>
+        <v>80</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>402</v>
+        <v>80</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>163</v>
+        <v>80</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>80</v>
@@ -11824,12 +11971,14 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="C79" s="2"/>
+        <v>520</v>
+      </c>
+      <c r="C79" t="s" s="2">
+        <v>524</v>
+      </c>
       <c r="D79" t="s" s="2">
         <v>80</v>
       </c>
@@ -11850,13 +11999,13 @@
         <v>80</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>159</v>
+        <v>525</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>160</v>
+        <v>526</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>161</v>
+        <v>527</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -11907,25 +12056,25 @@
         <v>80</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>80</v>
+        <v>528</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>80</v>
+        <v>140</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>163</v>
+        <v>529</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>80</v>
@@ -11942,21 +12091,21 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>519</v>
+        <v>530</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>404</v>
+        <v>531</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>134</v>
+        <v>80</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>80</v>
@@ -11968,17 +12117,15 @@
         <v>80</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>136</v>
+        <v>160</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>138</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="N80" s="2"/>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>80</v>
@@ -12015,31 +12162,31 @@
         <v>80</v>
       </c>
       <c r="AB80" t="s" s="2">
-        <v>166</v>
+        <v>80</v>
       </c>
       <c r="AC80" t="s" s="2">
-        <v>167</v>
+        <v>80</v>
       </c>
       <c r="AD80" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE80" t="s" s="2">
-        <v>153</v>
+        <v>80</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>140</v>
+        <v>80</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>80</v>
@@ -12062,10 +12209,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>520</v>
+        <v>532</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>405</v>
+        <v>533</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12076,32 +12223,28 @@
         <v>78</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I81" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>109</v>
+        <v>135</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>406</v>
+        <v>521</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="O81" t="s" s="2">
-        <v>409</v>
-      </c>
+        <v>522</v>
+      </c>
+      <c r="N81" s="2"/>
+      <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>80</v>
       </c>
@@ -12113,7 +12256,7 @@
         <v>80</v>
       </c>
       <c r="T81" t="s" s="2">
-        <v>410</v>
+        <v>80</v>
       </c>
       <c r="U81" t="s" s="2">
         <v>80</v>
@@ -12125,52 +12268,52 @@
         <v>80</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>174</v>
+        <v>80</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>411</v>
+        <v>80</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>412</v>
+        <v>80</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AB81" t="s" s="2">
-        <v>80</v>
+        <v>166</v>
       </c>
       <c r="AC81" t="s" s="2">
-        <v>80</v>
+        <v>167</v>
       </c>
       <c r="AD81" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE81" t="s" s="2">
-        <v>80</v>
+        <v>153</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>413</v>
+        <v>168</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>414</v>
+        <v>80</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>294</v>
+        <v>80</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>415</v>
+        <v>80</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>80</v>
@@ -12184,10 +12327,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>521</v>
+        <v>534</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>416</v>
+        <v>535</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12195,7 +12338,7 @@
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G82" t="s" s="2">
         <v>89</v>
@@ -12207,19 +12350,19 @@
         <v>80</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>417</v>
+        <v>536</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>418</v>
+        <v>537</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>419</v>
+        <v>538</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -12227,13 +12370,13 @@
       </c>
       <c r="Q82" s="2"/>
       <c r="R82" t="s" s="2">
-        <v>80</v>
+        <v>539</v>
       </c>
       <c r="S82" t="s" s="2">
         <v>80</v>
       </c>
       <c r="T82" t="s" s="2">
-        <v>420</v>
+        <v>80</v>
       </c>
       <c r="U82" t="s" s="2">
         <v>80</v>
@@ -12245,13 +12388,13 @@
         <v>80</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>174</v>
+        <v>80</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>421</v>
+        <v>80</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>422</v>
+        <v>80</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>80</v>
@@ -12269,10 +12412,10 @@
         <v>80</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>423</v>
+        <v>540</v>
       </c>
       <c r="AG82" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AH82" t="s" s="2">
         <v>89</v>
@@ -12281,13 +12424,13 @@
         <v>80</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>424</v>
+        <v>80</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>294</v>
+        <v>132</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>80</v>
@@ -12304,10 +12447,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>522</v>
+        <v>541</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>425</v>
+        <v>542</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12315,7 +12458,7 @@
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G83" t="s" s="2">
         <v>89</v>
@@ -12327,23 +12470,19 @@
         <v>80</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>159</v>
+        <v>109</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>426</v>
+        <v>543</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="O83" t="s" s="2">
-        <v>300</v>
-      </c>
+        <v>544</v>
+      </c>
+      <c r="N83" s="2"/>
+      <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>80</v>
       </c>
@@ -12355,7 +12494,7 @@
         <v>80</v>
       </c>
       <c r="T83" t="s" s="2">
-        <v>429</v>
+        <v>80</v>
       </c>
       <c r="U83" t="s" s="2">
         <v>80</v>
@@ -12367,13 +12506,13 @@
         <v>80</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>80</v>
+        <v>174</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>80</v>
+        <v>545</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>80</v>
+        <v>546</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>80</v>
@@ -12391,7 +12530,7 @@
         <v>80</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>430</v>
+        <v>547</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
@@ -12403,13 +12542,13 @@
         <v>80</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>101</v>
+        <v>548</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>431</v>
+        <v>80</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>303</v>
+        <v>132</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>80</v>
@@ -12418,18 +12557,18 @@
         <v>80</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>80</v>
+        <v>549</v>
       </c>
       <c r="AP83" t="s" s="2">
-        <v>80</v>
+        <v>508</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>523</v>
+        <v>550</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>432</v>
+        <v>551</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12440,25 +12579,25 @@
         <v>78</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>433</v>
+        <v>89</v>
       </c>
       <c r="H84" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="I84" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K84" t="s" s="2">
         <v>159</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>434</v>
+        <v>552</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>435</v>
+        <v>553</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -12473,7 +12612,7 @@
         <v>80</v>
       </c>
       <c r="T84" t="s" s="2">
-        <v>436</v>
+        <v>80</v>
       </c>
       <c r="U84" t="s" s="2">
         <v>80</v>
@@ -12482,7 +12621,7 @@
         <v>80</v>
       </c>
       <c r="W84" t="s" s="2">
-        <v>80</v>
+        <v>554</v>
       </c>
       <c r="X84" t="s" s="2">
         <v>80</v>
@@ -12509,49 +12648,49 @@
         <v>80</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>437</v>
+        <v>555</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>438</v>
+        <v>80</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>439</v>
+        <v>80</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>440</v>
+        <v>80</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>524</v>
+        <v>80</v>
       </c>
       <c r="AP84" t="s" s="2">
-        <v>525</v>
+        <v>80</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>526</v>
+        <v>556</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>441</v>
+        <v>486</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>442</v>
+        <v>80</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
@@ -12561,7 +12700,7 @@
         <v>89</v>
       </c>
       <c r="H85" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="I85" t="s" s="2">
         <v>80</v>
@@ -12570,16 +12709,18 @@
         <v>90</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>159</v>
+        <v>212</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>443</v>
+        <v>487</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>444</v>
+        <v>488</v>
       </c>
       <c r="N85" s="2"/>
-      <c r="O85" s="2"/>
+      <c r="O85" t="s" s="2">
+        <v>489</v>
+      </c>
       <c r="P85" t="s" s="2">
         <v>80</v>
       </c>
@@ -12591,7 +12732,7 @@
         <v>80</v>
       </c>
       <c r="T85" t="s" s="2">
-        <v>445</v>
+        <v>490</v>
       </c>
       <c r="U85" t="s" s="2">
         <v>80</v>
@@ -12627,7 +12768,7 @@
         <v>80</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>446</v>
+        <v>491</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>78</v>
@@ -12642,34 +12783,36 @@
         <v>101</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>447</v>
+        <v>492</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>448</v>
+        <v>342</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>449</v>
+        <v>218</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO85" t="s" s="2">
-        <v>527</v>
+        <v>80</v>
       </c>
       <c r="AP85" t="s" s="2">
-        <v>528</v>
+        <v>80</v>
       </c>
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>529</v>
+        <v>557</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="C86" s="2"/>
+        <v>394</v>
+      </c>
+      <c r="C86" t="s" s="2">
+        <v>558</v>
+      </c>
       <c r="D86" t="s" s="2">
-        <v>451</v>
+        <v>80</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
@@ -12679,7 +12822,7 @@
         <v>89</v>
       </c>
       <c r="H86" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="I86" t="s" s="2">
         <v>80</v>
@@ -12688,18 +12831,20 @@
         <v>90</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>159</v>
+        <v>395</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>452</v>
+        <v>396</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>453</v>
+        <v>397</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="O86" s="2"/>
+        <v>398</v>
+      </c>
+      <c r="O86" t="s" s="2">
+        <v>399</v>
+      </c>
       <c r="P86" t="s" s="2">
         <v>80</v>
       </c>
@@ -12711,7 +12856,7 @@
         <v>80</v>
       </c>
       <c r="T86" t="s" s="2">
-        <v>455</v>
+        <v>80</v>
       </c>
       <c r="U86" t="s" s="2">
         <v>80</v>
@@ -12747,13 +12892,13 @@
         <v>80</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>456</v>
+        <v>394</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>80</v>
@@ -12762,13 +12907,13 @@
         <v>101</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>457</v>
+        <v>401</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>458</v>
+        <v>402</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>80</v>
+        <v>163</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>80</v>
@@ -12782,14 +12927,14 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>530</v>
+        <v>559</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>459</v>
+        <v>403</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>460</v>
+        <v>80</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
@@ -12799,22 +12944,22 @@
         <v>89</v>
       </c>
       <c r="H87" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="I87" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K87" t="s" s="2">
         <v>159</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>461</v>
+        <v>160</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>462</v>
+        <v>161</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -12841,13 +12986,13 @@
         <v>80</v>
       </c>
       <c r="X87" t="s" s="2">
-        <v>185</v>
+        <v>80</v>
       </c>
       <c r="Y87" t="s" s="2">
-        <v>463</v>
+        <v>80</v>
       </c>
       <c r="Z87" t="s" s="2">
-        <v>464</v>
+        <v>80</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>80</v>
@@ -12865,7 +13010,7 @@
         <v>80</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>465</v>
+        <v>162</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>78</v>
@@ -12877,64 +13022,66 @@
         <v>80</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>466</v>
+        <v>80</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>467</v>
+        <v>163</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>468</v>
+        <v>80</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO87" t="s" s="2">
-        <v>531</v>
+        <v>80</v>
       </c>
       <c r="AP87" t="s" s="2">
-        <v>532</v>
+        <v>80</v>
       </c>
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>533</v>
+        <v>560</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>469</v>
+        <v>404</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>470</v>
+        <v>134</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H88" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="I88" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>159</v>
+        <v>135</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>471</v>
+        <v>136</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="N88" s="2"/>
+        <v>165</v>
+      </c>
+      <c r="N88" t="s" s="2">
+        <v>138</v>
+      </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
         <v>80</v>
@@ -12947,7 +13094,7 @@
         <v>80</v>
       </c>
       <c r="T88" t="s" s="2">
-        <v>473</v>
+        <v>80</v>
       </c>
       <c r="U88" t="s" s="2">
         <v>80</v>
@@ -12971,57 +13118,57 @@
         <v>80</v>
       </c>
       <c r="AB88" t="s" s="2">
-        <v>80</v>
+        <v>166</v>
       </c>
       <c r="AC88" t="s" s="2">
-        <v>80</v>
+        <v>167</v>
       </c>
       <c r="AD88" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE88" t="s" s="2">
-        <v>80</v>
+        <v>153</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>474</v>
+        <v>168</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>475</v>
+        <v>80</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>476</v>
+        <v>163</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>477</v>
+        <v>80</v>
       </c>
       <c r="AN88" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>534</v>
+        <v>80</v>
       </c>
       <c r="AP88" t="s" s="2">
-        <v>535</v>
+        <v>80</v>
       </c>
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>536</v>
+        <v>561</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>478</v>
+        <v>405</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13035,27 +13182,29 @@
         <v>89</v>
       </c>
       <c r="H89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I89" t="s" s="2">
         <v>90</v>
-      </c>
-      <c r="I89" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="J89" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>159</v>
+        <v>109</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>479</v>
+        <v>406</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>480</v>
+        <v>407</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="O89" s="2"/>
+        <v>408</v>
+      </c>
+      <c r="O89" t="s" s="2">
+        <v>409</v>
+      </c>
       <c r="P89" t="s" s="2">
         <v>80</v>
       </c>
@@ -13067,7 +13216,7 @@
         <v>80</v>
       </c>
       <c r="T89" t="s" s="2">
-        <v>80</v>
+        <v>410</v>
       </c>
       <c r="U89" t="s" s="2">
         <v>80</v>
@@ -13081,9 +13230,11 @@
       <c r="X89" t="s" s="2">
         <v>174</v>
       </c>
-      <c r="Y89" s="2"/>
+      <c r="Y89" t="s" s="2">
+        <v>411</v>
+      </c>
       <c r="Z89" t="s" s="2">
-        <v>513</v>
+        <v>412</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>80</v>
@@ -13101,7 +13252,7 @@
         <v>80</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>482</v>
+        <v>413</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>78</v>
@@ -13116,30 +13267,30 @@
         <v>101</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>483</v>
+        <v>414</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>484</v>
+        <v>294</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>485</v>
+        <v>415</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>537</v>
+        <v>80</v>
       </c>
       <c r="AP89" t="s" s="2">
-        <v>532</v>
+        <v>80</v>
       </c>
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>538</v>
+        <v>562</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>486</v>
+        <v>416</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13162,18 +13313,18 @@
         <v>90</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>212</v>
+        <v>109</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>487</v>
+        <v>417</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="N90" s="2"/>
-      <c r="O90" t="s" s="2">
-        <v>489</v>
-      </c>
+        <v>418</v>
+      </c>
+      <c r="N90" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
         <v>80</v>
       </c>
@@ -13185,7 +13336,7 @@
         <v>80</v>
       </c>
       <c r="T90" t="s" s="2">
-        <v>490</v>
+        <v>420</v>
       </c>
       <c r="U90" t="s" s="2">
         <v>80</v>
@@ -13197,13 +13348,13 @@
         <v>80</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>80</v>
+        <v>174</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>80</v>
+        <v>421</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>80</v>
+        <v>422</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>80</v>
@@ -13221,7 +13372,7 @@
         <v>80</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>491</v>
+        <v>423</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>78</v>
@@ -13236,13 +13387,13 @@
         <v>101</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>492</v>
+        <v>424</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>342</v>
+        <v>294</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>218</v>
+        <v>80</v>
       </c>
       <c r="AN90" t="s" s="2">
         <v>80</v>
@@ -13256,10 +13407,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>539</v>
+        <v>563</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>540</v>
+        <v>425</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13279,19 +13430,23 @@
         <v>80</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K91" t="s" s="2">
         <v>159</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>160</v>
+        <v>426</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="N91" s="2"/>
-      <c r="O91" s="2"/>
+        <v>427</v>
+      </c>
+      <c r="N91" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="O91" t="s" s="2">
+        <v>300</v>
+      </c>
       <c r="P91" t="s" s="2">
         <v>80</v>
       </c>
@@ -13303,7 +13458,7 @@
         <v>80</v>
       </c>
       <c r="T91" t="s" s="2">
-        <v>80</v>
+        <v>429</v>
       </c>
       <c r="U91" t="s" s="2">
         <v>80</v>
@@ -13339,7 +13494,7 @@
         <v>80</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>162</v>
+        <v>430</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>78</v>
@@ -13351,13 +13506,13 @@
         <v>80</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>80</v>
+        <v>431</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>163</v>
+        <v>303</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>80</v>
@@ -13374,43 +13529,41 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>541</v>
+        <v>564</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>542</v>
+        <v>432</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>134</v>
+        <v>80</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>79</v>
+        <v>433</v>
       </c>
       <c r="H92" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="I92" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J92" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>136</v>
+        <v>434</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="N92" t="s" s="2">
-        <v>138</v>
-      </c>
+        <v>435</v>
+      </c>
+      <c r="N92" s="2"/>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
         <v>80</v>
@@ -13423,7 +13576,7 @@
         <v>80</v>
       </c>
       <c r="T92" t="s" s="2">
-        <v>80</v>
+        <v>436</v>
       </c>
       <c r="U92" t="s" s="2">
         <v>80</v>
@@ -13447,19 +13600,19 @@
         <v>80</v>
       </c>
       <c r="AB92" t="s" s="2">
-        <v>166</v>
+        <v>80</v>
       </c>
       <c r="AC92" t="s" s="2">
-        <v>167</v>
+        <v>80</v>
       </c>
       <c r="AD92" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE92" t="s" s="2">
-        <v>153</v>
+        <v>80</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>168</v>
+        <v>437</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>78</v>
@@ -13471,37 +13624,37 @@
         <v>80</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>80</v>
+        <v>438</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>163</v>
+        <v>439</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>80</v>
+        <v>440</v>
       </c>
       <c r="AN92" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>80</v>
+        <v>565</v>
       </c>
       <c r="AP92" t="s" s="2">
-        <v>80</v>
+        <v>566</v>
       </c>
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>543</v>
+        <v>567</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>544</v>
+        <v>441</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>80</v>
+        <v>442</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
@@ -13511,7 +13664,7 @@
         <v>89</v>
       </c>
       <c r="H93" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="I93" t="s" s="2">
         <v>80</v>
@@ -13520,17 +13673,15 @@
         <v>90</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>246</v>
+        <v>159</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>247</v>
+        <v>443</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="N93" t="s" s="2">
-        <v>249</v>
-      </c>
+        <v>444</v>
+      </c>
+      <c r="N93" s="2"/>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
         <v>80</v>
@@ -13543,7 +13694,7 @@
         <v>80</v>
       </c>
       <c r="T93" t="s" s="2">
-        <v>80</v>
+        <v>445</v>
       </c>
       <c r="U93" t="s" s="2">
         <v>80</v>
@@ -13579,7 +13730,7 @@
         <v>80</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>250</v>
+        <v>446</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>78</v>
@@ -13588,40 +13739,40 @@
         <v>89</v>
       </c>
       <c r="AI93" t="s" s="2">
-        <v>251</v>
+        <v>80</v>
       </c>
       <c r="AJ93" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>252</v>
+        <v>447</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>253</v>
+        <v>448</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>80</v>
+        <v>449</v>
       </c>
       <c r="AN93" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>545</v>
+        <v>568</v>
       </c>
       <c r="AP93" t="s" s="2">
-        <v>546</v>
+        <v>569</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>547</v>
+        <v>570</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>548</v>
+        <v>450</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>80</v>
+        <v>451</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
@@ -13640,24 +13791,22 @@
         <v>90</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>246</v>
+        <v>159</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>257</v>
+        <v>452</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>258</v>
+        <v>453</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>259</v>
+        <v>454</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="Q94" t="s" s="2">
-        <v>260</v>
-      </c>
+      <c r="Q94" s="2"/>
       <c r="R94" t="s" s="2">
         <v>80</v>
       </c>
@@ -13665,7 +13814,7 @@
         <v>80</v>
       </c>
       <c r="T94" t="s" s="2">
-        <v>80</v>
+        <v>455</v>
       </c>
       <c r="U94" t="s" s="2">
         <v>80</v>
@@ -13701,7 +13850,7 @@
         <v>80</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>261</v>
+        <v>456</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>78</v>
@@ -13710,16 +13859,16 @@
         <v>89</v>
       </c>
       <c r="AI94" t="s" s="2">
-        <v>251</v>
+        <v>80</v>
       </c>
       <c r="AJ94" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK94" t="s" s="2">
-        <v>262</v>
+        <v>457</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>263</v>
+        <v>458</v>
       </c>
       <c r="AM94" t="s" s="2">
         <v>80</v>
@@ -13728,24 +13877,22 @@
         <v>80</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>549</v>
+        <v>80</v>
       </c>
       <c r="AP94" t="s" s="2">
-        <v>550</v>
+        <v>80</v>
       </c>
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>551</v>
+        <v>571</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="C95" t="s" s="2">
-        <v>552</v>
-      </c>
+        <v>459</v>
+      </c>
+      <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
-        <v>80</v>
+        <v>460</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
@@ -13764,20 +13911,16 @@
         <v>90</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>395</v>
+        <v>159</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>396</v>
+        <v>461</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="N95" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="O95" t="s" s="2">
-        <v>399</v>
-      </c>
+        <v>462</v>
+      </c>
+      <c r="N95" s="2"/>
+      <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
         <v>80</v>
       </c>
@@ -13801,13 +13944,13 @@
         <v>80</v>
       </c>
       <c r="X95" t="s" s="2">
-        <v>80</v>
+        <v>185</v>
       </c>
       <c r="Y95" t="s" s="2">
-        <v>80</v>
+        <v>463</v>
       </c>
       <c r="Z95" t="s" s="2">
-        <v>80</v>
+        <v>464</v>
       </c>
       <c r="AA95" t="s" s="2">
         <v>80</v>
@@ -13825,13 +13968,13 @@
         <v>80</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>394</v>
+        <v>465</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH95" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI95" t="s" s="2">
         <v>80</v>
@@ -13840,34 +13983,34 @@
         <v>101</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>401</v>
+        <v>466</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>402</v>
+        <v>467</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>163</v>
+        <v>468</v>
       </c>
       <c r="AN95" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO95" t="s" s="2">
-        <v>80</v>
+        <v>572</v>
       </c>
       <c r="AP95" t="s" s="2">
-        <v>80</v>
+        <v>573</v>
       </c>
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>553</v>
+        <v>574</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>403</v>
+        <v>469</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>80</v>
+        <v>470</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
@@ -13877,22 +14020,22 @@
         <v>89</v>
       </c>
       <c r="H96" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="I96" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J96" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K96" t="s" s="2">
         <v>159</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>160</v>
+        <v>471</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>161</v>
+        <v>472</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -13907,7 +14050,7 @@
         <v>80</v>
       </c>
       <c r="T96" t="s" s="2">
-        <v>80</v>
+        <v>473</v>
       </c>
       <c r="U96" t="s" s="2">
         <v>80</v>
@@ -13943,7 +14086,7 @@
         <v>80</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>162</v>
+        <v>474</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>78</v>
@@ -13955,65 +14098,65 @@
         <v>80</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>80</v>
+        <v>475</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>163</v>
+        <v>476</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>80</v>
+        <v>477</v>
       </c>
       <c r="AN96" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO96" t="s" s="2">
-        <v>80</v>
+        <v>575</v>
       </c>
       <c r="AP96" t="s" s="2">
-        <v>80</v>
+        <v>576</v>
       </c>
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>554</v>
+        <v>577</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>404</v>
+        <v>478</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>134</v>
+        <v>80</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H97" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="I97" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J97" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>136</v>
+        <v>479</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>165</v>
+        <v>480</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>138</v>
+        <v>481</v>
       </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
@@ -14039,69 +14182,67 @@
         <v>80</v>
       </c>
       <c r="X97" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y97" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="Y97" s="2"/>
       <c r="Z97" t="s" s="2">
-        <v>80</v>
+        <v>513</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AB97" t="s" s="2">
-        <v>166</v>
+        <v>80</v>
       </c>
       <c r="AC97" t="s" s="2">
-        <v>167</v>
+        <v>80</v>
       </c>
       <c r="AD97" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE97" t="s" s="2">
-        <v>153</v>
+        <v>80</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>168</v>
+        <v>482</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH97" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI97" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK97" t="s" s="2">
-        <v>80</v>
+        <v>483</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>163</v>
+        <v>484</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>80</v>
+        <v>485</v>
       </c>
       <c r="AN97" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO97" t="s" s="2">
-        <v>80</v>
+        <v>578</v>
       </c>
       <c r="AP97" t="s" s="2">
-        <v>80</v>
+        <v>573</v>
       </c>
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>555</v>
+        <v>579</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>405</v>
+        <v>516</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14118,26 +14259,22 @@
         <v>80</v>
       </c>
       <c r="I98" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="J98" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>109</v>
+        <v>159</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>406</v>
+        <v>517</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="N98" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="O98" t="s" s="2">
-        <v>409</v>
-      </c>
+        <v>518</v>
+      </c>
+      <c r="N98" s="2"/>
+      <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
         <v>80</v>
       </c>
@@ -14149,7 +14286,7 @@
         <v>80</v>
       </c>
       <c r="T98" t="s" s="2">
-        <v>410</v>
+        <v>80</v>
       </c>
       <c r="U98" t="s" s="2">
         <v>80</v>
@@ -14161,13 +14298,13 @@
         <v>80</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>174</v>
+        <v>80</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>411</v>
+        <v>80</v>
       </c>
       <c r="Z98" t="s" s="2">
-        <v>412</v>
+        <v>80</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>80</v>
@@ -14185,7 +14322,7 @@
         <v>80</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>413</v>
+        <v>162</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>78</v>
@@ -14197,16 +14334,16 @@
         <v>80</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="AK98" t="s" s="2">
-        <v>414</v>
+        <v>80</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>294</v>
+        <v>80</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>415</v>
+        <v>80</v>
       </c>
       <c r="AN98" t="s" s="2">
         <v>80</v>
@@ -14220,10 +14357,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>556</v>
+        <v>580</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>416</v>
+        <v>520</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14234,7 +14371,7 @@
         <v>78</v>
       </c>
       <c r="G99" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H99" t="s" s="2">
         <v>80</v>
@@ -14243,20 +14380,18 @@
         <v>80</v>
       </c>
       <c r="J99" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>109</v>
+        <v>135</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>417</v>
+        <v>521</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="N99" t="s" s="2">
-        <v>419</v>
-      </c>
+        <v>522</v>
+      </c>
+      <c r="N99" s="2"/>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
         <v>80</v>
@@ -14269,7 +14404,7 @@
         <v>80</v>
       </c>
       <c r="T99" t="s" s="2">
-        <v>420</v>
+        <v>80</v>
       </c>
       <c r="U99" t="s" s="2">
         <v>80</v>
@@ -14281,49 +14416,47 @@
         <v>80</v>
       </c>
       <c r="X99" t="s" s="2">
-        <v>174</v>
+        <v>80</v>
       </c>
       <c r="Y99" t="s" s="2">
-        <v>421</v>
+        <v>80</v>
       </c>
       <c r="Z99" t="s" s="2">
-        <v>422</v>
+        <v>80</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AB99" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC99" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="AC99" s="2"/>
       <c r="AD99" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE99" t="s" s="2">
-        <v>80</v>
+        <v>153</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>423</v>
+        <v>168</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH99" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI99" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK99" t="s" s="2">
-        <v>424</v>
+        <v>80</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>294</v>
+        <v>80</v>
       </c>
       <c r="AM99" t="s" s="2">
         <v>80</v>
@@ -14340,12 +14473,14 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>557</v>
+        <v>581</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="C100" s="2"/>
+        <v>520</v>
+      </c>
+      <c r="C100" t="s" s="2">
+        <v>524</v>
+      </c>
       <c r="D100" t="s" s="2">
         <v>80</v>
       </c>
@@ -14363,23 +14498,19 @@
         <v>80</v>
       </c>
       <c r="J100" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>159</v>
+        <v>525</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>426</v>
+        <v>526</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="N100" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="O100" t="s" s="2">
-        <v>300</v>
-      </c>
+        <v>527</v>
+      </c>
+      <c r="N100" s="2"/>
+      <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
         <v>80</v>
       </c>
@@ -14391,7 +14522,7 @@
         <v>80</v>
       </c>
       <c r="T100" t="s" s="2">
-        <v>429</v>
+        <v>80</v>
       </c>
       <c r="U100" t="s" s="2">
         <v>80</v>
@@ -14427,25 +14558,25 @@
         <v>80</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>430</v>
+        <v>168</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH100" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI100" t="s" s="2">
-        <v>80</v>
+        <v>528</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>431</v>
+        <v>80</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>303</v>
+        <v>529</v>
       </c>
       <c r="AM100" t="s" s="2">
         <v>80</v>
@@ -14462,10 +14593,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>558</v>
+        <v>582</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>432</v>
+        <v>531</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14476,25 +14607,25 @@
         <v>78</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>433</v>
+        <v>89</v>
       </c>
       <c r="H101" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="I101" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J101" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K101" t="s" s="2">
         <v>159</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>434</v>
+        <v>160</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>435</v>
+        <v>161</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -14509,7 +14640,7 @@
         <v>80</v>
       </c>
       <c r="T101" t="s" s="2">
-        <v>436</v>
+        <v>80</v>
       </c>
       <c r="U101" t="s" s="2">
         <v>80</v>
@@ -14545,28 +14676,28 @@
         <v>80</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>437</v>
+        <v>162</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH101" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI101" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="AK101" t="s" s="2">
-        <v>438</v>
+        <v>80</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>439</v>
+        <v>163</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>440</v>
+        <v>80</v>
       </c>
       <c r="AN101" t="s" s="2">
         <v>80</v>
@@ -14580,39 +14711,39 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>559</v>
+        <v>583</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>441</v>
+        <v>533</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
-        <v>442</v>
+        <v>80</v>
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G102" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H102" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="I102" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J102" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>159</v>
+        <v>135</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>443</v>
+        <v>521</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>444</v>
+        <v>522</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -14627,7 +14758,7 @@
         <v>80</v>
       </c>
       <c r="T102" t="s" s="2">
-        <v>445</v>
+        <v>80</v>
       </c>
       <c r="U102" t="s" s="2">
         <v>80</v>
@@ -14651,40 +14782,40 @@
         <v>80</v>
       </c>
       <c r="AB102" t="s" s="2">
-        <v>80</v>
+        <v>166</v>
       </c>
       <c r="AC102" t="s" s="2">
-        <v>80</v>
+        <v>167</v>
       </c>
       <c r="AD102" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE102" t="s" s="2">
-        <v>80</v>
+        <v>153</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>446</v>
+        <v>168</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH102" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI102" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>447</v>
+        <v>80</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>448</v>
+        <v>80</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>449</v>
+        <v>80</v>
       </c>
       <c r="AN102" t="s" s="2">
         <v>80</v>
@@ -14698,18 +14829,18 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>560</v>
+        <v>584</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>450</v>
+        <v>535</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
-        <v>451</v>
+        <v>80</v>
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G103" t="s" s="2">
         <v>89</v>
@@ -14721,19 +14852,19 @@
         <v>80</v>
       </c>
       <c r="J103" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>159</v>
+        <v>103</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>452</v>
+        <v>536</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>453</v>
+        <v>537</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>454</v>
+        <v>538</v>
       </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
@@ -14741,13 +14872,13 @@
       </c>
       <c r="Q103" s="2"/>
       <c r="R103" t="s" s="2">
-        <v>80</v>
+        <v>539</v>
       </c>
       <c r="S103" t="s" s="2">
         <v>80</v>
       </c>
       <c r="T103" t="s" s="2">
-        <v>455</v>
+        <v>80</v>
       </c>
       <c r="U103" t="s" s="2">
         <v>80</v>
@@ -14783,10 +14914,10 @@
         <v>80</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>456</v>
+        <v>540</v>
       </c>
       <c r="AG103" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AH103" t="s" s="2">
         <v>89</v>
@@ -14795,13 +14926,13 @@
         <v>80</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="AK103" t="s" s="2">
-        <v>457</v>
+        <v>80</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>458</v>
+        <v>132</v>
       </c>
       <c r="AM103" t="s" s="2">
         <v>80</v>
@@ -14818,39 +14949,39 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>561</v>
+        <v>585</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>459</v>
+        <v>542</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
-        <v>460</v>
+        <v>80</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G104" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H104" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="I104" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J104" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>159</v>
+        <v>109</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>461</v>
+        <v>543</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>462</v>
+        <v>544</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -14877,13 +15008,13 @@
         <v>80</v>
       </c>
       <c r="X104" t="s" s="2">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="Y104" t="s" s="2">
-        <v>463</v>
+        <v>545</v>
       </c>
       <c r="Z104" t="s" s="2">
-        <v>464</v>
+        <v>546</v>
       </c>
       <c r="AA104" t="s" s="2">
         <v>80</v>
@@ -14901,7 +15032,7 @@
         <v>80</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>465</v>
+        <v>547</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>78</v>
@@ -14913,37 +15044,37 @@
         <v>80</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>101</v>
+        <v>586</v>
       </c>
       <c r="AK104" t="s" s="2">
-        <v>466</v>
+        <v>80</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>467</v>
+        <v>132</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>468</v>
+        <v>80</v>
       </c>
       <c r="AN104" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO104" t="s" s="2">
-        <v>80</v>
+        <v>587</v>
       </c>
       <c r="AP104" t="s" s="2">
-        <v>80</v>
+        <v>573</v>
       </c>
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>562</v>
+        <v>588</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>469</v>
+        <v>551</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
-        <v>470</v>
+        <v>80</v>
       </c>
       <c r="E105" s="2"/>
       <c r="F105" t="s" s="2">
@@ -14953,22 +15084,22 @@
         <v>89</v>
       </c>
       <c r="H105" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="I105" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J105" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K105" t="s" s="2">
         <v>159</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>471</v>
+        <v>552</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>472</v>
+        <v>553</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -14983,7 +15114,7 @@
         <v>80</v>
       </c>
       <c r="T105" t="s" s="2">
-        <v>473</v>
+        <v>80</v>
       </c>
       <c r="U105" t="s" s="2">
         <v>80</v>
@@ -14992,7 +15123,7 @@
         <v>80</v>
       </c>
       <c r="W105" t="s" s="2">
-        <v>80</v>
+        <v>554</v>
       </c>
       <c r="X105" t="s" s="2">
         <v>80</v>
@@ -15019,7 +15150,7 @@
         <v>80</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>474</v>
+        <v>555</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>78</v>
@@ -15031,16 +15162,16 @@
         <v>80</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="AK105" t="s" s="2">
-        <v>475</v>
+        <v>80</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>476</v>
+        <v>80</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>477</v>
+        <v>80</v>
       </c>
       <c r="AN105" t="s" s="2">
         <v>80</v>
@@ -15054,10 +15185,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>563</v>
+        <v>589</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>478</v>
+        <v>486</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15071,7 +15202,7 @@
         <v>89</v>
       </c>
       <c r="H106" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="I106" t="s" s="2">
         <v>80</v>
@@ -15080,18 +15211,18 @@
         <v>90</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>159</v>
+        <v>212</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>479</v>
+        <v>487</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="N106" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="O106" s="2"/>
+        <v>488</v>
+      </c>
+      <c r="N106" s="2"/>
+      <c r="O106" t="s" s="2">
+        <v>489</v>
+      </c>
       <c r="P106" t="s" s="2">
         <v>80</v>
       </c>
@@ -15103,7 +15234,7 @@
         <v>80</v>
       </c>
       <c r="T106" t="s" s="2">
-        <v>80</v>
+        <v>490</v>
       </c>
       <c r="U106" t="s" s="2">
         <v>80</v>
@@ -15139,7 +15270,7 @@
         <v>80</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>482</v>
+        <v>491</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>78</v>
@@ -15154,13 +15285,13 @@
         <v>101</v>
       </c>
       <c r="AK106" t="s" s="2">
-        <v>483</v>
+        <v>492</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>484</v>
+        <v>342</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>485</v>
+        <v>218</v>
       </c>
       <c r="AN106" t="s" s="2">
         <v>80</v>
@@ -15174,10 +15305,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>564</v>
+        <v>590</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>486</v>
+        <v>591</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15197,21 +15328,19 @@
         <v>80</v>
       </c>
       <c r="J107" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>212</v>
+        <v>159</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>487</v>
+        <v>160</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>488</v>
+        <v>161</v>
       </c>
       <c r="N107" s="2"/>
-      <c r="O107" t="s" s="2">
-        <v>489</v>
-      </c>
+      <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
         <v>80</v>
       </c>
@@ -15223,7 +15352,7 @@
         <v>80</v>
       </c>
       <c r="T107" t="s" s="2">
-        <v>490</v>
+        <v>80</v>
       </c>
       <c r="U107" t="s" s="2">
         <v>80</v>
@@ -15259,7 +15388,7 @@
         <v>80</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>491</v>
+        <v>162</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>78</v>
@@ -15271,16 +15400,16 @@
         <v>80</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="AK107" t="s" s="2">
-        <v>492</v>
+        <v>80</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>342</v>
+        <v>163</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>218</v>
+        <v>80</v>
       </c>
       <c r="AN107" t="s" s="2">
         <v>80</v>
@@ -15294,48 +15423,44 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>565</v>
+        <v>592</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="C108" t="s" s="2">
-        <v>566</v>
-      </c>
+        <v>593</v>
+      </c>
+      <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
-        <v>80</v>
+        <v>134</v>
       </c>
       <c r="E108" s="2"/>
       <c r="F108" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G108" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H108" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="I108" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J108" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>395</v>
+        <v>135</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>396</v>
+        <v>136</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>397</v>
+        <v>165</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="O108" t="s" s="2">
-        <v>399</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
         <v>80</v>
       </c>
@@ -15371,19 +15496,19 @@
         <v>80</v>
       </c>
       <c r="AB108" t="s" s="2">
-        <v>80</v>
+        <v>166</v>
       </c>
       <c r="AC108" t="s" s="2">
-        <v>80</v>
+        <v>167</v>
       </c>
       <c r="AD108" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE108" t="s" s="2">
-        <v>80</v>
+        <v>153</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>394</v>
+        <v>168</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>78</v>
@@ -15395,16 +15520,16 @@
         <v>80</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK108" t="s" s="2">
-        <v>401</v>
+        <v>80</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>402</v>
+        <v>163</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>163</v>
+        <v>80</v>
       </c>
       <c r="AN108" t="s" s="2">
         <v>80</v>
@@ -15418,10 +15543,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>567</v>
+        <v>594</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>403</v>
+        <v>595</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15441,18 +15566,20 @@
         <v>80</v>
       </c>
       <c r="J109" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>159</v>
+        <v>246</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>160</v>
+        <v>247</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="N109" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="N109" t="s" s="2">
+        <v>249</v>
+      </c>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
         <v>80</v>
@@ -15501,7 +15628,7 @@
         <v>80</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>162</v>
+        <v>250</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>78</v>
@@ -15510,16 +15637,16 @@
         <v>89</v>
       </c>
       <c r="AI109" t="s" s="2">
-        <v>80</v>
+        <v>251</v>
       </c>
       <c r="AJ109" t="s" s="2">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>80</v>
+        <v>252</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>163</v>
+        <v>253</v>
       </c>
       <c r="AM109" t="s" s="2">
         <v>80</v>
@@ -15528,29 +15655,29 @@
         <v>80</v>
       </c>
       <c r="AO109" t="s" s="2">
-        <v>80</v>
+        <v>596</v>
       </c>
       <c r="AP109" t="s" s="2">
-        <v>80</v>
+        <v>597</v>
       </c>
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>568</v>
+        <v>598</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>404</v>
+        <v>599</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
-        <v>134</v>
+        <v>80</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G110" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H110" t="s" s="2">
         <v>80</v>
@@ -15559,25 +15686,27 @@
         <v>80</v>
       </c>
       <c r="J110" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>135</v>
+        <v>246</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>136</v>
+        <v>257</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>165</v>
+        <v>258</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>138</v>
+        <v>259</v>
       </c>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="Q110" s="2"/>
+      <c r="Q110" t="s" s="2">
+        <v>260</v>
+      </c>
       <c r="R110" t="s" s="2">
         <v>80</v>
       </c>
@@ -15609,37 +15738,37 @@
         <v>80</v>
       </c>
       <c r="AB110" t="s" s="2">
-        <v>166</v>
+        <v>80</v>
       </c>
       <c r="AC110" t="s" s="2">
-        <v>167</v>
+        <v>80</v>
       </c>
       <c r="AD110" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE110" t="s" s="2">
-        <v>153</v>
+        <v>80</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>168</v>
+        <v>261</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH110" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI110" t="s" s="2">
-        <v>80</v>
+        <v>251</v>
       </c>
       <c r="AJ110" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK110" t="s" s="2">
-        <v>80</v>
+        <v>262</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>163</v>
+        <v>263</v>
       </c>
       <c r="AM110" t="s" s="2">
         <v>80</v>
@@ -15648,20 +15777,22 @@
         <v>80</v>
       </c>
       <c r="AO110" t="s" s="2">
-        <v>80</v>
+        <v>600</v>
       </c>
       <c r="AP110" t="s" s="2">
-        <v>80</v>
+        <v>601</v>
       </c>
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>569</v>
+        <v>602</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="C111" s="2"/>
+        <v>394</v>
+      </c>
+      <c r="C111" t="s" s="2">
+        <v>603</v>
+      </c>
       <c r="D111" t="s" s="2">
         <v>80</v>
       </c>
@@ -15673,28 +15804,28 @@
         <v>89</v>
       </c>
       <c r="H111" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="I111" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="J111" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>109</v>
+        <v>395</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>406</v>
+        <v>396</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>407</v>
+        <v>397</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>408</v>
+        <v>398</v>
       </c>
       <c r="O111" t="s" s="2">
-        <v>409</v>
+        <v>399</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>80</v>
@@ -15707,7 +15838,7 @@
         <v>80</v>
       </c>
       <c r="T111" t="s" s="2">
-        <v>410</v>
+        <v>80</v>
       </c>
       <c r="U111" t="s" s="2">
         <v>80</v>
@@ -15719,13 +15850,13 @@
         <v>80</v>
       </c>
       <c r="X111" t="s" s="2">
-        <v>174</v>
+        <v>80</v>
       </c>
       <c r="Y111" t="s" s="2">
-        <v>411</v>
+        <v>80</v>
       </c>
       <c r="Z111" t="s" s="2">
-        <v>412</v>
+        <v>80</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>80</v>
@@ -15743,13 +15874,13 @@
         <v>80</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>413</v>
+        <v>394</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH111" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI111" t="s" s="2">
         <v>80</v>
@@ -15758,13 +15889,13 @@
         <v>101</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>414</v>
+        <v>401</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>294</v>
+        <v>402</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>415</v>
+        <v>163</v>
       </c>
       <c r="AN111" t="s" s="2">
         <v>80</v>
@@ -15778,10 +15909,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>570</v>
+        <v>604</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>416</v>
+        <v>403</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15801,20 +15932,18 @@
         <v>80</v>
       </c>
       <c r="J112" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>109</v>
+        <v>159</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>417</v>
+        <v>160</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="N112" t="s" s="2">
-        <v>419</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="N112" s="2"/>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
         <v>80</v>
@@ -15827,7 +15956,7 @@
         <v>80</v>
       </c>
       <c r="T112" t="s" s="2">
-        <v>420</v>
+        <v>80</v>
       </c>
       <c r="U112" t="s" s="2">
         <v>80</v>
@@ -15839,13 +15968,13 @@
         <v>80</v>
       </c>
       <c r="X112" t="s" s="2">
-        <v>174</v>
+        <v>80</v>
       </c>
       <c r="Y112" t="s" s="2">
-        <v>421</v>
+        <v>80</v>
       </c>
       <c r="Z112" t="s" s="2">
-        <v>422</v>
+        <v>80</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>80</v>
@@ -15863,7 +15992,7 @@
         <v>80</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>423</v>
+        <v>162</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>78</v>
@@ -15875,13 +16004,13 @@
         <v>80</v>
       </c>
       <c r="AJ112" t="s" s="2">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="AK112" t="s" s="2">
-        <v>424</v>
+        <v>80</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>294</v>
+        <v>163</v>
       </c>
       <c r="AM112" t="s" s="2">
         <v>80</v>
@@ -15898,21 +16027,21 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>571</v>
+        <v>605</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>425</v>
+        <v>404</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
-        <v>80</v>
+        <v>134</v>
       </c>
       <c r="E113" s="2"/>
       <c r="F113" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G113" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H113" t="s" s="2">
         <v>80</v>
@@ -15921,23 +16050,21 @@
         <v>80</v>
       </c>
       <c r="J113" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>159</v>
+        <v>135</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>426</v>
+        <v>136</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>427</v>
+        <v>165</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="O113" t="s" s="2">
-        <v>300</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
         <v>80</v>
       </c>
@@ -15949,7 +16076,7 @@
         <v>80</v>
       </c>
       <c r="T113" t="s" s="2">
-        <v>429</v>
+        <v>80</v>
       </c>
       <c r="U113" t="s" s="2">
         <v>80</v>
@@ -15973,37 +16100,37 @@
         <v>80</v>
       </c>
       <c r="AB113" t="s" s="2">
-        <v>80</v>
+        <v>166</v>
       </c>
       <c r="AC113" t="s" s="2">
-        <v>80</v>
+        <v>167</v>
       </c>
       <c r="AD113" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE113" t="s" s="2">
-        <v>80</v>
+        <v>153</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>430</v>
+        <v>168</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH113" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI113" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK113" t="s" s="2">
-        <v>431</v>
+        <v>80</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>303</v>
+        <v>163</v>
       </c>
       <c r="AM113" t="s" s="2">
         <v>80</v>
@@ -16020,10 +16147,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>572</v>
+        <v>606</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>432</v>
+        <v>405</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16034,28 +16161,32 @@
         <v>78</v>
       </c>
       <c r="G114" t="s" s="2">
-        <v>433</v>
+        <v>89</v>
       </c>
       <c r="H114" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I114" t="s" s="2">
         <v>90</v>
-      </c>
-      <c r="I114" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="J114" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>159</v>
+        <v>109</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>434</v>
+        <v>406</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="N114" s="2"/>
-      <c r="O114" s="2"/>
+        <v>407</v>
+      </c>
+      <c r="N114" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="O114" t="s" s="2">
+        <v>409</v>
+      </c>
       <c r="P114" t="s" s="2">
         <v>80</v>
       </c>
@@ -16067,7 +16198,7 @@
         <v>80</v>
       </c>
       <c r="T114" t="s" s="2">
-        <v>436</v>
+        <v>410</v>
       </c>
       <c r="U114" t="s" s="2">
         <v>80</v>
@@ -16079,13 +16210,13 @@
         <v>80</v>
       </c>
       <c r="X114" t="s" s="2">
-        <v>80</v>
+        <v>174</v>
       </c>
       <c r="Y114" t="s" s="2">
-        <v>80</v>
+        <v>411</v>
       </c>
       <c r="Z114" t="s" s="2">
-        <v>80</v>
+        <v>412</v>
       </c>
       <c r="AA114" t="s" s="2">
         <v>80</v>
@@ -16103,13 +16234,13 @@
         <v>80</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>437</v>
+        <v>413</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH114" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI114" t="s" s="2">
         <v>80</v>
@@ -16118,13 +16249,13 @@
         <v>101</v>
       </c>
       <c r="AK114" t="s" s="2">
-        <v>438</v>
+        <v>414</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>439</v>
+        <v>294</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>440</v>
+        <v>415</v>
       </c>
       <c r="AN114" t="s" s="2">
         <v>80</v>
@@ -16138,14 +16269,14 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>573</v>
+        <v>607</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>441</v>
+        <v>416</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
-        <v>442</v>
+        <v>80</v>
       </c>
       <c r="E115" s="2"/>
       <c r="F115" t="s" s="2">
@@ -16155,7 +16286,7 @@
         <v>89</v>
       </c>
       <c r="H115" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="I115" t="s" s="2">
         <v>80</v>
@@ -16164,15 +16295,17 @@
         <v>90</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>159</v>
+        <v>109</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>443</v>
+        <v>417</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="N115" s="2"/>
+        <v>418</v>
+      </c>
+      <c r="N115" t="s" s="2">
+        <v>419</v>
+      </c>
       <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
         <v>80</v>
@@ -16185,7 +16318,7 @@
         <v>80</v>
       </c>
       <c r="T115" t="s" s="2">
-        <v>445</v>
+        <v>420</v>
       </c>
       <c r="U115" t="s" s="2">
         <v>80</v>
@@ -16197,13 +16330,13 @@
         <v>80</v>
       </c>
       <c r="X115" t="s" s="2">
-        <v>80</v>
+        <v>174</v>
       </c>
       <c r="Y115" t="s" s="2">
-        <v>80</v>
+        <v>421</v>
       </c>
       <c r="Z115" t="s" s="2">
-        <v>80</v>
+        <v>422</v>
       </c>
       <c r="AA115" t="s" s="2">
         <v>80</v>
@@ -16221,7 +16354,7 @@
         <v>80</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>446</v>
+        <v>423</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>78</v>
@@ -16236,13 +16369,13 @@
         <v>101</v>
       </c>
       <c r="AK115" t="s" s="2">
-        <v>447</v>
+        <v>424</v>
       </c>
       <c r="AL115" t="s" s="2">
-        <v>448</v>
+        <v>294</v>
       </c>
       <c r="AM115" t="s" s="2">
-        <v>449</v>
+        <v>80</v>
       </c>
       <c r="AN115" t="s" s="2">
         <v>80</v>
@@ -16256,14 +16389,14 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>574</v>
+        <v>608</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>450</v>
+        <v>425</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
-        <v>451</v>
+        <v>80</v>
       </c>
       <c r="E116" s="2"/>
       <c r="F116" t="s" s="2">
@@ -16285,15 +16418,17 @@
         <v>159</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>452</v>
+        <v>426</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>453</v>
+        <v>427</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="O116" s="2"/>
+        <v>428</v>
+      </c>
+      <c r="O116" t="s" s="2">
+        <v>300</v>
+      </c>
       <c r="P116" t="s" s="2">
         <v>80</v>
       </c>
@@ -16305,7 +16440,7 @@
         <v>80</v>
       </c>
       <c r="T116" t="s" s="2">
-        <v>455</v>
+        <v>429</v>
       </c>
       <c r="U116" t="s" s="2">
         <v>80</v>
@@ -16341,7 +16476,7 @@
         <v>80</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>456</v>
+        <v>430</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>78</v>
@@ -16356,10 +16491,10 @@
         <v>101</v>
       </c>
       <c r="AK116" t="s" s="2">
-        <v>457</v>
+        <v>431</v>
       </c>
       <c r="AL116" t="s" s="2">
-        <v>458</v>
+        <v>303</v>
       </c>
       <c r="AM116" t="s" s="2">
         <v>80</v>
@@ -16376,21 +16511,21 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>575</v>
+        <v>609</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>459</v>
+        <v>432</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
-        <v>460</v>
+        <v>80</v>
       </c>
       <c r="E117" s="2"/>
       <c r="F117" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G117" t="s" s="2">
-        <v>89</v>
+        <v>433</v>
       </c>
       <c r="H117" t="s" s="2">
         <v>90</v>
@@ -16405,10 +16540,10 @@
         <v>159</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>461</v>
+        <v>434</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>462</v>
+        <v>435</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" s="2"/>
@@ -16423,7 +16558,7 @@
         <v>80</v>
       </c>
       <c r="T117" t="s" s="2">
-        <v>80</v>
+        <v>436</v>
       </c>
       <c r="U117" t="s" s="2">
         <v>80</v>
@@ -16435,13 +16570,13 @@
         <v>80</v>
       </c>
       <c r="X117" t="s" s="2">
-        <v>185</v>
+        <v>80</v>
       </c>
       <c r="Y117" t="s" s="2">
-        <v>463</v>
+        <v>80</v>
       </c>
       <c r="Z117" t="s" s="2">
-        <v>464</v>
+        <v>80</v>
       </c>
       <c r="AA117" t="s" s="2">
         <v>80</v>
@@ -16459,13 +16594,13 @@
         <v>80</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>465</v>
+        <v>437</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH117" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI117" t="s" s="2">
         <v>80</v>
@@ -16474,13 +16609,13 @@
         <v>101</v>
       </c>
       <c r="AK117" t="s" s="2">
-        <v>466</v>
+        <v>438</v>
       </c>
       <c r="AL117" t="s" s="2">
-        <v>467</v>
+        <v>439</v>
       </c>
       <c r="AM117" t="s" s="2">
-        <v>468</v>
+        <v>440</v>
       </c>
       <c r="AN117" t="s" s="2">
         <v>80</v>
@@ -16494,14 +16629,14 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>576</v>
+        <v>610</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>469</v>
+        <v>441</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
-        <v>470</v>
+        <v>442</v>
       </c>
       <c r="E118" s="2"/>
       <c r="F118" t="s" s="2">
@@ -16523,10 +16658,10 @@
         <v>159</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>471</v>
+        <v>443</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>472</v>
+        <v>444</v>
       </c>
       <c r="N118" s="2"/>
       <c r="O118" s="2"/>
@@ -16541,7 +16676,7 @@
         <v>80</v>
       </c>
       <c r="T118" t="s" s="2">
-        <v>473</v>
+        <v>445</v>
       </c>
       <c r="U118" t="s" s="2">
         <v>80</v>
@@ -16577,7 +16712,7 @@
         <v>80</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>474</v>
+        <v>446</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>78</v>
@@ -16592,13 +16727,13 @@
         <v>101</v>
       </c>
       <c r="AK118" t="s" s="2">
-        <v>475</v>
+        <v>447</v>
       </c>
       <c r="AL118" t="s" s="2">
-        <v>476</v>
+        <v>448</v>
       </c>
       <c r="AM118" t="s" s="2">
-        <v>477</v>
+        <v>449</v>
       </c>
       <c r="AN118" t="s" s="2">
         <v>80</v>
@@ -16612,14 +16747,14 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>577</v>
+        <v>611</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>478</v>
+        <v>450</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
-        <v>80</v>
+        <v>451</v>
       </c>
       <c r="E119" s="2"/>
       <c r="F119" t="s" s="2">
@@ -16629,7 +16764,7 @@
         <v>89</v>
       </c>
       <c r="H119" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="I119" t="s" s="2">
         <v>80</v>
@@ -16641,13 +16776,13 @@
         <v>159</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>479</v>
+        <v>452</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>480</v>
+        <v>453</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>481</v>
+        <v>454</v>
       </c>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
@@ -16661,7 +16796,7 @@
         <v>80</v>
       </c>
       <c r="T119" t="s" s="2">
-        <v>80</v>
+        <v>455</v>
       </c>
       <c r="U119" t="s" s="2">
         <v>80</v>
@@ -16697,7 +16832,7 @@
         <v>80</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>482</v>
+        <v>456</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>78</v>
@@ -16712,13 +16847,13 @@
         <v>101</v>
       </c>
       <c r="AK119" t="s" s="2">
-        <v>483</v>
+        <v>457</v>
       </c>
       <c r="AL119" t="s" s="2">
-        <v>484</v>
+        <v>458</v>
       </c>
       <c r="AM119" t="s" s="2">
-        <v>485</v>
+        <v>80</v>
       </c>
       <c r="AN119" t="s" s="2">
         <v>80</v>
@@ -16732,14 +16867,14 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>578</v>
+        <v>612</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>486</v>
+        <v>459</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
-        <v>80</v>
+        <v>460</v>
       </c>
       <c r="E120" s="2"/>
       <c r="F120" t="s" s="2">
@@ -16749,7 +16884,7 @@
         <v>89</v>
       </c>
       <c r="H120" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="I120" t="s" s="2">
         <v>80</v>
@@ -16758,18 +16893,16 @@
         <v>90</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>212</v>
+        <v>159</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>487</v>
+        <v>461</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>488</v>
+        <v>462</v>
       </c>
       <c r="N120" s="2"/>
-      <c r="O120" t="s" s="2">
-        <v>489</v>
-      </c>
+      <c r="O120" s="2"/>
       <c r="P120" t="s" s="2">
         <v>80</v>
       </c>
@@ -16781,7 +16914,7 @@
         <v>80</v>
       </c>
       <c r="T120" t="s" s="2">
-        <v>490</v>
+        <v>80</v>
       </c>
       <c r="U120" t="s" s="2">
         <v>80</v>
@@ -16793,13 +16926,13 @@
         <v>80</v>
       </c>
       <c r="X120" t="s" s="2">
-        <v>80</v>
+        <v>185</v>
       </c>
       <c r="Y120" t="s" s="2">
-        <v>80</v>
+        <v>463</v>
       </c>
       <c r="Z120" t="s" s="2">
-        <v>80</v>
+        <v>464</v>
       </c>
       <c r="AA120" t="s" s="2">
         <v>80</v>
@@ -16817,7 +16950,7 @@
         <v>80</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>491</v>
+        <v>465</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>78</v>
@@ -16832,13 +16965,13 @@
         <v>101</v>
       </c>
       <c r="AK120" t="s" s="2">
-        <v>492</v>
+        <v>466</v>
       </c>
       <c r="AL120" t="s" s="2">
-        <v>342</v>
+        <v>467</v>
       </c>
       <c r="AM120" t="s" s="2">
-        <v>218</v>
+        <v>468</v>
       </c>
       <c r="AN120" t="s" s="2">
         <v>80</v>
@@ -16852,14 +16985,14 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>579</v>
+        <v>613</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>579</v>
+        <v>469</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
-        <v>80</v>
+        <v>470</v>
       </c>
       <c r="E121" s="2"/>
       <c r="F121" t="s" s="2">
@@ -16869,7 +17002,7 @@
         <v>89</v>
       </c>
       <c r="H121" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="I121" t="s" s="2">
         <v>80</v>
@@ -16878,18 +17011,16 @@
         <v>90</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>109</v>
+        <v>159</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>580</v>
+        <v>471</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>581</v>
+        <v>472</v>
       </c>
       <c r="N121" s="2"/>
-      <c r="O121" t="s" s="2">
-        <v>582</v>
-      </c>
+      <c r="O121" s="2"/>
       <c r="P121" t="s" s="2">
         <v>80</v>
       </c>
@@ -16901,7 +17032,7 @@
         <v>80</v>
       </c>
       <c r="T121" t="s" s="2">
-        <v>80</v>
+        <v>473</v>
       </c>
       <c r="U121" t="s" s="2">
         <v>80</v>
@@ -16913,13 +17044,13 @@
         <v>80</v>
       </c>
       <c r="X121" t="s" s="2">
-        <v>174</v>
+        <v>80</v>
       </c>
       <c r="Y121" t="s" s="2">
-        <v>583</v>
+        <v>80</v>
       </c>
       <c r="Z121" t="s" s="2">
-        <v>584</v>
+        <v>80</v>
       </c>
       <c r="AA121" t="s" s="2">
         <v>80</v>
@@ -16937,7 +17068,7 @@
         <v>80</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>579</v>
+        <v>474</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>78</v>
@@ -16952,13 +17083,13 @@
         <v>101</v>
       </c>
       <c r="AK121" t="s" s="2">
-        <v>585</v>
+        <v>475</v>
       </c>
       <c r="AL121" t="s" s="2">
-        <v>586</v>
+        <v>476</v>
       </c>
       <c r="AM121" t="s" s="2">
-        <v>587</v>
+        <v>477</v>
       </c>
       <c r="AN121" t="s" s="2">
         <v>80</v>
@@ -16972,10 +17103,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>588</v>
+        <v>614</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>588</v>
+        <v>478</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16989,7 +17120,7 @@
         <v>89</v>
       </c>
       <c r="H122" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="I122" t="s" s="2">
         <v>80</v>
@@ -16998,18 +17129,18 @@
         <v>90</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>589</v>
+        <v>159</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>590</v>
+        <v>479</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>591</v>
-      </c>
-      <c r="N122" s="2"/>
-      <c r="O122" t="s" s="2">
-        <v>592</v>
-      </c>
+        <v>480</v>
+      </c>
+      <c r="N122" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="O122" s="2"/>
       <c r="P122" t="s" s="2">
         <v>80</v>
       </c>
@@ -17057,7 +17188,7 @@
         <v>80</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>588</v>
+        <v>482</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>78</v>
@@ -17072,30 +17203,30 @@
         <v>101</v>
       </c>
       <c r="AK122" t="s" s="2">
-        <v>593</v>
+        <v>483</v>
       </c>
       <c r="AL122" t="s" s="2">
-        <v>594</v>
+        <v>484</v>
       </c>
       <c r="AM122" t="s" s="2">
-        <v>595</v>
+        <v>485</v>
       </c>
       <c r="AN122" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO122" t="s" s="2">
-        <v>596</v>
+        <v>80</v>
       </c>
       <c r="AP122" t="s" s="2">
-        <v>597</v>
+        <v>80</v>
       </c>
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>598</v>
+        <v>615</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>598</v>
+        <v>486</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -17106,7 +17237,7 @@
         <v>78</v>
       </c>
       <c r="G123" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H123" t="s" s="2">
         <v>80</v>
@@ -17115,20 +17246,20 @@
         <v>80</v>
       </c>
       <c r="J123" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>599</v>
+        <v>212</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>600</v>
+        <v>487</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>601</v>
+        <v>488</v>
       </c>
       <c r="N123" s="2"/>
       <c r="O123" t="s" s="2">
-        <v>602</v>
+        <v>489</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>80</v>
@@ -17141,7 +17272,7 @@
         <v>80</v>
       </c>
       <c r="T123" t="s" s="2">
-        <v>80</v>
+        <v>490</v>
       </c>
       <c r="U123" t="s" s="2">
         <v>80</v>
@@ -17177,13 +17308,13 @@
         <v>80</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>598</v>
+        <v>491</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH123" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI123" t="s" s="2">
         <v>80</v>
@@ -17192,13 +17323,13 @@
         <v>101</v>
       </c>
       <c r="AK123" t="s" s="2">
-        <v>80</v>
+        <v>492</v>
       </c>
       <c r="AL123" t="s" s="2">
-        <v>603</v>
+        <v>342</v>
       </c>
       <c r="AM123" t="s" s="2">
-        <v>604</v>
+        <v>218</v>
       </c>
       <c r="AN123" t="s" s="2">
         <v>80</v>
@@ -17212,12 +17343,14 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>605</v>
+        <v>616</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>605</v>
-      </c>
-      <c r="C124" s="2"/>
+        <v>394</v>
+      </c>
+      <c r="C124" t="s" s="2">
+        <v>617</v>
+      </c>
       <c r="D124" t="s" s="2">
         <v>80</v>
       </c>
@@ -17226,28 +17359,32 @@
         <v>78</v>
       </c>
       <c r="G124" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H124" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="I124" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J124" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>606</v>
+        <v>395</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>607</v>
+        <v>396</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>608</v>
-      </c>
-      <c r="N124" s="2"/>
-      <c r="O124" s="2"/>
+        <v>397</v>
+      </c>
+      <c r="N124" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="O124" t="s" s="2">
+        <v>399</v>
+      </c>
       <c r="P124" t="s" s="2">
         <v>80</v>
       </c>
@@ -17295,7 +17432,7 @@
         <v>80</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>605</v>
+        <v>394</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>78</v>
@@ -17310,13 +17447,13 @@
         <v>101</v>
       </c>
       <c r="AK124" t="s" s="2">
-        <v>609</v>
+        <v>401</v>
       </c>
       <c r="AL124" t="s" s="2">
-        <v>610</v>
+        <v>402</v>
       </c>
       <c r="AM124" t="s" s="2">
-        <v>611</v>
+        <v>163</v>
       </c>
       <c r="AN124" t="s" s="2">
         <v>80</v>
@@ -17330,10 +17467,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>612</v>
+        <v>618</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>612</v>
+        <v>403</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17448,10 +17585,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>613</v>
+        <v>619</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>613</v>
+        <v>404</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17521,16 +17658,16 @@
         <v>80</v>
       </c>
       <c r="AB126" t="s" s="2">
-        <v>80</v>
+        <v>166</v>
       </c>
       <c r="AC126" t="s" s="2">
-        <v>80</v>
+        <v>167</v>
       </c>
       <c r="AD126" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE126" t="s" s="2">
-        <v>80</v>
+        <v>153</v>
       </c>
       <c r="AF126" t="s" s="2">
         <v>168</v>
@@ -17568,21 +17705,21 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>614</v>
+        <v>620</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>614</v>
+        <v>405</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
-        <v>615</v>
+        <v>80</v>
       </c>
       <c r="E127" s="2"/>
       <c r="F127" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G127" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H127" t="s" s="2">
         <v>80</v>
@@ -17594,19 +17731,19 @@
         <v>90</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>135</v>
+        <v>109</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>616</v>
+        <v>406</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>617</v>
+        <v>407</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>138</v>
+        <v>408</v>
       </c>
       <c r="O127" t="s" s="2">
-        <v>144</v>
+        <v>409</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>80</v>
@@ -17619,7 +17756,7 @@
         <v>80</v>
       </c>
       <c r="T127" t="s" s="2">
-        <v>80</v>
+        <v>410</v>
       </c>
       <c r="U127" t="s" s="2">
         <v>80</v>
@@ -17631,13 +17768,13 @@
         <v>80</v>
       </c>
       <c r="X127" t="s" s="2">
-        <v>80</v>
+        <v>174</v>
       </c>
       <c r="Y127" t="s" s="2">
-        <v>80</v>
+        <v>411</v>
       </c>
       <c r="Z127" t="s" s="2">
-        <v>80</v>
+        <v>412</v>
       </c>
       <c r="AA127" t="s" s="2">
         <v>80</v>
@@ -17655,28 +17792,28 @@
         <v>80</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>618</v>
+        <v>413</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH127" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI127" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ127" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK127" t="s" s="2">
-        <v>80</v>
+        <v>414</v>
       </c>
       <c r="AL127" t="s" s="2">
-        <v>132</v>
+        <v>294</v>
       </c>
       <c r="AM127" t="s" s="2">
-        <v>80</v>
+        <v>415</v>
       </c>
       <c r="AN127" t="s" s="2">
         <v>80</v>
@@ -17690,10 +17827,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>619</v>
+        <v>416</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17704,7 +17841,7 @@
         <v>78</v>
       </c>
       <c r="G128" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H128" t="s" s="2">
         <v>80</v>
@@ -17713,21 +17850,21 @@
         <v>80</v>
       </c>
       <c r="J128" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>147</v>
+        <v>109</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>620</v>
+        <v>417</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>621</v>
-      </c>
-      <c r="N128" s="2"/>
-      <c r="O128" t="s" s="2">
-        <v>622</v>
-      </c>
+        <v>418</v>
+      </c>
+      <c r="N128" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="O128" s="2"/>
       <c r="P128" t="s" s="2">
         <v>80</v>
       </c>
@@ -17739,7 +17876,7 @@
         <v>80</v>
       </c>
       <c r="T128" t="s" s="2">
-        <v>80</v>
+        <v>420</v>
       </c>
       <c r="U128" t="s" s="2">
         <v>80</v>
@@ -17751,13 +17888,13 @@
         <v>80</v>
       </c>
       <c r="X128" t="s" s="2">
-        <v>80</v>
+        <v>174</v>
       </c>
       <c r="Y128" t="s" s="2">
-        <v>80</v>
+        <v>421</v>
       </c>
       <c r="Z128" t="s" s="2">
-        <v>80</v>
+        <v>422</v>
       </c>
       <c r="AA128" t="s" s="2">
         <v>80</v>
@@ -17775,13 +17912,13 @@
         <v>80</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>619</v>
+        <v>423</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH128" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI128" t="s" s="2">
         <v>80</v>
@@ -17790,10 +17927,10 @@
         <v>101</v>
       </c>
       <c r="AK128" t="s" s="2">
-        <v>80</v>
+        <v>424</v>
       </c>
       <c r="AL128" t="s" s="2">
-        <v>623</v>
+        <v>294</v>
       </c>
       <c r="AM128" t="s" s="2">
         <v>80</v>
@@ -17810,10 +17947,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>624</v>
+        <v>425</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17821,7 +17958,7 @@
       </c>
       <c r="E129" s="2"/>
       <c r="F129" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G129" t="s" s="2">
         <v>89</v>
@@ -17833,19 +17970,23 @@
         <v>80</v>
       </c>
       <c r="J129" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>180</v>
+        <v>159</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>625</v>
+        <v>426</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>626</v>
-      </c>
-      <c r="N129" s="2"/>
-      <c r="O129" s="2"/>
+        <v>427</v>
+      </c>
+      <c r="N129" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="O129" t="s" s="2">
+        <v>300</v>
+      </c>
       <c r="P129" t="s" s="2">
         <v>80</v>
       </c>
@@ -17857,7 +17998,7 @@
         <v>80</v>
       </c>
       <c r="T129" t="s" s="2">
-        <v>80</v>
+        <v>429</v>
       </c>
       <c r="U129" t="s" s="2">
         <v>80</v>
@@ -17869,13 +18010,13 @@
         <v>80</v>
       </c>
       <c r="X129" t="s" s="2">
-        <v>627</v>
+        <v>80</v>
       </c>
       <c r="Y129" t="s" s="2">
-        <v>628</v>
+        <v>80</v>
       </c>
       <c r="Z129" t="s" s="2">
-        <v>629</v>
+        <v>80</v>
       </c>
       <c r="AA129" t="s" s="2">
         <v>80</v>
@@ -17893,10 +18034,10 @@
         <v>80</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>624</v>
+        <v>430</v>
       </c>
       <c r="AG129" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AH129" t="s" s="2">
         <v>89</v>
@@ -17908,13 +18049,13 @@
         <v>101</v>
       </c>
       <c r="AK129" t="s" s="2">
-        <v>80</v>
+        <v>431</v>
       </c>
       <c r="AL129" t="s" s="2">
-        <v>610</v>
+        <v>303</v>
       </c>
       <c r="AM129" t="s" s="2">
-        <v>630</v>
+        <v>80</v>
       </c>
       <c r="AN129" t="s" s="2">
         <v>80</v>
@@ -17928,10 +18069,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>631</v>
+        <v>623</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>631</v>
+        <v>432</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -17942,25 +18083,25 @@
         <v>78</v>
       </c>
       <c r="G130" t="s" s="2">
-        <v>89</v>
+        <v>433</v>
       </c>
       <c r="H130" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="I130" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J130" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K130" t="s" s="2">
         <v>159</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>160</v>
+        <v>434</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>161</v>
+        <v>435</v>
       </c>
       <c r="N130" s="2"/>
       <c r="O130" s="2"/>
@@ -17975,7 +18116,7 @@
         <v>80</v>
       </c>
       <c r="T130" t="s" s="2">
-        <v>80</v>
+        <v>436</v>
       </c>
       <c r="U130" t="s" s="2">
         <v>80</v>
@@ -18011,28 +18152,28 @@
         <v>80</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>162</v>
+        <v>437</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH130" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI130" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ130" t="s" s="2">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="AK130" t="s" s="2">
-        <v>80</v>
+        <v>438</v>
       </c>
       <c r="AL130" t="s" s="2">
-        <v>163</v>
+        <v>439</v>
       </c>
       <c r="AM130" t="s" s="2">
-        <v>80</v>
+        <v>440</v>
       </c>
       <c r="AN130" t="s" s="2">
         <v>80</v>
@@ -18046,43 +18187,41 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>632</v>
+        <v>624</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>632</v>
+        <v>441</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
-        <v>134</v>
+        <v>442</v>
       </c>
       <c r="E131" s="2"/>
       <c r="F131" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G131" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H131" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="I131" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J131" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>136</v>
+        <v>443</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="N131" t="s" s="2">
-        <v>138</v>
-      </c>
+        <v>444</v>
+      </c>
+      <c r="N131" s="2"/>
       <c r="O131" s="2"/>
       <c r="P131" t="s" s="2">
         <v>80</v>
@@ -18095,7 +18234,7 @@
         <v>80</v>
       </c>
       <c r="T131" t="s" s="2">
-        <v>80</v>
+        <v>445</v>
       </c>
       <c r="U131" t="s" s="2">
         <v>80</v>
@@ -18119,40 +18258,40 @@
         <v>80</v>
       </c>
       <c r="AB131" t="s" s="2">
-        <v>166</v>
+        <v>80</v>
       </c>
       <c r="AC131" t="s" s="2">
-        <v>167</v>
+        <v>80</v>
       </c>
       <c r="AD131" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE131" t="s" s="2">
-        <v>153</v>
+        <v>80</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>168</v>
+        <v>446</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH131" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI131" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ131" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK131" t="s" s="2">
-        <v>80</v>
+        <v>447</v>
       </c>
       <c r="AL131" t="s" s="2">
-        <v>163</v>
+        <v>448</v>
       </c>
       <c r="AM131" t="s" s="2">
-        <v>80</v>
+        <v>449</v>
       </c>
       <c r="AN131" t="s" s="2">
         <v>80</v>
@@ -18166,21 +18305,21 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>633</v>
+        <v>625</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>633</v>
+        <v>450</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
-        <v>80</v>
+        <v>451</v>
       </c>
       <c r="E132" s="2"/>
       <c r="F132" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G132" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H132" t="s" s="2">
         <v>80</v>
@@ -18192,20 +18331,18 @@
         <v>90</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>634</v>
+        <v>159</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>635</v>
+        <v>452</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>636</v>
+        <v>453</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>637</v>
-      </c>
-      <c r="O132" t="s" s="2">
-        <v>638</v>
-      </c>
+        <v>454</v>
+      </c>
+      <c r="O132" s="2"/>
       <c r="P132" t="s" s="2">
         <v>80</v>
       </c>
@@ -18217,7 +18354,7 @@
         <v>80</v>
       </c>
       <c r="T132" t="s" s="2">
-        <v>80</v>
+        <v>455</v>
       </c>
       <c r="U132" t="s" s="2">
         <v>80</v>
@@ -18253,13 +18390,13 @@
         <v>80</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>639</v>
+        <v>456</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH132" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI132" t="s" s="2">
         <v>80</v>
@@ -18268,10 +18405,10 @@
         <v>101</v>
       </c>
       <c r="AK132" t="s" s="2">
-        <v>640</v>
+        <v>457</v>
       </c>
       <c r="AL132" t="s" s="2">
-        <v>641</v>
+        <v>458</v>
       </c>
       <c r="AM132" t="s" s="2">
         <v>80</v>
@@ -18288,14 +18425,14 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>642</v>
+        <v>626</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>642</v>
+        <v>459</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
-        <v>80</v>
+        <v>460</v>
       </c>
       <c r="E133" s="2"/>
       <c r="F133" t="s" s="2">
@@ -18305,7 +18442,7 @@
         <v>89</v>
       </c>
       <c r="H133" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="I133" t="s" s="2">
         <v>80</v>
@@ -18317,17 +18454,13 @@
         <v>159</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>643</v>
+        <v>461</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>644</v>
-      </c>
-      <c r="N133" t="s" s="2">
-        <v>645</v>
-      </c>
-      <c r="O133" t="s" s="2">
-        <v>646</v>
-      </c>
+        <v>462</v>
+      </c>
+      <c r="N133" s="2"/>
+      <c r="O133" s="2"/>
       <c r="P133" t="s" s="2">
         <v>80</v>
       </c>
@@ -18351,13 +18484,13 @@
         <v>80</v>
       </c>
       <c r="X133" t="s" s="2">
-        <v>80</v>
+        <v>185</v>
       </c>
       <c r="Y133" t="s" s="2">
-        <v>80</v>
+        <v>463</v>
       </c>
       <c r="Z133" t="s" s="2">
-        <v>80</v>
+        <v>464</v>
       </c>
       <c r="AA133" t="s" s="2">
         <v>80</v>
@@ -18375,7 +18508,7 @@
         <v>80</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>647</v>
+        <v>465</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>78</v>
@@ -18390,19 +18523,19 @@
         <v>101</v>
       </c>
       <c r="AK133" t="s" s="2">
-        <v>648</v>
+        <v>466</v>
       </c>
       <c r="AL133" t="s" s="2">
-        <v>649</v>
+        <v>467</v>
       </c>
       <c r="AM133" t="s" s="2">
-        <v>80</v>
+        <v>468</v>
       </c>
       <c r="AN133" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO133" t="s" s="2">
-        <v>650</v>
+        <v>80</v>
       </c>
       <c r="AP133" t="s" s="2">
         <v>80</v>
@@ -18410,14 +18543,14 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>651</v>
+        <v>627</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>651</v>
+        <v>469</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
-        <v>80</v>
+        <v>470</v>
       </c>
       <c r="E134" s="2"/>
       <c r="F134" t="s" s="2">
@@ -18427,27 +18560,25 @@
         <v>89</v>
       </c>
       <c r="H134" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="I134" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J134" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>212</v>
+        <v>159</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>652</v>
+        <v>471</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>653</v>
+        <v>472</v>
       </c>
       <c r="N134" s="2"/>
-      <c r="O134" t="s" s="2">
-        <v>654</v>
-      </c>
+      <c r="O134" s="2"/>
       <c r="P134" t="s" s="2">
         <v>80</v>
       </c>
@@ -18459,7 +18590,7 @@
         <v>80</v>
       </c>
       <c r="T134" t="s" s="2">
-        <v>80</v>
+        <v>473</v>
       </c>
       <c r="U134" t="s" s="2">
         <v>80</v>
@@ -18495,7 +18626,7 @@
         <v>80</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>651</v>
+        <v>474</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>78</v>
@@ -18510,13 +18641,13 @@
         <v>101</v>
       </c>
       <c r="AK134" t="s" s="2">
-        <v>80</v>
+        <v>475</v>
       </c>
       <c r="AL134" t="s" s="2">
-        <v>655</v>
+        <v>476</v>
       </c>
       <c r="AM134" t="s" s="2">
-        <v>656</v>
+        <v>477</v>
       </c>
       <c r="AN134" t="s" s="2">
         <v>80</v>
@@ -18530,10 +18661,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>657</v>
+        <v>628</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>657</v>
+        <v>478</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18547,24 +18678,26 @@
         <v>89</v>
       </c>
       <c r="H135" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="I135" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J135" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>220</v>
+        <v>159</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>658</v>
+        <v>479</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>659</v>
-      </c>
-      <c r="N135" s="2"/>
+        <v>480</v>
+      </c>
+      <c r="N135" t="s" s="2">
+        <v>481</v>
+      </c>
       <c r="O135" s="2"/>
       <c r="P135" t="s" s="2">
         <v>80</v>
@@ -18613,7 +18746,7 @@
         <v>80</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>657</v>
+        <v>482</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>78</v>
@@ -18628,13 +18761,13 @@
         <v>101</v>
       </c>
       <c r="AK135" t="s" s="2">
-        <v>80</v>
+        <v>483</v>
       </c>
       <c r="AL135" t="s" s="2">
-        <v>660</v>
+        <v>484</v>
       </c>
       <c r="AM135" t="s" s="2">
-        <v>80</v>
+        <v>485</v>
       </c>
       <c r="AN135" t="s" s="2">
         <v>80</v>
@@ -18648,10 +18781,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>661</v>
+        <v>629</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>661</v>
+        <v>486</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -18662,7 +18795,7 @@
         <v>78</v>
       </c>
       <c r="G136" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H136" t="s" s="2">
         <v>80</v>
@@ -18671,22 +18804,20 @@
         <v>80</v>
       </c>
       <c r="J136" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>180</v>
+        <v>212</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>662</v>
+        <v>487</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>663</v>
-      </c>
-      <c r="N136" t="s" s="2">
-        <v>664</v>
-      </c>
+        <v>488</v>
+      </c>
+      <c r="N136" s="2"/>
       <c r="O136" t="s" s="2">
-        <v>665</v>
+        <v>489</v>
       </c>
       <c r="P136" t="s" s="2">
         <v>80</v>
@@ -18699,7 +18830,7 @@
         <v>80</v>
       </c>
       <c r="T136" t="s" s="2">
-        <v>80</v>
+        <v>490</v>
       </c>
       <c r="U136" t="s" s="2">
         <v>80</v>
@@ -18711,13 +18842,13 @@
         <v>80</v>
       </c>
       <c r="X136" t="s" s="2">
-        <v>113</v>
+        <v>80</v>
       </c>
       <c r="Y136" t="s" s="2">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="Z136" t="s" s="2">
-        <v>115</v>
+        <v>80</v>
       </c>
       <c r="AA136" t="s" s="2">
         <v>80</v>
@@ -18735,13 +18866,13 @@
         <v>80</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>661</v>
+        <v>491</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH136" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI136" t="s" s="2">
         <v>80</v>
@@ -18750,26 +18881,1944 @@
         <v>101</v>
       </c>
       <c r="AK136" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="AL136" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="AM136" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="AN136" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO136" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP136" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="137" hidden="true">
+      <c r="A137" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="B137" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="C137" s="2"/>
+      <c r="D137" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E137" s="2"/>
+      <c r="F137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G137" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H137" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I137" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J137" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K137" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="L137" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="M137" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="N137" s="2"/>
+      <c r="O137" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="P137" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q137" s="2"/>
+      <c r="R137" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S137" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T137" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U137" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V137" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W137" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X137" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="Y137" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="Z137" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="AA137" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB137" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC137" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD137" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE137" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF137" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="AG137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH137" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI137" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ137" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK137" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="AL137" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="AM137" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="AN137" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO137" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP137" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="138" hidden="true">
+      <c r="A138" t="s" s="2">
+        <v>639</v>
+      </c>
+      <c r="B138" t="s" s="2">
+        <v>639</v>
+      </c>
+      <c r="C138" s="2"/>
+      <c r="D138" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E138" s="2"/>
+      <c r="F138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G138" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H138" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I138" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J138" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K138" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="L138" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="M138" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="N138" s="2"/>
+      <c r="O138" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="P138" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q138" s="2"/>
+      <c r="R138" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S138" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T138" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U138" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V138" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W138" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X138" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y138" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z138" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA138" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB138" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC138" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD138" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE138" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF138" t="s" s="2">
+        <v>639</v>
+      </c>
+      <c r="AG138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH138" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI138" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ138" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK138" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="AL138" t="s" s="2">
+        <v>645</v>
+      </c>
+      <c r="AM138" t="s" s="2">
+        <v>646</v>
+      </c>
+      <c r="AN138" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO138" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="AP138" t="s" s="2">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="139" hidden="true">
+      <c r="A139" t="s" s="2">
+        <v>649</v>
+      </c>
+      <c r="B139" t="s" s="2">
+        <v>649</v>
+      </c>
+      <c r="C139" s="2"/>
+      <c r="D139" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E139" s="2"/>
+      <c r="F139" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G139" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H139" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I139" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J139" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K139" t="s" s="2">
+        <v>650</v>
+      </c>
+      <c r="L139" t="s" s="2">
+        <v>651</v>
+      </c>
+      <c r="M139" t="s" s="2">
+        <v>652</v>
+      </c>
+      <c r="N139" s="2"/>
+      <c r="O139" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="P139" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q139" s="2"/>
+      <c r="R139" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S139" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T139" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U139" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V139" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W139" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X139" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y139" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z139" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA139" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB139" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC139" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD139" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE139" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF139" t="s" s="2">
+        <v>649</v>
+      </c>
+      <c r="AG139" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH139" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI139" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ139" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK139" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL139" t="s" s="2">
+        <v>654</v>
+      </c>
+      <c r="AM139" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="AN139" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO139" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP139" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="140" hidden="true">
+      <c r="A140" t="s" s="2">
+        <v>656</v>
+      </c>
+      <c r="B140" t="s" s="2">
+        <v>656</v>
+      </c>
+      <c r="C140" s="2"/>
+      <c r="D140" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E140" s="2"/>
+      <c r="F140" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G140" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H140" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I140" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J140" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K140" t="s" s="2">
+        <v>657</v>
+      </c>
+      <c r="L140" t="s" s="2">
+        <v>658</v>
+      </c>
+      <c r="M140" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="N140" s="2"/>
+      <c r="O140" s="2"/>
+      <c r="P140" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q140" s="2"/>
+      <c r="R140" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S140" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T140" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U140" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V140" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W140" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X140" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y140" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z140" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA140" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB140" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC140" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD140" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE140" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF140" t="s" s="2">
+        <v>656</v>
+      </c>
+      <c r="AG140" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH140" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI140" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ140" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK140" t="s" s="2">
+        <v>660</v>
+      </c>
+      <c r="AL140" t="s" s="2">
+        <v>661</v>
+      </c>
+      <c r="AM140" t="s" s="2">
+        <v>662</v>
+      </c>
+      <c r="AN140" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO140" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP140" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="141" hidden="true">
+      <c r="A141" t="s" s="2">
+        <v>663</v>
+      </c>
+      <c r="B141" t="s" s="2">
+        <v>663</v>
+      </c>
+      <c r="C141" s="2"/>
+      <c r="D141" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E141" s="2"/>
+      <c r="F141" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G141" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H141" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I141" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J141" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K141" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="L141" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="M141" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="N141" s="2"/>
+      <c r="O141" s="2"/>
+      <c r="P141" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q141" s="2"/>
+      <c r="R141" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S141" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T141" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U141" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V141" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W141" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X141" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y141" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z141" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA141" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB141" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC141" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD141" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE141" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF141" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AG141" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH141" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI141" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ141" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK141" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL141" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="AM141" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN141" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO141" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP141" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="142" hidden="true">
+      <c r="A142" t="s" s="2">
+        <v>664</v>
+      </c>
+      <c r="B142" t="s" s="2">
+        <v>664</v>
+      </c>
+      <c r="C142" s="2"/>
+      <c r="D142" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="E142" s="2"/>
+      <c r="F142" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G142" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H142" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I142" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J142" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K142" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L142" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="M142" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="N142" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="O142" s="2"/>
+      <c r="P142" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q142" s="2"/>
+      <c r="R142" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S142" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T142" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U142" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V142" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W142" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X142" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y142" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z142" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA142" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB142" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC142" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD142" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE142" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF142" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="AG142" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH142" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI142" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ142" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK142" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL142" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="AM142" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN142" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO142" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP142" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="143" hidden="true">
+      <c r="A143" t="s" s="2">
+        <v>665</v>
+      </c>
+      <c r="B143" t="s" s="2">
+        <v>665</v>
+      </c>
+      <c r="C143" s="2"/>
+      <c r="D143" t="s" s="2">
         <v>666</v>
       </c>
-      <c r="AL136" t="s" s="2">
+      <c r="E143" s="2"/>
+      <c r="F143" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G143" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H143" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I143" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="J143" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K143" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L143" t="s" s="2">
         <v>667</v>
       </c>
-      <c r="AM136" t="s" s="2">
+      <c r="M143" t="s" s="2">
         <v>668</v>
       </c>
-      <c r="AN136" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO136" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP136" t="s" s="2">
+      <c r="N143" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="O143" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="P143" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q143" s="2"/>
+      <c r="R143" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S143" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T143" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U143" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V143" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W143" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X143" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y143" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z143" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA143" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB143" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC143" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD143" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE143" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF143" t="s" s="2">
+        <v>669</v>
+      </c>
+      <c r="AG143" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH143" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI143" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ143" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK143" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL143" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AM143" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN143" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO143" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP143" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="144" hidden="true">
+      <c r="A144" t="s" s="2">
+        <v>670</v>
+      </c>
+      <c r="B144" t="s" s="2">
+        <v>670</v>
+      </c>
+      <c r="C144" s="2"/>
+      <c r="D144" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E144" s="2"/>
+      <c r="F144" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G144" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H144" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I144" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J144" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K144" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="L144" t="s" s="2">
+        <v>671</v>
+      </c>
+      <c r="M144" t="s" s="2">
+        <v>672</v>
+      </c>
+      <c r="N144" s="2"/>
+      <c r="O144" t="s" s="2">
+        <v>673</v>
+      </c>
+      <c r="P144" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q144" s="2"/>
+      <c r="R144" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S144" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T144" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U144" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V144" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W144" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X144" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y144" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z144" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA144" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB144" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC144" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD144" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE144" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF144" t="s" s="2">
+        <v>670</v>
+      </c>
+      <c r="AG144" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH144" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI144" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ144" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK144" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL144" t="s" s="2">
+        <v>674</v>
+      </c>
+      <c r="AM144" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN144" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO144" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP144" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="145" hidden="true">
+      <c r="A145" t="s" s="2">
+        <v>675</v>
+      </c>
+      <c r="B145" t="s" s="2">
+        <v>675</v>
+      </c>
+      <c r="C145" s="2"/>
+      <c r="D145" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E145" s="2"/>
+      <c r="F145" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G145" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H145" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I145" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J145" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K145" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="L145" t="s" s="2">
+        <v>676</v>
+      </c>
+      <c r="M145" t="s" s="2">
+        <v>677</v>
+      </c>
+      <c r="N145" s="2"/>
+      <c r="O145" s="2"/>
+      <c r="P145" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q145" s="2"/>
+      <c r="R145" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S145" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T145" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U145" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V145" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W145" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X145" t="s" s="2">
+        <v>678</v>
+      </c>
+      <c r="Y145" t="s" s="2">
+        <v>679</v>
+      </c>
+      <c r="Z145" t="s" s="2">
+        <v>680</v>
+      </c>
+      <c r="AA145" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB145" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC145" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD145" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE145" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF145" t="s" s="2">
+        <v>675</v>
+      </c>
+      <c r="AG145" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AH145" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI145" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ145" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK145" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL145" t="s" s="2">
+        <v>661</v>
+      </c>
+      <c r="AM145" t="s" s="2">
+        <v>681</v>
+      </c>
+      <c r="AN145" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO145" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP145" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="146" hidden="true">
+      <c r="A146" t="s" s="2">
+        <v>682</v>
+      </c>
+      <c r="B146" t="s" s="2">
+        <v>682</v>
+      </c>
+      <c r="C146" s="2"/>
+      <c r="D146" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E146" s="2"/>
+      <c r="F146" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G146" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H146" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I146" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J146" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K146" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="L146" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="M146" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="N146" s="2"/>
+      <c r="O146" s="2"/>
+      <c r="P146" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q146" s="2"/>
+      <c r="R146" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S146" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T146" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U146" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V146" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W146" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X146" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y146" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z146" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA146" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB146" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC146" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD146" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE146" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF146" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AG146" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH146" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI146" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ146" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK146" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL146" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="AM146" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN146" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO146" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP146" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="147" hidden="true">
+      <c r="A147" t="s" s="2">
+        <v>683</v>
+      </c>
+      <c r="B147" t="s" s="2">
+        <v>683</v>
+      </c>
+      <c r="C147" s="2"/>
+      <c r="D147" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="E147" s="2"/>
+      <c r="F147" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G147" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H147" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I147" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J147" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K147" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L147" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="M147" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="N147" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="O147" s="2"/>
+      <c r="P147" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q147" s="2"/>
+      <c r="R147" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S147" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T147" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U147" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V147" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W147" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X147" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y147" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z147" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA147" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB147" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="AC147" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AD147" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE147" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AF147" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="AG147" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH147" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI147" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ147" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK147" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL147" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="AM147" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN147" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO147" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP147" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="148" hidden="true">
+      <c r="A148" t="s" s="2">
+        <v>684</v>
+      </c>
+      <c r="B148" t="s" s="2">
+        <v>684</v>
+      </c>
+      <c r="C148" s="2"/>
+      <c r="D148" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E148" s="2"/>
+      <c r="F148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G148" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H148" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I148" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J148" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K148" t="s" s="2">
+        <v>685</v>
+      </c>
+      <c r="L148" t="s" s="2">
+        <v>686</v>
+      </c>
+      <c r="M148" t="s" s="2">
+        <v>687</v>
+      </c>
+      <c r="N148" t="s" s="2">
+        <v>688</v>
+      </c>
+      <c r="O148" t="s" s="2">
+        <v>689</v>
+      </c>
+      <c r="P148" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q148" s="2"/>
+      <c r="R148" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S148" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T148" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U148" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V148" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W148" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X148" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y148" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z148" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA148" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB148" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC148" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD148" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE148" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF148" t="s" s="2">
+        <v>690</v>
+      </c>
+      <c r="AG148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH148" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI148" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ148" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK148" t="s" s="2">
+        <v>691</v>
+      </c>
+      <c r="AL148" t="s" s="2">
+        <v>692</v>
+      </c>
+      <c r="AM148" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN148" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO148" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP148" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="149" hidden="true">
+      <c r="A149" t="s" s="2">
+        <v>693</v>
+      </c>
+      <c r="B149" t="s" s="2">
+        <v>693</v>
+      </c>
+      <c r="C149" s="2"/>
+      <c r="D149" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E149" s="2"/>
+      <c r="F149" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G149" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H149" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I149" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J149" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K149" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="L149" t="s" s="2">
+        <v>694</v>
+      </c>
+      <c r="M149" t="s" s="2">
+        <v>695</v>
+      </c>
+      <c r="N149" t="s" s="2">
+        <v>696</v>
+      </c>
+      <c r="O149" t="s" s="2">
+        <v>697</v>
+      </c>
+      <c r="P149" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q149" s="2"/>
+      <c r="R149" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S149" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T149" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U149" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V149" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W149" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X149" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y149" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z149" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA149" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB149" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC149" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD149" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE149" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF149" t="s" s="2">
+        <v>698</v>
+      </c>
+      <c r="AG149" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH149" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI149" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ149" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK149" t="s" s="2">
+        <v>699</v>
+      </c>
+      <c r="AL149" t="s" s="2">
+        <v>700</v>
+      </c>
+      <c r="AM149" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN149" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO149" t="s" s="2">
+        <v>701</v>
+      </c>
+      <c r="AP149" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="150" hidden="true">
+      <c r="A150" t="s" s="2">
+        <v>702</v>
+      </c>
+      <c r="B150" t="s" s="2">
+        <v>702</v>
+      </c>
+      <c r="C150" s="2"/>
+      <c r="D150" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E150" s="2"/>
+      <c r="F150" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G150" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H150" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I150" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J150" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K150" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="L150" t="s" s="2">
+        <v>703</v>
+      </c>
+      <c r="M150" t="s" s="2">
+        <v>704</v>
+      </c>
+      <c r="N150" s="2"/>
+      <c r="O150" t="s" s="2">
+        <v>705</v>
+      </c>
+      <c r="P150" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q150" s="2"/>
+      <c r="R150" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S150" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T150" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U150" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V150" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W150" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X150" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y150" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z150" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA150" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB150" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC150" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD150" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE150" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF150" t="s" s="2">
+        <v>702</v>
+      </c>
+      <c r="AG150" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH150" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI150" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ150" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK150" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL150" t="s" s="2">
+        <v>706</v>
+      </c>
+      <c r="AM150" t="s" s="2">
+        <v>707</v>
+      </c>
+      <c r="AN150" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO150" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP150" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="151" hidden="true">
+      <c r="A151" t="s" s="2">
+        <v>708</v>
+      </c>
+      <c r="B151" t="s" s="2">
+        <v>708</v>
+      </c>
+      <c r="C151" s="2"/>
+      <c r="D151" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E151" s="2"/>
+      <c r="F151" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G151" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H151" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I151" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J151" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K151" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="L151" t="s" s="2">
+        <v>709</v>
+      </c>
+      <c r="M151" t="s" s="2">
+        <v>710</v>
+      </c>
+      <c r="N151" s="2"/>
+      <c r="O151" s="2"/>
+      <c r="P151" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q151" s="2"/>
+      <c r="R151" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S151" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T151" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U151" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V151" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W151" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X151" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y151" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z151" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA151" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB151" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC151" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD151" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE151" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF151" t="s" s="2">
+        <v>708</v>
+      </c>
+      <c r="AG151" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH151" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI151" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ151" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK151" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL151" t="s" s="2">
+        <v>711</v>
+      </c>
+      <c r="AM151" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN151" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO151" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP151" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="152" hidden="true">
+      <c r="A152" t="s" s="2">
+        <v>712</v>
+      </c>
+      <c r="B152" t="s" s="2">
+        <v>712</v>
+      </c>
+      <c r="C152" s="2"/>
+      <c r="D152" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E152" s="2"/>
+      <c r="F152" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G152" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H152" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I152" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J152" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K152" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="L152" t="s" s="2">
+        <v>713</v>
+      </c>
+      <c r="M152" t="s" s="2">
+        <v>714</v>
+      </c>
+      <c r="N152" t="s" s="2">
+        <v>715</v>
+      </c>
+      <c r="O152" t="s" s="2">
+        <v>716</v>
+      </c>
+      <c r="P152" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q152" s="2"/>
+      <c r="R152" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S152" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T152" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U152" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V152" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W152" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X152" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="Y152" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="Z152" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AA152" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB152" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC152" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD152" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE152" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF152" t="s" s="2">
+        <v>712</v>
+      </c>
+      <c r="AG152" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH152" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI152" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ152" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK152" t="s" s="2">
+        <v>717</v>
+      </c>
+      <c r="AL152" t="s" s="2">
+        <v>718</v>
+      </c>
+      <c r="AM152" t="s" s="2">
+        <v>719</v>
+      </c>
+      <c r="AN152" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO152" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP152" t="s" s="2">
         <v>80</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP136">
+  <autoFilter ref="A1:AP152">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -18779,7 +20828,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI135">
+  <conditionalFormatting sqref="A2:AI151">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-29T21:08:10+00:00</t>
+    <t>2023-12-12T19:04:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.0</t>
+    <t>0.9.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-12T19:04:11+00:00</t>
+    <t>2023-12-21T07:51:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -808,7 +808,7 @@
     <t>./low</t>
   </si>
   <si>
-    <t>380: source value from NEW PERSON - EFFECTIVE DATE/TIME (#200-42) case For NPI only</t>
+    <t>380: source value from NEW PERSON - EFFECTIVE DATE/TIME (#200-42)</t>
   </si>
   <si>
     <t>Practitioner.identifier:NPI.period.end</t>
@@ -968,7 +968,7 @@
     <t>./formatted</t>
   </si>
   <si>
-    <t>382: source value from NEW PERSON - NAME COMPONENTS &gt; NAME COMPONENTS - (#200-10.1 &gt; 20-)</t>
+    <t>382: source value from NEW PERSON - NAME COMPONENTS &gt; NAME COMPONENTS - (#200-10.1 &gt; 20 -)</t>
   </si>
   <si>
     <t>Practitioner.name.family</t>
@@ -1723,7 +1723,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-27:1531: fixed value = unknown if NEW PERSON - STATE (#200-.115) case NULL {null}</t>
+inv-28:1531: fixed value = unknown if NEW PERSON - STATE (#200-.115) case NULL {null}</t>
   </si>
   <si>
     <t>1531: fixed value = unknown if NEW PERSON - STATE (#200-.115) case NULL</t>
@@ -1838,7 +1838,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-28:1533: fixed value = unknown if NEW PERSON - STATE (#200-.1215) case NULL {null}</t>
+inv-29:1533: fixed value = unknown if NEW PERSON - STATE (#200-.1215) case NULL {null}</t>
   </si>
   <si>
     <t>1533: fixed value = unknown if NEW PERSON - STATE (#200-.1215) case NULL</t>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.0</t>
+    <t>0.10.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-21T07:51:53+00:00</t>
+    <t>2023-12-21T16:22:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.10.0</t>
+    <t>0.11.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-21T16:22:28+00:00</t>
+    <t>2023-12-28T09:08:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.11.0</t>
+    <t>0.12.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-28T09:08:39+00:00</t>
+    <t>2023-12-29T17:54:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.12.0</t>
+    <t>0.13.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-29T17:54:36+00:00</t>
+    <t>2024-01-03T19:41:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA NEW PERSON (file 200) to FHIR Practitioner</t>
+    <t>This StructureDefinition contains the maps for VistA file NEW PERSON (#200) to us-core-practitioner</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -1723,10 +1723,10 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-28:1531: fixed value = unknown if NEW PERSON - STATE (#200-.115) case NULL {null}</t>
-  </si>
-  <si>
-    <t>1531: fixed value = unknown if NEW PERSON - STATE (#200-.115) case NULL</t>
+inv-28:1531: fixed value = unknown when NEW PERSON - STATE (#200-.115) case NULL {null}</t>
+  </si>
+  <si>
+    <t>1531: fixed value = unknown when NEW PERSON - STATE (#200-.115) case NULL</t>
   </si>
   <si>
     <t>Practitioner.address:home.country.value</t>
@@ -1838,10 +1838,10 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-29:1533: fixed value = unknown if NEW PERSON - STATE (#200-.1215) case NULL {null}</t>
-  </si>
-  <si>
-    <t>1533: fixed value = unknown if NEW PERSON - STATE (#200-.1215) case NULL</t>
+inv-29:1533: fixed value = unknown when NEW PERSON - STATE (#200-.1215) case NULL {null}</t>
+  </si>
+  <si>
+    <t>1533: fixed value = unknown when NEW PERSON - STATE (#200-.1215) case NULL</t>
   </si>
   <si>
     <t>Practitioner.address:temp.country.value</t>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$152</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$126</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5798" uniqueCount="720">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4812" uniqueCount="690">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.13.0</t>
+    <t>0.14.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-03T19:41:50+00:00</t>
+    <t>2024-01-13T13:47:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1722,10 +1722,6 @@
     <t>Extension.value[x]</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-28:1531: fixed value = unknown when NEW PERSON - STATE (#200-.115) case NULL {null}</t>
-  </si>
-  <si>
     <t>1531: fixed value = unknown when NEW PERSON - STATE (#200-.115) case NULL</t>
   </si>
   <si>
@@ -1837,10 +1833,6 @@
     <t>Practitioner.address:temp.country.extension:data-absent-reason.value[x]</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-29:1533: fixed value = unknown when NEW PERSON - STATE (#200-.1215) case NULL {null}</t>
-  </si>
-  <si>
     <t>1533: fixed value = unknown when NEW PERSON - STATE (#200-.1215) case NULL</t>
   </si>
   <si>
@@ -1884,90 +1876,6 @@
   </si>
   <si>
     <t>SStaff.SStaff.TemporaryAddressEndDate</t>
-  </si>
-  <si>
-    <t>Practitioner.address:physical</t>
-  </si>
-  <si>
-    <t>physical</t>
-  </si>
-  <si>
-    <t>Practitioner.address:physical.id</t>
-  </si>
-  <si>
-    <t>Practitioner.address:physical.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.address:physical.use</t>
-  </si>
-  <si>
-    <t>Practitioner.address:physical.type</t>
-  </si>
-  <si>
-    <t>Practitioner.address:physical.text</t>
-  </si>
-  <si>
-    <t>Practitioner.address:physical.line</t>
-  </si>
-  <si>
-    <t>Practitioner.address:physical.city</t>
-  </si>
-  <si>
-    <t>Practitioner.address:physical.district</t>
-  </si>
-  <si>
-    <t>Practitioner.address:physical.state</t>
-  </si>
-  <si>
-    <t>Practitioner.address:physical.postalCode</t>
-  </si>
-  <si>
-    <t>Practitioner.address:physical.country</t>
-  </si>
-  <si>
-    <t>Practitioner.address:physical.period</t>
-  </si>
-  <si>
-    <t>Practitioner.address:postal</t>
-  </si>
-  <si>
-    <t>postal</t>
-  </si>
-  <si>
-    <t>Practitioner.address:postal.id</t>
-  </si>
-  <si>
-    <t>Practitioner.address:postal.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.address:postal.use</t>
-  </si>
-  <si>
-    <t>Practitioner.address:postal.type</t>
-  </si>
-  <si>
-    <t>Practitioner.address:postal.text</t>
-  </si>
-  <si>
-    <t>Practitioner.address:postal.line</t>
-  </si>
-  <si>
-    <t>Practitioner.address:postal.city</t>
-  </si>
-  <si>
-    <t>Practitioner.address:postal.district</t>
-  </si>
-  <si>
-    <t>Practitioner.address:postal.state</t>
-  </si>
-  <si>
-    <t>Practitioner.address:postal.postalCode</t>
-  </si>
-  <si>
-    <t>Practitioner.address:postal.country</t>
-  </si>
-  <si>
-    <t>Practitioner.address:postal.period</t>
   </si>
   <si>
     <t>Practitioner.gender</t>
@@ -2561,7 +2469,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP152"/>
+  <dimension ref="A1:AP126"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="70.5625" customWidth="true" bestFit="true"/>
@@ -6118,7 +6026,7 @@
         <v>89</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>80</v>
@@ -7086,7 +6994,7 @@
         <v>89</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>80</v>
@@ -12464,7 +12372,7 @@
         <v>89</v>
       </c>
       <c r="H83" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="I83" t="s" s="2">
         <v>80</v>
@@ -12542,7 +12450,7 @@
         <v>80</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>548</v>
+        <v>101</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>80</v>
@@ -12557,7 +12465,7 @@
         <v>80</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="AP83" t="s" s="2">
         <v>508</v>
@@ -12565,10 +12473,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="B84" t="s" s="2">
         <v>550</v>
-      </c>
-      <c r="B84" t="s" s="2">
-        <v>551</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12594,10 +12502,10 @@
         <v>159</v>
       </c>
       <c r="L84" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="M84" t="s" s="2">
         <v>552</v>
-      </c>
-      <c r="M84" t="s" s="2">
-        <v>553</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -12621,34 +12529,34 @@
         <v>80</v>
       </c>
       <c r="W84" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="X84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF84" t="s" s="2">
         <v>554</v>
-      </c>
-      <c r="X84" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y84" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z84" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA84" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB84" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC84" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD84" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE84" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF84" t="s" s="2">
-        <v>555</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>78</v>
@@ -12683,7 +12591,7 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B85" t="s" s="2">
         <v>486</v>
@@ -12803,13 +12711,13 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B86" t="s" s="2">
         <v>394</v>
       </c>
       <c r="C86" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="D86" t="s" s="2">
         <v>80</v>
@@ -12927,7 +12835,7 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B87" t="s" s="2">
         <v>403</v>
@@ -13045,7 +12953,7 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B88" t="s" s="2">
         <v>404</v>
@@ -13165,7 +13073,7 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B89" t="s" s="2">
         <v>405</v>
@@ -13287,7 +13195,7 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B90" t="s" s="2">
         <v>416</v>
@@ -13407,7 +13315,7 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B91" t="s" s="2">
         <v>425</v>
@@ -13529,7 +13437,7 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B92" t="s" s="2">
         <v>432</v>
@@ -13639,15 +13547,15 @@
         <v>80</v>
       </c>
       <c r="AO92" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="AP92" t="s" s="2">
         <v>565</v>
-      </c>
-      <c r="AP92" t="s" s="2">
-        <v>566</v>
       </c>
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B93" t="s" s="2">
         <v>441</v>
@@ -13757,15 +13665,15 @@
         <v>80</v>
       </c>
       <c r="AO93" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="AP93" t="s" s="2">
         <v>568</v>
-      </c>
-      <c r="AP93" t="s" s="2">
-        <v>569</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="B94" t="s" s="2">
         <v>450</v>
@@ -13885,7 +13793,7 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B95" t="s" s="2">
         <v>459</v>
@@ -13995,15 +13903,15 @@
         <v>80</v>
       </c>
       <c r="AO95" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="AP95" t="s" s="2">
         <v>572</v>
-      </c>
-      <c r="AP95" t="s" s="2">
-        <v>573</v>
       </c>
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B96" t="s" s="2">
         <v>469</v>
@@ -14113,15 +14021,15 @@
         <v>80</v>
       </c>
       <c r="AO96" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="AP96" t="s" s="2">
         <v>575</v>
-      </c>
-      <c r="AP96" t="s" s="2">
-        <v>576</v>
       </c>
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B97" t="s" s="2">
         <v>478</v>
@@ -14231,15 +14139,15 @@
         <v>80</v>
       </c>
       <c r="AO97" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="AP97" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B98" t="s" s="2">
         <v>516</v>
@@ -14357,7 +14265,7 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B99" t="s" s="2">
         <v>520</v>
@@ -14473,7 +14381,7 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B100" t="s" s="2">
         <v>520</v>
@@ -14593,7 +14501,7 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B101" t="s" s="2">
         <v>531</v>
@@ -14711,7 +14619,7 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B102" t="s" s="2">
         <v>533</v>
@@ -14829,7 +14737,7 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B103" t="s" s="2">
         <v>535</v>
@@ -14949,7 +14857,7 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B104" t="s" s="2">
         <v>542</v>
@@ -14966,7 +14874,7 @@
         <v>89</v>
       </c>
       <c r="H104" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="I104" t="s" s="2">
         <v>80</v>
@@ -15044,7 +14952,7 @@
         <v>80</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>586</v>
+        <v>101</v>
       </c>
       <c r="AK104" t="s" s="2">
         <v>80</v>
@@ -15059,18 +14967,18 @@
         <v>80</v>
       </c>
       <c r="AO104" t="s" s="2">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="AP104" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15096,10 +15004,10 @@
         <v>159</v>
       </c>
       <c r="L105" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="M105" t="s" s="2">
         <v>552</v>
-      </c>
-      <c r="M105" t="s" s="2">
-        <v>553</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -15123,34 +15031,34 @@
         <v>80</v>
       </c>
       <c r="W105" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="X105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF105" t="s" s="2">
         <v>554</v>
-      </c>
-      <c r="X105" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y105" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z105" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA105" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB105" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC105" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD105" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE105" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF105" t="s" s="2">
-        <v>555</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>78</v>
@@ -15185,7 +15093,7 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="B106" t="s" s="2">
         <v>486</v>
@@ -15305,10 +15213,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15423,10 +15331,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15543,10 +15451,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15560,7 +15468,7 @@
         <v>89</v>
       </c>
       <c r="H109" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="I109" t="s" s="2">
         <v>80</v>
@@ -15655,18 +15563,18 @@
         <v>80</v>
       </c>
       <c r="AO109" t="s" s="2">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="AP109" t="s" s="2">
-        <v>597</v>
+        <v>595</v>
       </c>
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15680,7 +15588,7 @@
         <v>89</v>
       </c>
       <c r="H110" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="I110" t="s" s="2">
         <v>80</v>
@@ -15777,22 +15685,20 @@
         <v>80</v>
       </c>
       <c r="AO110" t="s" s="2">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="AP110" t="s" s="2">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="C111" t="s" s="2">
-        <v>603</v>
-      </c>
+        <v>600</v>
+      </c>
+      <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
         <v>80</v>
       </c>
@@ -15804,7 +15710,7 @@
         <v>89</v>
       </c>
       <c r="H111" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="I111" t="s" s="2">
         <v>80</v>
@@ -15813,19 +15719,17 @@
         <v>90</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>395</v>
+        <v>109</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>396</v>
+        <v>601</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="N111" t="s" s="2">
-        <v>398</v>
-      </c>
+        <v>602</v>
+      </c>
+      <c r="N111" s="2"/>
       <c r="O111" t="s" s="2">
-        <v>399</v>
+        <v>603</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>80</v>
@@ -15850,13 +15754,13 @@
         <v>80</v>
       </c>
       <c r="X111" t="s" s="2">
-        <v>80</v>
+        <v>174</v>
       </c>
       <c r="Y111" t="s" s="2">
-        <v>80</v>
+        <v>604</v>
       </c>
       <c r="Z111" t="s" s="2">
-        <v>80</v>
+        <v>605</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>80</v>
@@ -15874,13 +15778,13 @@
         <v>80</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>394</v>
+        <v>600</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH111" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI111" t="s" s="2">
         <v>80</v>
@@ -15889,13 +15793,13 @@
         <v>101</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>401</v>
+        <v>606</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>402</v>
+        <v>607</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>163</v>
+        <v>608</v>
       </c>
       <c r="AN111" t="s" s="2">
         <v>80</v>
@@ -15909,10 +15813,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>604</v>
+        <v>609</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>403</v>
+        <v>609</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15926,25 +15830,27 @@
         <v>89</v>
       </c>
       <c r="H112" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="I112" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J112" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>159</v>
+        <v>610</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>160</v>
+        <v>611</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>161</v>
+        <v>612</v>
       </c>
       <c r="N112" s="2"/>
-      <c r="O112" s="2"/>
+      <c r="O112" t="s" s="2">
+        <v>613</v>
+      </c>
       <c r="P112" t="s" s="2">
         <v>80</v>
       </c>
@@ -15992,7 +15898,7 @@
         <v>80</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>162</v>
+        <v>609</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>78</v>
@@ -16004,37 +15910,37 @@
         <v>80</v>
       </c>
       <c r="AJ112" t="s" s="2">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="AK112" t="s" s="2">
-        <v>80</v>
+        <v>614</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>163</v>
+        <v>615</v>
       </c>
       <c r="AM112" t="s" s="2">
-        <v>80</v>
+        <v>616</v>
       </c>
       <c r="AN112" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO112" t="s" s="2">
-        <v>80</v>
+        <v>617</v>
       </c>
       <c r="AP112" t="s" s="2">
-        <v>80</v>
+        <v>618</v>
       </c>
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>605</v>
+        <v>619</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>404</v>
+        <v>619</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
-        <v>134</v>
+        <v>80</v>
       </c>
       <c r="E113" s="2"/>
       <c r="F113" t="s" s="2">
@@ -16053,18 +15959,18 @@
         <v>80</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>135</v>
+        <v>620</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>136</v>
+        <v>621</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="N113" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O113" s="2"/>
+        <v>622</v>
+      </c>
+      <c r="N113" s="2"/>
+      <c r="O113" t="s" s="2">
+        <v>623</v>
+      </c>
       <c r="P113" t="s" s="2">
         <v>80</v>
       </c>
@@ -16100,19 +16006,19 @@
         <v>80</v>
       </c>
       <c r="AB113" t="s" s="2">
-        <v>166</v>
+        <v>80</v>
       </c>
       <c r="AC113" t="s" s="2">
-        <v>167</v>
+        <v>80</v>
       </c>
       <c r="AD113" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE113" t="s" s="2">
-        <v>153</v>
+        <v>80</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>168</v>
+        <v>619</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>78</v>
@@ -16124,16 +16030,16 @@
         <v>80</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK113" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>163</v>
+        <v>624</v>
       </c>
       <c r="AM113" t="s" s="2">
-        <v>80</v>
+        <v>625</v>
       </c>
       <c r="AN113" t="s" s="2">
         <v>80</v>
@@ -16147,10 +16053,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>606</v>
+        <v>626</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>405</v>
+        <v>626</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16161,32 +16067,28 @@
         <v>78</v>
       </c>
       <c r="G114" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H114" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I114" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="J114" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>109</v>
+        <v>627</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>406</v>
+        <v>628</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="N114" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="O114" t="s" s="2">
-        <v>409</v>
-      </c>
+        <v>629</v>
+      </c>
+      <c r="N114" s="2"/>
+      <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
         <v>80</v>
       </c>
@@ -16198,7 +16100,7 @@
         <v>80</v>
       </c>
       <c r="T114" t="s" s="2">
-        <v>410</v>
+        <v>80</v>
       </c>
       <c r="U114" t="s" s="2">
         <v>80</v>
@@ -16210,13 +16112,13 @@
         <v>80</v>
       </c>
       <c r="X114" t="s" s="2">
-        <v>174</v>
+        <v>80</v>
       </c>
       <c r="Y114" t="s" s="2">
-        <v>411</v>
+        <v>80</v>
       </c>
       <c r="Z114" t="s" s="2">
-        <v>412</v>
+        <v>80</v>
       </c>
       <c r="AA114" t="s" s="2">
         <v>80</v>
@@ -16234,13 +16136,13 @@
         <v>80</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>413</v>
+        <v>626</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH114" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI114" t="s" s="2">
         <v>80</v>
@@ -16249,13 +16151,13 @@
         <v>101</v>
       </c>
       <c r="AK114" t="s" s="2">
-        <v>414</v>
+        <v>630</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>294</v>
+        <v>631</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>415</v>
+        <v>632</v>
       </c>
       <c r="AN114" t="s" s="2">
         <v>80</v>
@@ -16269,10 +16171,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>607</v>
+        <v>633</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>416</v>
+        <v>633</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16292,20 +16194,18 @@
         <v>80</v>
       </c>
       <c r="J115" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>109</v>
+        <v>159</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>417</v>
+        <v>160</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="N115" t="s" s="2">
-        <v>419</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="N115" s="2"/>
       <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
         <v>80</v>
@@ -16318,7 +16218,7 @@
         <v>80</v>
       </c>
       <c r="T115" t="s" s="2">
-        <v>420</v>
+        <v>80</v>
       </c>
       <c r="U115" t="s" s="2">
         <v>80</v>
@@ -16330,13 +16230,13 @@
         <v>80</v>
       </c>
       <c r="X115" t="s" s="2">
-        <v>174</v>
+        <v>80</v>
       </c>
       <c r="Y115" t="s" s="2">
-        <v>421</v>
+        <v>80</v>
       </c>
       <c r="Z115" t="s" s="2">
-        <v>422</v>
+        <v>80</v>
       </c>
       <c r="AA115" t="s" s="2">
         <v>80</v>
@@ -16354,7 +16254,7 @@
         <v>80</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>423</v>
+        <v>162</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>78</v>
@@ -16366,13 +16266,13 @@
         <v>80</v>
       </c>
       <c r="AJ115" t="s" s="2">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="AK115" t="s" s="2">
-        <v>424</v>
+        <v>80</v>
       </c>
       <c r="AL115" t="s" s="2">
-        <v>294</v>
+        <v>163</v>
       </c>
       <c r="AM115" t="s" s="2">
         <v>80</v>
@@ -16389,21 +16289,21 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>608</v>
+        <v>634</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>425</v>
+        <v>634</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
-        <v>80</v>
+        <v>134</v>
       </c>
       <c r="E116" s="2"/>
       <c r="F116" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G116" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H116" t="s" s="2">
         <v>80</v>
@@ -16412,23 +16312,21 @@
         <v>80</v>
       </c>
       <c r="J116" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>159</v>
+        <v>135</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>426</v>
+        <v>136</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>427</v>
+        <v>165</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="O116" t="s" s="2">
-        <v>300</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="O116" s="2"/>
       <c r="P116" t="s" s="2">
         <v>80</v>
       </c>
@@ -16440,7 +16338,7 @@
         <v>80</v>
       </c>
       <c r="T116" t="s" s="2">
-        <v>429</v>
+        <v>80</v>
       </c>
       <c r="U116" t="s" s="2">
         <v>80</v>
@@ -16476,25 +16374,25 @@
         <v>80</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>430</v>
+        <v>168</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH116" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI116" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ116" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK116" t="s" s="2">
-        <v>431</v>
+        <v>80</v>
       </c>
       <c r="AL116" t="s" s="2">
-        <v>303</v>
+        <v>163</v>
       </c>
       <c r="AM116" t="s" s="2">
         <v>80</v>
@@ -16511,42 +16409,46 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>609</v>
+        <v>635</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>432</v>
+        <v>635</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
-        <v>80</v>
+        <v>636</v>
       </c>
       <c r="E117" s="2"/>
       <c r="F117" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G117" t="s" s="2">
-        <v>433</v>
+        <v>79</v>
       </c>
       <c r="H117" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I117" t="s" s="2">
         <v>90</v>
-      </c>
-      <c r="I117" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="J117" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>159</v>
+        <v>135</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>434</v>
+        <v>637</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="N117" s="2"/>
-      <c r="O117" s="2"/>
+        <v>638</v>
+      </c>
+      <c r="N117" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="O117" t="s" s="2">
+        <v>144</v>
+      </c>
       <c r="P117" t="s" s="2">
         <v>80</v>
       </c>
@@ -16558,7 +16460,7 @@
         <v>80</v>
       </c>
       <c r="T117" t="s" s="2">
-        <v>436</v>
+        <v>80</v>
       </c>
       <c r="U117" t="s" s="2">
         <v>80</v>
@@ -16594,7 +16496,7 @@
         <v>80</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>437</v>
+        <v>639</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>78</v>
@@ -16606,16 +16508,16 @@
         <v>80</v>
       </c>
       <c r="AJ117" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK117" t="s" s="2">
-        <v>438</v>
+        <v>80</v>
       </c>
       <c r="AL117" t="s" s="2">
-        <v>439</v>
+        <v>132</v>
       </c>
       <c r="AM117" t="s" s="2">
-        <v>440</v>
+        <v>80</v>
       </c>
       <c r="AN117" t="s" s="2">
         <v>80</v>
@@ -16629,42 +16531,44 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>610</v>
+        <v>640</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>441</v>
+        <v>640</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
-        <v>442</v>
+        <v>80</v>
       </c>
       <c r="E118" s="2"/>
       <c r="F118" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G118" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H118" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="I118" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J118" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>443</v>
+        <v>641</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>444</v>
+        <v>642</v>
       </c>
       <c r="N118" s="2"/>
-      <c r="O118" s="2"/>
+      <c r="O118" t="s" s="2">
+        <v>643</v>
+      </c>
       <c r="P118" t="s" s="2">
         <v>80</v>
       </c>
@@ -16676,7 +16580,7 @@
         <v>80</v>
       </c>
       <c r="T118" t="s" s="2">
-        <v>445</v>
+        <v>80</v>
       </c>
       <c r="U118" t="s" s="2">
         <v>80</v>
@@ -16712,13 +16616,13 @@
         <v>80</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>446</v>
+        <v>640</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH118" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI118" t="s" s="2">
         <v>80</v>
@@ -16727,13 +16631,13 @@
         <v>101</v>
       </c>
       <c r="AK118" t="s" s="2">
-        <v>447</v>
+        <v>80</v>
       </c>
       <c r="AL118" t="s" s="2">
-        <v>448</v>
+        <v>644</v>
       </c>
       <c r="AM118" t="s" s="2">
-        <v>449</v>
+        <v>80</v>
       </c>
       <c r="AN118" t="s" s="2">
         <v>80</v>
@@ -16747,18 +16651,18 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>611</v>
+        <v>645</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>450</v>
+        <v>645</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
-        <v>451</v>
+        <v>80</v>
       </c>
       <c r="E119" s="2"/>
       <c r="F119" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G119" t="s" s="2">
         <v>89</v>
@@ -16770,20 +16674,18 @@
         <v>80</v>
       </c>
       <c r="J119" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>159</v>
+        <v>180</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>452</v>
+        <v>646</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="N119" t="s" s="2">
-        <v>454</v>
-      </c>
+        <v>647</v>
+      </c>
+      <c r="N119" s="2"/>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
         <v>80</v>
@@ -16796,7 +16698,7 @@
         <v>80</v>
       </c>
       <c r="T119" t="s" s="2">
-        <v>455</v>
+        <v>80</v>
       </c>
       <c r="U119" t="s" s="2">
         <v>80</v>
@@ -16808,13 +16710,13 @@
         <v>80</v>
       </c>
       <c r="X119" t="s" s="2">
-        <v>80</v>
+        <v>648</v>
       </c>
       <c r="Y119" t="s" s="2">
-        <v>80</v>
+        <v>649</v>
       </c>
       <c r="Z119" t="s" s="2">
-        <v>80</v>
+        <v>650</v>
       </c>
       <c r="AA119" t="s" s="2">
         <v>80</v>
@@ -16832,10 +16734,10 @@
         <v>80</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>456</v>
+        <v>645</v>
       </c>
       <c r="AG119" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AH119" t="s" s="2">
         <v>89</v>
@@ -16847,13 +16749,13 @@
         <v>101</v>
       </c>
       <c r="AK119" t="s" s="2">
-        <v>457</v>
+        <v>80</v>
       </c>
       <c r="AL119" t="s" s="2">
-        <v>458</v>
+        <v>631</v>
       </c>
       <c r="AM119" t="s" s="2">
-        <v>80</v>
+        <v>651</v>
       </c>
       <c r="AN119" t="s" s="2">
         <v>80</v>
@@ -16867,14 +16769,14 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>612</v>
+        <v>652</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>459</v>
+        <v>652</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
-        <v>460</v>
+        <v>80</v>
       </c>
       <c r="E120" s="2"/>
       <c r="F120" t="s" s="2">
@@ -16884,22 +16786,22 @@
         <v>89</v>
       </c>
       <c r="H120" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="I120" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J120" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K120" t="s" s="2">
         <v>159</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>461</v>
+        <v>160</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>462</v>
+        <v>161</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" s="2"/>
@@ -16926,13 +16828,13 @@
         <v>80</v>
       </c>
       <c r="X120" t="s" s="2">
-        <v>185</v>
+        <v>80</v>
       </c>
       <c r="Y120" t="s" s="2">
-        <v>463</v>
+        <v>80</v>
       </c>
       <c r="Z120" t="s" s="2">
-        <v>464</v>
+        <v>80</v>
       </c>
       <c r="AA120" t="s" s="2">
         <v>80</v>
@@ -16950,7 +16852,7 @@
         <v>80</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>465</v>
+        <v>162</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>78</v>
@@ -16962,16 +16864,16 @@
         <v>80</v>
       </c>
       <c r="AJ120" t="s" s="2">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="AK120" t="s" s="2">
-        <v>466</v>
+        <v>80</v>
       </c>
       <c r="AL120" t="s" s="2">
-        <v>467</v>
+        <v>163</v>
       </c>
       <c r="AM120" t="s" s="2">
-        <v>468</v>
+        <v>80</v>
       </c>
       <c r="AN120" t="s" s="2">
         <v>80</v>
@@ -16985,41 +16887,43 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>613</v>
+        <v>653</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>469</v>
+        <v>653</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
-        <v>470</v>
+        <v>134</v>
       </c>
       <c r="E121" s="2"/>
       <c r="F121" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G121" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H121" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="I121" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J121" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>159</v>
+        <v>135</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>471</v>
+        <v>136</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="N121" s="2"/>
+        <v>165</v>
+      </c>
+      <c r="N121" t="s" s="2">
+        <v>138</v>
+      </c>
       <c r="O121" s="2"/>
       <c r="P121" t="s" s="2">
         <v>80</v>
@@ -17032,7 +16936,7 @@
         <v>80</v>
       </c>
       <c r="T121" t="s" s="2">
-        <v>473</v>
+        <v>80</v>
       </c>
       <c r="U121" t="s" s="2">
         <v>80</v>
@@ -17056,40 +16960,40 @@
         <v>80</v>
       </c>
       <c r="AB121" t="s" s="2">
-        <v>80</v>
+        <v>166</v>
       </c>
       <c r="AC121" t="s" s="2">
-        <v>80</v>
+        <v>167</v>
       </c>
       <c r="AD121" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE121" t="s" s="2">
-        <v>80</v>
+        <v>153</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>474</v>
+        <v>168</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH121" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI121" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ121" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK121" t="s" s="2">
-        <v>475</v>
+        <v>80</v>
       </c>
       <c r="AL121" t="s" s="2">
-        <v>476</v>
+        <v>163</v>
       </c>
       <c r="AM121" t="s" s="2">
-        <v>477</v>
+        <v>80</v>
       </c>
       <c r="AN121" t="s" s="2">
         <v>80</v>
@@ -17103,10 +17007,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>614</v>
+        <v>654</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>478</v>
+        <v>654</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -17117,10 +17021,10 @@
         <v>78</v>
       </c>
       <c r="G122" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H122" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="I122" t="s" s="2">
         <v>80</v>
@@ -17129,18 +17033,20 @@
         <v>90</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>159</v>
+        <v>655</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>479</v>
+        <v>656</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>480</v>
+        <v>657</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="O122" s="2"/>
+        <v>658</v>
+      </c>
+      <c r="O122" t="s" s="2">
+        <v>659</v>
+      </c>
       <c r="P122" t="s" s="2">
         <v>80</v>
       </c>
@@ -17188,13 +17094,13 @@
         <v>80</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>482</v>
+        <v>660</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH122" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI122" t="s" s="2">
         <v>80</v>
@@ -17203,13 +17109,13 @@
         <v>101</v>
       </c>
       <c r="AK122" t="s" s="2">
-        <v>483</v>
+        <v>661</v>
       </c>
       <c r="AL122" t="s" s="2">
-        <v>484</v>
+        <v>662</v>
       </c>
       <c r="AM122" t="s" s="2">
-        <v>485</v>
+        <v>80</v>
       </c>
       <c r="AN122" t="s" s="2">
         <v>80</v>
@@ -17223,10 +17129,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>615</v>
+        <v>663</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>486</v>
+        <v>663</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -17240,7 +17146,7 @@
         <v>89</v>
       </c>
       <c r="H123" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="I123" t="s" s="2">
         <v>80</v>
@@ -17249,17 +17155,19 @@
         <v>90</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>212</v>
+        <v>159</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>487</v>
+        <v>664</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="N123" s="2"/>
+        <v>665</v>
+      </c>
+      <c r="N123" t="s" s="2">
+        <v>666</v>
+      </c>
       <c r="O123" t="s" s="2">
-        <v>489</v>
+        <v>667</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>80</v>
@@ -17272,7 +17180,7 @@
         <v>80</v>
       </c>
       <c r="T123" t="s" s="2">
-        <v>490</v>
+        <v>80</v>
       </c>
       <c r="U123" t="s" s="2">
         <v>80</v>
@@ -17308,7 +17216,7 @@
         <v>80</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>491</v>
+        <v>668</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>78</v>
@@ -17323,19 +17231,19 @@
         <v>101</v>
       </c>
       <c r="AK123" t="s" s="2">
-        <v>492</v>
+        <v>669</v>
       </c>
       <c r="AL123" t="s" s="2">
-        <v>342</v>
+        <v>670</v>
       </c>
       <c r="AM123" t="s" s="2">
-        <v>218</v>
+        <v>80</v>
       </c>
       <c r="AN123" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO123" t="s" s="2">
-        <v>80</v>
+        <v>671</v>
       </c>
       <c r="AP123" t="s" s="2">
         <v>80</v>
@@ -17343,14 +17251,12 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>616</v>
+        <v>672</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="C124" t="s" s="2">
-        <v>617</v>
-      </c>
+        <v>672</v>
+      </c>
+      <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
         <v>80</v>
       </c>
@@ -17362,28 +17268,26 @@
         <v>89</v>
       </c>
       <c r="H124" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="I124" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J124" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>395</v>
+        <v>212</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>396</v>
+        <v>673</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="N124" t="s" s="2">
-        <v>398</v>
-      </c>
+        <v>674</v>
+      </c>
+      <c r="N124" s="2"/>
       <c r="O124" t="s" s="2">
-        <v>399</v>
+        <v>675</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>80</v>
@@ -17432,13 +17336,13 @@
         <v>80</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>394</v>
+        <v>672</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH124" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI124" t="s" s="2">
         <v>80</v>
@@ -17447,13 +17351,13 @@
         <v>101</v>
       </c>
       <c r="AK124" t="s" s="2">
-        <v>401</v>
+        <v>80</v>
       </c>
       <c r="AL124" t="s" s="2">
-        <v>402</v>
+        <v>676</v>
       </c>
       <c r="AM124" t="s" s="2">
-        <v>163</v>
+        <v>677</v>
       </c>
       <c r="AN124" t="s" s="2">
         <v>80</v>
@@ -17467,10 +17371,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>618</v>
+        <v>678</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>403</v>
+        <v>678</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17493,13 +17397,13 @@
         <v>80</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>159</v>
+        <v>220</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>160</v>
+        <v>679</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>161</v>
+        <v>680</v>
       </c>
       <c r="N125" s="2"/>
       <c r="O125" s="2"/>
@@ -17550,7 +17454,7 @@
         <v>80</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>162</v>
+        <v>678</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>78</v>
@@ -17562,13 +17466,13 @@
         <v>80</v>
       </c>
       <c r="AJ125" t="s" s="2">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="AK125" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL125" t="s" s="2">
-        <v>163</v>
+        <v>681</v>
       </c>
       <c r="AM125" t="s" s="2">
         <v>80</v>
@@ -17585,14 +17489,14 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>619</v>
+        <v>682</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>404</v>
+        <v>682</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
-        <v>134</v>
+        <v>80</v>
       </c>
       <c r="E126" s="2"/>
       <c r="F126" t="s" s="2">
@@ -17611,18 +17515,20 @@
         <v>80</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>136</v>
+        <v>683</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>165</v>
+        <v>684</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O126" s="2"/>
+        <v>685</v>
+      </c>
+      <c r="O126" t="s" s="2">
+        <v>686</v>
+      </c>
       <c r="P126" t="s" s="2">
         <v>80</v>
       </c>
@@ -17646,31 +17552,31 @@
         <v>80</v>
       </c>
       <c r="X126" t="s" s="2">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="Y126" t="s" s="2">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="Z126" t="s" s="2">
-        <v>80</v>
+        <v>115</v>
       </c>
       <c r="AA126" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AB126" t="s" s="2">
-        <v>166</v>
+        <v>80</v>
       </c>
       <c r="AC126" t="s" s="2">
-        <v>167</v>
+        <v>80</v>
       </c>
       <c r="AD126" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE126" t="s" s="2">
-        <v>153</v>
+        <v>80</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>168</v>
+        <v>682</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>78</v>
@@ -17682,16 +17588,16 @@
         <v>80</v>
       </c>
       <c r="AJ126" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK126" t="s" s="2">
-        <v>80</v>
+        <v>687</v>
       </c>
       <c r="AL126" t="s" s="2">
-        <v>163</v>
+        <v>688</v>
       </c>
       <c r="AM126" t="s" s="2">
-        <v>80</v>
+        <v>689</v>
       </c>
       <c r="AN126" t="s" s="2">
         <v>80</v>
@@ -17700,3125 +17606,11 @@
         <v>80</v>
       </c>
       <c r="AP126" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="127" hidden="true">
-      <c r="A127" t="s" s="2">
-        <v>620</v>
-      </c>
-      <c r="B127" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="C127" s="2"/>
-      <c r="D127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E127" s="2"/>
-      <c r="F127" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G127" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I127" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="J127" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K127" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="L127" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="M127" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="N127" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="O127" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="P127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q127" s="2"/>
-      <c r="R127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T127" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="U127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X127" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="Y127" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="Z127" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="AA127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF127" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="AG127" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH127" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ127" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK127" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="AL127" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="AM127" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="AN127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP127" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="128" hidden="true">
-      <c r="A128" t="s" s="2">
-        <v>621</v>
-      </c>
-      <c r="B128" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="C128" s="2"/>
-      <c r="D128" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E128" s="2"/>
-      <c r="F128" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G128" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H128" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I128" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J128" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K128" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="L128" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="M128" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="N128" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="O128" s="2"/>
-      <c r="P128" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q128" s="2"/>
-      <c r="R128" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S128" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T128" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="U128" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V128" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W128" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X128" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="Y128" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="Z128" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="AA128" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB128" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC128" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD128" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE128" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF128" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="AG128" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH128" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI128" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ128" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK128" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="AL128" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="AM128" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN128" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO128" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP128" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="129" hidden="true">
-      <c r="A129" t="s" s="2">
-        <v>622</v>
-      </c>
-      <c r="B129" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="C129" s="2"/>
-      <c r="D129" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E129" s="2"/>
-      <c r="F129" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G129" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H129" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I129" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J129" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K129" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="L129" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="M129" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="N129" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="O129" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="P129" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q129" s="2"/>
-      <c r="R129" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S129" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T129" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="U129" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V129" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W129" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X129" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y129" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z129" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA129" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB129" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC129" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD129" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE129" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF129" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="AG129" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH129" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI129" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ129" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK129" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="AL129" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="AM129" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN129" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO129" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP129" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="130" hidden="true">
-      <c r="A130" t="s" s="2">
-        <v>623</v>
-      </c>
-      <c r="B130" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="C130" s="2"/>
-      <c r="D130" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E130" s="2"/>
-      <c r="F130" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G130" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="H130" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="I130" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J130" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K130" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="L130" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="M130" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="N130" s="2"/>
-      <c r="O130" s="2"/>
-      <c r="P130" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q130" s="2"/>
-      <c r="R130" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S130" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T130" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="U130" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V130" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W130" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X130" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y130" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z130" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA130" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB130" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC130" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD130" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE130" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF130" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="AG130" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH130" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI130" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ130" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK130" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="AL130" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="AM130" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="AN130" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO130" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP130" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="131" hidden="true">
-      <c r="A131" t="s" s="2">
-        <v>624</v>
-      </c>
-      <c r="B131" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="C131" s="2"/>
-      <c r="D131" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="E131" s="2"/>
-      <c r="F131" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G131" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H131" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="I131" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J131" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K131" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="L131" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="M131" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="N131" s="2"/>
-      <c r="O131" s="2"/>
-      <c r="P131" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q131" s="2"/>
-      <c r="R131" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S131" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T131" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="U131" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V131" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W131" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X131" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y131" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z131" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA131" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB131" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC131" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD131" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE131" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF131" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="AG131" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH131" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI131" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ131" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK131" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="AL131" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="AM131" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="AN131" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO131" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP131" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="132" hidden="true">
-      <c r="A132" t="s" s="2">
-        <v>625</v>
-      </c>
-      <c r="B132" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="C132" s="2"/>
-      <c r="D132" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="E132" s="2"/>
-      <c r="F132" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G132" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H132" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I132" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J132" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K132" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="L132" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="M132" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="N132" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="O132" s="2"/>
-      <c r="P132" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q132" s="2"/>
-      <c r="R132" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S132" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T132" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="U132" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V132" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W132" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X132" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y132" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z132" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA132" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB132" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC132" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD132" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE132" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF132" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="AG132" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH132" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI132" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ132" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK132" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="AL132" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="AM132" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN132" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO132" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP132" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="133" hidden="true">
-      <c r="A133" t="s" s="2">
-        <v>626</v>
-      </c>
-      <c r="B133" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="C133" s="2"/>
-      <c r="D133" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="E133" s="2"/>
-      <c r="F133" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G133" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H133" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="I133" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J133" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K133" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="L133" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="M133" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="N133" s="2"/>
-      <c r="O133" s="2"/>
-      <c r="P133" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q133" s="2"/>
-      <c r="R133" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S133" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T133" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U133" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V133" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W133" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X133" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="Y133" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="Z133" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="AA133" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB133" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC133" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD133" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE133" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF133" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="AG133" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH133" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI133" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ133" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK133" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="AL133" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="AM133" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="AN133" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO133" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP133" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="134" hidden="true">
-      <c r="A134" t="s" s="2">
-        <v>627</v>
-      </c>
-      <c r="B134" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="C134" s="2"/>
-      <c r="D134" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="E134" s="2"/>
-      <c r="F134" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G134" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H134" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="I134" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J134" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K134" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="L134" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="M134" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="N134" s="2"/>
-      <c r="O134" s="2"/>
-      <c r="P134" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q134" s="2"/>
-      <c r="R134" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S134" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T134" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="U134" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V134" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W134" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X134" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y134" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z134" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA134" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB134" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC134" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD134" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE134" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF134" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="AG134" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH134" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI134" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ134" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK134" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="AL134" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="AM134" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="AN134" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO134" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP134" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="135" hidden="true">
-      <c r="A135" t="s" s="2">
-        <v>628</v>
-      </c>
-      <c r="B135" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="C135" s="2"/>
-      <c r="D135" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E135" s="2"/>
-      <c r="F135" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G135" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H135" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="I135" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J135" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K135" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="L135" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="M135" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="N135" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="O135" s="2"/>
-      <c r="P135" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q135" s="2"/>
-      <c r="R135" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S135" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T135" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U135" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V135" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W135" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X135" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y135" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z135" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA135" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB135" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC135" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD135" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE135" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF135" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="AG135" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH135" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI135" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ135" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK135" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="AL135" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="AM135" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="AN135" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO135" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP135" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="136" hidden="true">
-      <c r="A136" t="s" s="2">
-        <v>629</v>
-      </c>
-      <c r="B136" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="C136" s="2"/>
-      <c r="D136" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E136" s="2"/>
-      <c r="F136" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G136" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H136" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I136" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J136" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K136" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="L136" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="M136" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="N136" s="2"/>
-      <c r="O136" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="P136" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q136" s="2"/>
-      <c r="R136" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S136" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T136" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="U136" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V136" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W136" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X136" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y136" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z136" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA136" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB136" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC136" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD136" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE136" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF136" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="AG136" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH136" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI136" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ136" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK136" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="AL136" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="AM136" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="AN136" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO136" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP136" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="137" hidden="true">
-      <c r="A137" t="s" s="2">
-        <v>630</v>
-      </c>
-      <c r="B137" t="s" s="2">
-        <v>630</v>
-      </c>
-      <c r="C137" s="2"/>
-      <c r="D137" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E137" s="2"/>
-      <c r="F137" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G137" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H137" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I137" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J137" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K137" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="L137" t="s" s="2">
-        <v>631</v>
-      </c>
-      <c r="M137" t="s" s="2">
-        <v>632</v>
-      </c>
-      <c r="N137" s="2"/>
-      <c r="O137" t="s" s="2">
-        <v>633</v>
-      </c>
-      <c r="P137" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q137" s="2"/>
-      <c r="R137" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S137" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T137" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U137" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V137" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W137" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X137" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="Y137" t="s" s="2">
-        <v>634</v>
-      </c>
-      <c r="Z137" t="s" s="2">
-        <v>635</v>
-      </c>
-      <c r="AA137" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB137" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC137" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD137" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE137" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF137" t="s" s="2">
-        <v>630</v>
-      </c>
-      <c r="AG137" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH137" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI137" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ137" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK137" t="s" s="2">
-        <v>636</v>
-      </c>
-      <c r="AL137" t="s" s="2">
-        <v>637</v>
-      </c>
-      <c r="AM137" t="s" s="2">
-        <v>638</v>
-      </c>
-      <c r="AN137" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO137" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP137" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="138" hidden="true">
-      <c r="A138" t="s" s="2">
-        <v>639</v>
-      </c>
-      <c r="B138" t="s" s="2">
-        <v>639</v>
-      </c>
-      <c r="C138" s="2"/>
-      <c r="D138" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E138" s="2"/>
-      <c r="F138" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G138" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H138" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I138" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J138" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K138" t="s" s="2">
-        <v>640</v>
-      </c>
-      <c r="L138" t="s" s="2">
-        <v>641</v>
-      </c>
-      <c r="M138" t="s" s="2">
-        <v>642</v>
-      </c>
-      <c r="N138" s="2"/>
-      <c r="O138" t="s" s="2">
-        <v>643</v>
-      </c>
-      <c r="P138" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q138" s="2"/>
-      <c r="R138" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S138" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T138" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U138" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V138" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W138" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X138" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y138" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z138" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA138" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB138" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC138" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD138" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE138" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF138" t="s" s="2">
-        <v>639</v>
-      </c>
-      <c r="AG138" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH138" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI138" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ138" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK138" t="s" s="2">
-        <v>644</v>
-      </c>
-      <c r="AL138" t="s" s="2">
-        <v>645</v>
-      </c>
-      <c r="AM138" t="s" s="2">
-        <v>646</v>
-      </c>
-      <c r="AN138" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO138" t="s" s="2">
-        <v>647</v>
-      </c>
-      <c r="AP138" t="s" s="2">
-        <v>648</v>
-      </c>
-    </row>
-    <row r="139" hidden="true">
-      <c r="A139" t="s" s="2">
-        <v>649</v>
-      </c>
-      <c r="B139" t="s" s="2">
-        <v>649</v>
-      </c>
-      <c r="C139" s="2"/>
-      <c r="D139" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E139" s="2"/>
-      <c r="F139" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G139" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H139" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I139" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J139" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K139" t="s" s="2">
-        <v>650</v>
-      </c>
-      <c r="L139" t="s" s="2">
-        <v>651</v>
-      </c>
-      <c r="M139" t="s" s="2">
-        <v>652</v>
-      </c>
-      <c r="N139" s="2"/>
-      <c r="O139" t="s" s="2">
-        <v>653</v>
-      </c>
-      <c r="P139" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q139" s="2"/>
-      <c r="R139" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S139" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T139" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U139" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V139" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W139" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X139" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y139" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z139" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA139" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB139" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC139" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD139" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE139" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF139" t="s" s="2">
-        <v>649</v>
-      </c>
-      <c r="AG139" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH139" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI139" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ139" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK139" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL139" t="s" s="2">
-        <v>654</v>
-      </c>
-      <c r="AM139" t="s" s="2">
-        <v>655</v>
-      </c>
-      <c r="AN139" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO139" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP139" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="140" hidden="true">
-      <c r="A140" t="s" s="2">
-        <v>656</v>
-      </c>
-      <c r="B140" t="s" s="2">
-        <v>656</v>
-      </c>
-      <c r="C140" s="2"/>
-      <c r="D140" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E140" s="2"/>
-      <c r="F140" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G140" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H140" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I140" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J140" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K140" t="s" s="2">
-        <v>657</v>
-      </c>
-      <c r="L140" t="s" s="2">
-        <v>658</v>
-      </c>
-      <c r="M140" t="s" s="2">
-        <v>659</v>
-      </c>
-      <c r="N140" s="2"/>
-      <c r="O140" s="2"/>
-      <c r="P140" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q140" s="2"/>
-      <c r="R140" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S140" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T140" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U140" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V140" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W140" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X140" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y140" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z140" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA140" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB140" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC140" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD140" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE140" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF140" t="s" s="2">
-        <v>656</v>
-      </c>
-      <c r="AG140" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH140" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI140" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ140" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK140" t="s" s="2">
-        <v>660</v>
-      </c>
-      <c r="AL140" t="s" s="2">
-        <v>661</v>
-      </c>
-      <c r="AM140" t="s" s="2">
-        <v>662</v>
-      </c>
-      <c r="AN140" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO140" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP140" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="141" hidden="true">
-      <c r="A141" t="s" s="2">
-        <v>663</v>
-      </c>
-      <c r="B141" t="s" s="2">
-        <v>663</v>
-      </c>
-      <c r="C141" s="2"/>
-      <c r="D141" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E141" s="2"/>
-      <c r="F141" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G141" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H141" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I141" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J141" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K141" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="L141" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="M141" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="N141" s="2"/>
-      <c r="O141" s="2"/>
-      <c r="P141" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q141" s="2"/>
-      <c r="R141" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S141" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T141" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U141" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V141" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W141" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X141" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y141" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z141" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA141" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB141" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC141" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD141" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE141" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF141" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="AG141" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH141" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI141" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ141" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AK141" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL141" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="AM141" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN141" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO141" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP141" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="142" hidden="true">
-      <c r="A142" t="s" s="2">
-        <v>664</v>
-      </c>
-      <c r="B142" t="s" s="2">
-        <v>664</v>
-      </c>
-      <c r="C142" s="2"/>
-      <c r="D142" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="E142" s="2"/>
-      <c r="F142" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G142" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H142" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I142" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J142" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K142" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="L142" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="M142" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="N142" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O142" s="2"/>
-      <c r="P142" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q142" s="2"/>
-      <c r="R142" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S142" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T142" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U142" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V142" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W142" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X142" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y142" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z142" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA142" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB142" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC142" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD142" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE142" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF142" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="AG142" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH142" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI142" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ142" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="AK142" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL142" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="AM142" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN142" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO142" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP142" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="143" hidden="true">
-      <c r="A143" t="s" s="2">
-        <v>665</v>
-      </c>
-      <c r="B143" t="s" s="2">
-        <v>665</v>
-      </c>
-      <c r="C143" s="2"/>
-      <c r="D143" t="s" s="2">
-        <v>666</v>
-      </c>
-      <c r="E143" s="2"/>
-      <c r="F143" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G143" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H143" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I143" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="J143" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K143" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="L143" t="s" s="2">
-        <v>667</v>
-      </c>
-      <c r="M143" t="s" s="2">
-        <v>668</v>
-      </c>
-      <c r="N143" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O143" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="P143" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q143" s="2"/>
-      <c r="R143" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S143" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T143" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U143" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V143" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W143" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X143" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y143" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z143" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA143" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB143" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC143" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD143" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE143" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF143" t="s" s="2">
-        <v>669</v>
-      </c>
-      <c r="AG143" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH143" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI143" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ143" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="AK143" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL143" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="AM143" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN143" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO143" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP143" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="144" hidden="true">
-      <c r="A144" t="s" s="2">
-        <v>670</v>
-      </c>
-      <c r="B144" t="s" s="2">
-        <v>670</v>
-      </c>
-      <c r="C144" s="2"/>
-      <c r="D144" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E144" s="2"/>
-      <c r="F144" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G144" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H144" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I144" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J144" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K144" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="L144" t="s" s="2">
-        <v>671</v>
-      </c>
-      <c r="M144" t="s" s="2">
-        <v>672</v>
-      </c>
-      <c r="N144" s="2"/>
-      <c r="O144" t="s" s="2">
-        <v>673</v>
-      </c>
-      <c r="P144" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q144" s="2"/>
-      <c r="R144" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S144" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T144" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U144" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V144" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W144" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X144" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y144" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z144" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA144" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB144" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC144" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD144" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE144" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF144" t="s" s="2">
-        <v>670</v>
-      </c>
-      <c r="AG144" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH144" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI144" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ144" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK144" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL144" t="s" s="2">
-        <v>674</v>
-      </c>
-      <c r="AM144" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN144" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO144" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP144" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="145" hidden="true">
-      <c r="A145" t="s" s="2">
-        <v>675</v>
-      </c>
-      <c r="B145" t="s" s="2">
-        <v>675</v>
-      </c>
-      <c r="C145" s="2"/>
-      <c r="D145" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E145" s="2"/>
-      <c r="F145" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="G145" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H145" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I145" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J145" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K145" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="L145" t="s" s="2">
-        <v>676</v>
-      </c>
-      <c r="M145" t="s" s="2">
-        <v>677</v>
-      </c>
-      <c r="N145" s="2"/>
-      <c r="O145" s="2"/>
-      <c r="P145" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q145" s="2"/>
-      <c r="R145" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S145" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T145" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U145" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V145" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W145" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X145" t="s" s="2">
-        <v>678</v>
-      </c>
-      <c r="Y145" t="s" s="2">
-        <v>679</v>
-      </c>
-      <c r="Z145" t="s" s="2">
-        <v>680</v>
-      </c>
-      <c r="AA145" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB145" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC145" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD145" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE145" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF145" t="s" s="2">
-        <v>675</v>
-      </c>
-      <c r="AG145" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AH145" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI145" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ145" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK145" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL145" t="s" s="2">
-        <v>661</v>
-      </c>
-      <c r="AM145" t="s" s="2">
-        <v>681</v>
-      </c>
-      <c r="AN145" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO145" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP145" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="146" hidden="true">
-      <c r="A146" t="s" s="2">
-        <v>682</v>
-      </c>
-      <c r="B146" t="s" s="2">
-        <v>682</v>
-      </c>
-      <c r="C146" s="2"/>
-      <c r="D146" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E146" s="2"/>
-      <c r="F146" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G146" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H146" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I146" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J146" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K146" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="L146" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="M146" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="N146" s="2"/>
-      <c r="O146" s="2"/>
-      <c r="P146" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q146" s="2"/>
-      <c r="R146" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S146" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T146" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U146" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V146" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W146" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X146" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y146" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z146" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA146" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB146" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC146" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD146" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE146" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF146" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="AG146" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH146" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI146" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ146" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AK146" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL146" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="AM146" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN146" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO146" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP146" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="147" hidden="true">
-      <c r="A147" t="s" s="2">
-        <v>683</v>
-      </c>
-      <c r="B147" t="s" s="2">
-        <v>683</v>
-      </c>
-      <c r="C147" s="2"/>
-      <c r="D147" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="E147" s="2"/>
-      <c r="F147" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G147" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H147" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I147" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J147" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K147" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="L147" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="M147" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="N147" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O147" s="2"/>
-      <c r="P147" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q147" s="2"/>
-      <c r="R147" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S147" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T147" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U147" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V147" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W147" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X147" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y147" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z147" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA147" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB147" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="AC147" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="AD147" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE147" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="AF147" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="AG147" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH147" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI147" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ147" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="AK147" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL147" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="AM147" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN147" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO147" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP147" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="148" hidden="true">
-      <c r="A148" t="s" s="2">
-        <v>684</v>
-      </c>
-      <c r="B148" t="s" s="2">
-        <v>684</v>
-      </c>
-      <c r="C148" s="2"/>
-      <c r="D148" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E148" s="2"/>
-      <c r="F148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G148" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H148" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I148" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J148" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K148" t="s" s="2">
-        <v>685</v>
-      </c>
-      <c r="L148" t="s" s="2">
-        <v>686</v>
-      </c>
-      <c r="M148" t="s" s="2">
-        <v>687</v>
-      </c>
-      <c r="N148" t="s" s="2">
-        <v>688</v>
-      </c>
-      <c r="O148" t="s" s="2">
-        <v>689</v>
-      </c>
-      <c r="P148" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q148" s="2"/>
-      <c r="R148" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S148" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T148" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U148" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V148" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W148" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X148" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y148" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z148" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA148" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB148" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC148" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD148" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE148" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF148" t="s" s="2">
-        <v>690</v>
-      </c>
-      <c r="AG148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH148" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI148" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ148" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK148" t="s" s="2">
-        <v>691</v>
-      </c>
-      <c r="AL148" t="s" s="2">
-        <v>692</v>
-      </c>
-      <c r="AM148" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN148" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO148" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP148" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="149" hidden="true">
-      <c r="A149" t="s" s="2">
-        <v>693</v>
-      </c>
-      <c r="B149" t="s" s="2">
-        <v>693</v>
-      </c>
-      <c r="C149" s="2"/>
-      <c r="D149" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E149" s="2"/>
-      <c r="F149" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G149" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H149" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I149" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J149" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K149" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="L149" t="s" s="2">
-        <v>694</v>
-      </c>
-      <c r="M149" t="s" s="2">
-        <v>695</v>
-      </c>
-      <c r="N149" t="s" s="2">
-        <v>696</v>
-      </c>
-      <c r="O149" t="s" s="2">
-        <v>697</v>
-      </c>
-      <c r="P149" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q149" s="2"/>
-      <c r="R149" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S149" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T149" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U149" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V149" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W149" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X149" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y149" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z149" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA149" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB149" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC149" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD149" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE149" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF149" t="s" s="2">
-        <v>698</v>
-      </c>
-      <c r="AG149" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH149" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI149" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ149" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK149" t="s" s="2">
-        <v>699</v>
-      </c>
-      <c r="AL149" t="s" s="2">
-        <v>700</v>
-      </c>
-      <c r="AM149" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN149" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO149" t="s" s="2">
-        <v>701</v>
-      </c>
-      <c r="AP149" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="150" hidden="true">
-      <c r="A150" t="s" s="2">
-        <v>702</v>
-      </c>
-      <c r="B150" t="s" s="2">
-        <v>702</v>
-      </c>
-      <c r="C150" s="2"/>
-      <c r="D150" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E150" s="2"/>
-      <c r="F150" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G150" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H150" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I150" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J150" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K150" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="L150" t="s" s="2">
-        <v>703</v>
-      </c>
-      <c r="M150" t="s" s="2">
-        <v>704</v>
-      </c>
-      <c r="N150" s="2"/>
-      <c r="O150" t="s" s="2">
-        <v>705</v>
-      </c>
-      <c r="P150" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q150" s="2"/>
-      <c r="R150" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S150" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T150" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U150" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V150" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W150" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X150" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y150" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z150" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA150" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB150" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC150" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD150" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE150" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF150" t="s" s="2">
-        <v>702</v>
-      </c>
-      <c r="AG150" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH150" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI150" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ150" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK150" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL150" t="s" s="2">
-        <v>706</v>
-      </c>
-      <c r="AM150" t="s" s="2">
-        <v>707</v>
-      </c>
-      <c r="AN150" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO150" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP150" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="151" hidden="true">
-      <c r="A151" t="s" s="2">
-        <v>708</v>
-      </c>
-      <c r="B151" t="s" s="2">
-        <v>708</v>
-      </c>
-      <c r="C151" s="2"/>
-      <c r="D151" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E151" s="2"/>
-      <c r="F151" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G151" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H151" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I151" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J151" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K151" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="L151" t="s" s="2">
-        <v>709</v>
-      </c>
-      <c r="M151" t="s" s="2">
-        <v>710</v>
-      </c>
-      <c r="N151" s="2"/>
-      <c r="O151" s="2"/>
-      <c r="P151" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q151" s="2"/>
-      <c r="R151" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S151" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T151" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U151" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V151" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W151" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X151" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y151" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z151" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA151" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB151" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC151" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD151" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE151" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF151" t="s" s="2">
-        <v>708</v>
-      </c>
-      <c r="AG151" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH151" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI151" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ151" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK151" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL151" t="s" s="2">
-        <v>711</v>
-      </c>
-      <c r="AM151" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN151" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO151" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP151" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="152" hidden="true">
-      <c r="A152" t="s" s="2">
-        <v>712</v>
-      </c>
-      <c r="B152" t="s" s="2">
-        <v>712</v>
-      </c>
-      <c r="C152" s="2"/>
-      <c r="D152" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E152" s="2"/>
-      <c r="F152" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G152" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H152" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I152" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J152" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K152" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="L152" t="s" s="2">
-        <v>713</v>
-      </c>
-      <c r="M152" t="s" s="2">
-        <v>714</v>
-      </c>
-      <c r="N152" t="s" s="2">
-        <v>715</v>
-      </c>
-      <c r="O152" t="s" s="2">
-        <v>716</v>
-      </c>
-      <c r="P152" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q152" s="2"/>
-      <c r="R152" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S152" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T152" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U152" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V152" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W152" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X152" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="Y152" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="Z152" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="AA152" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB152" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC152" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD152" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE152" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF152" t="s" s="2">
-        <v>712</v>
-      </c>
-      <c r="AG152" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH152" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI152" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ152" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK152" t="s" s="2">
-        <v>717</v>
-      </c>
-      <c r="AL152" t="s" s="2">
-        <v>718</v>
-      </c>
-      <c r="AM152" t="s" s="2">
-        <v>719</v>
-      </c>
-      <c r="AN152" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO152" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP152" t="s" s="2">
         <v>80</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP152">
+  <autoFilter ref="A1:AP126">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -20828,7 +17620,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI151">
+  <conditionalFormatting sqref="A2:AI125">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.14.0</t>
+    <t>0.15.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-13T13:47:03+00:00</t>
+    <t>2024-01-14T11:16:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.15.0</t>
+    <t>0.16.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-14T11:16:16+00:00</t>
+    <t>2024-02-08T09:36:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-08T09:36:20+00:00</t>
+    <t>2024-02-09T16:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-09T16:38:59+00:00</t>
+    <t>2024-02-11T14:24:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.16.0</t>
+    <t>0.17.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-11T14:24:24+00:00</t>
+    <t>2024-02-12T08:51:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.17.0</t>
+    <t>0.18.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T08:51:11+00:00</t>
+    <t>2024-02-13T17:27:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.18.0</t>
+    <t>0.19.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T17:27:52+00:00</t>
+    <t>2024-02-13T18:57:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T18:57:41+00:00</t>
+    <t>2024-02-13T19:55:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.19.0</t>
+    <t>0.20.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T19:55:01+00:00</t>
+    <t>2024-02-17T09:04:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.20.0</t>
+    <t>0.21.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:04:28+00:00</t>
+    <t>2024-02-17T09:43:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.21.0</t>
+    <t>0.22.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:43:43+00:00</t>
+    <t>2024-02-18T11:03:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.22.0</t>
+    <t>0.23.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-18T11:03:00+00:00</t>
+    <t>2024-02-23T15:31:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1722,7 +1722,7 @@
     <t>Extension.value[x]</t>
   </si>
   <si>
-    <t>1531: fixed value = unknown when NEW PERSON - STATE (#200-.115) case NULL</t>
+    <t>1531: fixed value = #unknown when NEW PERSON - STATE (#200-.115) case NULL</t>
   </si>
   <si>
     <t>Practitioner.address:home.country.value</t>
@@ -1833,7 +1833,7 @@
     <t>Practitioner.address:temp.country.extension:data-absent-reason.value[x]</t>
   </si>
   <si>
-    <t>1533: fixed value = unknown when NEW PERSON - STATE (#200-.1215) case NULL</t>
+    <t>1533: fixed value = #unknown when NEW PERSON - STATE (#200-.1215) case NULL</t>
   </si>
   <si>
     <t>Practitioner.address:temp.country.value</t>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.23.0</t>
+    <t>0.24.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-23T15:31:48+00:00</t>
+    <t>2024-02-28T12:35:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.24.0</t>
+    <t>0.26.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-28T12:35:36+00:00</t>
+    <t>2024-03-08T13:22:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.26.0</t>
+    <t>0.27.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-08T13:22:05+00:00</t>
+    <t>2024-03-08T18:48:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$126</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$136</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4812" uniqueCount="690">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5190" uniqueCount="707">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.27.0</t>
+    <t>0.28.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-08T18:48:53+00:00</t>
+    <t>2024-03-09T10:17:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -757,8 +757,7 @@
     <t>376: source value from NEW PERSON - NPI (#200-41.99)</t>
   </si>
   <si>
-    <t>SStaff.PrescribingProvider.NPI
-SStaff.SStaff.NPI</t>
+    <t>SStaff.PrescribingProvider.NPI,SStaff.SStaff.NPI</t>
   </si>
   <si>
     <t>Practitioner.identifier:NPI.period</t>
@@ -1179,8 +1178,7 @@
     <t>383: source value from NEW PERSON - PHONE (HOME) (#200-.131)</t>
   </si>
   <si>
-    <t>SStaff.PrescribingProvider.HomePhone
-SStaff.SStaff.HomePhone</t>
+    <t>SStaff.PrescribingProvider.HomePhone,SStaff.SStaff.HomePhone</t>
   </si>
   <si>
     <t>Practitioner.telecom.use</t>
@@ -1575,8 +1573,7 @@
     <t>398: source value from NEW PERSON - STREET ADDRESS 3 (#200-.113)</t>
   </si>
   <si>
-    <t>SStaff.PrescribingProvider.StreetAddress3
-SStaff.SStaff.StreetAddress3</t>
+    <t>SStaff.PrescribingProvider.StreetAddress3,SStaff.SStaff.StreetAddress3</t>
   </si>
   <si>
     <t>Practitioner.address:home.city</t>
@@ -1585,8 +1582,7 @@
     <t>399: source value from NEW PERSON - CITY (#200-.114)</t>
   </si>
   <si>
-    <t>SStaff.PrescribingProvider.City
-SStaff.SStaff.City</t>
+    <t>SStaff.PrescribingProvider.City,SStaff.SStaff.City</t>
   </si>
   <si>
     <t>Practitioner.address:home.district</t>
@@ -1598,8 +1594,7 @@
     <t>400: source value from NEW PERSON - STATE (#200-.115)</t>
   </si>
   <si>
-    <t>SStaff.PrescribingProvider.StateIEN
-SStaff.SStaff.StateName</t>
+    <t>SStaff.PrescribingProvider.StateIEN,SStaff.SStaff.StateName</t>
   </si>
   <si>
     <t>Practitioner.address:home.postalCode</t>
@@ -1608,17 +1603,13 @@
     <t>401: source value from NEW PERSON - ZIP CODE (#200-.116)</t>
   </si>
   <si>
-    <t>SStaff.PrescribingProvider.ZipCode
-SStaff.SStaff.ZipCode</t>
+    <t>SStaff.PrescribingProvider.ZipCode,SStaff.SStaff.ZipCode</t>
   </si>
   <si>
     <t>Practitioner.address:home.country</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFPractitionerCountry</t>
-  </si>
-  <si>
-    <t>1530: terminologyMaps using VF_PractitionerCountry on NEW PERSON - STATE (#200-.115) case not NULL</t>
+    <t>1530: transform using VF_PractitionerCountry on NEW PERSON - STATE (#200-.115) case not NULL</t>
   </si>
   <si>
     <t>Practitioner.address:home.country.id</t>
@@ -1725,6 +1716,47 @@
     <t>1531: fixed value = #unknown when NEW PERSON - STATE (#200-.115) case NULL</t>
   </si>
   <si>
+    <t>Practitioner.address:home.country.extension:11179-permitted-value-conceptmap</t>
+  </si>
+  <si>
+    <t>11179-permitted-value-conceptmap</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {11179-permitted-value-conceptmap}
+</t>
+  </si>
+  <si>
+    <t>Mapping from permitted to transmitted</t>
+  </si>
+  <si>
+    <t>Expresses the linkage between the internal codes used for storage and the codes used for exchange.</t>
+  </si>
+  <si>
+    <t>The permitted value set must have a 1..1 set of codes for each code in the value meaning value set.  The source for the concept map is the value set the extension appears on.  The target is the permitted-value-valueset.</t>
+  </si>
+  <si>
+    <t>Practitioner.address:home.country.extension:11179-permitted-value-conceptmap.id</t>
+  </si>
+  <si>
+    <t>Practitioner.address:home.country.extension:11179-permitted-value-conceptmap.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.address:home.country.extension:11179-permitted-value-conceptmap.url</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/StructureDefinition/11179-permitted-value-conceptmap</t>
+  </si>
+  <si>
+    <t>Practitioner.address:home.country.extension:11179-permitted-value-conceptmap.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canonical(ConceptMap)
+</t>
+  </si>
+  <si>
+    <t>http://va.gov/fhir/ConceptMap/CMVFPractitionerCountry</t>
+  </si>
+  <si>
     <t>Practitioner.address:home.country.value</t>
   </si>
   <si>
@@ -1809,7 +1841,7 @@
     <t>Practitioner.address:temp.country</t>
   </si>
   <si>
-    <t>1532: terminologyMaps using VF_PractitionerCountry on NEW PERSON - STATE (#200-.1215) case not NULL</t>
+    <t>1532: transform using VF_PractitionerCountry on NEW PERSON - STATE (#200-.1215) case not NULL</t>
   </si>
   <si>
     <t>Practitioner.address:temp.country.id</t>
@@ -1834,6 +1866,21 @@
   </si>
   <si>
     <t>1533: fixed value = #unknown when NEW PERSON - STATE (#200-.1215) case NULL</t>
+  </si>
+  <si>
+    <t>Practitioner.address:temp.country.extension:11179-permitted-value-conceptmap</t>
+  </si>
+  <si>
+    <t>Practitioner.address:temp.country.extension:11179-permitted-value-conceptmap.id</t>
+  </si>
+  <si>
+    <t>Practitioner.address:temp.country.extension:11179-permitted-value-conceptmap.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.address:temp.country.extension:11179-permitted-value-conceptmap.url</t>
+  </si>
+  <si>
+    <t>Practitioner.address:temp.country.extension:11179-permitted-value-conceptmap.value[x]</t>
   </si>
   <si>
     <t>Practitioner.address:temp.country.value</t>
@@ -1933,8 +1980,7 @@
     <t>394: source value from NEW PERSON - DOB (#200-5)</t>
   </si>
   <si>
-    <t>SStaff.SStaff.DateOfBirth
-Staff.Staff.DateofBirth</t>
+    <t>SStaff.SStaff.DateOfBirth,Staff.Staff.DateofBirth</t>
   </si>
   <si>
     <t>Practitioner.photo</t>
@@ -2469,12 +2515,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP126"/>
+  <dimension ref="A1:AP136"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="70.5625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="85.890625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="46.1796875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="18.9921875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="34.3203125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -2482,7 +2528,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="30.90625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="46.23828125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2511,8 +2557,8 @@
     <col min="38" max="38" width="102.6171875" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="52.3828125" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="100.24609375" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="43.94140625" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="97.1953125" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="66.4765625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11588,11 +11634,13 @@
         <v>80</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="Y76" s="2"/>
+        <v>80</v>
+      </c>
+      <c r="Y76" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="Z76" t="s" s="2">
-        <v>513</v>
+        <v>80</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>80</v>
@@ -11637,7 +11685,7 @@
         <v>80</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="AP76" t="s" s="2">
         <v>508</v>
@@ -11645,10 +11693,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="B77" t="s" s="2">
         <v>515</v>
-      </c>
-      <c r="B77" t="s" s="2">
-        <v>516</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11674,10 +11722,10 @@
         <v>159</v>
       </c>
       <c r="L77" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="M77" t="s" s="2">
         <v>517</v>
-      </c>
-      <c r="M77" t="s" s="2">
-        <v>518</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11763,10 +11811,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="B78" t="s" s="2">
         <v>519</v>
-      </c>
-      <c r="B78" t="s" s="2">
-        <v>520</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11792,10 +11840,10 @@
         <v>135</v>
       </c>
       <c r="L78" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="M78" t="s" s="2">
         <v>521</v>
-      </c>
-      <c r="M78" t="s" s="2">
-        <v>522</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11879,13 +11927,13 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="B79" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="C79" t="s" s="2">
         <v>523</v>
-      </c>
-      <c r="B79" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="C79" t="s" s="2">
-        <v>524</v>
       </c>
       <c r="D79" t="s" s="2">
         <v>80</v>
@@ -11907,13 +11955,13 @@
         <v>80</v>
       </c>
       <c r="K79" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="L79" t="s" s="2">
         <v>525</v>
       </c>
-      <c r="L79" t="s" s="2">
+      <c r="M79" t="s" s="2">
         <v>526</v>
-      </c>
-      <c r="M79" t="s" s="2">
-        <v>527</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -11973,7 +12021,7 @@
         <v>79</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="AJ79" t="s" s="2">
         <v>140</v>
@@ -11982,7 +12030,7 @@
         <v>80</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>80</v>
@@ -11999,10 +12047,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="B80" t="s" s="2">
         <v>530</v>
-      </c>
-      <c r="B80" t="s" s="2">
-        <v>531</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12117,10 +12165,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="B81" t="s" s="2">
         <v>532</v>
-      </c>
-      <c r="B81" t="s" s="2">
-        <v>533</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12146,10 +12194,10 @@
         <v>135</v>
       </c>
       <c r="L81" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="M81" t="s" s="2">
         <v>521</v>
-      </c>
-      <c r="M81" t="s" s="2">
-        <v>522</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -12235,10 +12283,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="B82" t="s" s="2">
         <v>534</v>
-      </c>
-      <c r="B82" t="s" s="2">
-        <v>535</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12264,13 +12312,13 @@
         <v>103</v>
       </c>
       <c r="L82" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="M82" t="s" s="2">
         <v>536</v>
       </c>
-      <c r="M82" t="s" s="2">
+      <c r="N82" t="s" s="2">
         <v>537</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>538</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -12278,49 +12326,49 @@
       </c>
       <c r="Q82" s="2"/>
       <c r="R82" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="S82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF82" t="s" s="2">
         <v>539</v>
-      </c>
-      <c r="S82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF82" t="s" s="2">
-        <v>540</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>89</v>
@@ -12355,10 +12403,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="B83" t="s" s="2">
         <v>541</v>
-      </c>
-      <c r="B83" t="s" s="2">
-        <v>542</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12384,10 +12432,10 @@
         <v>109</v>
       </c>
       <c r="L83" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="M83" t="s" s="2">
         <v>543</v>
-      </c>
-      <c r="M83" t="s" s="2">
-        <v>544</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -12417,28 +12465,28 @@
         <v>174</v>
       </c>
       <c r="Y83" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="Z83" t="s" s="2">
         <v>545</v>
       </c>
-      <c r="Z83" t="s" s="2">
+      <c r="AA83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF83" t="s" s="2">
         <v>546</v>
-      </c>
-      <c r="AA83" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB83" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC83" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD83" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE83" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF83" t="s" s="2">
-        <v>547</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
@@ -12465,7 +12513,7 @@
         <v>80</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="AP83" t="s" s="2">
         <v>508</v>
@@ -12473,12 +12521,14 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="B84" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="C84" t="s" s="2">
         <v>549</v>
       </c>
-      <c r="B84" t="s" s="2">
-        <v>550</v>
-      </c>
-      <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
         <v>80</v>
       </c>
@@ -12499,7 +12549,7 @@
         <v>80</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>159</v>
+        <v>550</v>
       </c>
       <c r="L84" t="s" s="2">
         <v>551</v>
@@ -12507,7 +12557,9 @@
       <c r="M84" t="s" s="2">
         <v>552</v>
       </c>
-      <c r="N84" s="2"/>
+      <c r="N84" t="s" s="2">
+        <v>553</v>
+      </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>80</v>
@@ -12529,7 +12581,7 @@
         <v>80</v>
       </c>
       <c r="W84" t="s" s="2">
-        <v>553</v>
+        <v>80</v>
       </c>
       <c r="X84" t="s" s="2">
         <v>80</v>
@@ -12556,25 +12608,25 @@
         <v>80</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>554</v>
+        <v>168</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>80</v>
+        <v>527</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>80</v>
+        <v>140</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>80</v>
+        <v>132</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>80</v>
+        <v>132</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>80</v>
@@ -12591,10 +12643,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>486</v>
+        <v>530</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12614,21 +12666,19 @@
         <v>80</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>212</v>
+        <v>159</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>487</v>
+        <v>160</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>488</v>
+        <v>161</v>
       </c>
       <c r="N85" s="2"/>
-      <c r="O85" t="s" s="2">
-        <v>489</v>
-      </c>
+      <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>80</v>
       </c>
@@ -12640,7 +12690,7 @@
         <v>80</v>
       </c>
       <c r="T85" t="s" s="2">
-        <v>490</v>
+        <v>80</v>
       </c>
       <c r="U85" t="s" s="2">
         <v>80</v>
@@ -12676,7 +12726,7 @@
         <v>80</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>491</v>
+        <v>162</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>78</v>
@@ -12688,16 +12738,16 @@
         <v>80</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>492</v>
+        <v>80</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>342</v>
+        <v>163</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>218</v>
+        <v>80</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>80</v>
@@ -12711,14 +12761,12 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="C86" t="s" s="2">
-        <v>557</v>
-      </c>
+        <v>532</v>
+      </c>
+      <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
         <v>80</v>
       </c>
@@ -12727,32 +12775,28 @@
         <v>78</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H86" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="I86" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>395</v>
+        <v>135</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>396</v>
+        <v>520</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="O86" t="s" s="2">
-        <v>399</v>
-      </c>
+        <v>521</v>
+      </c>
+      <c r="N86" s="2"/>
+      <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>80</v>
       </c>
@@ -12788,19 +12832,19 @@
         <v>80</v>
       </c>
       <c r="AB86" t="s" s="2">
-        <v>80</v>
+        <v>166</v>
       </c>
       <c r="AC86" t="s" s="2">
-        <v>80</v>
+        <v>167</v>
       </c>
       <c r="AD86" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE86" t="s" s="2">
-        <v>80</v>
+        <v>153</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>394</v>
+        <v>168</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>78</v>
@@ -12812,16 +12856,16 @@
         <v>80</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>401</v>
+        <v>80</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>402</v>
+        <v>80</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>163</v>
+        <v>80</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>80</v>
@@ -12835,10 +12879,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>403</v>
+        <v>534</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12846,7 +12890,7 @@
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G87" t="s" s="2">
         <v>89</v>
@@ -12861,22 +12905,24 @@
         <v>80</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>159</v>
+        <v>103</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>160</v>
+        <v>535</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="N87" s="2"/>
+        <v>536</v>
+      </c>
+      <c r="N87" t="s" s="2">
+        <v>537</v>
+      </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q87" s="2"/>
       <c r="R87" t="s" s="2">
-        <v>80</v>
+        <v>557</v>
       </c>
       <c r="S87" t="s" s="2">
         <v>80</v>
@@ -12918,10 +12964,10 @@
         <v>80</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>162</v>
+        <v>539</v>
       </c>
       <c r="AG87" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AH87" t="s" s="2">
         <v>89</v>
@@ -12936,7 +12982,7 @@
         <v>80</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>163</v>
+        <v>132</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>80</v>
@@ -12953,21 +12999,21 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>404</v>
+        <v>541</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>134</v>
+        <v>80</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>80</v>
@@ -12979,17 +13025,15 @@
         <v>80</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>135</v>
+        <v>559</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>136</v>
+        <v>542</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>138</v>
-      </c>
+        <v>543</v>
+      </c>
+      <c r="N88" s="2"/>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
         <v>80</v>
@@ -12999,7 +13043,7 @@
         <v>80</v>
       </c>
       <c r="S88" t="s" s="2">
-        <v>80</v>
+        <v>560</v>
       </c>
       <c r="T88" t="s" s="2">
         <v>80</v>
@@ -13026,37 +13070,37 @@
         <v>80</v>
       </c>
       <c r="AB88" t="s" s="2">
-        <v>166</v>
+        <v>80</v>
       </c>
       <c r="AC88" t="s" s="2">
-        <v>167</v>
+        <v>80</v>
       </c>
       <c r="AD88" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE88" t="s" s="2">
-        <v>153</v>
+        <v>80</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>168</v>
+        <v>546</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>163</v>
+        <v>132</v>
       </c>
       <c r="AM88" t="s" s="2">
         <v>80</v>
@@ -13073,10 +13117,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>405</v>
+        <v>562</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13093,26 +13137,22 @@
         <v>80</v>
       </c>
       <c r="I89" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="J89" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>109</v>
+        <v>159</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>406</v>
+        <v>563</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="N89" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="O89" t="s" s="2">
-        <v>409</v>
-      </c>
+        <v>564</v>
+      </c>
+      <c r="N89" s="2"/>
+      <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>80</v>
       </c>
@@ -13124,7 +13164,7 @@
         <v>80</v>
       </c>
       <c r="T89" t="s" s="2">
-        <v>410</v>
+        <v>80</v>
       </c>
       <c r="U89" t="s" s="2">
         <v>80</v>
@@ -13133,16 +13173,16 @@
         <v>80</v>
       </c>
       <c r="W89" t="s" s="2">
-        <v>80</v>
+        <v>565</v>
       </c>
       <c r="X89" t="s" s="2">
-        <v>174</v>
+        <v>80</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>411</v>
+        <v>80</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>412</v>
+        <v>80</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>80</v>
@@ -13160,7 +13200,7 @@
         <v>80</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>413</v>
+        <v>566</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>78</v>
@@ -13172,16 +13212,16 @@
         <v>80</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>414</v>
+        <v>80</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>294</v>
+        <v>80</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>415</v>
+        <v>80</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>80</v>
@@ -13195,10 +13235,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>561</v>
+        <v>567</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>416</v>
+        <v>486</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13221,18 +13261,18 @@
         <v>90</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>109</v>
+        <v>212</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>417</v>
+        <v>487</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="N90" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="O90" s="2"/>
+        <v>488</v>
+      </c>
+      <c r="N90" s="2"/>
+      <c r="O90" t="s" s="2">
+        <v>489</v>
+      </c>
       <c r="P90" t="s" s="2">
         <v>80</v>
       </c>
@@ -13244,7 +13284,7 @@
         <v>80</v>
       </c>
       <c r="T90" t="s" s="2">
-        <v>420</v>
+        <v>490</v>
       </c>
       <c r="U90" t="s" s="2">
         <v>80</v>
@@ -13256,13 +13296,13 @@
         <v>80</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>174</v>
+        <v>80</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>421</v>
+        <v>80</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>422</v>
+        <v>80</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>80</v>
@@ -13280,7 +13320,7 @@
         <v>80</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>423</v>
+        <v>491</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>78</v>
@@ -13295,13 +13335,13 @@
         <v>101</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>424</v>
+        <v>492</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>294</v>
+        <v>342</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>80</v>
+        <v>218</v>
       </c>
       <c r="AN90" t="s" s="2">
         <v>80</v>
@@ -13315,12 +13355,14 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>562</v>
+        <v>568</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="C91" s="2"/>
+        <v>394</v>
+      </c>
+      <c r="C91" t="s" s="2">
+        <v>569</v>
+      </c>
       <c r="D91" t="s" s="2">
         <v>80</v>
       </c>
@@ -13332,7 +13374,7 @@
         <v>89</v>
       </c>
       <c r="H91" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="I91" t="s" s="2">
         <v>80</v>
@@ -13341,19 +13383,19 @@
         <v>90</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>159</v>
+        <v>395</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>426</v>
+        <v>396</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>427</v>
+        <v>397</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>428</v>
+        <v>398</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>300</v>
+        <v>399</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>80</v>
@@ -13366,7 +13408,7 @@
         <v>80</v>
       </c>
       <c r="T91" t="s" s="2">
-        <v>429</v>
+        <v>80</v>
       </c>
       <c r="U91" t="s" s="2">
         <v>80</v>
@@ -13402,13 +13444,13 @@
         <v>80</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>430</v>
+        <v>394</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI91" t="s" s="2">
         <v>80</v>
@@ -13417,13 +13459,13 @@
         <v>101</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>431</v>
+        <v>401</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>303</v>
+        <v>402</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>80</v>
+        <v>163</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>80</v>
@@ -13437,10 +13479,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>563</v>
+        <v>570</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>432</v>
+        <v>403</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13451,25 +13493,25 @@
         <v>78</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>433</v>
+        <v>89</v>
       </c>
       <c r="H92" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="I92" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J92" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K92" t="s" s="2">
         <v>159</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>434</v>
+        <v>160</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>435</v>
+        <v>161</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -13484,7 +13526,7 @@
         <v>80</v>
       </c>
       <c r="T92" t="s" s="2">
-        <v>436</v>
+        <v>80</v>
       </c>
       <c r="U92" t="s" s="2">
         <v>80</v>
@@ -13520,76 +13562,78 @@
         <v>80</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>437</v>
+        <v>162</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI92" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>438</v>
+        <v>80</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>439</v>
+        <v>163</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>440</v>
+        <v>80</v>
       </c>
       <c r="AN92" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>564</v>
+        <v>80</v>
       </c>
       <c r="AP92" t="s" s="2">
-        <v>565</v>
+        <v>80</v>
       </c>
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>441</v>
+        <v>404</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>442</v>
+        <v>134</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H93" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="I93" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J93" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>159</v>
+        <v>135</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>443</v>
+        <v>136</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="N93" s="2"/>
+        <v>165</v>
+      </c>
+      <c r="N93" t="s" s="2">
+        <v>138</v>
+      </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
         <v>80</v>
@@ -13602,7 +13646,7 @@
         <v>80</v>
       </c>
       <c r="T93" t="s" s="2">
-        <v>445</v>
+        <v>80</v>
       </c>
       <c r="U93" t="s" s="2">
         <v>80</v>
@@ -13626,61 +13670,61 @@
         <v>80</v>
       </c>
       <c r="AB93" t="s" s="2">
-        <v>80</v>
+        <v>166</v>
       </c>
       <c r="AC93" t="s" s="2">
-        <v>80</v>
+        <v>167</v>
       </c>
       <c r="AD93" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE93" t="s" s="2">
-        <v>80</v>
+        <v>153</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>446</v>
+        <v>168</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI93" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>447</v>
+        <v>80</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>448</v>
+        <v>163</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>449</v>
+        <v>80</v>
       </c>
       <c r="AN93" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>567</v>
+        <v>80</v>
       </c>
       <c r="AP93" t="s" s="2">
-        <v>568</v>
+        <v>80</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>450</v>
+        <v>405</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>451</v>
+        <v>80</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
@@ -13693,24 +13737,26 @@
         <v>80</v>
       </c>
       <c r="I94" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="J94" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>159</v>
+        <v>109</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>452</v>
+        <v>406</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>453</v>
+        <v>407</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="O94" s="2"/>
+        <v>408</v>
+      </c>
+      <c r="O94" t="s" s="2">
+        <v>409</v>
+      </c>
       <c r="P94" t="s" s="2">
         <v>80</v>
       </c>
@@ -13722,7 +13768,7 @@
         <v>80</v>
       </c>
       <c r="T94" t="s" s="2">
-        <v>455</v>
+        <v>410</v>
       </c>
       <c r="U94" t="s" s="2">
         <v>80</v>
@@ -13734,13 +13780,13 @@
         <v>80</v>
       </c>
       <c r="X94" t="s" s="2">
-        <v>80</v>
+        <v>174</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>80</v>
+        <v>411</v>
       </c>
       <c r="Z94" t="s" s="2">
-        <v>80</v>
+        <v>412</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>80</v>
@@ -13758,7 +13804,7 @@
         <v>80</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>456</v>
+        <v>413</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>78</v>
@@ -13773,13 +13819,13 @@
         <v>101</v>
       </c>
       <c r="AK94" t="s" s="2">
-        <v>457</v>
+        <v>414</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>458</v>
+        <v>294</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>80</v>
+        <v>415</v>
       </c>
       <c r="AN94" t="s" s="2">
         <v>80</v>
@@ -13793,14 +13839,14 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>459</v>
+        <v>416</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
-        <v>460</v>
+        <v>80</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
@@ -13810,7 +13856,7 @@
         <v>89</v>
       </c>
       <c r="H95" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="I95" t="s" s="2">
         <v>80</v>
@@ -13819,15 +13865,17 @@
         <v>90</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>159</v>
+        <v>109</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>461</v>
+        <v>417</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="N95" s="2"/>
+        <v>418</v>
+      </c>
+      <c r="N95" t="s" s="2">
+        <v>419</v>
+      </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
         <v>80</v>
@@ -13840,7 +13888,7 @@
         <v>80</v>
       </c>
       <c r="T95" t="s" s="2">
-        <v>80</v>
+        <v>420</v>
       </c>
       <c r="U95" t="s" s="2">
         <v>80</v>
@@ -13852,13 +13900,13 @@
         <v>80</v>
       </c>
       <c r="X95" t="s" s="2">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="Y95" t="s" s="2">
-        <v>463</v>
+        <v>421</v>
       </c>
       <c r="Z95" t="s" s="2">
-        <v>464</v>
+        <v>422</v>
       </c>
       <c r="AA95" t="s" s="2">
         <v>80</v>
@@ -13876,7 +13924,7 @@
         <v>80</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>465</v>
+        <v>423</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>78</v>
@@ -13891,34 +13939,34 @@
         <v>101</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>466</v>
+        <v>424</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>467</v>
+        <v>294</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>468</v>
+        <v>80</v>
       </c>
       <c r="AN95" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO95" t="s" s="2">
-        <v>571</v>
+        <v>80</v>
       </c>
       <c r="AP95" t="s" s="2">
-        <v>572</v>
+        <v>80</v>
       </c>
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>469</v>
+        <v>425</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>470</v>
+        <v>80</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
@@ -13928,7 +13976,7 @@
         <v>89</v>
       </c>
       <c r="H96" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="I96" t="s" s="2">
         <v>80</v>
@@ -13940,13 +13988,17 @@
         <v>159</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>471</v>
+        <v>426</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="N96" s="2"/>
-      <c r="O96" s="2"/>
+        <v>427</v>
+      </c>
+      <c r="N96" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="O96" t="s" s="2">
+        <v>300</v>
+      </c>
       <c r="P96" t="s" s="2">
         <v>80</v>
       </c>
@@ -13958,7 +14010,7 @@
         <v>80</v>
       </c>
       <c r="T96" t="s" s="2">
-        <v>473</v>
+        <v>429</v>
       </c>
       <c r="U96" t="s" s="2">
         <v>80</v>
@@ -13994,7 +14046,7 @@
         <v>80</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>474</v>
+        <v>430</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>78</v>
@@ -14009,30 +14061,30 @@
         <v>101</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>475</v>
+        <v>431</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>476</v>
+        <v>303</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>477</v>
+        <v>80</v>
       </c>
       <c r="AN96" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO96" t="s" s="2">
-        <v>574</v>
+        <v>80</v>
       </c>
       <c r="AP96" t="s" s="2">
-        <v>575</v>
+        <v>80</v>
       </c>
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>478</v>
+        <v>432</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14043,7 +14095,7 @@
         <v>78</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>89</v>
+        <v>433</v>
       </c>
       <c r="H97" t="s" s="2">
         <v>90</v>
@@ -14058,14 +14110,12 @@
         <v>159</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>479</v>
+        <v>434</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>481</v>
-      </c>
+        <v>435</v>
+      </c>
+      <c r="N97" s="2"/>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
         <v>80</v>
@@ -14078,7 +14128,7 @@
         <v>80</v>
       </c>
       <c r="T97" t="s" s="2">
-        <v>80</v>
+        <v>436</v>
       </c>
       <c r="U97" t="s" s="2">
         <v>80</v>
@@ -14090,11 +14140,13 @@
         <v>80</v>
       </c>
       <c r="X97" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="Y97" s="2"/>
+        <v>80</v>
+      </c>
+      <c r="Y97" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="Z97" t="s" s="2">
-        <v>513</v>
+        <v>80</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>80</v>
@@ -14112,13 +14164,13 @@
         <v>80</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>482</v>
+        <v>437</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH97" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI97" t="s" s="2">
         <v>80</v>
@@ -14127,22 +14179,22 @@
         <v>101</v>
       </c>
       <c r="AK97" t="s" s="2">
-        <v>483</v>
+        <v>438</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>484</v>
+        <v>439</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>485</v>
+        <v>440</v>
       </c>
       <c r="AN97" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO97" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="AP97" t="s" s="2">
         <v>577</v>
-      </c>
-      <c r="AP97" t="s" s="2">
-        <v>572</v>
       </c>
     </row>
     <row r="98" hidden="true">
@@ -14150,11 +14202,11 @@
         <v>578</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>516</v>
+        <v>441</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
-        <v>80</v>
+        <v>442</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
@@ -14164,22 +14216,22 @@
         <v>89</v>
       </c>
       <c r="H98" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="I98" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J98" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K98" t="s" s="2">
         <v>159</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>517</v>
+        <v>443</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>518</v>
+        <v>444</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -14194,7 +14246,7 @@
         <v>80</v>
       </c>
       <c r="T98" t="s" s="2">
-        <v>80</v>
+        <v>445</v>
       </c>
       <c r="U98" t="s" s="2">
         <v>80</v>
@@ -14230,7 +14282,7 @@
         <v>80</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>162</v>
+        <v>446</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>78</v>
@@ -14242,44 +14294,44 @@
         <v>80</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="AK98" t="s" s="2">
-        <v>80</v>
+        <v>447</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>80</v>
+        <v>448</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>80</v>
+        <v>449</v>
       </c>
       <c r="AN98" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO98" t="s" s="2">
-        <v>80</v>
+        <v>579</v>
       </c>
       <c r="AP98" t="s" s="2">
-        <v>80</v>
+        <v>580</v>
       </c>
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>520</v>
+        <v>450</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>80</v>
+        <v>451</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G99" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H99" t="s" s="2">
         <v>80</v>
@@ -14288,18 +14340,20 @@
         <v>80</v>
       </c>
       <c r="J99" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>521</v>
+        <v>452</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="N99" s="2"/>
+        <v>453</v>
+      </c>
+      <c r="N99" t="s" s="2">
+        <v>454</v>
+      </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
         <v>80</v>
@@ -14312,7 +14366,7 @@
         <v>80</v>
       </c>
       <c r="T99" t="s" s="2">
-        <v>80</v>
+        <v>455</v>
       </c>
       <c r="U99" t="s" s="2">
         <v>80</v>
@@ -14336,35 +14390,37 @@
         <v>80</v>
       </c>
       <c r="AB99" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="AC99" s="2"/>
+        <v>80</v>
+      </c>
+      <c r="AC99" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="AD99" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE99" t="s" s="2">
-        <v>153</v>
+        <v>80</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>168</v>
+        <v>456</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH99" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI99" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK99" t="s" s="2">
-        <v>80</v>
+        <v>457</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>80</v>
+        <v>458</v>
       </c>
       <c r="AM99" t="s" s="2">
         <v>80</v>
@@ -14381,16 +14437,14 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="C100" t="s" s="2">
-        <v>524</v>
-      </c>
+        <v>459</v>
+      </c>
+      <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
-        <v>80</v>
+        <v>460</v>
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
@@ -14400,22 +14454,22 @@
         <v>89</v>
       </c>
       <c r="H100" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="I100" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J100" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>525</v>
+        <v>159</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>526</v>
+        <v>461</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>527</v>
+        <v>462</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -14442,13 +14496,13 @@
         <v>80</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>80</v>
+        <v>185</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>80</v>
+        <v>463</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>80</v>
+        <v>464</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>80</v>
@@ -14466,49 +14520,49 @@
         <v>80</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>168</v>
+        <v>465</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH100" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI100" t="s" s="2">
-        <v>528</v>
+        <v>80</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>80</v>
+        <v>466</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>529</v>
+        <v>467</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>80</v>
+        <v>468</v>
       </c>
       <c r="AN100" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>80</v>
+        <v>583</v>
       </c>
       <c r="AP100" t="s" s="2">
-        <v>80</v>
+        <v>584</v>
       </c>
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>531</v>
+        <v>469</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>80</v>
+        <v>470</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
@@ -14518,22 +14572,22 @@
         <v>89</v>
       </c>
       <c r="H101" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="I101" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J101" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K101" t="s" s="2">
         <v>159</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>160</v>
+        <v>471</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>161</v>
+        <v>472</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -14548,7 +14602,7 @@
         <v>80</v>
       </c>
       <c r="T101" t="s" s="2">
-        <v>80</v>
+        <v>473</v>
       </c>
       <c r="U101" t="s" s="2">
         <v>80</v>
@@ -14584,7 +14638,7 @@
         <v>80</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>162</v>
+        <v>474</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>78</v>
@@ -14596,33 +14650,33 @@
         <v>80</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="AK101" t="s" s="2">
-        <v>80</v>
+        <v>475</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>163</v>
+        <v>476</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>80</v>
+        <v>477</v>
       </c>
       <c r="AN101" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>80</v>
+        <v>586</v>
       </c>
       <c r="AP101" t="s" s="2">
-        <v>80</v>
+        <v>587</v>
       </c>
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>582</v>
+        <v>588</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>533</v>
+        <v>478</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14633,27 +14687,29 @@
         <v>78</v>
       </c>
       <c r="G102" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H102" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="I102" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J102" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>521</v>
+        <v>479</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="N102" s="2"/>
+        <v>480</v>
+      </c>
+      <c r="N102" t="s" s="2">
+        <v>481</v>
+      </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
         <v>80</v>
@@ -14690,57 +14746,57 @@
         <v>80</v>
       </c>
       <c r="AB102" t="s" s="2">
-        <v>166</v>
+        <v>80</v>
       </c>
       <c r="AC102" t="s" s="2">
-        <v>167</v>
+        <v>80</v>
       </c>
       <c r="AD102" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE102" t="s" s="2">
-        <v>153</v>
+        <v>80</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>168</v>
+        <v>482</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH102" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI102" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>80</v>
+        <v>483</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>80</v>
+        <v>484</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>80</v>
+        <v>485</v>
       </c>
       <c r="AN102" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO102" t="s" s="2">
-        <v>80</v>
+        <v>589</v>
       </c>
       <c r="AP102" t="s" s="2">
-        <v>80</v>
+        <v>584</v>
       </c>
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>583</v>
+        <v>590</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>535</v>
+        <v>515</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14748,7 +14804,7 @@
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G103" t="s" s="2">
         <v>89</v>
@@ -14763,24 +14819,22 @@
         <v>80</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>103</v>
+        <v>159</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>536</v>
+        <v>516</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>537</v>
-      </c>
-      <c r="N103" t="s" s="2">
-        <v>538</v>
-      </c>
+        <v>517</v>
+      </c>
+      <c r="N103" s="2"/>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q103" s="2"/>
       <c r="R103" t="s" s="2">
-        <v>539</v>
+        <v>80</v>
       </c>
       <c r="S103" t="s" s="2">
         <v>80</v>
@@ -14822,10 +14876,10 @@
         <v>80</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>540</v>
+        <v>162</v>
       </c>
       <c r="AG103" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AH103" t="s" s="2">
         <v>89</v>
@@ -14840,7 +14894,7 @@
         <v>80</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>132</v>
+        <v>80</v>
       </c>
       <c r="AM103" t="s" s="2">
         <v>80</v>
@@ -14857,10 +14911,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>584</v>
+        <v>591</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>542</v>
+        <v>519</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14868,13 +14922,13 @@
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G104" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H104" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="I104" t="s" s="2">
         <v>80</v>
@@ -14883,13 +14937,13 @@
         <v>80</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>109</v>
+        <v>135</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>543</v>
+        <v>520</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>544</v>
+        <v>521</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -14916,49 +14970,47 @@
         <v>80</v>
       </c>
       <c r="X104" t="s" s="2">
-        <v>174</v>
+        <v>80</v>
       </c>
       <c r="Y104" t="s" s="2">
-        <v>545</v>
+        <v>80</v>
       </c>
       <c r="Z104" t="s" s="2">
-        <v>546</v>
+        <v>80</v>
       </c>
       <c r="AA104" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AB104" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC104" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="AC104" s="2"/>
       <c r="AD104" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE104" t="s" s="2">
-        <v>80</v>
+        <v>153</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>547</v>
+        <v>168</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH104" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI104" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK104" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>132</v>
+        <v>80</v>
       </c>
       <c r="AM104" t="s" s="2">
         <v>80</v>
@@ -14967,20 +15019,22 @@
         <v>80</v>
       </c>
       <c r="AO104" t="s" s="2">
-        <v>585</v>
+        <v>80</v>
       </c>
       <c r="AP104" t="s" s="2">
-        <v>572</v>
+        <v>80</v>
       </c>
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>586</v>
+        <v>592</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>550</v>
-      </c>
-      <c r="C105" s="2"/>
+        <v>519</v>
+      </c>
+      <c r="C105" t="s" s="2">
+        <v>523</v>
+      </c>
       <c r="D105" t="s" s="2">
         <v>80</v>
       </c>
@@ -15001,13 +15055,13 @@
         <v>80</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>159</v>
+        <v>524</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>551</v>
+        <v>525</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>552</v>
+        <v>526</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -15031,7 +15085,7 @@
         <v>80</v>
       </c>
       <c r="W105" t="s" s="2">
-        <v>553</v>
+        <v>80</v>
       </c>
       <c r="X105" t="s" s="2">
         <v>80</v>
@@ -15058,25 +15112,25 @@
         <v>80</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>554</v>
+        <v>168</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH105" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI105" t="s" s="2">
-        <v>80</v>
+        <v>527</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>80</v>
+        <v>140</v>
       </c>
       <c r="AK105" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>80</v>
+        <v>528</v>
       </c>
       <c r="AM105" t="s" s="2">
         <v>80</v>
@@ -15093,10 +15147,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>587</v>
+        <v>593</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>486</v>
+        <v>530</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15116,21 +15170,19 @@
         <v>80</v>
       </c>
       <c r="J106" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>212</v>
+        <v>159</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>487</v>
+        <v>160</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>488</v>
+        <v>161</v>
       </c>
       <c r="N106" s="2"/>
-      <c r="O106" t="s" s="2">
-        <v>489</v>
-      </c>
+      <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
         <v>80</v>
       </c>
@@ -15142,7 +15194,7 @@
         <v>80</v>
       </c>
       <c r="T106" t="s" s="2">
-        <v>490</v>
+        <v>80</v>
       </c>
       <c r="U106" t="s" s="2">
         <v>80</v>
@@ -15178,7 +15230,7 @@
         <v>80</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>491</v>
+        <v>162</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>78</v>
@@ -15190,16 +15242,16 @@
         <v>80</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="AK106" t="s" s="2">
-        <v>492</v>
+        <v>80</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>342</v>
+        <v>163</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>218</v>
+        <v>80</v>
       </c>
       <c r="AN106" t="s" s="2">
         <v>80</v>
@@ -15213,10 +15265,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>588</v>
+        <v>594</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>589</v>
+        <v>532</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15227,7 +15279,7 @@
         <v>78</v>
       </c>
       <c r="G107" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H107" t="s" s="2">
         <v>80</v>
@@ -15239,13 +15291,13 @@
         <v>80</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>159</v>
+        <v>135</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>160</v>
+        <v>520</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>161</v>
+        <v>521</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -15284,37 +15336,37 @@
         <v>80</v>
       </c>
       <c r="AB107" t="s" s="2">
-        <v>80</v>
+        <v>166</v>
       </c>
       <c r="AC107" t="s" s="2">
-        <v>80</v>
+        <v>167</v>
       </c>
       <c r="AD107" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE107" t="s" s="2">
-        <v>80</v>
+        <v>153</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH107" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI107" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>80</v>
+        <v>140</v>
       </c>
       <c r="AK107" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>163</v>
+        <v>80</v>
       </c>
       <c r="AM107" t="s" s="2">
         <v>80</v>
@@ -15331,21 +15383,21 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>591</v>
+        <v>534</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
-        <v>134</v>
+        <v>80</v>
       </c>
       <c r="E108" s="2"/>
       <c r="F108" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G108" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H108" t="s" s="2">
         <v>80</v>
@@ -15357,16 +15409,16 @@
         <v>80</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>135</v>
+        <v>103</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>136</v>
+        <v>535</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>165</v>
+        <v>536</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>138</v>
+        <v>537</v>
       </c>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
@@ -15374,7 +15426,7 @@
       </c>
       <c r="Q108" s="2"/>
       <c r="R108" t="s" s="2">
-        <v>80</v>
+        <v>538</v>
       </c>
       <c r="S108" t="s" s="2">
         <v>80</v>
@@ -15404,37 +15456,37 @@
         <v>80</v>
       </c>
       <c r="AB108" t="s" s="2">
-        <v>166</v>
+        <v>80</v>
       </c>
       <c r="AC108" t="s" s="2">
-        <v>167</v>
+        <v>80</v>
       </c>
       <c r="AD108" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE108" t="s" s="2">
-        <v>153</v>
+        <v>80</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>168</v>
+        <v>539</v>
       </c>
       <c r="AG108" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AH108" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI108" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>140</v>
+        <v>80</v>
       </c>
       <c r="AK108" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>163</v>
+        <v>132</v>
       </c>
       <c r="AM108" t="s" s="2">
         <v>80</v>
@@ -15451,10 +15503,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>593</v>
+        <v>541</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15462,7 +15514,7 @@
       </c>
       <c r="E109" s="2"/>
       <c r="F109" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G109" t="s" s="2">
         <v>89</v>
@@ -15474,20 +15526,18 @@
         <v>80</v>
       </c>
       <c r="J109" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>246</v>
+        <v>109</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>247</v>
+        <v>542</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="N109" t="s" s="2">
-        <v>249</v>
-      </c>
+        <v>543</v>
+      </c>
+      <c r="N109" s="2"/>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
         <v>80</v>
@@ -15512,13 +15562,13 @@
         <v>80</v>
       </c>
       <c r="X109" t="s" s="2">
-        <v>80</v>
+        <v>174</v>
       </c>
       <c r="Y109" t="s" s="2">
-        <v>80</v>
+        <v>544</v>
       </c>
       <c r="Z109" t="s" s="2">
-        <v>80</v>
+        <v>545</v>
       </c>
       <c r="AA109" t="s" s="2">
         <v>80</v>
@@ -15536,7 +15586,7 @@
         <v>80</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>250</v>
+        <v>546</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>78</v>
@@ -15545,16 +15595,16 @@
         <v>89</v>
       </c>
       <c r="AI109" t="s" s="2">
-        <v>251</v>
+        <v>80</v>
       </c>
       <c r="AJ109" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>252</v>
+        <v>80</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>253</v>
+        <v>132</v>
       </c>
       <c r="AM109" t="s" s="2">
         <v>80</v>
@@ -15563,20 +15613,22 @@
         <v>80</v>
       </c>
       <c r="AO109" t="s" s="2">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="AP109" t="s" s="2">
-        <v>595</v>
+        <v>584</v>
       </c>
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>597</v>
-      </c>
-      <c r="C110" s="2"/>
+        <v>519</v>
+      </c>
+      <c r="C110" t="s" s="2">
+        <v>549</v>
+      </c>
       <c r="D110" t="s" s="2">
         <v>80</v>
       </c>
@@ -15588,33 +15640,31 @@
         <v>89</v>
       </c>
       <c r="H110" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="I110" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J110" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>246</v>
+        <v>550</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>257</v>
+        <v>551</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>258</v>
+        <v>552</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>259</v>
+        <v>553</v>
       </c>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="Q110" t="s" s="2">
-        <v>260</v>
-      </c>
+      <c r="Q110" s="2"/>
       <c r="R110" t="s" s="2">
         <v>80</v>
       </c>
@@ -15658,25 +15708,25 @@
         <v>80</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>261</v>
+        <v>168</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH110" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI110" t="s" s="2">
-        <v>251</v>
+        <v>527</v>
       </c>
       <c r="AJ110" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK110" t="s" s="2">
-        <v>262</v>
+        <v>132</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>263</v>
+        <v>132</v>
       </c>
       <c r="AM110" t="s" s="2">
         <v>80</v>
@@ -15685,18 +15735,18 @@
         <v>80</v>
       </c>
       <c r="AO110" t="s" s="2">
-        <v>598</v>
+        <v>80</v>
       </c>
       <c r="AP110" t="s" s="2">
-        <v>599</v>
+        <v>80</v>
       </c>
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>600</v>
+        <v>530</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15716,21 +15766,19 @@
         <v>80</v>
       </c>
       <c r="J111" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>109</v>
+        <v>159</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>601</v>
+        <v>160</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>602</v>
+        <v>161</v>
       </c>
       <c r="N111" s="2"/>
-      <c r="O111" t="s" s="2">
-        <v>603</v>
-      </c>
+      <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
         <v>80</v>
       </c>
@@ -15754,13 +15802,13 @@
         <v>80</v>
       </c>
       <c r="X111" t="s" s="2">
-        <v>174</v>
+        <v>80</v>
       </c>
       <c r="Y111" t="s" s="2">
-        <v>604</v>
+        <v>80</v>
       </c>
       <c r="Z111" t="s" s="2">
-        <v>605</v>
+        <v>80</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>80</v>
@@ -15778,7 +15826,7 @@
         <v>80</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>600</v>
+        <v>162</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>78</v>
@@ -15790,16 +15838,16 @@
         <v>80</v>
       </c>
       <c r="AJ111" t="s" s="2">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>606</v>
+        <v>80</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>607</v>
+        <v>163</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>608</v>
+        <v>80</v>
       </c>
       <c r="AN111" t="s" s="2">
         <v>80</v>
@@ -15813,10 +15861,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>609</v>
+        <v>600</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>609</v>
+        <v>532</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15827,30 +15875,28 @@
         <v>78</v>
       </c>
       <c r="G112" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H112" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="I112" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J112" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>610</v>
+        <v>135</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>611</v>
+        <v>520</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>612</v>
+        <v>521</v>
       </c>
       <c r="N112" s="2"/>
-      <c r="O112" t="s" s="2">
-        <v>613</v>
-      </c>
+      <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
         <v>80</v>
       </c>
@@ -15886,57 +15932,57 @@
         <v>80</v>
       </c>
       <c r="AB112" t="s" s="2">
-        <v>80</v>
+        <v>166</v>
       </c>
       <c r="AC112" t="s" s="2">
-        <v>80</v>
+        <v>167</v>
       </c>
       <c r="AD112" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE112" t="s" s="2">
-        <v>80</v>
+        <v>153</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>609</v>
+        <v>168</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH112" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI112" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ112" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK112" t="s" s="2">
-        <v>614</v>
+        <v>80</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>615</v>
+        <v>80</v>
       </c>
       <c r="AM112" t="s" s="2">
-        <v>616</v>
+        <v>80</v>
       </c>
       <c r="AN112" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO112" t="s" s="2">
-        <v>617</v>
+        <v>80</v>
       </c>
       <c r="AP112" t="s" s="2">
-        <v>618</v>
+        <v>80</v>
       </c>
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>619</v>
+        <v>601</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>619</v>
+        <v>534</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15944,10 +15990,10 @@
       </c>
       <c r="E113" s="2"/>
       <c r="F113" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G113" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H113" t="s" s="2">
         <v>80</v>
@@ -15959,24 +16005,24 @@
         <v>80</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>620</v>
+        <v>103</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>621</v>
+        <v>535</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>622</v>
-      </c>
-      <c r="N113" s="2"/>
-      <c r="O113" t="s" s="2">
-        <v>623</v>
-      </c>
+        <v>536</v>
+      </c>
+      <c r="N113" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q113" s="2"/>
       <c r="R113" t="s" s="2">
-        <v>80</v>
+        <v>557</v>
       </c>
       <c r="S113" t="s" s="2">
         <v>80</v>
@@ -16018,28 +16064,28 @@
         <v>80</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>619</v>
+        <v>539</v>
       </c>
       <c r="AG113" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AH113" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI113" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="AK113" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>624</v>
+        <v>132</v>
       </c>
       <c r="AM113" t="s" s="2">
-        <v>625</v>
+        <v>80</v>
       </c>
       <c r="AN113" t="s" s="2">
         <v>80</v>
@@ -16053,10 +16099,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>626</v>
+        <v>602</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>626</v>
+        <v>541</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16064,10 +16110,10 @@
       </c>
       <c r="E114" s="2"/>
       <c r="F114" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G114" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H114" t="s" s="2">
         <v>80</v>
@@ -16079,13 +16125,13 @@
         <v>80</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>627</v>
+        <v>559</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>628</v>
+        <v>542</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>629</v>
+        <v>543</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
@@ -16097,7 +16143,7 @@
         <v>80</v>
       </c>
       <c r="S114" t="s" s="2">
-        <v>80</v>
+        <v>560</v>
       </c>
       <c r="T114" t="s" s="2">
         <v>80</v>
@@ -16136,13 +16182,13 @@
         <v>80</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>626</v>
+        <v>546</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH114" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI114" t="s" s="2">
         <v>80</v>
@@ -16151,13 +16197,13 @@
         <v>101</v>
       </c>
       <c r="AK114" t="s" s="2">
-        <v>630</v>
+        <v>80</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>631</v>
+        <v>132</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>632</v>
+        <v>80</v>
       </c>
       <c r="AN114" t="s" s="2">
         <v>80</v>
@@ -16171,10 +16217,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>633</v>
+        <v>603</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>633</v>
+        <v>562</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16200,10 +16246,10 @@
         <v>159</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>160</v>
+        <v>563</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>161</v>
+        <v>564</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" s="2"/>
@@ -16227,7 +16273,7 @@
         <v>80</v>
       </c>
       <c r="W115" t="s" s="2">
-        <v>80</v>
+        <v>565</v>
       </c>
       <c r="X115" t="s" s="2">
         <v>80</v>
@@ -16254,7 +16300,7 @@
         <v>80</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>162</v>
+        <v>566</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>78</v>
@@ -16272,7 +16318,7 @@
         <v>80</v>
       </c>
       <c r="AL115" t="s" s="2">
-        <v>163</v>
+        <v>80</v>
       </c>
       <c r="AM115" t="s" s="2">
         <v>80</v>
@@ -16289,21 +16335,21 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>634</v>
+        <v>604</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>634</v>
+        <v>486</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
-        <v>134</v>
+        <v>80</v>
       </c>
       <c r="E116" s="2"/>
       <c r="F116" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G116" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H116" t="s" s="2">
         <v>80</v>
@@ -16312,21 +16358,21 @@
         <v>80</v>
       </c>
       <c r="J116" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>135</v>
+        <v>212</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>136</v>
+        <v>487</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="N116" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O116" s="2"/>
+        <v>488</v>
+      </c>
+      <c r="N116" s="2"/>
+      <c r="O116" t="s" s="2">
+        <v>489</v>
+      </c>
       <c r="P116" t="s" s="2">
         <v>80</v>
       </c>
@@ -16338,7 +16384,7 @@
         <v>80</v>
       </c>
       <c r="T116" t="s" s="2">
-        <v>80</v>
+        <v>490</v>
       </c>
       <c r="U116" t="s" s="2">
         <v>80</v>
@@ -16374,28 +16420,28 @@
         <v>80</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>168</v>
+        <v>491</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH116" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI116" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ116" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK116" t="s" s="2">
-        <v>80</v>
+        <v>492</v>
       </c>
       <c r="AL116" t="s" s="2">
-        <v>163</v>
+        <v>342</v>
       </c>
       <c r="AM116" t="s" s="2">
-        <v>80</v>
+        <v>218</v>
       </c>
       <c r="AN116" t="s" s="2">
         <v>80</v>
@@ -16409,46 +16455,42 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>635</v>
+        <v>605</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>635</v>
+        <v>606</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
-        <v>636</v>
+        <v>80</v>
       </c>
       <c r="E117" s="2"/>
       <c r="F117" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G117" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H117" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I117" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="J117" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>637</v>
+        <v>160</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>638</v>
-      </c>
-      <c r="N117" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O117" t="s" s="2">
-        <v>144</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="N117" s="2"/>
+      <c r="O117" s="2"/>
       <c r="P117" t="s" s="2">
         <v>80</v>
       </c>
@@ -16496,25 +16538,25 @@
         <v>80</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>639</v>
+        <v>162</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH117" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI117" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ117" t="s" s="2">
-        <v>140</v>
+        <v>80</v>
       </c>
       <c r="AK117" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL117" t="s" s="2">
-        <v>132</v>
+        <v>163</v>
       </c>
       <c r="AM117" t="s" s="2">
         <v>80</v>
@@ -16531,14 +16573,14 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>640</v>
+        <v>607</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>640</v>
+        <v>608</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
-        <v>80</v>
+        <v>134</v>
       </c>
       <c r="E118" s="2"/>
       <c r="F118" t="s" s="2">
@@ -16557,18 +16599,18 @@
         <v>80</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>147</v>
+        <v>135</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>641</v>
+        <v>136</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>642</v>
-      </c>
-      <c r="N118" s="2"/>
-      <c r="O118" t="s" s="2">
-        <v>643</v>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="N118" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
         <v>80</v>
       </c>
@@ -16604,19 +16646,19 @@
         <v>80</v>
       </c>
       <c r="AB118" t="s" s="2">
-        <v>80</v>
+        <v>166</v>
       </c>
       <c r="AC118" t="s" s="2">
-        <v>80</v>
+        <v>167</v>
       </c>
       <c r="AD118" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE118" t="s" s="2">
-        <v>80</v>
+        <v>153</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>640</v>
+        <v>168</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>78</v>
@@ -16628,13 +16670,13 @@
         <v>80</v>
       </c>
       <c r="AJ118" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK118" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL118" t="s" s="2">
-        <v>644</v>
+        <v>163</v>
       </c>
       <c r="AM118" t="s" s="2">
         <v>80</v>
@@ -16651,10 +16693,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>645</v>
+        <v>609</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>645</v>
+        <v>610</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16662,30 +16704,32 @@
       </c>
       <c r="E119" s="2"/>
       <c r="F119" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G119" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H119" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="I119" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J119" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>180</v>
+        <v>246</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>646</v>
+        <v>247</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>647</v>
-      </c>
-      <c r="N119" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="N119" t="s" s="2">
+        <v>249</v>
+      </c>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
         <v>80</v>
@@ -16710,13 +16754,13 @@
         <v>80</v>
       </c>
       <c r="X119" t="s" s="2">
-        <v>648</v>
+        <v>80</v>
       </c>
       <c r="Y119" t="s" s="2">
-        <v>649</v>
+        <v>80</v>
       </c>
       <c r="Z119" t="s" s="2">
-        <v>650</v>
+        <v>80</v>
       </c>
       <c r="AA119" t="s" s="2">
         <v>80</v>
@@ -16734,45 +16778,45 @@
         <v>80</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>645</v>
+        <v>250</v>
       </c>
       <c r="AG119" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AH119" t="s" s="2">
         <v>89</v>
       </c>
       <c r="AI119" t="s" s="2">
-        <v>80</v>
+        <v>251</v>
       </c>
       <c r="AJ119" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK119" t="s" s="2">
-        <v>80</v>
+        <v>252</v>
       </c>
       <c r="AL119" t="s" s="2">
-        <v>631</v>
+        <v>253</v>
       </c>
       <c r="AM119" t="s" s="2">
-        <v>651</v>
+        <v>80</v>
       </c>
       <c r="AN119" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO119" t="s" s="2">
-        <v>80</v>
+        <v>611</v>
       </c>
       <c r="AP119" t="s" s="2">
-        <v>80</v>
+        <v>612</v>
       </c>
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>652</v>
+        <v>613</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>652</v>
+        <v>614</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16786,29 +16830,33 @@
         <v>89</v>
       </c>
       <c r="H120" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="I120" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J120" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>159</v>
+        <v>246</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>160</v>
+        <v>257</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="N120" s="2"/>
+        <v>258</v>
+      </c>
+      <c r="N120" t="s" s="2">
+        <v>259</v>
+      </c>
       <c r="O120" s="2"/>
       <c r="P120" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="Q120" s="2"/>
+      <c r="Q120" t="s" s="2">
+        <v>260</v>
+      </c>
       <c r="R120" t="s" s="2">
         <v>80</v>
       </c>
@@ -16852,7 +16900,7 @@
         <v>80</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>162</v>
+        <v>261</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>78</v>
@@ -16861,16 +16909,16 @@
         <v>89</v>
       </c>
       <c r="AI120" t="s" s="2">
-        <v>80</v>
+        <v>251</v>
       </c>
       <c r="AJ120" t="s" s="2">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="AK120" t="s" s="2">
-        <v>80</v>
+        <v>262</v>
       </c>
       <c r="AL120" t="s" s="2">
-        <v>163</v>
+        <v>263</v>
       </c>
       <c r="AM120" t="s" s="2">
         <v>80</v>
@@ -16879,29 +16927,29 @@
         <v>80</v>
       </c>
       <c r="AO120" t="s" s="2">
-        <v>80</v>
+        <v>615</v>
       </c>
       <c r="AP120" t="s" s="2">
-        <v>80</v>
+        <v>616</v>
       </c>
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>653</v>
+        <v>617</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>653</v>
+        <v>617</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
-        <v>134</v>
+        <v>80</v>
       </c>
       <c r="E121" s="2"/>
       <c r="F121" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G121" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H121" t="s" s="2">
         <v>80</v>
@@ -16910,21 +16958,21 @@
         <v>80</v>
       </c>
       <c r="J121" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>135</v>
+        <v>109</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>136</v>
+        <v>618</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="N121" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O121" s="2"/>
+        <v>619</v>
+      </c>
+      <c r="N121" s="2"/>
+      <c r="O121" t="s" s="2">
+        <v>620</v>
+      </c>
       <c r="P121" t="s" s="2">
         <v>80</v>
       </c>
@@ -16948,52 +16996,52 @@
         <v>80</v>
       </c>
       <c r="X121" t="s" s="2">
-        <v>80</v>
+        <v>174</v>
       </c>
       <c r="Y121" t="s" s="2">
-        <v>80</v>
+        <v>621</v>
       </c>
       <c r="Z121" t="s" s="2">
-        <v>80</v>
+        <v>622</v>
       </c>
       <c r="AA121" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AB121" t="s" s="2">
-        <v>166</v>
+        <v>80</v>
       </c>
       <c r="AC121" t="s" s="2">
-        <v>167</v>
+        <v>80</v>
       </c>
       <c r="AD121" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE121" t="s" s="2">
-        <v>153</v>
+        <v>80</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>168</v>
+        <v>617</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH121" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI121" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ121" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK121" t="s" s="2">
-        <v>80</v>
+        <v>623</v>
       </c>
       <c r="AL121" t="s" s="2">
-        <v>163</v>
+        <v>624</v>
       </c>
       <c r="AM121" t="s" s="2">
-        <v>80</v>
+        <v>625</v>
       </c>
       <c r="AN121" t="s" s="2">
         <v>80</v>
@@ -17007,10 +17055,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>654</v>
+        <v>626</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>654</v>
+        <v>626</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -17021,10 +17069,10 @@
         <v>78</v>
       </c>
       <c r="G122" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H122" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="I122" t="s" s="2">
         <v>80</v>
@@ -17033,19 +17081,17 @@
         <v>90</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>655</v>
+        <v>627</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>656</v>
+        <v>628</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>657</v>
-      </c>
-      <c r="N122" t="s" s="2">
-        <v>658</v>
-      </c>
+        <v>629</v>
+      </c>
+      <c r="N122" s="2"/>
       <c r="O122" t="s" s="2">
-        <v>659</v>
+        <v>630</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>80</v>
@@ -17094,13 +17140,13 @@
         <v>80</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>660</v>
+        <v>626</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH122" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI122" t="s" s="2">
         <v>80</v>
@@ -17109,30 +17155,30 @@
         <v>101</v>
       </c>
       <c r="AK122" t="s" s="2">
-        <v>661</v>
+        <v>631</v>
       </c>
       <c r="AL122" t="s" s="2">
-        <v>662</v>
+        <v>632</v>
       </c>
       <c r="AM122" t="s" s="2">
-        <v>80</v>
+        <v>633</v>
       </c>
       <c r="AN122" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO122" t="s" s="2">
-        <v>80</v>
+        <v>634</v>
       </c>
       <c r="AP122" t="s" s="2">
-        <v>80</v>
+        <v>635</v>
       </c>
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>663</v>
+        <v>636</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>663</v>
+        <v>636</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -17143,31 +17189,29 @@
         <v>78</v>
       </c>
       <c r="G123" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H123" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="I123" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J123" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>159</v>
+        <v>637</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>664</v>
+        <v>638</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>665</v>
-      </c>
-      <c r="N123" t="s" s="2">
-        <v>666</v>
-      </c>
+        <v>639</v>
+      </c>
+      <c r="N123" s="2"/>
       <c r="O123" t="s" s="2">
-        <v>667</v>
+        <v>640</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>80</v>
@@ -17216,13 +17260,13 @@
         <v>80</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>668</v>
+        <v>636</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH123" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI123" t="s" s="2">
         <v>80</v>
@@ -17231,19 +17275,19 @@
         <v>101</v>
       </c>
       <c r="AK123" t="s" s="2">
-        <v>669</v>
+        <v>80</v>
       </c>
       <c r="AL123" t="s" s="2">
-        <v>670</v>
+        <v>641</v>
       </c>
       <c r="AM123" t="s" s="2">
-        <v>80</v>
+        <v>642</v>
       </c>
       <c r="AN123" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO123" t="s" s="2">
-        <v>671</v>
+        <v>80</v>
       </c>
       <c r="AP123" t="s" s="2">
         <v>80</v>
@@ -17251,10 +17295,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>672</v>
+        <v>643</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>672</v>
+        <v>643</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17265,7 +17309,7 @@
         <v>78</v>
       </c>
       <c r="G124" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H124" t="s" s="2">
         <v>80</v>
@@ -17277,18 +17321,16 @@
         <v>80</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>212</v>
+        <v>644</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>673</v>
+        <v>645</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>674</v>
+        <v>646</v>
       </c>
       <c r="N124" s="2"/>
-      <c r="O124" t="s" s="2">
-        <v>675</v>
-      </c>
+      <c r="O124" s="2"/>
       <c r="P124" t="s" s="2">
         <v>80</v>
       </c>
@@ -17336,13 +17378,13 @@
         <v>80</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>672</v>
+        <v>643</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH124" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI124" t="s" s="2">
         <v>80</v>
@@ -17351,13 +17393,13 @@
         <v>101</v>
       </c>
       <c r="AK124" t="s" s="2">
-        <v>80</v>
+        <v>647</v>
       </c>
       <c r="AL124" t="s" s="2">
-        <v>676</v>
+        <v>648</v>
       </c>
       <c r="AM124" t="s" s="2">
-        <v>677</v>
+        <v>649</v>
       </c>
       <c r="AN124" t="s" s="2">
         <v>80</v>
@@ -17371,10 +17413,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>678</v>
+        <v>650</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>678</v>
+        <v>650</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17397,13 +17439,13 @@
         <v>80</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>220</v>
+        <v>159</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>679</v>
+        <v>160</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>680</v>
+        <v>161</v>
       </c>
       <c r="N125" s="2"/>
       <c r="O125" s="2"/>
@@ -17454,7 +17496,7 @@
         <v>80</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>678</v>
+        <v>162</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>78</v>
@@ -17466,13 +17508,13 @@
         <v>80</v>
       </c>
       <c r="AJ125" t="s" s="2">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="AK125" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL125" t="s" s="2">
-        <v>681</v>
+        <v>163</v>
       </c>
       <c r="AM125" t="s" s="2">
         <v>80</v>
@@ -17489,14 +17531,14 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>682</v>
+        <v>651</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>682</v>
+        <v>651</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
-        <v>80</v>
+        <v>134</v>
       </c>
       <c r="E126" s="2"/>
       <c r="F126" t="s" s="2">
@@ -17515,20 +17557,18 @@
         <v>80</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>180</v>
+        <v>135</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>683</v>
+        <v>136</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>684</v>
+        <v>165</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>685</v>
-      </c>
-      <c r="O126" t="s" s="2">
-        <v>686</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="O126" s="2"/>
       <c r="P126" t="s" s="2">
         <v>80</v>
       </c>
@@ -17552,13 +17592,13 @@
         <v>80</v>
       </c>
       <c r="X126" t="s" s="2">
-        <v>113</v>
+        <v>80</v>
       </c>
       <c r="Y126" t="s" s="2">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="Z126" t="s" s="2">
-        <v>115</v>
+        <v>80</v>
       </c>
       <c r="AA126" t="s" s="2">
         <v>80</v>
@@ -17576,7 +17616,7 @@
         <v>80</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>682</v>
+        <v>168</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>78</v>
@@ -17588,29 +17628,1231 @@
         <v>80</v>
       </c>
       <c r="AJ126" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK126" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL126" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="AM126" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN126" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO126" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP126" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="127" hidden="true">
+      <c r="A127" t="s" s="2">
+        <v>652</v>
+      </c>
+      <c r="B127" t="s" s="2">
+        <v>652</v>
+      </c>
+      <c r="C127" s="2"/>
+      <c r="D127" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="E127" s="2"/>
+      <c r="F127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G127" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H127" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I127" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="J127" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K127" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L127" t="s" s="2">
+        <v>654</v>
+      </c>
+      <c r="M127" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="N127" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="O127" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="P127" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q127" s="2"/>
+      <c r="R127" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S127" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T127" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U127" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V127" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W127" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X127" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y127" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z127" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA127" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB127" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC127" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD127" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE127" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF127" t="s" s="2">
+        <v>656</v>
+      </c>
+      <c r="AG127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH127" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI127" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ127" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK127" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL127" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AM127" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN127" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO127" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP127" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="128" hidden="true">
+      <c r="A128" t="s" s="2">
+        <v>657</v>
+      </c>
+      <c r="B128" t="s" s="2">
+        <v>657</v>
+      </c>
+      <c r="C128" s="2"/>
+      <c r="D128" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E128" s="2"/>
+      <c r="F128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G128" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H128" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I128" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J128" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K128" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="L128" t="s" s="2">
+        <v>658</v>
+      </c>
+      <c r="M128" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="N128" s="2"/>
+      <c r="O128" t="s" s="2">
+        <v>660</v>
+      </c>
+      <c r="P128" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q128" s="2"/>
+      <c r="R128" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S128" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T128" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U128" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V128" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W128" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X128" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y128" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z128" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA128" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB128" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC128" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD128" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE128" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF128" t="s" s="2">
+        <v>657</v>
+      </c>
+      <c r="AG128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH128" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI128" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ128" t="s" s="2">
         <v>101</v>
       </c>
-      <c r="AK126" t="s" s="2">
+      <c r="AK128" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL128" t="s" s="2">
+        <v>661</v>
+      </c>
+      <c r="AM128" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN128" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO128" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP128" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="129" hidden="true">
+      <c r="A129" t="s" s="2">
+        <v>662</v>
+      </c>
+      <c r="B129" t="s" s="2">
+        <v>662</v>
+      </c>
+      <c r="C129" s="2"/>
+      <c r="D129" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E129" s="2"/>
+      <c r="F129" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G129" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H129" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I129" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J129" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K129" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="L129" t="s" s="2">
+        <v>663</v>
+      </c>
+      <c r="M129" t="s" s="2">
+        <v>664</v>
+      </c>
+      <c r="N129" s="2"/>
+      <c r="O129" s="2"/>
+      <c r="P129" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q129" s="2"/>
+      <c r="R129" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S129" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T129" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U129" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V129" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W129" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X129" t="s" s="2">
+        <v>665</v>
+      </c>
+      <c r="Y129" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="Z129" t="s" s="2">
+        <v>667</v>
+      </c>
+      <c r="AA129" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB129" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC129" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD129" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE129" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF129" t="s" s="2">
+        <v>662</v>
+      </c>
+      <c r="AG129" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AH129" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI129" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ129" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK129" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL129" t="s" s="2">
+        <v>648</v>
+      </c>
+      <c r="AM129" t="s" s="2">
+        <v>668</v>
+      </c>
+      <c r="AN129" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO129" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP129" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="130" hidden="true">
+      <c r="A130" t="s" s="2">
+        <v>669</v>
+      </c>
+      <c r="B130" t="s" s="2">
+        <v>669</v>
+      </c>
+      <c r="C130" s="2"/>
+      <c r="D130" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E130" s="2"/>
+      <c r="F130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G130" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H130" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I130" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J130" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K130" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="L130" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="M130" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="N130" s="2"/>
+      <c r="O130" s="2"/>
+      <c r="P130" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q130" s="2"/>
+      <c r="R130" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S130" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T130" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U130" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V130" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W130" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X130" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y130" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z130" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA130" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB130" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC130" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD130" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE130" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF130" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AG130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH130" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI130" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ130" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK130" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL130" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="AM130" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN130" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO130" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP130" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="131" hidden="true">
+      <c r="A131" t="s" s="2">
+        <v>670</v>
+      </c>
+      <c r="B131" t="s" s="2">
+        <v>670</v>
+      </c>
+      <c r="C131" s="2"/>
+      <c r="D131" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="E131" s="2"/>
+      <c r="F131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G131" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H131" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I131" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J131" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K131" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L131" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="M131" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="N131" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="O131" s="2"/>
+      <c r="P131" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q131" s="2"/>
+      <c r="R131" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S131" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T131" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U131" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V131" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W131" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X131" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y131" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z131" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA131" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB131" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="AC131" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AD131" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE131" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AF131" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="AG131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH131" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI131" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ131" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK131" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL131" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="AM131" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN131" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO131" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP131" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="132" hidden="true">
+      <c r="A132" t="s" s="2">
+        <v>671</v>
+      </c>
+      <c r="B132" t="s" s="2">
+        <v>671</v>
+      </c>
+      <c r="C132" s="2"/>
+      <c r="D132" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E132" s="2"/>
+      <c r="F132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G132" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H132" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I132" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J132" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K132" t="s" s="2">
+        <v>672</v>
+      </c>
+      <c r="L132" t="s" s="2">
+        <v>673</v>
+      </c>
+      <c r="M132" t="s" s="2">
+        <v>674</v>
+      </c>
+      <c r="N132" t="s" s="2">
+        <v>675</v>
+      </c>
+      <c r="O132" t="s" s="2">
+        <v>676</v>
+      </c>
+      <c r="P132" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q132" s="2"/>
+      <c r="R132" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S132" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T132" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U132" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V132" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W132" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X132" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y132" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z132" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA132" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB132" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC132" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD132" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE132" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF132" t="s" s="2">
+        <v>677</v>
+      </c>
+      <c r="AG132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH132" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI132" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ132" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK132" t="s" s="2">
+        <v>678</v>
+      </c>
+      <c r="AL132" t="s" s="2">
+        <v>679</v>
+      </c>
+      <c r="AM132" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN132" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO132" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP132" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="133" hidden="true">
+      <c r="A133" t="s" s="2">
+        <v>680</v>
+      </c>
+      <c r="B133" t="s" s="2">
+        <v>680</v>
+      </c>
+      <c r="C133" s="2"/>
+      <c r="D133" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E133" s="2"/>
+      <c r="F133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G133" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H133" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="I133" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J133" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K133" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="L133" t="s" s="2">
+        <v>681</v>
+      </c>
+      <c r="M133" t="s" s="2">
+        <v>682</v>
+      </c>
+      <c r="N133" t="s" s="2">
+        <v>683</v>
+      </c>
+      <c r="O133" t="s" s="2">
+        <v>684</v>
+      </c>
+      <c r="P133" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q133" s="2"/>
+      <c r="R133" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S133" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T133" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U133" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V133" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W133" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X133" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y133" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z133" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA133" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB133" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC133" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD133" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE133" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF133" t="s" s="2">
+        <v>685</v>
+      </c>
+      <c r="AG133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH133" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI133" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ133" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK133" t="s" s="2">
+        <v>686</v>
+      </c>
+      <c r="AL133" t="s" s="2">
         <v>687</v>
       </c>
-      <c r="AL126" t="s" s="2">
+      <c r="AM133" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN133" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO133" t="s" s="2">
         <v>688</v>
       </c>
-      <c r="AM126" t="s" s="2">
+      <c r="AP133" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="134" hidden="true">
+      <c r="A134" t="s" s="2">
         <v>689</v>
       </c>
-      <c r="AN126" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO126" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP126" t="s" s="2">
+      <c r="B134" t="s" s="2">
+        <v>689</v>
+      </c>
+      <c r="C134" s="2"/>
+      <c r="D134" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E134" s="2"/>
+      <c r="F134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G134" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H134" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I134" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J134" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K134" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="L134" t="s" s="2">
+        <v>690</v>
+      </c>
+      <c r="M134" t="s" s="2">
+        <v>691</v>
+      </c>
+      <c r="N134" s="2"/>
+      <c r="O134" t="s" s="2">
+        <v>692</v>
+      </c>
+      <c r="P134" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q134" s="2"/>
+      <c r="R134" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S134" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T134" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U134" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V134" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W134" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X134" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y134" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z134" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA134" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB134" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC134" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD134" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE134" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF134" t="s" s="2">
+        <v>689</v>
+      </c>
+      <c r="AG134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH134" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI134" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ134" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK134" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL134" t="s" s="2">
+        <v>693</v>
+      </c>
+      <c r="AM134" t="s" s="2">
+        <v>694</v>
+      </c>
+      <c r="AN134" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO134" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP134" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="135" hidden="true">
+      <c r="A135" t="s" s="2">
+        <v>695</v>
+      </c>
+      <c r="B135" t="s" s="2">
+        <v>695</v>
+      </c>
+      <c r="C135" s="2"/>
+      <c r="D135" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E135" s="2"/>
+      <c r="F135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G135" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H135" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I135" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J135" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K135" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="L135" t="s" s="2">
+        <v>696</v>
+      </c>
+      <c r="M135" t="s" s="2">
+        <v>697</v>
+      </c>
+      <c r="N135" s="2"/>
+      <c r="O135" s="2"/>
+      <c r="P135" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q135" s="2"/>
+      <c r="R135" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S135" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T135" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U135" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V135" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W135" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X135" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y135" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z135" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA135" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB135" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC135" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD135" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE135" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF135" t="s" s="2">
+        <v>695</v>
+      </c>
+      <c r="AG135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH135" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI135" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ135" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK135" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL135" t="s" s="2">
+        <v>698</v>
+      </c>
+      <c r="AM135" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN135" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO135" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP135" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="136" hidden="true">
+      <c r="A136" t="s" s="2">
+        <v>699</v>
+      </c>
+      <c r="B136" t="s" s="2">
+        <v>699</v>
+      </c>
+      <c r="C136" s="2"/>
+      <c r="D136" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E136" s="2"/>
+      <c r="F136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G136" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H136" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I136" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J136" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K136" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="L136" t="s" s="2">
+        <v>700</v>
+      </c>
+      <c r="M136" t="s" s="2">
+        <v>701</v>
+      </c>
+      <c r="N136" t="s" s="2">
+        <v>702</v>
+      </c>
+      <c r="O136" t="s" s="2">
+        <v>703</v>
+      </c>
+      <c r="P136" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q136" s="2"/>
+      <c r="R136" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S136" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T136" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U136" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V136" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W136" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X136" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="Y136" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="Z136" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AA136" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB136" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC136" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD136" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE136" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF136" t="s" s="2">
+        <v>699</v>
+      </c>
+      <c r="AG136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH136" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI136" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ136" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK136" t="s" s="2">
+        <v>704</v>
+      </c>
+      <c r="AL136" t="s" s="2">
+        <v>705</v>
+      </c>
+      <c r="AM136" t="s" s="2">
+        <v>706</v>
+      </c>
+      <c r="AN136" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO136" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP136" t="s" s="2">
         <v>80</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP126">
+  <autoFilter ref="A1:AP136">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -17620,7 +18862,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI125">
+  <conditionalFormatting sqref="A2:AI135">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.28.0</t>
+    <t>0.30.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-09T10:17:01+00:00</t>
+    <t>2024-03-21T09:40:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -231,6 +231,12 @@
     <t>Constraint(s)</t>
   </si>
   <si>
+    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
+  </si>
+  <si>
+    <t>Mapping: Clinical Data Warehouse (CDW)</t>
+  </si>
+  <si>
     <t>Mapping: HL7 v2 Mapping</t>
   </si>
   <si>
@@ -241,12 +247,6 @@
   </si>
   <si>
     <t>Mapping: FiveWs Pattern Mapping</t>
-  </si>
-  <si>
-    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
-  </si>
-  <si>
-    <t>Mapping: Clinical Data Warehouse (CDW)</t>
   </si>
   <si>
     <t xml:space="preserve">Provider
@@ -657,6 +657,12 @@
     <t>Identifier.value</t>
   </si>
   <si>
+    <t>415: source value from NEW PERSON - IEN (#200-.001)</t>
+  </si>
+  <si>
+    <t>SStaff.PrescribingProvider.VPID</t>
+  </si>
+  <si>
     <t>CX.1 / EI.1</t>
   </si>
   <si>
@@ -664,12 +670,6 @@
   </si>
   <si>
     <t>./Value</t>
-  </si>
-  <si>
-    <t>415: source value from NEW PERSON - IEN (#200-.001)</t>
-  </si>
-  <si>
-    <t>SStaff.PrescribingProvider.VPID</t>
   </si>
   <si>
     <t>Practitioner.identifier.period</t>
@@ -801,13 +801,13 @@
 </t>
   </si>
   <si>
+    <t>380: source value from NEW PERSON - EFFECTIVE DATE/TIME (#200-42)</t>
+  </si>
+  <si>
     <t>DR.1</t>
   </si>
   <si>
     <t>./low</t>
-  </si>
-  <si>
-    <t>380: source value from NEW PERSON - EFFECTIVE DATE/TIME (#200-42)</t>
   </si>
   <si>
     <t>Practitioner.identifier:NPI.period.end</t>
@@ -961,13 +961,13 @@
     <t>HumanName.text</t>
   </si>
   <si>
+    <t>382: source value from NEW PERSON - NAME COMPONENTS &gt; NAME COMPONENTS - (#200-10.1 &gt; 20 -)</t>
+  </si>
+  <si>
     <t>implied by XPN.11</t>
   </si>
   <si>
     <t>./formatted</t>
-  </si>
-  <si>
-    <t>382: source value from NEW PERSON - NAME COMPONENTS &gt; NAME COMPONENTS - (#200-10.1 &gt; 20 -)</t>
   </si>
   <si>
     <t>Practitioner.name.family</t>
@@ -1169,16 +1169,16 @@
     <t>ContactPoint.value</t>
   </si>
   <si>
+    <t>383: source value from NEW PERSON - PHONE (HOME) (#200-.131)</t>
+  </si>
+  <si>
+    <t>SStaff.PrescribingProvider.HomePhone,SStaff.SStaff.HomePhone</t>
+  </si>
+  <si>
     <t>XTN.1 (or XTN.12)</t>
   </si>
   <si>
     <t>./url</t>
-  </si>
-  <si>
-    <t>383: source value from NEW PERSON - PHONE (HOME) (#200-.131)</t>
-  </si>
-  <si>
-    <t>SStaff.PrescribingProvider.HomePhone,SStaff.SStaff.HomePhone</t>
   </si>
   <si>
     <t>Practitioner.telecom.use</t>
@@ -1968,6 +1968,12 @@
     <t>Needed for identification.</t>
   </si>
   <si>
+    <t>394: source value from NEW PERSON - DOB (#200-5)</t>
+  </si>
+  <si>
+    <t>SStaff.SStaff.DateOfBirth,Staff.Staff.DateofBirth</t>
+  </si>
+  <si>
     <t>STF-6</t>
   </si>
   <si>
@@ -1975,12 +1981,6 @@
   </si>
   <si>
     <t>(not represented in ServD)</t>
-  </si>
-  <si>
-    <t>394: source value from NEW PERSON - DOB (#200-5)</t>
-  </si>
-  <si>
-    <t>SStaff.SStaff.DateOfBirth,Staff.Staff.DateofBirth</t>
   </si>
   <si>
     <t>Practitioner.photo</t>
@@ -2138,13 +2138,13 @@
     <t>CodeableConcept.text</t>
   </si>
   <si>
+    <t>395: source value from NEW PERSON - DEGREE (#200-10.6)</t>
+  </si>
+  <si>
     <t>C*E.9. But note many systems use C*E.2 for this</t>
   </si>
   <si>
     <t>./originalText[mediaType/code="text/plain"]/data</t>
-  </si>
-  <si>
-    <t>395: source value from NEW PERSON - DEGREE (#200-10.6)</t>
   </si>
   <si>
     <t>Practitioner.qualification.period</t>
@@ -2553,12 +2553,12 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="107.3984375" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="102.6171875" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="52.3828125" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="97.1953125" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="66.4765625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="97.1953125" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="66.4765625" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="107.3984375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="102.6171875" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="52.3828125" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="36.91796875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2791,19 +2791,19 @@
         <v>84</v>
       </c>
       <c r="AK2" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL2" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM2" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="AL2" t="s" s="2">
+      <c r="AN2" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="AM2" t="s" s="2">
+      <c r="AO2" t="s" s="2">
         <v>87</v>
-      </c>
-      <c r="AN2" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO2" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AP2" t="s" s="2">
         <v>80</v>
@@ -3392,13 +3392,13 @@
         <v>80</v>
       </c>
       <c r="AL7" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM7" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN7" t="s" s="2">
         <v>124</v>
-      </c>
-      <c r="AM7" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN7" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AO7" t="s" s="2">
         <v>80</v>
@@ -3512,13 +3512,13 @@
         <v>80</v>
       </c>
       <c r="AL8" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM8" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN8" t="s" s="2">
         <v>132</v>
-      </c>
-      <c r="AM8" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN8" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AO8" t="s" s="2">
         <v>80</v>
@@ -3632,13 +3632,13 @@
         <v>80</v>
       </c>
       <c r="AL9" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM9" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN9" t="s" s="2">
         <v>132</v>
-      </c>
-      <c r="AM9" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN9" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AO9" t="s" s="2">
         <v>80</v>
@@ -3754,13 +3754,13 @@
         <v>80</v>
       </c>
       <c r="AL10" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM10" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN10" t="s" s="2">
         <v>132</v>
-      </c>
-      <c r="AM10" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN10" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AO10" t="s" s="2">
         <v>80</v>
@@ -3871,22 +3871,22 @@
         <v>101</v>
       </c>
       <c r="AK11" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL11" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM11" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="AL11" t="s" s="2">
+      <c r="AN11" t="s" s="2">
         <v>155</v>
       </c>
-      <c r="AM11" t="s" s="2">
+      <c r="AO11" t="s" s="2">
         <v>156</v>
       </c>
-      <c r="AN11" t="s" s="2">
+      <c r="AP11" t="s" s="2">
         <v>157</v>
-      </c>
-      <c r="AO11" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP11" t="s" s="2">
-        <v>80</v>
       </c>
     </row>
     <row r="12" hidden="true">
@@ -3992,13 +3992,13 @@
         <v>80</v>
       </c>
       <c r="AL12" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM12" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN12" t="s" s="2">
         <v>163</v>
-      </c>
-      <c r="AM12" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN12" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AO12" t="s" s="2">
         <v>80</v>
@@ -4112,13 +4112,13 @@
         <v>80</v>
       </c>
       <c r="AL13" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM13" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN13" t="s" s="2">
         <v>163</v>
-      </c>
-      <c r="AM13" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN13" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>80</v>
@@ -4231,16 +4231,16 @@
         <v>101</v>
       </c>
       <c r="AK14" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL14" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM14" t="s" s="2">
         <v>132</v>
       </c>
-      <c r="AL14" t="s" s="2">
+      <c r="AN14" t="s" s="2">
         <v>178</v>
-      </c>
-      <c r="AM14" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN14" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AO14" t="s" s="2">
         <v>80</v>
@@ -4353,16 +4353,16 @@
         <v>101</v>
       </c>
       <c r="AK15" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL15" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM15" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="AL15" t="s" s="2">
+      <c r="AN15" t="s" s="2">
         <v>178</v>
-      </c>
-      <c r="AM15" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN15" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AO15" t="s" s="2">
         <v>80</v>
@@ -4475,19 +4475,19 @@
         <v>101</v>
       </c>
       <c r="AK16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM16" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="AL16" t="s" s="2">
+      <c r="AN16" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="AM16" t="s" s="2">
+      <c r="AO16" t="s" s="2">
         <v>199</v>
-      </c>
-      <c r="AN16" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO16" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AP16" t="s" s="2">
         <v>80</v>
@@ -4604,13 +4604,13 @@
         <v>208</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>80</v>
+        <v>209</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AP17" t="s" s="2">
-        <v>210</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18" hidden="true">
@@ -4713,19 +4713,19 @@
         <v>101</v>
       </c>
       <c r="AK18" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL18" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM18" t="s" s="2">
         <v>216</v>
       </c>
-      <c r="AL18" t="s" s="2">
+      <c r="AN18" t="s" s="2">
         <v>217</v>
       </c>
-      <c r="AM18" t="s" s="2">
+      <c r="AO18" t="s" s="2">
         <v>218</v>
-      </c>
-      <c r="AN18" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO18" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>80</v>
@@ -4833,19 +4833,19 @@
         <v>101</v>
       </c>
       <c r="AK19" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL19" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM19" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="AL19" t="s" s="2">
+      <c r="AN19" t="s" s="2">
         <v>226</v>
       </c>
-      <c r="AM19" t="s" s="2">
+      <c r="AO19" t="s" s="2">
         <v>227</v>
-      </c>
-      <c r="AN19" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO19" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AP19" t="s" s="2">
         <v>80</v>
@@ -4955,22 +4955,22 @@
         <v>101</v>
       </c>
       <c r="AK20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM20" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="AL20" t="s" s="2">
+      <c r="AN20" t="s" s="2">
         <v>155</v>
       </c>
-      <c r="AM20" t="s" s="2">
+      <c r="AO20" t="s" s="2">
         <v>156</v>
       </c>
-      <c r="AN20" t="s" s="2">
+      <c r="AP20" t="s" s="2">
         <v>157</v>
-      </c>
-      <c r="AO20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP20" t="s" s="2">
-        <v>80</v>
       </c>
     </row>
     <row r="21" hidden="true">
@@ -5076,13 +5076,13 @@
         <v>80</v>
       </c>
       <c r="AL21" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM21" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN21" t="s" s="2">
         <v>163</v>
-      </c>
-      <c r="AM21" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN21" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>80</v>
@@ -5196,13 +5196,13 @@
         <v>80</v>
       </c>
       <c r="AL22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN22" t="s" s="2">
         <v>163</v>
-      </c>
-      <c r="AM22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN22" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>80</v>
@@ -5315,16 +5315,16 @@
         <v>101</v>
       </c>
       <c r="AK23" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL23" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM23" t="s" s="2">
         <v>132</v>
       </c>
-      <c r="AL23" t="s" s="2">
+      <c r="AN23" t="s" s="2">
         <v>178</v>
-      </c>
-      <c r="AM23" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN23" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>80</v>
@@ -5437,16 +5437,16 @@
         <v>101</v>
       </c>
       <c r="AK24" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL24" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM24" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="AL24" t="s" s="2">
+      <c r="AN24" t="s" s="2">
         <v>178</v>
-      </c>
-      <c r="AM24" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN24" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>80</v>
@@ -5559,19 +5559,19 @@
         <v>101</v>
       </c>
       <c r="AK25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM25" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="AL25" t="s" s="2">
+      <c r="AN25" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="AM25" t="s" s="2">
+      <c r="AO25" t="s" s="2">
         <v>199</v>
-      </c>
-      <c r="AN25" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO25" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>80</v>
@@ -5679,22 +5679,22 @@
         <v>101</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>206</v>
+        <v>237</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>207</v>
+        <v>238</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>208</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>80</v>
+        <v>209</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>237</v>
+        <v>210</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>238</v>
+        <v>80</v>
       </c>
     </row>
     <row r="27" hidden="true">
@@ -5797,19 +5797,19 @@
         <v>101</v>
       </c>
       <c r="AK27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM27" t="s" s="2">
         <v>216</v>
       </c>
-      <c r="AL27" t="s" s="2">
+      <c r="AN27" t="s" s="2">
         <v>217</v>
       </c>
-      <c r="AM27" t="s" s="2">
+      <c r="AO27" t="s" s="2">
         <v>218</v>
-      </c>
-      <c r="AN27" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO27" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>80</v>
@@ -5918,13 +5918,13 @@
         <v>80</v>
       </c>
       <c r="AL28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN28" t="s" s="2">
         <v>163</v>
-      </c>
-      <c r="AM28" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN28" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>80</v>
@@ -6038,13 +6038,13 @@
         <v>80</v>
       </c>
       <c r="AL29" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM29" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN29" t="s" s="2">
         <v>163</v>
-      </c>
-      <c r="AM29" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN29" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>80</v>
@@ -6158,16 +6158,16 @@
         <v>252</v>
       </c>
       <c r="AL30" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM30" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="AM30" t="s" s="2">
-        <v>80</v>
-      </c>
       <c r="AN30" t="s" s="2">
-        <v>80</v>
+        <v>254</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>254</v>
+        <v>80</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>80</v>
@@ -6277,16 +6277,16 @@
         <v>101</v>
       </c>
       <c r="AK31" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL31" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM31" t="s" s="2">
         <v>262</v>
       </c>
-      <c r="AL31" t="s" s="2">
+      <c r="AN31" t="s" s="2">
         <v>263</v>
-      </c>
-      <c r="AM31" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN31" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>80</v>
@@ -6397,19 +6397,19 @@
         <v>101</v>
       </c>
       <c r="AK32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM32" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="AL32" t="s" s="2">
+      <c r="AN32" t="s" s="2">
         <v>226</v>
       </c>
-      <c r="AM32" t="s" s="2">
+      <c r="AO32" t="s" s="2">
         <v>227</v>
-      </c>
-      <c r="AN32" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO32" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>80</v>
@@ -6524,19 +6524,19 @@
         <v>80</v>
       </c>
       <c r="AL33" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM33" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN33" t="s" s="2">
         <v>272</v>
       </c>
-      <c r="AM33" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN33" t="s" s="2">
+      <c r="AO33" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP33" t="s" s="2">
         <v>273</v>
-      </c>
-      <c r="AO33" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP33" t="s" s="2">
-        <v>80</v>
       </c>
     </row>
     <row r="34" hidden="true">
@@ -6643,19 +6643,19 @@
         <v>101</v>
       </c>
       <c r="AK34" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL34" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM34" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="AL34" t="s" s="2">
+      <c r="AN34" t="s" s="2">
         <v>281</v>
       </c>
-      <c r="AM34" t="s" s="2">
+      <c r="AO34" t="s" s="2">
         <v>282</v>
-      </c>
-      <c r="AN34" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO34" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AP34" t="s" s="2">
         <v>80</v>
@@ -6764,13 +6764,13 @@
         <v>80</v>
       </c>
       <c r="AL35" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM35" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN35" t="s" s="2">
         <v>163</v>
-      </c>
-      <c r="AM35" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN35" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>80</v>
@@ -6884,13 +6884,13 @@
         <v>80</v>
       </c>
       <c r="AL36" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM36" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN36" t="s" s="2">
         <v>163</v>
-      </c>
-      <c r="AM36" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN36" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>80</v>
@@ -7003,19 +7003,19 @@
         <v>101</v>
       </c>
       <c r="AK37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM37" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="AL37" t="s" s="2">
+      <c r="AN37" t="s" s="2">
         <v>294</v>
       </c>
-      <c r="AM37" t="s" s="2">
+      <c r="AO37" t="s" s="2">
         <v>295</v>
-      </c>
-      <c r="AN37" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO37" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AP37" t="s" s="2">
         <v>80</v>
@@ -7128,16 +7128,16 @@
         <v>302</v>
       </c>
       <c r="AL38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM38" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="AM38" t="s" s="2">
-        <v>80</v>
-      </c>
       <c r="AN38" t="s" s="2">
-        <v>80</v>
+        <v>304</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>304</v>
+        <v>80</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>80</v>
@@ -7245,19 +7245,19 @@
         <v>101</v>
       </c>
       <c r="AK39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM39" t="s" s="2">
         <v>311</v>
       </c>
-      <c r="AL39" t="s" s="2">
+      <c r="AN39" t="s" s="2">
         <v>312</v>
       </c>
-      <c r="AM39" t="s" s="2">
+      <c r="AO39" t="s" s="2">
         <v>313</v>
-      </c>
-      <c r="AN39" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO39" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>80</v>
@@ -7365,19 +7365,19 @@
         <v>101</v>
       </c>
       <c r="AK40" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL40" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM40" t="s" s="2">
         <v>320</v>
       </c>
-      <c r="AL40" t="s" s="2">
+      <c r="AN40" t="s" s="2">
         <v>321</v>
       </c>
-      <c r="AM40" t="s" s="2">
+      <c r="AO40" t="s" s="2">
         <v>322</v>
-      </c>
-      <c r="AN40" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO40" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>80</v>
@@ -7483,19 +7483,19 @@
         <v>101</v>
       </c>
       <c r="AK41" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL41" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM41" t="s" s="2">
         <v>327</v>
       </c>
-      <c r="AL41" t="s" s="2">
+      <c r="AN41" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="AM41" t="s" s="2">
+      <c r="AO41" t="s" s="2">
         <v>329</v>
-      </c>
-      <c r="AN41" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO41" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>80</v>
@@ -7601,16 +7601,16 @@
         <v>101</v>
       </c>
       <c r="AK42" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL42" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM42" t="s" s="2">
         <v>334</v>
       </c>
-      <c r="AL42" t="s" s="2">
+      <c r="AN42" t="s" s="2">
         <v>335</v>
-      </c>
-      <c r="AM42" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN42" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>80</v>
@@ -7721,19 +7721,19 @@
         <v>101</v>
       </c>
       <c r="AK43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM43" t="s" s="2">
         <v>341</v>
       </c>
-      <c r="AL43" t="s" s="2">
+      <c r="AN43" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="AM43" t="s" s="2">
+      <c r="AO43" t="s" s="2">
         <v>218</v>
-      </c>
-      <c r="AN43" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO43" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>80</v>
@@ -7843,19 +7843,19 @@
         <v>101</v>
       </c>
       <c r="AK44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM44" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="AL44" t="s" s="2">
+      <c r="AN44" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="AM44" t="s" s="2">
+      <c r="AO44" t="s" s="2">
         <v>351</v>
-      </c>
-      <c r="AN44" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO44" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>80</v>
@@ -7964,13 +7964,13 @@
         <v>80</v>
       </c>
       <c r="AL45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN45" t="s" s="2">
         <v>163</v>
-      </c>
-      <c r="AM45" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN45" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>80</v>
@@ -8084,13 +8084,13 @@
         <v>80</v>
       </c>
       <c r="AL46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN46" t="s" s="2">
         <v>163</v>
-      </c>
-      <c r="AM46" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN46" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>80</v>
@@ -8199,19 +8199,19 @@
         <v>101</v>
       </c>
       <c r="AK47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM47" t="s" s="2">
         <v>361</v>
       </c>
-      <c r="AL47" t="s" s="2">
+      <c r="AN47" t="s" s="2">
         <v>362</v>
       </c>
-      <c r="AM47" t="s" s="2">
+      <c r="AO47" t="s" s="2">
         <v>363</v>
-      </c>
-      <c r="AN47" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO47" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>80</v>
@@ -8327,16 +8327,16 @@
         <v>371</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>208</v>
+        <v>372</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>80</v>
+        <v>373</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>372</v>
+        <v>210</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>373</v>
+        <v>80</v>
       </c>
     </row>
     <row r="49" hidden="true">
@@ -8443,19 +8443,19 @@
         <v>101</v>
       </c>
       <c r="AK49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM49" t="s" s="2">
         <v>382</v>
       </c>
-      <c r="AL49" t="s" s="2">
+      <c r="AN49" t="s" s="2">
         <v>294</v>
       </c>
-      <c r="AM49" t="s" s="2">
+      <c r="AO49" t="s" s="2">
         <v>383</v>
-      </c>
-      <c r="AN49" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO49" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>80</v>
@@ -8563,16 +8563,16 @@
         <v>101</v>
       </c>
       <c r="AK50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM50" t="s" s="2">
         <v>163</v>
       </c>
-      <c r="AL50" t="s" s="2">
+      <c r="AN50" t="s" s="2">
         <v>163</v>
-      </c>
-      <c r="AM50" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN50" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>80</v>
@@ -8681,19 +8681,19 @@
         <v>101</v>
       </c>
       <c r="AK51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM51" t="s" s="2">
         <v>132</v>
       </c>
-      <c r="AL51" t="s" s="2">
+      <c r="AN51" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="AM51" t="s" s="2">
+      <c r="AO51" t="s" s="2">
         <v>218</v>
-      </c>
-      <c r="AN51" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO51" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>80</v>
@@ -8801,19 +8801,19 @@
         <v>101</v>
       </c>
       <c r="AK52" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL52" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM52" t="s" s="2">
         <v>401</v>
       </c>
-      <c r="AL52" t="s" s="2">
+      <c r="AN52" t="s" s="2">
         <v>402</v>
       </c>
-      <c r="AM52" t="s" s="2">
+      <c r="AO52" t="s" s="2">
         <v>163</v>
-      </c>
-      <c r="AN52" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO52" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>80</v>
@@ -8922,13 +8922,13 @@
         <v>80</v>
       </c>
       <c r="AL53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN53" t="s" s="2">
         <v>163</v>
-      </c>
-      <c r="AM53" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN53" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>80</v>
@@ -9042,13 +9042,13 @@
         <v>80</v>
       </c>
       <c r="AL54" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM54" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN54" t="s" s="2">
         <v>163</v>
-      </c>
-      <c r="AM54" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN54" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>80</v>
@@ -9161,19 +9161,19 @@
         <v>101</v>
       </c>
       <c r="AK55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM55" t="s" s="2">
         <v>414</v>
       </c>
-      <c r="AL55" t="s" s="2">
+      <c r="AN55" t="s" s="2">
         <v>294</v>
       </c>
-      <c r="AM55" t="s" s="2">
+      <c r="AO55" t="s" s="2">
         <v>415</v>
-      </c>
-      <c r="AN55" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO55" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>80</v>
@@ -9281,16 +9281,16 @@
         <v>101</v>
       </c>
       <c r="AK56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM56" t="s" s="2">
         <v>424</v>
       </c>
-      <c r="AL56" t="s" s="2">
+      <c r="AN56" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="AM56" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN56" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>80</v>
@@ -9403,16 +9403,16 @@
         <v>101</v>
       </c>
       <c r="AK57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM57" t="s" s="2">
         <v>431</v>
       </c>
-      <c r="AL57" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="AM57" t="s" s="2">
-        <v>80</v>
-      </c>
       <c r="AN57" t="s" s="2">
-        <v>80</v>
+        <v>304</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>80</v>
@@ -9521,19 +9521,19 @@
         <v>101</v>
       </c>
       <c r="AK58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM58" t="s" s="2">
         <v>438</v>
       </c>
-      <c r="AL58" t="s" s="2">
+      <c r="AN58" t="s" s="2">
         <v>439</v>
       </c>
-      <c r="AM58" t="s" s="2">
+      <c r="AO58" t="s" s="2">
         <v>440</v>
-      </c>
-      <c r="AN58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO58" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>80</v>
@@ -9639,19 +9639,19 @@
         <v>101</v>
       </c>
       <c r="AK59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM59" t="s" s="2">
         <v>447</v>
       </c>
-      <c r="AL59" t="s" s="2">
+      <c r="AN59" t="s" s="2">
         <v>448</v>
       </c>
-      <c r="AM59" t="s" s="2">
+      <c r="AO59" t="s" s="2">
         <v>449</v>
-      </c>
-      <c r="AN59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO59" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>80</v>
@@ -9759,16 +9759,16 @@
         <v>101</v>
       </c>
       <c r="AK60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM60" t="s" s="2">
         <v>457</v>
       </c>
-      <c r="AL60" t="s" s="2">
+      <c r="AN60" t="s" s="2">
         <v>458</v>
-      </c>
-      <c r="AM60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN60" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>80</v>
@@ -9877,19 +9877,19 @@
         <v>101</v>
       </c>
       <c r="AK61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM61" t="s" s="2">
         <v>466</v>
       </c>
-      <c r="AL61" t="s" s="2">
+      <c r="AN61" t="s" s="2">
         <v>467</v>
       </c>
-      <c r="AM61" t="s" s="2">
+      <c r="AO61" t="s" s="2">
         <v>468</v>
-      </c>
-      <c r="AN61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO61" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AP61" t="s" s="2">
         <v>80</v>
@@ -9995,19 +9995,19 @@
         <v>101</v>
       </c>
       <c r="AK62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM62" t="s" s="2">
         <v>475</v>
       </c>
-      <c r="AL62" t="s" s="2">
+      <c r="AN62" t="s" s="2">
         <v>476</v>
       </c>
-      <c r="AM62" t="s" s="2">
+      <c r="AO62" t="s" s="2">
         <v>477</v>
-      </c>
-      <c r="AN62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO62" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AP62" t="s" s="2">
         <v>80</v>
@@ -10115,19 +10115,19 @@
         <v>101</v>
       </c>
       <c r="AK63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM63" t="s" s="2">
         <v>483</v>
       </c>
-      <c r="AL63" t="s" s="2">
+      <c r="AN63" t="s" s="2">
         <v>484</v>
       </c>
-      <c r="AM63" t="s" s="2">
+      <c r="AO63" t="s" s="2">
         <v>485</v>
-      </c>
-      <c r="AN63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO63" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AP63" t="s" s="2">
         <v>80</v>
@@ -10235,19 +10235,19 @@
         <v>101</v>
       </c>
       <c r="AK64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM64" t="s" s="2">
         <v>492</v>
       </c>
-      <c r="AL64" t="s" s="2">
+      <c r="AN64" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="AM64" t="s" s="2">
+      <c r="AO64" t="s" s="2">
         <v>218</v>
-      </c>
-      <c r="AN64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO64" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AP64" t="s" s="2">
         <v>80</v>
@@ -10359,19 +10359,19 @@
         <v>101</v>
       </c>
       <c r="AK65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM65" t="s" s="2">
         <v>401</v>
       </c>
-      <c r="AL65" t="s" s="2">
+      <c r="AN65" t="s" s="2">
         <v>402</v>
       </c>
-      <c r="AM65" t="s" s="2">
+      <c r="AO65" t="s" s="2">
         <v>163</v>
-      </c>
-      <c r="AN65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO65" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>80</v>
@@ -10480,13 +10480,13 @@
         <v>80</v>
       </c>
       <c r="AL66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN66" t="s" s="2">
         <v>163</v>
-      </c>
-      <c r="AM66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN66" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>80</v>
@@ -10600,13 +10600,13 @@
         <v>80</v>
       </c>
       <c r="AL67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN67" t="s" s="2">
         <v>163</v>
-      </c>
-      <c r="AM67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN67" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>80</v>
@@ -10719,19 +10719,19 @@
         <v>101</v>
       </c>
       <c r="AK68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM68" t="s" s="2">
         <v>414</v>
       </c>
-      <c r="AL68" t="s" s="2">
+      <c r="AN68" t="s" s="2">
         <v>294</v>
       </c>
-      <c r="AM68" t="s" s="2">
+      <c r="AO68" t="s" s="2">
         <v>415</v>
-      </c>
-      <c r="AN68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO68" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AP68" t="s" s="2">
         <v>80</v>
@@ -10839,16 +10839,16 @@
         <v>101</v>
       </c>
       <c r="AK69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM69" t="s" s="2">
         <v>424</v>
       </c>
-      <c r="AL69" t="s" s="2">
+      <c r="AN69" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="AM69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN69" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>80</v>
@@ -10961,16 +10961,16 @@
         <v>101</v>
       </c>
       <c r="AK70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM70" t="s" s="2">
         <v>431</v>
       </c>
-      <c r="AL70" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="AM70" t="s" s="2">
-        <v>80</v>
-      </c>
       <c r="AN70" t="s" s="2">
-        <v>80</v>
+        <v>304</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>80</v>
@@ -11079,22 +11079,22 @@
         <v>101</v>
       </c>
       <c r="AK71" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="AM71" t="s" s="2">
         <v>438</v>
       </c>
-      <c r="AL71" t="s" s="2">
+      <c r="AN71" t="s" s="2">
         <v>439</v>
       </c>
-      <c r="AM71" t="s" s="2">
+      <c r="AO71" t="s" s="2">
         <v>440</v>
       </c>
-      <c r="AN71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO71" t="s" s="2">
-        <v>500</v>
-      </c>
       <c r="AP71" t="s" s="2">
-        <v>501</v>
+        <v>80</v>
       </c>
     </row>
     <row r="72" hidden="true">
@@ -11197,22 +11197,22 @@
         <v>101</v>
       </c>
       <c r="AK72" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="AL72" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="AM72" t="s" s="2">
         <v>447</v>
       </c>
-      <c r="AL72" t="s" s="2">
+      <c r="AN72" t="s" s="2">
         <v>448</v>
       </c>
-      <c r="AM72" t="s" s="2">
+      <c r="AO72" t="s" s="2">
         <v>449</v>
       </c>
-      <c r="AN72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO72" t="s" s="2">
-        <v>503</v>
-      </c>
       <c r="AP72" t="s" s="2">
-        <v>504</v>
+        <v>80</v>
       </c>
     </row>
     <row r="73" hidden="true">
@@ -11317,16 +11317,16 @@
         <v>101</v>
       </c>
       <c r="AK73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM73" t="s" s="2">
         <v>457</v>
       </c>
-      <c r="AL73" t="s" s="2">
+      <c r="AN73" t="s" s="2">
         <v>458</v>
-      </c>
-      <c r="AM73" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN73" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>80</v>
@@ -11435,22 +11435,22 @@
         <v>101</v>
       </c>
       <c r="AK74" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="AM74" t="s" s="2">
         <v>466</v>
       </c>
-      <c r="AL74" t="s" s="2">
+      <c r="AN74" t="s" s="2">
         <v>467</v>
       </c>
-      <c r="AM74" t="s" s="2">
+      <c r="AO74" t="s" s="2">
         <v>468</v>
       </c>
-      <c r="AN74" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO74" t="s" s="2">
-        <v>507</v>
-      </c>
       <c r="AP74" t="s" s="2">
-        <v>508</v>
+        <v>80</v>
       </c>
     </row>
     <row r="75" hidden="true">
@@ -11553,22 +11553,22 @@
         <v>101</v>
       </c>
       <c r="AK75" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="AL75" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="AM75" t="s" s="2">
         <v>475</v>
       </c>
-      <c r="AL75" t="s" s="2">
+      <c r="AN75" t="s" s="2">
         <v>476</v>
       </c>
-      <c r="AM75" t="s" s="2">
+      <c r="AO75" t="s" s="2">
         <v>477</v>
       </c>
-      <c r="AN75" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO75" t="s" s="2">
-        <v>510</v>
-      </c>
       <c r="AP75" t="s" s="2">
-        <v>511</v>
+        <v>80</v>
       </c>
     </row>
     <row r="76" hidden="true">
@@ -11673,22 +11673,22 @@
         <v>101</v>
       </c>
       <c r="AK76" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="AL76" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="AM76" t="s" s="2">
         <v>483</v>
       </c>
-      <c r="AL76" t="s" s="2">
+      <c r="AN76" t="s" s="2">
         <v>484</v>
       </c>
-      <c r="AM76" t="s" s="2">
+      <c r="AO76" t="s" s="2">
         <v>485</v>
       </c>
-      <c r="AN76" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO76" t="s" s="2">
-        <v>513</v>
-      </c>
       <c r="AP76" t="s" s="2">
-        <v>508</v>
+        <v>80</v>
       </c>
     </row>
     <row r="77" hidden="true">
@@ -12030,13 +12030,13 @@
         <v>80</v>
       </c>
       <c r="AL79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN79" t="s" s="2">
         <v>528</v>
-      </c>
-      <c r="AM79" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN79" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>80</v>
@@ -12148,13 +12148,13 @@
         <v>80</v>
       </c>
       <c r="AL80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN80" t="s" s="2">
         <v>163</v>
-      </c>
-      <c r="AM80" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN80" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>80</v>
@@ -12386,13 +12386,13 @@
         <v>80</v>
       </c>
       <c r="AL82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN82" t="s" s="2">
         <v>132</v>
-      </c>
-      <c r="AM82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN82" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>80</v>
@@ -12501,22 +12501,22 @@
         <v>101</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>80</v>
+        <v>547</v>
       </c>
       <c r="AL83" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="AM83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN83" t="s" s="2">
         <v>132</v>
       </c>
-      <c r="AM83" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN83" t="s" s="2">
-        <v>80</v>
-      </c>
       <c r="AO83" t="s" s="2">
-        <v>547</v>
+        <v>80</v>
       </c>
       <c r="AP83" t="s" s="2">
-        <v>508</v>
+        <v>80</v>
       </c>
     </row>
     <row r="84" hidden="true">
@@ -12623,16 +12623,16 @@
         <v>140</v>
       </c>
       <c r="AK84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM84" t="s" s="2">
         <v>132</v>
       </c>
-      <c r="AL84" t="s" s="2">
+      <c r="AN84" t="s" s="2">
         <v>132</v>
-      </c>
-      <c r="AM84" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN84" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>80</v>
@@ -12744,13 +12744,13 @@
         <v>80</v>
       </c>
       <c r="AL85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN85" t="s" s="2">
         <v>163</v>
-      </c>
-      <c r="AM85" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN85" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>80</v>
@@ -12982,13 +12982,13 @@
         <v>80</v>
       </c>
       <c r="AL87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN87" t="s" s="2">
         <v>132</v>
-      </c>
-      <c r="AM87" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN87" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>80</v>
@@ -13100,13 +13100,13 @@
         <v>80</v>
       </c>
       <c r="AL88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN88" t="s" s="2">
         <v>132</v>
-      </c>
-      <c r="AM88" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN88" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>80</v>
@@ -13335,19 +13335,19 @@
         <v>101</v>
       </c>
       <c r="AK90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM90" t="s" s="2">
         <v>492</v>
       </c>
-      <c r="AL90" t="s" s="2">
+      <c r="AN90" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="AM90" t="s" s="2">
+      <c r="AO90" t="s" s="2">
         <v>218</v>
-      </c>
-      <c r="AN90" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO90" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AP90" t="s" s="2">
         <v>80</v>
@@ -13459,19 +13459,19 @@
         <v>101</v>
       </c>
       <c r="AK91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM91" t="s" s="2">
         <v>401</v>
       </c>
-      <c r="AL91" t="s" s="2">
+      <c r="AN91" t="s" s="2">
         <v>402</v>
       </c>
-      <c r="AM91" t="s" s="2">
+      <c r="AO91" t="s" s="2">
         <v>163</v>
-      </c>
-      <c r="AN91" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO91" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AP91" t="s" s="2">
         <v>80</v>
@@ -13580,13 +13580,13 @@
         <v>80</v>
       </c>
       <c r="AL92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN92" t="s" s="2">
         <v>163</v>
-      </c>
-      <c r="AM92" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN92" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>80</v>
@@ -13700,13 +13700,13 @@
         <v>80</v>
       </c>
       <c r="AL93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN93" t="s" s="2">
         <v>163</v>
-      </c>
-      <c r="AM93" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN93" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>80</v>
@@ -13819,19 +13819,19 @@
         <v>101</v>
       </c>
       <c r="AK94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM94" t="s" s="2">
         <v>414</v>
       </c>
-      <c r="AL94" t="s" s="2">
+      <c r="AN94" t="s" s="2">
         <v>294</v>
       </c>
-      <c r="AM94" t="s" s="2">
+      <c r="AO94" t="s" s="2">
         <v>415</v>
-      </c>
-      <c r="AN94" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO94" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AP94" t="s" s="2">
         <v>80</v>
@@ -13939,16 +13939,16 @@
         <v>101</v>
       </c>
       <c r="AK95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM95" t="s" s="2">
         <v>424</v>
       </c>
-      <c r="AL95" t="s" s="2">
+      <c r="AN95" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="AM95" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN95" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>80</v>
@@ -14061,16 +14061,16 @@
         <v>101</v>
       </c>
       <c r="AK96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM96" t="s" s="2">
         <v>431</v>
       </c>
-      <c r="AL96" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="AM96" t="s" s="2">
-        <v>80</v>
-      </c>
       <c r="AN96" t="s" s="2">
-        <v>80</v>
+        <v>304</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>80</v>
@@ -14179,22 +14179,22 @@
         <v>101</v>
       </c>
       <c r="AK97" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="AL97" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="AM97" t="s" s="2">
         <v>438</v>
       </c>
-      <c r="AL97" t="s" s="2">
+      <c r="AN97" t="s" s="2">
         <v>439</v>
       </c>
-      <c r="AM97" t="s" s="2">
+      <c r="AO97" t="s" s="2">
         <v>440</v>
       </c>
-      <c r="AN97" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO97" t="s" s="2">
-        <v>576</v>
-      </c>
       <c r="AP97" t="s" s="2">
-        <v>577</v>
+        <v>80</v>
       </c>
     </row>
     <row r="98" hidden="true">
@@ -14297,22 +14297,22 @@
         <v>101</v>
       </c>
       <c r="AK98" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="AL98" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="AM98" t="s" s="2">
         <v>447</v>
       </c>
-      <c r="AL98" t="s" s="2">
+      <c r="AN98" t="s" s="2">
         <v>448</v>
       </c>
-      <c r="AM98" t="s" s="2">
+      <c r="AO98" t="s" s="2">
         <v>449</v>
       </c>
-      <c r="AN98" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO98" t="s" s="2">
-        <v>579</v>
-      </c>
       <c r="AP98" t="s" s="2">
-        <v>580</v>
+        <v>80</v>
       </c>
     </row>
     <row r="99" hidden="true">
@@ -14417,16 +14417,16 @@
         <v>101</v>
       </c>
       <c r="AK99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM99" t="s" s="2">
         <v>457</v>
       </c>
-      <c r="AL99" t="s" s="2">
+      <c r="AN99" t="s" s="2">
         <v>458</v>
-      </c>
-      <c r="AM99" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN99" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>80</v>
@@ -14535,22 +14535,22 @@
         <v>101</v>
       </c>
       <c r="AK100" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="AL100" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="AM100" t="s" s="2">
         <v>466</v>
       </c>
-      <c r="AL100" t="s" s="2">
+      <c r="AN100" t="s" s="2">
         <v>467</v>
       </c>
-      <c r="AM100" t="s" s="2">
+      <c r="AO100" t="s" s="2">
         <v>468</v>
       </c>
-      <c r="AN100" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO100" t="s" s="2">
-        <v>583</v>
-      </c>
       <c r="AP100" t="s" s="2">
-        <v>584</v>
+        <v>80</v>
       </c>
     </row>
     <row r="101" hidden="true">
@@ -14653,22 +14653,22 @@
         <v>101</v>
       </c>
       <c r="AK101" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="AL101" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="AM101" t="s" s="2">
         <v>475</v>
       </c>
-      <c r="AL101" t="s" s="2">
+      <c r="AN101" t="s" s="2">
         <v>476</v>
       </c>
-      <c r="AM101" t="s" s="2">
+      <c r="AO101" t="s" s="2">
         <v>477</v>
       </c>
-      <c r="AN101" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO101" t="s" s="2">
-        <v>586</v>
-      </c>
       <c r="AP101" t="s" s="2">
-        <v>587</v>
+        <v>80</v>
       </c>
     </row>
     <row r="102" hidden="true">
@@ -14773,22 +14773,22 @@
         <v>101</v>
       </c>
       <c r="AK102" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="AL102" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="AM102" t="s" s="2">
         <v>483</v>
       </c>
-      <c r="AL102" t="s" s="2">
+      <c r="AN102" t="s" s="2">
         <v>484</v>
       </c>
-      <c r="AM102" t="s" s="2">
+      <c r="AO102" t="s" s="2">
         <v>485</v>
       </c>
-      <c r="AN102" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO102" t="s" s="2">
-        <v>589</v>
-      </c>
       <c r="AP102" t="s" s="2">
-        <v>584</v>
+        <v>80</v>
       </c>
     </row>
     <row r="103" hidden="true">
@@ -15130,13 +15130,13 @@
         <v>80</v>
       </c>
       <c r="AL105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN105" t="s" s="2">
         <v>528</v>
-      </c>
-      <c r="AM105" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN105" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>80</v>
@@ -15248,13 +15248,13 @@
         <v>80</v>
       </c>
       <c r="AL106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN106" t="s" s="2">
         <v>163</v>
-      </c>
-      <c r="AM106" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN106" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AO106" t="s" s="2">
         <v>80</v>
@@ -15486,13 +15486,13 @@
         <v>80</v>
       </c>
       <c r="AL108" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM108" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN108" t="s" s="2">
         <v>132</v>
-      </c>
-      <c r="AM108" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN108" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AO108" t="s" s="2">
         <v>80</v>
@@ -15601,22 +15601,22 @@
         <v>101</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>80</v>
+        <v>597</v>
       </c>
       <c r="AL109" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="AM109" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN109" t="s" s="2">
         <v>132</v>
       </c>
-      <c r="AM109" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN109" t="s" s="2">
-        <v>80</v>
-      </c>
       <c r="AO109" t="s" s="2">
-        <v>597</v>
+        <v>80</v>
       </c>
       <c r="AP109" t="s" s="2">
-        <v>584</v>
+        <v>80</v>
       </c>
     </row>
     <row r="110" hidden="true">
@@ -15723,16 +15723,16 @@
         <v>140</v>
       </c>
       <c r="AK110" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL110" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM110" t="s" s="2">
         <v>132</v>
       </c>
-      <c r="AL110" t="s" s="2">
+      <c r="AN110" t="s" s="2">
         <v>132</v>
-      </c>
-      <c r="AM110" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN110" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AO110" t="s" s="2">
         <v>80</v>
@@ -15844,13 +15844,13 @@
         <v>80</v>
       </c>
       <c r="AL111" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM111" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN111" t="s" s="2">
         <v>163</v>
-      </c>
-      <c r="AM111" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN111" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AO111" t="s" s="2">
         <v>80</v>
@@ -16082,13 +16082,13 @@
         <v>80</v>
       </c>
       <c r="AL113" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM113" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN113" t="s" s="2">
         <v>132</v>
-      </c>
-      <c r="AM113" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN113" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AO113" t="s" s="2">
         <v>80</v>
@@ -16200,13 +16200,13 @@
         <v>80</v>
       </c>
       <c r="AL114" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM114" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN114" t="s" s="2">
         <v>132</v>
-      </c>
-      <c r="AM114" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN114" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AO114" t="s" s="2">
         <v>80</v>
@@ -16435,19 +16435,19 @@
         <v>101</v>
       </c>
       <c r="AK116" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL116" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM116" t="s" s="2">
         <v>492</v>
       </c>
-      <c r="AL116" t="s" s="2">
+      <c r="AN116" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="AM116" t="s" s="2">
+      <c r="AO116" t="s" s="2">
         <v>218</v>
-      </c>
-      <c r="AN116" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO116" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AP116" t="s" s="2">
         <v>80</v>
@@ -16556,13 +16556,13 @@
         <v>80</v>
       </c>
       <c r="AL117" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM117" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN117" t="s" s="2">
         <v>163</v>
-      </c>
-      <c r="AM117" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN117" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AO117" t="s" s="2">
         <v>80</v>
@@ -16676,13 +16676,13 @@
         <v>80</v>
       </c>
       <c r="AL118" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM118" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN118" t="s" s="2">
         <v>163</v>
-      </c>
-      <c r="AM118" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN118" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AO118" t="s" s="2">
         <v>80</v>
@@ -16793,22 +16793,22 @@
         <v>101</v>
       </c>
       <c r="AK119" t="s" s="2">
-        <v>252</v>
+        <v>611</v>
       </c>
       <c r="AL119" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="AM119" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="AM119" t="s" s="2">
-        <v>80</v>
-      </c>
       <c r="AN119" t="s" s="2">
-        <v>80</v>
+        <v>254</v>
       </c>
       <c r="AO119" t="s" s="2">
-        <v>611</v>
+        <v>80</v>
       </c>
       <c r="AP119" t="s" s="2">
-        <v>612</v>
+        <v>80</v>
       </c>
     </row>
     <row r="120" hidden="true">
@@ -16915,22 +16915,22 @@
         <v>101</v>
       </c>
       <c r="AK120" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="AL120" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="AM120" t="s" s="2">
         <v>262</v>
       </c>
-      <c r="AL120" t="s" s="2">
+      <c r="AN120" t="s" s="2">
         <v>263</v>
       </c>
-      <c r="AM120" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN120" t="s" s="2">
-        <v>80</v>
-      </c>
       <c r="AO120" t="s" s="2">
-        <v>615</v>
+        <v>80</v>
       </c>
       <c r="AP120" t="s" s="2">
-        <v>616</v>
+        <v>80</v>
       </c>
     </row>
     <row r="121" hidden="true">
@@ -17035,19 +17035,19 @@
         <v>101</v>
       </c>
       <c r="AK121" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL121" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM121" t="s" s="2">
         <v>623</v>
       </c>
-      <c r="AL121" t="s" s="2">
+      <c r="AN121" t="s" s="2">
         <v>624</v>
       </c>
-      <c r="AM121" t="s" s="2">
+      <c r="AO121" t="s" s="2">
         <v>625</v>
-      </c>
-      <c r="AN121" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO121" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AP121" t="s" s="2">
         <v>80</v>
@@ -17164,13 +17164,13 @@
         <v>633</v>
       </c>
       <c r="AN122" t="s" s="2">
-        <v>80</v>
+        <v>634</v>
       </c>
       <c r="AO122" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="AP122" t="s" s="2">
-        <v>635</v>
+        <v>80</v>
       </c>
     </row>
     <row r="123" hidden="true">
@@ -17278,16 +17278,16 @@
         <v>80</v>
       </c>
       <c r="AL123" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM123" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN123" t="s" s="2">
         <v>641</v>
       </c>
-      <c r="AM123" t="s" s="2">
+      <c r="AO123" t="s" s="2">
         <v>642</v>
-      </c>
-      <c r="AN123" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO123" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AP123" t="s" s="2">
         <v>80</v>
@@ -17393,19 +17393,19 @@
         <v>101</v>
       </c>
       <c r="AK124" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL124" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM124" t="s" s="2">
         <v>647</v>
       </c>
-      <c r="AL124" t="s" s="2">
+      <c r="AN124" t="s" s="2">
         <v>648</v>
       </c>
-      <c r="AM124" t="s" s="2">
+      <c r="AO124" t="s" s="2">
         <v>649</v>
-      </c>
-      <c r="AN124" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO124" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AP124" t="s" s="2">
         <v>80</v>
@@ -17514,13 +17514,13 @@
         <v>80</v>
       </c>
       <c r="AL125" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM125" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN125" t="s" s="2">
         <v>163</v>
-      </c>
-      <c r="AM125" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN125" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AO125" t="s" s="2">
         <v>80</v>
@@ -17634,13 +17634,13 @@
         <v>80</v>
       </c>
       <c r="AL126" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM126" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN126" t="s" s="2">
         <v>163</v>
-      </c>
-      <c r="AM126" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN126" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AO126" t="s" s="2">
         <v>80</v>
@@ -17756,13 +17756,13 @@
         <v>80</v>
       </c>
       <c r="AL127" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM127" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN127" t="s" s="2">
         <v>132</v>
-      </c>
-      <c r="AM127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN127" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AO127" t="s" s="2">
         <v>80</v>
@@ -17876,13 +17876,13 @@
         <v>80</v>
       </c>
       <c r="AL128" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM128" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN128" t="s" s="2">
         <v>661</v>
-      </c>
-      <c r="AM128" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN128" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AO128" t="s" s="2">
         <v>80</v>
@@ -17994,16 +17994,16 @@
         <v>80</v>
       </c>
       <c r="AL129" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM129" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN129" t="s" s="2">
         <v>648</v>
       </c>
-      <c r="AM129" t="s" s="2">
+      <c r="AO129" t="s" s="2">
         <v>668</v>
-      </c>
-      <c r="AN129" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO129" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AP129" t="s" s="2">
         <v>80</v>
@@ -18112,13 +18112,13 @@
         <v>80</v>
       </c>
       <c r="AL130" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM130" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN130" t="s" s="2">
         <v>163</v>
-      </c>
-      <c r="AM130" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN130" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AO130" t="s" s="2">
         <v>80</v>
@@ -18232,13 +18232,13 @@
         <v>80</v>
       </c>
       <c r="AL131" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM131" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN131" t="s" s="2">
         <v>163</v>
-      </c>
-      <c r="AM131" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN131" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AO131" t="s" s="2">
         <v>80</v>
@@ -18351,16 +18351,16 @@
         <v>101</v>
       </c>
       <c r="AK132" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL132" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM132" t="s" s="2">
         <v>678</v>
       </c>
-      <c r="AL132" t="s" s="2">
+      <c r="AN132" t="s" s="2">
         <v>679</v>
-      </c>
-      <c r="AM132" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN132" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AO132" t="s" s="2">
         <v>80</v>
@@ -18476,16 +18476,16 @@
         <v>686</v>
       </c>
       <c r="AL133" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM133" t="s" s="2">
         <v>687</v>
       </c>
-      <c r="AM133" t="s" s="2">
-        <v>80</v>
-      </c>
       <c r="AN133" t="s" s="2">
-        <v>80</v>
+        <v>688</v>
       </c>
       <c r="AO133" t="s" s="2">
-        <v>688</v>
+        <v>80</v>
       </c>
       <c r="AP133" t="s" s="2">
         <v>80</v>
@@ -18596,16 +18596,16 @@
         <v>80</v>
       </c>
       <c r="AL134" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM134" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN134" t="s" s="2">
         <v>693</v>
       </c>
-      <c r="AM134" t="s" s="2">
+      <c r="AO134" t="s" s="2">
         <v>694</v>
-      </c>
-      <c r="AN134" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO134" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AP134" t="s" s="2">
         <v>80</v>
@@ -18714,13 +18714,13 @@
         <v>80</v>
       </c>
       <c r="AL135" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM135" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN135" t="s" s="2">
         <v>698</v>
-      </c>
-      <c r="AM135" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN135" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AO135" t="s" s="2">
         <v>80</v>
@@ -18833,19 +18833,19 @@
         <v>101</v>
       </c>
       <c r="AK136" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL136" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM136" t="s" s="2">
         <v>704</v>
       </c>
-      <c r="AL136" t="s" s="2">
+      <c r="AN136" t="s" s="2">
         <v>705</v>
       </c>
-      <c r="AM136" t="s" s="2">
+      <c r="AO136" t="s" s="2">
         <v>706</v>
-      </c>
-      <c r="AN136" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO136" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AP136" t="s" s="2">
         <v>80</v>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.30.0</t>
+    <t>0.32.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-21T09:40:56+00:00</t>
+    <t>2024-03-22T16:04:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5190" uniqueCount="707">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5189" uniqueCount="708">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.32.0</t>
+    <t>0.34.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-22T16:04:14+00:00</t>
+    <t>2024-03-29T18:32:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1937,10 +1937,13 @@
     <t>Needed to address the person correctly.</t>
   </si>
   <si>
-    <t>The gender of a person used for administrative purposes.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/administrative-gender|4.0.1</t>
+    <t>http://va.gov/fhir/ValueSet/VSVFproviderGender</t>
+  </si>
+  <si>
+    <t>1790: terminologyMaps using VF_providerGender on NEW PERSON - SEX (#200-4)</t>
+  </si>
+  <si>
+    <t>SStaff.SStaff.Gender,Staff.Staff.Gender</t>
   </si>
   <si>
     <t>STF-5</t>
@@ -2543,7 +2546,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="98.375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="51.921875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="51.0" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
@@ -16952,7 +16955,7 @@
         <v>89</v>
       </c>
       <c r="H121" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="I121" t="s" s="2">
         <v>80</v>
@@ -16998,11 +17001,9 @@
       <c r="X121" t="s" s="2">
         <v>174</v>
       </c>
-      <c r="Y121" t="s" s="2">
+      <c r="Y121" s="2"/>
+      <c r="Z121" t="s" s="2">
         <v>621</v>
-      </c>
-      <c r="Z121" t="s" s="2">
-        <v>622</v>
       </c>
       <c r="AA121" t="s" s="2">
         <v>80</v>
@@ -17035,19 +17036,19 @@
         <v>101</v>
       </c>
       <c r="AK121" t="s" s="2">
-        <v>80</v>
+        <v>622</v>
       </c>
       <c r="AL121" t="s" s="2">
-        <v>80</v>
+        <v>623</v>
       </c>
       <c r="AM121" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="AN121" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AO121" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="AP121" t="s" s="2">
         <v>80</v>
@@ -17055,10 +17056,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -17081,17 +17082,17 @@
         <v>90</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>80</v>
@@ -17140,7 +17141,7 @@
         <v>80</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>78</v>
@@ -17155,19 +17156,19 @@
         <v>101</v>
       </c>
       <c r="AK122" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="AL122" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="AM122" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="AN122" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="AO122" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="AP122" t="s" s="2">
         <v>80</v>
@@ -17175,10 +17176,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -17201,17 +17202,17 @@
         <v>80</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="N123" s="2"/>
       <c r="O123" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>80</v>
@@ -17260,7 +17261,7 @@
         <v>80</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>78</v>
@@ -17284,10 +17285,10 @@
         <v>80</v>
       </c>
       <c r="AN123" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="AO123" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="AP123" t="s" s="2">
         <v>80</v>
@@ -17295,10 +17296,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17321,13 +17322,13 @@
         <v>80</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="N124" s="2"/>
       <c r="O124" s="2"/>
@@ -17378,7 +17379,7 @@
         <v>80</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>78</v>
@@ -17399,13 +17400,13 @@
         <v>80</v>
       </c>
       <c r="AM124" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="AN124" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="AO124" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="AP124" t="s" s="2">
         <v>80</v>
@@ -17413,10 +17414,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17531,10 +17532,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17651,14 +17652,14 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="E127" s="2"/>
       <c r="F127" t="s" s="2">
@@ -17680,10 +17681,10 @@
         <v>135</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="N127" t="s" s="2">
         <v>138</v>
@@ -17738,7 +17739,7 @@
         <v>80</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>78</v>
@@ -17773,10 +17774,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17802,14 +17803,14 @@
         <v>147</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="N128" s="2"/>
       <c r="O128" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>80</v>
@@ -17858,7 +17859,7 @@
         <v>80</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>78</v>
@@ -17882,7 +17883,7 @@
         <v>80</v>
       </c>
       <c r="AN128" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="AO128" t="s" s="2">
         <v>80</v>
@@ -17893,10 +17894,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17922,10 +17923,10 @@
         <v>180</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="N129" s="2"/>
       <c r="O129" s="2"/>
@@ -17952,13 +17953,13 @@
         <v>80</v>
       </c>
       <c r="X129" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="Y129" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="Z129" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="AA129" t="s" s="2">
         <v>80</v>
@@ -17976,7 +17977,7 @@
         <v>80</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>89</v>
@@ -18000,10 +18001,10 @@
         <v>80</v>
       </c>
       <c r="AN129" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="AO129" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="AP129" t="s" s="2">
         <v>80</v>
@@ -18011,10 +18012,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -18129,10 +18130,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -18249,10 +18250,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18275,19 +18276,19 @@
         <v>90</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="O132" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="P132" t="s" s="2">
         <v>80</v>
@@ -18336,7 +18337,7 @@
         <v>80</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>78</v>
@@ -18357,10 +18358,10 @@
         <v>80</v>
       </c>
       <c r="AM132" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="AN132" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="AO132" t="s" s="2">
         <v>80</v>
@@ -18371,10 +18372,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18400,16 +18401,16 @@
         <v>159</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="O133" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="P133" t="s" s="2">
         <v>80</v>
@@ -18458,7 +18459,7 @@
         <v>80</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>78</v>
@@ -18473,16 +18474,16 @@
         <v>101</v>
       </c>
       <c r="AK133" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="AL133" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM133" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="AN133" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="AO133" t="s" s="2">
         <v>80</v>
@@ -18493,10 +18494,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18522,14 +18523,14 @@
         <v>212</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="N134" s="2"/>
       <c r="O134" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>80</v>
@@ -18578,7 +18579,7 @@
         <v>80</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>78</v>
@@ -18602,10 +18603,10 @@
         <v>80</v>
       </c>
       <c r="AN134" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="AO134" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="AP134" t="s" s="2">
         <v>80</v>
@@ -18613,10 +18614,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18642,10 +18643,10 @@
         <v>220</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="N135" s="2"/>
       <c r="O135" s="2"/>
@@ -18696,7 +18697,7 @@
         <v>80</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>78</v>
@@ -18720,7 +18721,7 @@
         <v>80</v>
       </c>
       <c r="AN135" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="AO135" t="s" s="2">
         <v>80</v>
@@ -18731,10 +18732,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -18760,16 +18761,16 @@
         <v>180</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="O136" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="P136" t="s" s="2">
         <v>80</v>
@@ -18818,7 +18819,7 @@
         <v>80</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>78</v>
@@ -18839,13 +18840,13 @@
         <v>80</v>
       </c>
       <c r="AM136" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="AN136" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="AO136" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="AP136" t="s" s="2">
         <v>80</v>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-29T18:32:47+00:00</t>
+    <t>2024-03-30T09:34:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.34.0</t>
+    <t>0.36.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-30T09:34:15+00:00</t>
+    <t>2024-04-03T07:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T07:33:38+00:00</t>
+    <t>2024-04-03T08:58:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T08:58:56+00:00</t>
+    <t>2024-04-10T18:17:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file NEW PERSON (#200) to us-core-practitioner</t>
+    <t>This StructureDefinition contains the maps for VistA file NEW PERSON (200) to us-core-practitioner</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -657,7 +657,7 @@
     <t>Identifier.value</t>
   </si>
   <si>
-    <t>415: source value from NEW PERSON - IEN (#200-.001)</t>
+    <t>415: source value from NEW PERSON - IEN (200-.001)</t>
   </si>
   <si>
     <t>SStaff.PrescribingProvider.VPID</t>
@@ -754,7 +754,7 @@
     <t>Practitioner.identifier:NPI.value</t>
   </si>
   <si>
-    <t>376: source value from NEW PERSON - NPI (#200-41.99)</t>
+    <t>376: source value from NEW PERSON - NPI (200-41.99)</t>
   </si>
   <si>
     <t>SStaff.PrescribingProvider.NPI,SStaff.SStaff.NPI</t>
@@ -801,7 +801,7 @@
 </t>
   </si>
   <si>
-    <t>380: source value from NEW PERSON - EFFECTIVE DATE/TIME (#200-42)</t>
+    <t>380: source value from NEW PERSON - EFFECTIVE DATE/TIME (200-42)</t>
   </si>
   <si>
     <t>DR.1</t>
@@ -961,7 +961,7 @@
     <t>HumanName.text</t>
   </si>
   <si>
-    <t>382: source value from NEW PERSON - NAME COMPONENTS &gt; NAME COMPONENTS - (#200-10.1 &gt; 20 -)</t>
+    <t>382: source value from NEW PERSON - NAME COMPONENTS &gt; NAME COMPONENTS - (200-10.1 &gt; 20 -)</t>
   </si>
   <si>
     <t>implied by XPN.11</t>
@@ -1169,7 +1169,7 @@
     <t>ContactPoint.value</t>
   </si>
   <si>
-    <t>383: source value from NEW PERSON - PHONE (HOME) (#200-.131)</t>
+    <t>383: source value from NEW PERSON - PHONE (HOME) (200-.131)</t>
   </si>
   <si>
     <t>SStaff.PrescribingProvider.HomePhone,SStaff.SStaff.HomePhone</t>
@@ -1570,7 +1570,7 @@
     <t>Practitioner.address:home.line</t>
   </si>
   <si>
-    <t>398: source value from NEW PERSON - STREET ADDRESS 3 (#200-.113)</t>
+    <t>398: source value from NEW PERSON - STREET ADDRESS 3 (200-.113)</t>
   </si>
   <si>
     <t>SStaff.PrescribingProvider.StreetAddress3,SStaff.SStaff.StreetAddress3</t>
@@ -1579,7 +1579,7 @@
     <t>Practitioner.address:home.city</t>
   </si>
   <si>
-    <t>399: source value from NEW PERSON - CITY (#200-.114)</t>
+    <t>399: source value from NEW PERSON - CITY (200-.114)</t>
   </si>
   <si>
     <t>SStaff.PrescribingProvider.City,SStaff.SStaff.City</t>
@@ -1591,7 +1591,7 @@
     <t>Practitioner.address:home.state</t>
   </si>
   <si>
-    <t>400: source value from NEW PERSON - STATE (#200-.115)</t>
+    <t>400: source value from NEW PERSON - STATE (200-.115)</t>
   </si>
   <si>
     <t>SStaff.PrescribingProvider.StateIEN,SStaff.SStaff.StateName</t>
@@ -1600,7 +1600,7 @@
     <t>Practitioner.address:home.postalCode</t>
   </si>
   <si>
-    <t>401: source value from NEW PERSON - ZIP CODE (#200-.116)</t>
+    <t>401: source value from NEW PERSON - ZIP CODE (200-.116)</t>
   </si>
   <si>
     <t>SStaff.PrescribingProvider.ZipCode,SStaff.SStaff.ZipCode</t>
@@ -1609,7 +1609,7 @@
     <t>Practitioner.address:home.country</t>
   </si>
   <si>
-    <t>1530: transform using VF_PractitionerCountry on NEW PERSON - STATE (#200-.115) case not NULL</t>
+    <t>1530: transform using VF_PractitionerCountry on NEW PERSON - STATE (200-.115) case not NULL</t>
   </si>
   <si>
     <t>Practitioner.address:home.country.id</t>
@@ -1713,7 +1713,7 @@
     <t>Extension.value[x]</t>
   </si>
   <si>
-    <t>1531: fixed value = #unknown when NEW PERSON - STATE (#200-.115) case NULL</t>
+    <t>1531: fixed value = #unknown when NEW PERSON - STATE (200-.115) case NULL</t>
   </si>
   <si>
     <t>Practitioner.address:home.country.extension:11179-permitted-value-conceptmap</t>
@@ -1802,7 +1802,7 @@
     <t>Practitioner.address:temp.line</t>
   </si>
   <si>
-    <t>404: source value from NEW PERSON - TEMPORARY ADDRESS 3 (#200-.1213)</t>
+    <t>404: source value from NEW PERSON - TEMPORARY ADDRESS 3 (200-.1213)</t>
   </si>
   <si>
     <t>SStaff.SStaff.TemporaryAddress3</t>
@@ -1811,7 +1811,7 @@
     <t>Practitioner.address:temp.city</t>
   </si>
   <si>
-    <t>405: source value from NEW PERSON - TEMPORARY CITY (#200-.1214)</t>
+    <t>405: source value from NEW PERSON - TEMPORARY CITY (200-.1214)</t>
   </si>
   <si>
     <t>SStaff.SStaff.TemporaryCity</t>
@@ -1823,7 +1823,7 @@
     <t>Practitioner.address:temp.state</t>
   </si>
   <si>
-    <t>406: source value from NEW PERSON - TEMPORARY STATE (#200-.1215)</t>
+    <t>406: source value from NEW PERSON - TEMPORARY STATE (200-.1215)</t>
   </si>
   <si>
     <t>SStaff.SStaff.TemporaryStateName</t>
@@ -1832,7 +1832,7 @@
     <t>Practitioner.address:temp.postalCode</t>
   </si>
   <si>
-    <t>407: source value from NEW PERSON - TEMPORARY ZIP CODE (#200-.1216)</t>
+    <t>407: source value from NEW PERSON - TEMPORARY ZIP CODE (200-.1216)</t>
   </si>
   <si>
     <t>SStaff.SStaff.TemporaryZipCode</t>
@@ -1841,7 +1841,7 @@
     <t>Practitioner.address:temp.country</t>
   </si>
   <si>
-    <t>1532: transform using VF_PractitionerCountry on NEW PERSON - STATE (#200-.1215) case not NULL</t>
+    <t>1532: transform using VF_PractitionerCountry on NEW PERSON - TEMPORARY STATE (200-.1215) case not NULL</t>
   </si>
   <si>
     <t>Practitioner.address:temp.country.id</t>
@@ -1865,7 +1865,7 @@
     <t>Practitioner.address:temp.country.extension:data-absent-reason.value[x]</t>
   </si>
   <si>
-    <t>1533: fixed value = #unknown when NEW PERSON - STATE (#200-.1215) case NULL</t>
+    <t>1533: fixed value = #unknown when NEW PERSON - TEMPORARY STATE (200-.1215) case NULL</t>
   </si>
   <si>
     <t>Practitioner.address:temp.country.extension:11179-permitted-value-conceptmap</t>
@@ -1907,7 +1907,7 @@
     <t>Practitioner.address.period.start</t>
   </si>
   <si>
-    <t>408: source value from NEW PERSON - START DATE OF TEMP ADDRES (#200-.1217)</t>
+    <t>408: source value from NEW PERSON - START DATE OF TEMP ADDRES (200-.1217)</t>
   </si>
   <si>
     <t>SStaff.SStaff.TemporaryAddressStartDate</t>
@@ -1919,7 +1919,7 @@
     <t>Practitioner.address.period.end</t>
   </si>
   <si>
-    <t>409: source value from NEW PERSON - END DATE OF TEMP ADDRESS (#200-.1218)</t>
+    <t>409: source value from NEW PERSON - END DATE OF TEMP ADDRESS (200-.1218)</t>
   </si>
   <si>
     <t>SStaff.SStaff.TemporaryAddressEndDate</t>
@@ -1940,7 +1940,7 @@
     <t>http://va.gov/fhir/ValueSet/VSVFproviderGender</t>
   </si>
   <si>
-    <t>1790: terminologyMaps using VF_providerGender on NEW PERSON - SEX (#200-4)</t>
+    <t>1790: terminologyMaps using VF_providerGender on NEW PERSON - SEX (200-4)</t>
   </si>
   <si>
     <t>SStaff.SStaff.Gender,Staff.Staff.Gender</t>
@@ -1971,7 +1971,7 @@
     <t>Needed for identification.</t>
   </si>
   <si>
-    <t>394: source value from NEW PERSON - DOB (#200-5)</t>
+    <t>394: source value from NEW PERSON - DOB (200-5)</t>
   </si>
   <si>
     <t>SStaff.SStaff.DateOfBirth,Staff.Staff.DateofBirth</t>
@@ -2141,7 +2141,7 @@
     <t>CodeableConcept.text</t>
   </si>
   <si>
-    <t>395: source value from NEW PERSON - DEGREE (#200-10.6)</t>
+    <t>395: source value from NEW PERSON - DEGREE (200-10.6)</t>
   </si>
   <si>
     <t>C*E.9. But note many systems use C*E.2 for this</t>
@@ -2556,7 +2556,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="97.1953125" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="103.7578125" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="66.4765625" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="107.3984375" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="102.6171875" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.36.0</t>
+    <t>0.37.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T18:17:58+00:00</t>
+    <t>2024-04-10T21:21:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.37.0</t>
+    <t>0.38.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T21:21:54+00:00</t>
+    <t>2024-04-12T10:04:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -69,7 +69,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>VA (https://www.va.gov)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.38.0</t>
+    <t>0.39.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T10:04:01+00:00</t>
+    <t>2024-04-12T16:57:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.39.0</t>
+    <t>0.40.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T16:57:46+00:00</t>
+    <t>2024-04-13T07:20:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.40.0</t>
+    <t>0.41.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-13T07:20:06+00:00</t>
+    <t>2024-04-21T15:38:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -961,7 +961,7 @@
     <t>HumanName.text</t>
   </si>
   <si>
-    <t>382: source value from NEW PERSON - NAME COMPONENTS &gt; NAME COMPONENTS - (200-10.1 &gt; 20 -)</t>
+    <t>382: source value from NEW PERSON - NAME COMPONENTS &gt; NAME COMPONENTS - (200-10.1 &gt; 20-)</t>
   </si>
   <si>
     <t>implied by XPN.11</t>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.41.0</t>
+    <t>0.42.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-21T15:38:45+00:00</t>
+    <t>2024-04-22T07:04:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.42.0</t>
+    <t>0.43.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T07:04:34+00:00</t>
+    <t>2024-04-24T08:47:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.43.0</t>
+    <t>0.44.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-24T08:47:54+00:00</t>
+    <t>2024-04-25T08:17:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5189" uniqueCount="708">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5187" uniqueCount="708">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.44.0</t>
+    <t>0.45.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-25T08:17:47+00:00</t>
+    <t>2024-05-01T09:37:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1652,19 +1652,19 @@
     <t>Provides a reason why the expected value or elements in the element that is extended are missing.</t>
   </si>
   <si>
+    <t>ANY.nullFlavor</t>
+  </si>
+  <si>
+    <t>Practitioner.address:home.country.extension:data-absent-reason.id</t>
+  </si>
+  <si>
+    <t>Practitioner.address.country.extension.id</t>
+  </si>
+  <si>
     <t xml:space="preserve">ele-1
 </t>
   </si>
   <si>
-    <t>ANY.nullFlavor</t>
-  </si>
-  <si>
-    <t>Practitioner.address:home.country.extension:data-absent-reason.id</t>
-  </si>
-  <si>
-    <t>Practitioner.address.country.extension.id</t>
-  </si>
-  <si>
     <t>Practitioner.address:home.country.extension:data-absent-reason.extension</t>
   </si>
   <si>
@@ -1701,16 +1701,17 @@
     <t>Value of extension</t>
   </si>
   <si>
-    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/extensibility.html) for a list).</t>
-  </si>
-  <si>
-    <t>Used to specify why the normally expected content of the data element is missing.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/data-absent-reason|4.0.1</t>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R5/extensibility.html) for a list).</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
   </si>
   <si>
     <t>Extension.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ext-1
+</t>
   </si>
   <si>
     <t>1531: fixed value = #unknown when NEW PERSON - STATE (200-.115) case NULL</t>
@@ -12024,7 +12025,7 @@
         <v>79</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>527</v>
+        <v>80</v>
       </c>
       <c r="AJ79" t="s" s="2">
         <v>140</v>
@@ -12039,7 +12040,7 @@
         <v>80</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>80</v>
@@ -12050,10 +12051,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="B80" t="s" s="2">
         <v>529</v>
-      </c>
-      <c r="B80" t="s" s="2">
-        <v>530</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12076,7 +12077,7 @@
         <v>80</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>159</v>
+        <v>91</v>
       </c>
       <c r="L80" t="s" s="2">
         <v>160</v>
@@ -12142,7 +12143,7 @@
         <v>89</v>
       </c>
       <c r="AI80" t="s" s="2">
-        <v>80</v>
+        <v>530</v>
       </c>
       <c r="AJ80" t="s" s="2">
         <v>80</v>
@@ -12467,38 +12468,36 @@
       <c r="X83" t="s" s="2">
         <v>174</v>
       </c>
-      <c r="Y83" t="s" s="2">
+      <c r="Y83" s="2"/>
+      <c r="Z83" t="s" s="2">
         <v>544</v>
       </c>
-      <c r="Z83" t="s" s="2">
+      <c r="AA83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF83" t="s" s="2">
         <v>545</v>
       </c>
-      <c r="AA83" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB83" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC83" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD83" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE83" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF83" t="s" s="2">
+      <c r="AG83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH83" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI83" t="s" s="2">
         <v>546</v>
-      </c>
-      <c r="AG83" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH83" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI83" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AJ83" t="s" s="2">
         <v>101</v>
@@ -12620,7 +12619,7 @@
         <v>79</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>527</v>
+        <v>80</v>
       </c>
       <c r="AJ84" t="s" s="2">
         <v>140</v>
@@ -12649,7 +12648,7 @@
         <v>554</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12672,7 +12671,7 @@
         <v>80</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>159</v>
+        <v>91</v>
       </c>
       <c r="L85" t="s" s="2">
         <v>160</v>
@@ -12738,7 +12737,7 @@
         <v>89</v>
       </c>
       <c r="AI85" t="s" s="2">
-        <v>80</v>
+        <v>530</v>
       </c>
       <c r="AJ85" t="s" s="2">
         <v>80</v>
@@ -13085,16 +13084,16 @@
         <v>80</v>
       </c>
       <c r="AF88" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="AG88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH88" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI88" t="s" s="2">
         <v>546</v>
-      </c>
-      <c r="AG88" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH88" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI88" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AJ88" t="s" s="2">
         <v>101</v>
@@ -15124,7 +15123,7 @@
         <v>79</v>
       </c>
       <c r="AI105" t="s" s="2">
-        <v>527</v>
+        <v>80</v>
       </c>
       <c r="AJ105" t="s" s="2">
         <v>140</v>
@@ -15139,7 +15138,7 @@
         <v>80</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>80</v>
@@ -15153,7 +15152,7 @@
         <v>593</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15176,7 +15175,7 @@
         <v>80</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>159</v>
+        <v>91</v>
       </c>
       <c r="L106" t="s" s="2">
         <v>160</v>
@@ -15242,7 +15241,7 @@
         <v>89</v>
       </c>
       <c r="AI106" t="s" s="2">
-        <v>80</v>
+        <v>530</v>
       </c>
       <c r="AJ106" t="s" s="2">
         <v>80</v>
@@ -15567,38 +15566,36 @@
       <c r="X109" t="s" s="2">
         <v>174</v>
       </c>
-      <c r="Y109" t="s" s="2">
+      <c r="Y109" s="2"/>
+      <c r="Z109" t="s" s="2">
         <v>544</v>
       </c>
-      <c r="Z109" t="s" s="2">
+      <c r="AA109" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB109" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC109" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD109" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE109" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF109" t="s" s="2">
         <v>545</v>
       </c>
-      <c r="AA109" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB109" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC109" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD109" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE109" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF109" t="s" s="2">
+      <c r="AG109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH109" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI109" t="s" s="2">
         <v>546</v>
-      </c>
-      <c r="AG109" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH109" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI109" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AJ109" t="s" s="2">
         <v>101</v>
@@ -15720,7 +15717,7 @@
         <v>79</v>
       </c>
       <c r="AI110" t="s" s="2">
-        <v>527</v>
+        <v>80</v>
       </c>
       <c r="AJ110" t="s" s="2">
         <v>140</v>
@@ -15749,7 +15746,7 @@
         <v>599</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15772,7 +15769,7 @@
         <v>80</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>159</v>
+        <v>91</v>
       </c>
       <c r="L111" t="s" s="2">
         <v>160</v>
@@ -15838,7 +15835,7 @@
         <v>89</v>
       </c>
       <c r="AI111" t="s" s="2">
-        <v>80</v>
+        <v>530</v>
       </c>
       <c r="AJ111" t="s" s="2">
         <v>80</v>
@@ -16185,16 +16182,16 @@
         <v>80</v>
       </c>
       <c r="AF114" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="AG114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH114" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI114" t="s" s="2">
         <v>546</v>
-      </c>
-      <c r="AG114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH114" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI114" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AJ114" t="s" s="2">
         <v>101</v>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.45.0</t>
+    <t>0.46.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T09:37:14+00:00</t>
+    <t>2024-05-01T10:34:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5187" uniqueCount="708">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5187" uniqueCount="710">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.46.0</t>
+    <t>0.47.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T10:34:27+00:00</t>
+    <t>2024-05-04T09:18:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -660,7 +660,7 @@
     <t>415: source value from NEW PERSON - IEN (200-.001)</t>
   </si>
   <si>
-    <t>SStaff.PrescribingProvider.VPID</t>
+    <t>SStaff.PrescribingProvider.VPID,SStaff.SStaff.VAPersonIdentificationNumber</t>
   </si>
   <si>
     <t>CX.1 / EI.1</t>
@@ -964,6 +964,9 @@
     <t>382: source value from NEW PERSON - NAME COMPONENTS &gt; NAME COMPONENTS - (200-10.1 &gt; 20-)</t>
   </si>
   <si>
+    <t>SStaff.SStaff.FirstName,SStaff.SStaff.LastName,SStaff.SStaff.MiddleName,SStaff.SStaff.StaffNamePrefix,SStaff.SStaff.StaffNameSuffix</t>
+  </si>
+  <si>
     <t>implied by XPN.11</t>
   </si>
   <si>
@@ -1911,7 +1914,7 @@
     <t>408: source value from NEW PERSON - START DATE OF TEMP ADDRES (200-.1217)</t>
   </si>
   <si>
-    <t>SStaff.SStaff.TemporaryAddressStartDate</t>
+    <t>SStaff.SStaff.TemporaryAddressStartDateTime</t>
   </si>
   <si>
     <t>Practitioner.address:temp.period.end</t>
@@ -1923,7 +1926,7 @@
     <t>409: source value from NEW PERSON - END DATE OF TEMP ADDRESS (200-.1218)</t>
   </si>
   <si>
-    <t>SStaff.SStaff.TemporaryAddressEndDate</t>
+    <t>SStaff.SStaff.TemporaryAddressEndDateTime</t>
   </si>
   <si>
     <t>Practitioner.gender</t>
@@ -1975,7 +1978,7 @@
     <t>394: source value from NEW PERSON - DOB (200-5)</t>
   </si>
   <si>
-    <t>SStaff.SStaff.DateOfBirth,Staff.Staff.DateofBirth</t>
+    <t>SStaff.SStaff.BirthDateTime,Staff.Staff.BirthDateTime</t>
   </si>
   <si>
     <t>STF-6</t>
@@ -2143,6 +2146,9 @@
   </si>
   <si>
     <t>395: source value from NEW PERSON - DEGREE (200-10.6)</t>
+  </si>
+  <si>
+    <t>SStaff.SStaff.Degree,Staff.Staff.Degree</t>
   </si>
   <si>
     <t>C*E.9. But note many systems use C*E.2 for this</t>
@@ -2558,7 +2564,7 @@
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="103.7578125" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="66.4765625" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="123.75" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="107.3984375" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="102.6171875" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="52.3828125" customWidth="true" bestFit="true"/>
@@ -7132,13 +7138,13 @@
         <v>302</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>80</v>
+        <v>303</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>80</v>
@@ -7149,14 +7155,14 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -7178,13 +7184,13 @@
         <v>159</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -7234,7 +7240,7 @@
         <v>80</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -7255,13 +7261,13 @@
         <v>80</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>80</v>
@@ -7269,14 +7275,14 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -7298,13 +7304,13 @@
         <v>159</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -7354,7 +7360,7 @@
         <v>80</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -7375,13 +7381,13 @@
         <v>80</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>80</v>
@@ -7389,10 +7395,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7418,10 +7424,10 @@
         <v>159</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -7472,7 +7478,7 @@
         <v>80</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -7493,13 +7499,13 @@
         <v>80</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>80</v>
@@ -7507,10 +7513,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7536,10 +7542,10 @@
         <v>159</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -7590,7 +7596,7 @@
         <v>80</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -7611,10 +7617,10 @@
         <v>80</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>80</v>
@@ -7625,10 +7631,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7654,14 +7660,14 @@
         <v>212</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>80</v>
@@ -7710,7 +7716,7 @@
         <v>80</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -7731,10 +7737,10 @@
         <v>80</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>218</v>
@@ -7745,10 +7751,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7771,19 +7777,19 @@
         <v>90</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>80</v>
@@ -7832,7 +7838,7 @@
         <v>80</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -7853,13 +7859,13 @@
         <v>80</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>80</v>
@@ -7867,10 +7873,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7985,10 +7991,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8105,10 +8111,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8134,10 +8140,10 @@
         <v>109</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -8167,10 +8173,10 @@
         <v>174</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>80</v>
@@ -8188,7 +8194,7 @@
         <v>80</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -8197,7 +8203,7 @@
         <v>89</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>101</v>
@@ -8209,13 +8215,13 @@
         <v>80</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>80</v>
@@ -8223,10 +8229,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8252,16 +8258,16 @@
         <v>159</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>80</v>
@@ -8310,7 +8316,7 @@
         <v>80</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -8325,16 +8331,16 @@
         <v>101</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>210</v>
@@ -8345,10 +8351,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8374,16 +8380,16 @@
         <v>109</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>80</v>
@@ -8411,10 +8417,10 @@
         <v>174</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>80</v>
@@ -8432,7 +8438,7 @@
         <v>80</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -8453,13 +8459,13 @@
         <v>80</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>294</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>80</v>
@@ -8467,10 +8473,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8493,16 +8499,16 @@
         <v>90</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -8552,7 +8558,7 @@
         <v>80</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -8587,10 +8593,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8616,10 +8622,10 @@
         <v>212</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8670,7 +8676,7 @@
         <v>80</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -8694,7 +8700,7 @@
         <v>132</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>218</v>
@@ -8705,10 +8711,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8731,19 +8737,19 @@
         <v>90</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>80</v>
@@ -8780,7 +8786,7 @@
         <v>80</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AC52" s="2"/>
       <c r="AD52" t="s" s="2">
@@ -8790,7 +8796,7 @@
         <v>153</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -8811,10 +8817,10 @@
         <v>80</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>163</v>
@@ -8825,10 +8831,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8943,10 +8949,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9063,10 +9069,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9092,16 +9098,16 @@
         <v>109</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>80</v>
@@ -9114,7 +9120,7 @@
         <v>80</v>
       </c>
       <c r="T55" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="U55" t="s" s="2">
         <v>80</v>
@@ -9129,10 +9135,10 @@
         <v>174</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>80</v>
@@ -9150,7 +9156,7 @@
         <v>80</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -9171,13 +9177,13 @@
         <v>80</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>294</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>80</v>
@@ -9185,10 +9191,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9214,13 +9220,13 @@
         <v>109</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -9234,7 +9240,7 @@
         <v>80</v>
       </c>
       <c r="T56" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="U56" t="s" s="2">
         <v>80</v>
@@ -9249,10 +9255,10 @@
         <v>174</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>80</v>
@@ -9270,7 +9276,7 @@
         <v>80</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -9291,7 +9297,7 @@
         <v>80</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>294</v>
@@ -9305,10 +9311,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9334,13 +9340,13 @@
         <v>159</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="O57" t="s" s="2">
         <v>300</v>
@@ -9356,7 +9362,7 @@
         <v>80</v>
       </c>
       <c r="T57" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="U57" t="s" s="2">
         <v>80</v>
@@ -9392,7 +9398,7 @@
         <v>80</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -9413,10 +9419,10 @@
         <v>80</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>80</v>
@@ -9427,10 +9433,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9441,7 +9447,7 @@
         <v>78</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>90</v>
@@ -9456,10 +9462,10 @@
         <v>159</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -9474,7 +9480,7 @@
         <v>80</v>
       </c>
       <c r="T58" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="U58" t="s" s="2">
         <v>80</v>
@@ -9510,7 +9516,7 @@
         <v>80</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -9531,13 +9537,13 @@
         <v>80</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>80</v>
@@ -9545,14 +9551,14 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -9574,10 +9580,10 @@
         <v>159</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9592,7 +9598,7 @@
         <v>80</v>
       </c>
       <c r="T59" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="U59" t="s" s="2">
         <v>80</v>
@@ -9628,7 +9634,7 @@
         <v>80</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -9649,13 +9655,13 @@
         <v>80</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>80</v>
@@ -9663,14 +9669,14 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -9692,13 +9698,13 @@
         <v>159</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9712,7 +9718,7 @@
         <v>80</v>
       </c>
       <c r="T60" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="U60" t="s" s="2">
         <v>80</v>
@@ -9748,7 +9754,7 @@
         <v>80</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -9769,10 +9775,10 @@
         <v>80</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>80</v>
@@ -9783,14 +9789,14 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -9812,10 +9818,10 @@
         <v>159</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9845,10 +9851,10 @@
         <v>185</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>80</v>
@@ -9866,7 +9872,7 @@
         <v>80</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -9887,13 +9893,13 @@
         <v>80</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AP61" t="s" s="2">
         <v>80</v>
@@ -9901,14 +9907,14 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
@@ -9930,10 +9936,10 @@
         <v>159</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9948,7 +9954,7 @@
         <v>80</v>
       </c>
       <c r="T62" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="U62" t="s" s="2">
         <v>80</v>
@@ -9984,7 +9990,7 @@
         <v>80</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -10005,13 +10011,13 @@
         <v>80</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AP62" t="s" s="2">
         <v>80</v>
@@ -10019,10 +10025,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10048,13 +10054,13 @@
         <v>159</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -10104,7 +10110,7 @@
         <v>80</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -10125,13 +10131,13 @@
         <v>80</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AP63" t="s" s="2">
         <v>80</v>
@@ -10139,10 +10145,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10168,14 +10174,14 @@
         <v>212</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>80</v>
@@ -10188,7 +10194,7 @@
         <v>80</v>
       </c>
       <c r="T64" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="U64" t="s" s="2">
         <v>80</v>
@@ -10224,7 +10230,7 @@
         <v>80</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -10245,10 +10251,10 @@
         <v>80</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>218</v>
@@ -10259,13 +10265,13 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C65" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D65" t="s" s="2">
         <v>80</v>
@@ -10287,19 +10293,19 @@
         <v>90</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>80</v>
@@ -10348,7 +10354,7 @@
         <v>80</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
@@ -10369,10 +10375,10 @@
         <v>80</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>163</v>
@@ -10383,10 +10389,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10501,10 +10507,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10621,10 +10627,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10650,16 +10656,16 @@
         <v>109</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>80</v>
@@ -10672,7 +10678,7 @@
         <v>80</v>
       </c>
       <c r="T68" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="U68" t="s" s="2">
         <v>80</v>
@@ -10687,10 +10693,10 @@
         <v>174</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>80</v>
@@ -10708,7 +10714,7 @@
         <v>80</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -10729,13 +10735,13 @@
         <v>80</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>294</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AP68" t="s" s="2">
         <v>80</v>
@@ -10743,10 +10749,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10772,13 +10778,13 @@
         <v>109</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -10792,7 +10798,7 @@
         <v>80</v>
       </c>
       <c r="T69" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="U69" t="s" s="2">
         <v>80</v>
@@ -10807,10 +10813,10 @@
         <v>174</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>80</v>
@@ -10828,7 +10834,7 @@
         <v>80</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -10849,7 +10855,7 @@
         <v>80</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>294</v>
@@ -10863,10 +10869,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10892,13 +10898,13 @@
         <v>159</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="O70" t="s" s="2">
         <v>300</v>
@@ -10914,7 +10920,7 @@
         <v>80</v>
       </c>
       <c r="T70" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="U70" t="s" s="2">
         <v>80</v>
@@ -10950,7 +10956,7 @@
         <v>80</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -10971,10 +10977,10 @@
         <v>80</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>80</v>
@@ -10985,10 +10991,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10999,7 +11005,7 @@
         <v>78</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>90</v>
@@ -11014,10 +11020,10 @@
         <v>159</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -11032,7 +11038,7 @@
         <v>80</v>
       </c>
       <c r="T71" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="U71" t="s" s="2">
         <v>80</v>
@@ -11068,7 +11074,7 @@
         <v>80</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
@@ -11083,19 +11089,19 @@
         <v>101</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AP71" t="s" s="2">
         <v>80</v>
@@ -11103,14 +11109,14 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -11132,10 +11138,10 @@
         <v>159</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -11150,7 +11156,7 @@
         <v>80</v>
       </c>
       <c r="T72" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="U72" t="s" s="2">
         <v>80</v>
@@ -11186,7 +11192,7 @@
         <v>80</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
@@ -11201,19 +11207,19 @@
         <v>101</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AP72" t="s" s="2">
         <v>80</v>
@@ -11221,14 +11227,14 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
@@ -11250,13 +11256,13 @@
         <v>159</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -11270,7 +11276,7 @@
         <v>80</v>
       </c>
       <c r="T73" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="U73" t="s" s="2">
         <v>80</v>
@@ -11306,7 +11312,7 @@
         <v>80</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
@@ -11327,10 +11333,10 @@
         <v>80</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>80</v>
@@ -11341,14 +11347,14 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -11370,10 +11376,10 @@
         <v>159</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -11403,10 +11409,10 @@
         <v>185</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>80</v>
@@ -11424,7 +11430,7 @@
         <v>80</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -11439,19 +11445,19 @@
         <v>101</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AP74" t="s" s="2">
         <v>80</v>
@@ -11459,14 +11465,14 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
@@ -11488,10 +11494,10 @@
         <v>159</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -11506,7 +11512,7 @@
         <v>80</v>
       </c>
       <c r="T75" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="U75" t="s" s="2">
         <v>80</v>
@@ -11542,7 +11548,7 @@
         <v>80</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
@@ -11557,19 +11563,19 @@
         <v>101</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AP75" t="s" s="2">
         <v>80</v>
@@ -11577,10 +11583,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11606,13 +11612,13 @@
         <v>159</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -11662,7 +11668,7 @@
         <v>80</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>78</v>
@@ -11677,19 +11683,19 @@
         <v>101</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AP76" t="s" s="2">
         <v>80</v>
@@ -11697,10 +11703,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11726,10 +11732,10 @@
         <v>159</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11815,10 +11821,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11844,10 +11850,10 @@
         <v>135</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11931,13 +11937,13 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C79" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="D79" t="s" s="2">
         <v>80</v>
@@ -11959,13 +11965,13 @@
         <v>80</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -12040,7 +12046,7 @@
         <v>80</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>80</v>
@@ -12051,10 +12057,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12143,7 +12149,7 @@
         <v>89</v>
       </c>
       <c r="AI80" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AJ80" t="s" s="2">
         <v>80</v>
@@ -12169,10 +12175,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12198,10 +12204,10 @@
         <v>135</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -12287,10 +12293,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12316,13 +12322,13 @@
         <v>103</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -12330,7 +12336,7 @@
       </c>
       <c r="Q82" s="2"/>
       <c r="R82" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="S82" t="s" s="2">
         <v>80</v>
@@ -12372,7 +12378,7 @@
         <v>80</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>89</v>
@@ -12407,10 +12413,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12436,10 +12442,10 @@
         <v>109</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -12470,7 +12476,7 @@
       </c>
       <c r="Y83" s="2"/>
       <c r="Z83" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>80</v>
@@ -12488,7 +12494,7 @@
         <v>80</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
@@ -12497,16 +12503,16 @@
         <v>89</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AJ83" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>80</v>
@@ -12523,13 +12529,13 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C84" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="D84" t="s" s="2">
         <v>80</v>
@@ -12551,16 +12557,16 @@
         <v>80</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -12645,10 +12651,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12737,7 +12743,7 @@
         <v>89</v>
       </c>
       <c r="AI85" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AJ85" t="s" s="2">
         <v>80</v>
@@ -12763,10 +12769,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12792,10 +12798,10 @@
         <v>135</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -12881,10 +12887,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12910,13 +12916,13 @@
         <v>103</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -12924,7 +12930,7 @@
       </c>
       <c r="Q87" s="2"/>
       <c r="R87" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="S87" t="s" s="2">
         <v>80</v>
@@ -12966,7 +12972,7 @@
         <v>80</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>89</v>
@@ -13001,10 +13007,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13027,13 +13033,13 @@
         <v>80</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -13045,7 +13051,7 @@
         <v>80</v>
       </c>
       <c r="S88" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="T88" t="s" s="2">
         <v>80</v>
@@ -13084,7 +13090,7 @@
         <v>80</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>78</v>
@@ -13093,7 +13099,7 @@
         <v>89</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AJ88" t="s" s="2">
         <v>101</v>
@@ -13119,10 +13125,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13148,10 +13154,10 @@
         <v>159</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -13175,7 +13181,7 @@
         <v>80</v>
       </c>
       <c r="W89" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="X89" t="s" s="2">
         <v>80</v>
@@ -13202,7 +13208,7 @@
         <v>80</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>78</v>
@@ -13237,10 +13243,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13266,14 +13272,14 @@
         <v>212</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>80</v>
@@ -13286,7 +13292,7 @@
         <v>80</v>
       </c>
       <c r="T90" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="U90" t="s" s="2">
         <v>80</v>
@@ -13322,7 +13328,7 @@
         <v>80</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>78</v>
@@ -13343,10 +13349,10 @@
         <v>80</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>218</v>
@@ -13357,13 +13363,13 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C91" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="D91" t="s" s="2">
         <v>80</v>
@@ -13385,19 +13391,19 @@
         <v>90</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>80</v>
@@ -13446,7 +13452,7 @@
         <v>80</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>78</v>
@@ -13467,10 +13473,10 @@
         <v>80</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>163</v>
@@ -13481,10 +13487,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13599,10 +13605,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13719,10 +13725,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13748,16 +13754,16 @@
         <v>109</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>80</v>
@@ -13770,7 +13776,7 @@
         <v>80</v>
       </c>
       <c r="T94" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="U94" t="s" s="2">
         <v>80</v>
@@ -13785,10 +13791,10 @@
         <v>174</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="Z94" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>80</v>
@@ -13806,7 +13812,7 @@
         <v>80</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>78</v>
@@ -13827,13 +13833,13 @@
         <v>80</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AN94" t="s" s="2">
         <v>294</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AP94" t="s" s="2">
         <v>80</v>
@@ -13841,10 +13847,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13870,13 +13876,13 @@
         <v>109</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -13890,7 +13896,7 @@
         <v>80</v>
       </c>
       <c r="T95" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="U95" t="s" s="2">
         <v>80</v>
@@ -13905,10 +13911,10 @@
         <v>174</v>
       </c>
       <c r="Y95" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="Z95" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AA95" t="s" s="2">
         <v>80</v>
@@ -13926,7 +13932,7 @@
         <v>80</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>78</v>
@@ -13947,7 +13953,7 @@
         <v>80</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AN95" t="s" s="2">
         <v>294</v>
@@ -13961,10 +13967,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13990,13 +13996,13 @@
         <v>159</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="O96" t="s" s="2">
         <v>300</v>
@@ -14012,7 +14018,7 @@
         <v>80</v>
       </c>
       <c r="T96" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="U96" t="s" s="2">
         <v>80</v>
@@ -14048,7 +14054,7 @@
         <v>80</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>78</v>
@@ -14069,10 +14075,10 @@
         <v>80</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>80</v>
@@ -14083,10 +14089,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14097,7 +14103,7 @@
         <v>78</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H97" t="s" s="2">
         <v>90</v>
@@ -14112,10 +14118,10 @@
         <v>159</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -14130,7 +14136,7 @@
         <v>80</v>
       </c>
       <c r="T97" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="U97" t="s" s="2">
         <v>80</v>
@@ -14166,7 +14172,7 @@
         <v>80</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>78</v>
@@ -14181,19 +14187,19 @@
         <v>101</v>
       </c>
       <c r="AK97" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AO97" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AP97" t="s" s="2">
         <v>80</v>
@@ -14201,14 +14207,14 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
@@ -14230,10 +14236,10 @@
         <v>159</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -14248,7 +14254,7 @@
         <v>80</v>
       </c>
       <c r="T98" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="U98" t="s" s="2">
         <v>80</v>
@@ -14284,7 +14290,7 @@
         <v>80</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>78</v>
@@ -14299,19 +14305,19 @@
         <v>101</v>
       </c>
       <c r="AK98" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AO98" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AP98" t="s" s="2">
         <v>80</v>
@@ -14319,14 +14325,14 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
@@ -14348,13 +14354,13 @@
         <v>159</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -14368,7 +14374,7 @@
         <v>80</v>
       </c>
       <c r="T99" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="U99" t="s" s="2">
         <v>80</v>
@@ -14404,7 +14410,7 @@
         <v>80</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>78</v>
@@ -14425,10 +14431,10 @@
         <v>80</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>80</v>
@@ -14439,14 +14445,14 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
@@ -14468,10 +14474,10 @@
         <v>159</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -14501,10 +14507,10 @@
         <v>185</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>80</v>
@@ -14522,7 +14528,7 @@
         <v>80</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>78</v>
@@ -14537,19 +14543,19 @@
         <v>101</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AP100" t="s" s="2">
         <v>80</v>
@@ -14557,14 +14563,14 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
@@ -14586,10 +14592,10 @@
         <v>159</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -14604,7 +14610,7 @@
         <v>80</v>
       </c>
       <c r="T101" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="U101" t="s" s="2">
         <v>80</v>
@@ -14640,7 +14646,7 @@
         <v>80</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>78</v>
@@ -14655,19 +14661,19 @@
         <v>101</v>
       </c>
       <c r="AK101" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AP101" t="s" s="2">
         <v>80</v>
@@ -14675,10 +14681,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14704,13 +14710,13 @@
         <v>159</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -14760,7 +14766,7 @@
         <v>80</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>78</v>
@@ -14775,19 +14781,19 @@
         <v>101</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AO102" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AP102" t="s" s="2">
         <v>80</v>
@@ -14795,10 +14801,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14824,10 +14830,10 @@
         <v>159</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -14913,10 +14919,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14942,10 +14948,10 @@
         <v>135</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -15029,13 +15035,13 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C105" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="D105" t="s" s="2">
         <v>80</v>
@@ -15057,13 +15063,13 @@
         <v>80</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -15138,7 +15144,7 @@
         <v>80</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>80</v>
@@ -15149,10 +15155,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15241,7 +15247,7 @@
         <v>89</v>
       </c>
       <c r="AI106" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AJ106" t="s" s="2">
         <v>80</v>
@@ -15267,10 +15273,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15296,10 +15302,10 @@
         <v>135</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -15385,10 +15391,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15414,13 +15420,13 @@
         <v>103</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
@@ -15428,7 +15434,7 @@
       </c>
       <c r="Q108" s="2"/>
       <c r="R108" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="S108" t="s" s="2">
         <v>80</v>
@@ -15470,7 +15476,7 @@
         <v>80</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>89</v>
@@ -15505,10 +15511,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15534,10 +15540,10 @@
         <v>109</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" s="2"/>
@@ -15568,7 +15574,7 @@
       </c>
       <c r="Y109" s="2"/>
       <c r="Z109" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AA109" t="s" s="2">
         <v>80</v>
@@ -15586,7 +15592,7 @@
         <v>80</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>78</v>
@@ -15595,16 +15601,16 @@
         <v>89</v>
       </c>
       <c r="AI109" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AJ109" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AM109" t="s" s="2">
         <v>80</v>
@@ -15621,13 +15627,13 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C110" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="D110" t="s" s="2">
         <v>80</v>
@@ -15649,16 +15655,16 @@
         <v>80</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
@@ -15743,10 +15749,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15835,7 +15841,7 @@
         <v>89</v>
       </c>
       <c r="AI111" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AJ111" t="s" s="2">
         <v>80</v>
@@ -15861,10 +15867,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15890,10 +15896,10 @@
         <v>135</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" s="2"/>
@@ -15979,10 +15985,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16008,13 +16014,13 @@
         <v>103</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
@@ -16022,7 +16028,7 @@
       </c>
       <c r="Q113" s="2"/>
       <c r="R113" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="S113" t="s" s="2">
         <v>80</v>
@@ -16064,7 +16070,7 @@
         <v>80</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>89</v>
@@ -16099,10 +16105,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16125,13 +16131,13 @@
         <v>80</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
@@ -16143,7 +16149,7 @@
         <v>80</v>
       </c>
       <c r="S114" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="T114" t="s" s="2">
         <v>80</v>
@@ -16182,7 +16188,7 @@
         <v>80</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>78</v>
@@ -16191,7 +16197,7 @@
         <v>89</v>
       </c>
       <c r="AI114" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AJ114" t="s" s="2">
         <v>101</v>
@@ -16217,10 +16223,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16246,10 +16252,10 @@
         <v>159</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" s="2"/>
@@ -16273,7 +16279,7 @@
         <v>80</v>
       </c>
       <c r="W115" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="X115" t="s" s="2">
         <v>80</v>
@@ -16300,7 +16306,7 @@
         <v>80</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>78</v>
@@ -16335,10 +16341,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16364,14 +16370,14 @@
         <v>212</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>80</v>
@@ -16384,7 +16390,7 @@
         <v>80</v>
       </c>
       <c r="T116" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="U116" t="s" s="2">
         <v>80</v>
@@ -16420,7 +16426,7 @@
         <v>80</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>78</v>
@@ -16441,10 +16447,10 @@
         <v>80</v>
       </c>
       <c r="AM116" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AN116" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AO116" t="s" s="2">
         <v>218</v>
@@ -16455,10 +16461,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16573,10 +16579,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16693,10 +16699,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16793,10 +16799,10 @@
         <v>101</v>
       </c>
       <c r="AK119" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="AL119" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="AM119" t="s" s="2">
         <v>253</v>
@@ -16813,10 +16819,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16915,10 +16921,10 @@
         <v>101</v>
       </c>
       <c r="AK120" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="AL120" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="AM120" t="s" s="2">
         <v>262</v>
@@ -16935,10 +16941,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16964,14 +16970,14 @@
         <v>109</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="P121" t="s" s="2">
         <v>80</v>
@@ -17000,7 +17006,7 @@
       </c>
       <c r="Y121" s="2"/>
       <c r="Z121" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="AA121" t="s" s="2">
         <v>80</v>
@@ -17018,7 +17024,7 @@
         <v>80</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>78</v>
@@ -17033,19 +17039,19 @@
         <v>101</v>
       </c>
       <c r="AK121" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="AL121" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="AM121" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AN121" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="AO121" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="AP121" t="s" s="2">
         <v>80</v>
@@ -17053,10 +17059,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -17079,17 +17085,17 @@
         <v>90</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>80</v>
@@ -17138,7 +17144,7 @@
         <v>80</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>78</v>
@@ -17153,19 +17159,19 @@
         <v>101</v>
       </c>
       <c r="AK122" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="AL122" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="AM122" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="AN122" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="AO122" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="AP122" t="s" s="2">
         <v>80</v>
@@ -17173,10 +17179,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -17199,17 +17205,17 @@
         <v>80</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="N123" s="2"/>
       <c r="O123" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>80</v>
@@ -17258,7 +17264,7 @@
         <v>80</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>78</v>
@@ -17282,10 +17288,10 @@
         <v>80</v>
       </c>
       <c r="AN123" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="AO123" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="AP123" t="s" s="2">
         <v>80</v>
@@ -17293,10 +17299,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17319,13 +17325,13 @@
         <v>80</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="N124" s="2"/>
       <c r="O124" s="2"/>
@@ -17376,7 +17382,7 @@
         <v>80</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>78</v>
@@ -17397,13 +17403,13 @@
         <v>80</v>
       </c>
       <c r="AM124" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="AN124" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="AO124" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="AP124" t="s" s="2">
         <v>80</v>
@@ -17411,10 +17417,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17529,10 +17535,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17649,14 +17655,14 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="E127" s="2"/>
       <c r="F127" t="s" s="2">
@@ -17678,10 +17684,10 @@
         <v>135</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="N127" t="s" s="2">
         <v>138</v>
@@ -17736,7 +17742,7 @@
         <v>80</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>78</v>
@@ -17771,10 +17777,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17800,14 +17806,14 @@
         <v>147</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="N128" s="2"/>
       <c r="O128" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>80</v>
@@ -17856,7 +17862,7 @@
         <v>80</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>78</v>
@@ -17880,7 +17886,7 @@
         <v>80</v>
       </c>
       <c r="AN128" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="AO128" t="s" s="2">
         <v>80</v>
@@ -17891,10 +17897,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17920,10 +17926,10 @@
         <v>180</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="N129" s="2"/>
       <c r="O129" s="2"/>
@@ -17950,13 +17956,13 @@
         <v>80</v>
       </c>
       <c r="X129" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="Y129" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="Z129" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="AA129" t="s" s="2">
         <v>80</v>
@@ -17974,7 +17980,7 @@
         <v>80</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>89</v>
@@ -17998,10 +18004,10 @@
         <v>80</v>
       </c>
       <c r="AN129" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="AO129" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="AP129" t="s" s="2">
         <v>80</v>
@@ -18009,10 +18015,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -18127,10 +18133,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -18247,10 +18253,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18273,19 +18279,19 @@
         <v>90</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="O132" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="P132" t="s" s="2">
         <v>80</v>
@@ -18334,7 +18340,7 @@
         <v>80</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>78</v>
@@ -18355,10 +18361,10 @@
         <v>80</v>
       </c>
       <c r="AM132" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="AN132" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="AO132" t="s" s="2">
         <v>80</v>
@@ -18369,10 +18375,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18398,16 +18404,16 @@
         <v>159</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="O133" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="P133" t="s" s="2">
         <v>80</v>
@@ -18456,7 +18462,7 @@
         <v>80</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>78</v>
@@ -18471,16 +18477,16 @@
         <v>101</v>
       </c>
       <c r="AK133" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="AL133" t="s" s="2">
-        <v>80</v>
+        <v>689</v>
       </c>
       <c r="AM133" t="s" s="2">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="AN133" t="s" s="2">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="AO133" t="s" s="2">
         <v>80</v>
@@ -18491,10 +18497,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18520,14 +18526,14 @@
         <v>212</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="N134" s="2"/>
       <c r="O134" t="s" s="2">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>80</v>
@@ -18576,7 +18582,7 @@
         <v>80</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>78</v>
@@ -18600,10 +18606,10 @@
         <v>80</v>
       </c>
       <c r="AN134" t="s" s="2">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="AO134" t="s" s="2">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="AP134" t="s" s="2">
         <v>80</v>
@@ -18611,10 +18617,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18640,10 +18646,10 @@
         <v>220</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="N135" s="2"/>
       <c r="O135" s="2"/>
@@ -18694,7 +18700,7 @@
         <v>80</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>78</v>
@@ -18718,7 +18724,7 @@
         <v>80</v>
       </c>
       <c r="AN135" t="s" s="2">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="AO135" t="s" s="2">
         <v>80</v>
@@ -18729,10 +18735,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -18758,16 +18764,16 @@
         <v>180</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="O136" t="s" s="2">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="P136" t="s" s="2">
         <v>80</v>
@@ -18816,7 +18822,7 @@
         <v>80</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>78</v>
@@ -18837,13 +18843,13 @@
         <v>80</v>
       </c>
       <c r="AM136" t="s" s="2">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="AN136" t="s" s="2">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="AO136" t="s" s="2">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="AP136" t="s" s="2">
         <v>80</v>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.47.0</t>
+    <t>0.48.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-04T09:18:00+00:00</t>
+    <t>2024-05-06T08:00:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.48.0</t>
+    <t>0.49.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T08:00:03+00:00</t>
+    <t>2024-05-06T11:38:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.49.0</t>
+    <t>0.50.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T11:38:53+00:00</t>
+    <t>2024-05-08T06:31:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5187" uniqueCount="710">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5187" uniqueCount="711">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.50.0</t>
+    <t>0.51.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-08T06:31:45+00:00</t>
+    <t>2024-05-11T08:27:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1552,25 +1552,28 @@
     <t>XAD.12 / XAD.13 + XAD.14</t>
   </si>
   <si>
-    <t>Practitioner.address:home</t>
-  </si>
-  <si>
-    <t>Practitioner.address:home.id</t>
-  </si>
-  <si>
-    <t>Practitioner.address:home.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.address:home.use</t>
-  </si>
-  <si>
-    <t>Practitioner.address:home.type</t>
-  </si>
-  <si>
-    <t>Practitioner.address:home.text</t>
-  </si>
-  <si>
-    <t>Practitioner.address:home.line</t>
+    <t>Practitioner.address:va-home</t>
+  </si>
+  <si>
+    <t>va-home</t>
+  </si>
+  <si>
+    <t>Practitioner.address:va-home.id</t>
+  </si>
+  <si>
+    <t>Practitioner.address:va-home.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.address:va-home.use</t>
+  </si>
+  <si>
+    <t>Practitioner.address:va-home.type</t>
+  </si>
+  <si>
+    <t>Practitioner.address:va-home.text</t>
+  </si>
+  <si>
+    <t>Practitioner.address:va-home.line</t>
   </si>
   <si>
     <t>398: source value from NEW PERSON - STREET ADDRESS 3 (200-.113)</t>
@@ -1579,7 +1582,7 @@
     <t>SStaff.PrescribingProvider.StreetAddress3,SStaff.SStaff.StreetAddress3</t>
   </si>
   <si>
-    <t>Practitioner.address:home.city</t>
+    <t>Practitioner.address:va-home.city</t>
   </si>
   <si>
     <t>399: source value from NEW PERSON - CITY (200-.114)</t>
@@ -1588,10 +1591,10 @@
     <t>SStaff.PrescribingProvider.City,SStaff.SStaff.City</t>
   </si>
   <si>
-    <t>Practitioner.address:home.district</t>
-  </si>
-  <si>
-    <t>Practitioner.address:home.state</t>
+    <t>Practitioner.address:va-home.district</t>
+  </si>
+  <si>
+    <t>Practitioner.address:va-home.state</t>
   </si>
   <si>
     <t>400: source value from NEW PERSON - STATE (200-.115)</t>
@@ -1600,7 +1603,7 @@
     <t>SStaff.PrescribingProvider.StateIEN,SStaff.SStaff.StateName</t>
   </si>
   <si>
-    <t>Practitioner.address:home.postalCode</t>
+    <t>Practitioner.address:va-home.postalCode</t>
   </si>
   <si>
     <t>401: source value from NEW PERSON - ZIP CODE (200-.116)</t>
@@ -1609,13 +1612,13 @@
     <t>SStaff.PrescribingProvider.ZipCode,SStaff.SStaff.ZipCode</t>
   </si>
   <si>
-    <t>Practitioner.address:home.country</t>
+    <t>Practitioner.address:va-home.country</t>
   </si>
   <si>
     <t>1530: transform using VF_PractitionerCountry on NEW PERSON - STATE (200-.115) case not NULL</t>
   </si>
   <si>
-    <t>Practitioner.address:home.country.id</t>
+    <t>Practitioner.address:va-home.country.id</t>
   </si>
   <si>
     <t>Practitioner.address.country.id</t>
@@ -1627,7 +1630,7 @@
     <t>unique id for the element within a resource (for internal references)</t>
   </si>
   <si>
-    <t>Practitioner.address:home.country.extension</t>
+    <t>Practitioner.address:va-home.country.extension</t>
   </si>
   <si>
     <t>Practitioner.address.country.extension</t>
@@ -1639,7 +1642,7 @@
     <t>An Extension</t>
   </si>
   <si>
-    <t>Practitioner.address:home.country.extension:data-absent-reason</t>
+    <t>Practitioner.address:va-home.country.extension:data-absent-reason</t>
   </si>
   <si>
     <t>data-absent-reason</t>
@@ -1658,7 +1661,7 @@
     <t>ANY.nullFlavor</t>
   </si>
   <si>
-    <t>Practitioner.address:home.country.extension:data-absent-reason.id</t>
+    <t>Practitioner.address:va-home.country.extension:data-absent-reason.id</t>
   </si>
   <si>
     <t>Practitioner.address.country.extension.id</t>
@@ -1668,13 +1671,13 @@
 </t>
   </si>
   <si>
-    <t>Practitioner.address:home.country.extension:data-absent-reason.extension</t>
+    <t>Practitioner.address:va-home.country.extension:data-absent-reason.extension</t>
   </si>
   <si>
     <t>Practitioner.address.country.extension.extension</t>
   </si>
   <si>
-    <t>Practitioner.address:home.country.extension:data-absent-reason.url</t>
+    <t>Practitioner.address:va-home.country.extension:data-absent-reason.url</t>
   </si>
   <si>
     <t>Practitioner.address.country.extension.url</t>
@@ -1695,7 +1698,7 @@
     <t>Extension.url</t>
   </si>
   <si>
-    <t>Practitioner.address:home.country.extension:data-absent-reason.value[x]</t>
+    <t>Practitioner.address:va-home.country.extension:data-absent-reason.value[x]</t>
   </si>
   <si>
     <t>Practitioner.address.country.extension.value[x]</t>
@@ -1720,7 +1723,7 @@
     <t>1531: fixed value = #unknown when NEW PERSON - STATE (200-.115) case NULL</t>
   </si>
   <si>
-    <t>Practitioner.address:home.country.extension:11179-permitted-value-conceptmap</t>
+    <t>Practitioner.address:va-home.country.extension:11179-permitted-value-conceptmap</t>
   </si>
   <si>
     <t>11179-permitted-value-conceptmap</t>
@@ -1739,19 +1742,19 @@
     <t>The permitted value set must have a 1..1 set of codes for each code in the value meaning value set.  The source for the concept map is the value set the extension appears on.  The target is the permitted-value-valueset.</t>
   </si>
   <si>
-    <t>Practitioner.address:home.country.extension:11179-permitted-value-conceptmap.id</t>
-  </si>
-  <si>
-    <t>Practitioner.address:home.country.extension:11179-permitted-value-conceptmap.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.address:home.country.extension:11179-permitted-value-conceptmap.url</t>
+    <t>Practitioner.address:va-home.country.extension:11179-permitted-value-conceptmap.id</t>
+  </si>
+  <si>
+    <t>Practitioner.address:va-home.country.extension:11179-permitted-value-conceptmap.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.address:va-home.country.extension:11179-permitted-value-conceptmap.url</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/StructureDefinition/11179-permitted-value-conceptmap</t>
   </si>
   <si>
-    <t>Practitioner.address:home.country.extension:11179-permitted-value-conceptmap.value[x]</t>
+    <t>Practitioner.address:va-home.country.extension:11179-permitted-value-conceptmap.value[x]</t>
   </si>
   <si>
     <t xml:space="preserve">canonical(ConceptMap)
@@ -1761,7 +1764,7 @@
     <t>http://va.gov/fhir/ConceptMap/CMVFPractitionerCountry</t>
   </si>
   <si>
-    <t>Practitioner.address:home.country.value</t>
+    <t>Practitioner.address:va-home.country.value</t>
   </si>
   <si>
     <t>Practitioner.address.country.value</t>
@@ -1779,31 +1782,31 @@
     <t>string.value</t>
   </si>
   <si>
-    <t>Practitioner.address:home.period</t>
-  </si>
-  <si>
-    <t>Practitioner.address:temp</t>
-  </si>
-  <si>
-    <t>temp</t>
-  </si>
-  <si>
-    <t>Practitioner.address:temp.id</t>
-  </si>
-  <si>
-    <t>Practitioner.address:temp.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.address:temp.use</t>
-  </si>
-  <si>
-    <t>Practitioner.address:temp.type</t>
-  </si>
-  <si>
-    <t>Practitioner.address:temp.text</t>
-  </si>
-  <si>
-    <t>Practitioner.address:temp.line</t>
+    <t>Practitioner.address:va-home.period</t>
+  </si>
+  <si>
+    <t>Practitioner.address:va-temp</t>
+  </si>
+  <si>
+    <t>va-temp</t>
+  </si>
+  <si>
+    <t>Practitioner.address:va-temp.id</t>
+  </si>
+  <si>
+    <t>Practitioner.address:va-temp.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.address:va-temp.use</t>
+  </si>
+  <si>
+    <t>Practitioner.address:va-temp.type</t>
+  </si>
+  <si>
+    <t>Practitioner.address:va-temp.text</t>
+  </si>
+  <si>
+    <t>Practitioner.address:va-temp.line</t>
   </si>
   <si>
     <t>404: source value from NEW PERSON - TEMPORARY ADDRESS 3 (200-.1213)</t>
@@ -1812,7 +1815,7 @@
     <t>SStaff.SStaff.TemporaryAddress3</t>
   </si>
   <si>
-    <t>Practitioner.address:temp.city</t>
+    <t>Practitioner.address:va-temp.city</t>
   </si>
   <si>
     <t>405: source value from NEW PERSON - TEMPORARY CITY (200-.1214)</t>
@@ -1821,10 +1824,10 @@
     <t>SStaff.SStaff.TemporaryCity</t>
   </si>
   <si>
-    <t>Practitioner.address:temp.district</t>
-  </si>
-  <si>
-    <t>Practitioner.address:temp.state</t>
+    <t>Practitioner.address:va-temp.district</t>
+  </si>
+  <si>
+    <t>Practitioner.address:va-temp.state</t>
   </si>
   <si>
     <t>406: source value from NEW PERSON - TEMPORARY STATE (200-.1215)</t>
@@ -1833,7 +1836,7 @@
     <t>SStaff.SStaff.TemporaryStateName</t>
   </si>
   <si>
-    <t>Practitioner.address:temp.postalCode</t>
+    <t>Practitioner.address:va-temp.postalCode</t>
   </si>
   <si>
     <t>407: source value from NEW PERSON - TEMPORARY ZIP CODE (200-.1216)</t>
@@ -1842,70 +1845,70 @@
     <t>SStaff.SStaff.TemporaryZipCode</t>
   </si>
   <si>
-    <t>Practitioner.address:temp.country</t>
+    <t>Practitioner.address:va-temp.country</t>
   </si>
   <si>
     <t>1532: transform using VF_PractitionerCountry on NEW PERSON - TEMPORARY STATE (200-.1215) case not NULL</t>
   </si>
   <si>
-    <t>Practitioner.address:temp.country.id</t>
-  </si>
-  <si>
-    <t>Practitioner.address:temp.country.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.address:temp.country.extension:data-absent-reason</t>
-  </si>
-  <si>
-    <t>Practitioner.address:temp.country.extension:data-absent-reason.id</t>
-  </si>
-  <si>
-    <t>Practitioner.address:temp.country.extension:data-absent-reason.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.address:temp.country.extension:data-absent-reason.url</t>
-  </si>
-  <si>
-    <t>Practitioner.address:temp.country.extension:data-absent-reason.value[x]</t>
+    <t>Practitioner.address:va-temp.country.id</t>
+  </si>
+  <si>
+    <t>Practitioner.address:va-temp.country.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.address:va-temp.country.extension:data-absent-reason</t>
+  </si>
+  <si>
+    <t>Practitioner.address:va-temp.country.extension:data-absent-reason.id</t>
+  </si>
+  <si>
+    <t>Practitioner.address:va-temp.country.extension:data-absent-reason.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.address:va-temp.country.extension:data-absent-reason.url</t>
+  </si>
+  <si>
+    <t>Practitioner.address:va-temp.country.extension:data-absent-reason.value[x]</t>
   </si>
   <si>
     <t>1533: fixed value = #unknown when NEW PERSON - TEMPORARY STATE (200-.1215) case NULL</t>
   </si>
   <si>
-    <t>Practitioner.address:temp.country.extension:11179-permitted-value-conceptmap</t>
-  </si>
-  <si>
-    <t>Practitioner.address:temp.country.extension:11179-permitted-value-conceptmap.id</t>
-  </si>
-  <si>
-    <t>Practitioner.address:temp.country.extension:11179-permitted-value-conceptmap.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.address:temp.country.extension:11179-permitted-value-conceptmap.url</t>
-  </si>
-  <si>
-    <t>Practitioner.address:temp.country.extension:11179-permitted-value-conceptmap.value[x]</t>
-  </si>
-  <si>
-    <t>Practitioner.address:temp.country.value</t>
-  </si>
-  <si>
-    <t>Practitioner.address:temp.period</t>
-  </si>
-  <si>
-    <t>Practitioner.address:temp.period.id</t>
+    <t>Practitioner.address:va-temp.country.extension:11179-permitted-value-conceptmap</t>
+  </si>
+  <si>
+    <t>Practitioner.address:va-temp.country.extension:11179-permitted-value-conceptmap.id</t>
+  </si>
+  <si>
+    <t>Practitioner.address:va-temp.country.extension:11179-permitted-value-conceptmap.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.address:va-temp.country.extension:11179-permitted-value-conceptmap.url</t>
+  </si>
+  <si>
+    <t>Practitioner.address:va-temp.country.extension:11179-permitted-value-conceptmap.value[x]</t>
+  </si>
+  <si>
+    <t>Practitioner.address:va-temp.country.value</t>
+  </si>
+  <si>
+    <t>Practitioner.address:va-temp.period</t>
+  </si>
+  <si>
+    <t>Practitioner.address:va-temp.period.id</t>
   </si>
   <si>
     <t>Practitioner.address.period.id</t>
   </si>
   <si>
-    <t>Practitioner.address:temp.period.extension</t>
+    <t>Practitioner.address:va-temp.period.extension</t>
   </si>
   <si>
     <t>Practitioner.address.period.extension</t>
   </si>
   <si>
-    <t>Practitioner.address:temp.period.start</t>
+    <t>Practitioner.address:va-temp.period.start</t>
   </si>
   <si>
     <t>Practitioner.address.period.start</t>
@@ -1917,7 +1920,7 @@
     <t>SStaff.SStaff.TemporaryAddressStartDateTime</t>
   </si>
   <si>
-    <t>Practitioner.address:temp.period.end</t>
+    <t>Practitioner.address:va-temp.period.end</t>
   </si>
   <si>
     <t>Practitioner.address.period.end</t>
@@ -2528,7 +2531,7 @@
   <dimension ref="A1:AP136"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="85.890625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="88.76171875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="46.1796875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="34.3203125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
@@ -10271,7 +10274,7 @@
         <v>395</v>
       </c>
       <c r="C65" t="s" s="2">
-        <v>411</v>
+        <v>495</v>
       </c>
       <c r="D65" t="s" s="2">
         <v>80</v>
@@ -10389,7 +10392,7 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B66" t="s" s="2">
         <v>404</v>
@@ -10507,7 +10510,7 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B67" t="s" s="2">
         <v>405</v>
@@ -10627,7 +10630,7 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B68" t="s" s="2">
         <v>406</v>
@@ -10749,7 +10752,7 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B69" t="s" s="2">
         <v>417</v>
@@ -10869,7 +10872,7 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B70" t="s" s="2">
         <v>426</v>
@@ -10991,7 +10994,7 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B71" t="s" s="2">
         <v>433</v>
@@ -11089,10 +11092,10 @@
         <v>101</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>439</v>
@@ -11109,7 +11112,7 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B72" t="s" s="2">
         <v>442</v>
@@ -11207,10 +11210,10 @@
         <v>101</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>448</v>
@@ -11227,7 +11230,7 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B73" t="s" s="2">
         <v>451</v>
@@ -11347,7 +11350,7 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B74" t="s" s="2">
         <v>460</v>
@@ -11445,10 +11448,10 @@
         <v>101</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>467</v>
@@ -11465,7 +11468,7 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B75" t="s" s="2">
         <v>470</v>
@@ -11563,10 +11566,10 @@
         <v>101</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>476</v>
@@ -11583,7 +11586,7 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B76" t="s" s="2">
         <v>479</v>
@@ -11683,10 +11686,10 @@
         <v>101</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>484</v>
@@ -11703,10 +11706,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11732,10 +11735,10 @@
         <v>159</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11821,10 +11824,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11850,10 +11853,10 @@
         <v>135</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11937,13 +11940,13 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C79" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="D79" t="s" s="2">
         <v>80</v>
@@ -11965,13 +11968,13 @@
         <v>80</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -12046,7 +12049,7 @@
         <v>80</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>80</v>
@@ -12057,10 +12060,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12149,7 +12152,7 @@
         <v>89</v>
       </c>
       <c r="AI80" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AJ80" t="s" s="2">
         <v>80</v>
@@ -12175,10 +12178,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12204,10 +12207,10 @@
         <v>135</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -12293,10 +12296,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12322,13 +12325,13 @@
         <v>103</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -12336,7 +12339,7 @@
       </c>
       <c r="Q82" s="2"/>
       <c r="R82" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="S82" t="s" s="2">
         <v>80</v>
@@ -12378,7 +12381,7 @@
         <v>80</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>89</v>
@@ -12413,10 +12416,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12442,10 +12445,10 @@
         <v>109</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -12476,7 +12479,7 @@
       </c>
       <c r="Y83" s="2"/>
       <c r="Z83" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>80</v>
@@ -12494,7 +12497,7 @@
         <v>80</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
@@ -12503,16 +12506,16 @@
         <v>89</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AJ83" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>80</v>
@@ -12529,13 +12532,13 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C84" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="D84" t="s" s="2">
         <v>80</v>
@@ -12557,16 +12560,16 @@
         <v>80</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -12651,10 +12654,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12743,7 +12746,7 @@
         <v>89</v>
       </c>
       <c r="AI85" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AJ85" t="s" s="2">
         <v>80</v>
@@ -12769,10 +12772,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12798,10 +12801,10 @@
         <v>135</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -12887,10 +12890,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12916,13 +12919,13 @@
         <v>103</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -12930,7 +12933,7 @@
       </c>
       <c r="Q87" s="2"/>
       <c r="R87" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="S87" t="s" s="2">
         <v>80</v>
@@ -12972,7 +12975,7 @@
         <v>80</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>89</v>
@@ -13007,10 +13010,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13033,13 +13036,13 @@
         <v>80</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -13051,7 +13054,7 @@
         <v>80</v>
       </c>
       <c r="S88" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="T88" t="s" s="2">
         <v>80</v>
@@ -13090,7 +13093,7 @@
         <v>80</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>78</v>
@@ -13099,7 +13102,7 @@
         <v>89</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AJ88" t="s" s="2">
         <v>101</v>
@@ -13125,10 +13128,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13154,10 +13157,10 @@
         <v>159</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -13181,7 +13184,7 @@
         <v>80</v>
       </c>
       <c r="W89" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="X89" t="s" s="2">
         <v>80</v>
@@ -13208,7 +13211,7 @@
         <v>80</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>78</v>
@@ -13243,7 +13246,7 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B90" t="s" s="2">
         <v>487</v>
@@ -13363,13 +13366,13 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B91" t="s" s="2">
         <v>395</v>
       </c>
       <c r="C91" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="D91" t="s" s="2">
         <v>80</v>
@@ -13487,7 +13490,7 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B92" t="s" s="2">
         <v>404</v>
@@ -13605,7 +13608,7 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B93" t="s" s="2">
         <v>405</v>
@@ -13725,7 +13728,7 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B94" t="s" s="2">
         <v>406</v>
@@ -13847,7 +13850,7 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B95" t="s" s="2">
         <v>417</v>
@@ -13967,7 +13970,7 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B96" t="s" s="2">
         <v>426</v>
@@ -14089,7 +14092,7 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B97" t="s" s="2">
         <v>433</v>
@@ -14187,10 +14190,10 @@
         <v>101</v>
       </c>
       <c r="AK97" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="AM97" t="s" s="2">
         <v>439</v>
@@ -14207,7 +14210,7 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B98" t="s" s="2">
         <v>442</v>
@@ -14305,10 +14308,10 @@
         <v>101</v>
       </c>
       <c r="AK98" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AM98" t="s" s="2">
         <v>448</v>
@@ -14325,7 +14328,7 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B99" t="s" s="2">
         <v>451</v>
@@ -14445,7 +14448,7 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B100" t="s" s="2">
         <v>460</v>
@@ -14543,10 +14546,10 @@
         <v>101</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AM100" t="s" s="2">
         <v>467</v>
@@ -14563,7 +14566,7 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B101" t="s" s="2">
         <v>470</v>
@@ -14661,10 +14664,10 @@
         <v>101</v>
       </c>
       <c r="AK101" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AM101" t="s" s="2">
         <v>476</v>
@@ -14681,7 +14684,7 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B102" t="s" s="2">
         <v>479</v>
@@ -14781,10 +14784,10 @@
         <v>101</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AM102" t="s" s="2">
         <v>484</v>
@@ -14801,10 +14804,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14830,10 +14833,10 @@
         <v>159</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -14919,10 +14922,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14948,10 +14951,10 @@
         <v>135</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -15035,13 +15038,13 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C105" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="D105" t="s" s="2">
         <v>80</v>
@@ -15063,13 +15066,13 @@
         <v>80</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -15144,7 +15147,7 @@
         <v>80</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>80</v>
@@ -15155,10 +15158,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15247,7 +15250,7 @@
         <v>89</v>
       </c>
       <c r="AI106" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AJ106" t="s" s="2">
         <v>80</v>
@@ -15273,10 +15276,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15302,10 +15305,10 @@
         <v>135</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -15391,10 +15394,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15420,13 +15423,13 @@
         <v>103</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
@@ -15434,7 +15437,7 @@
       </c>
       <c r="Q108" s="2"/>
       <c r="R108" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="S108" t="s" s="2">
         <v>80</v>
@@ -15476,7 +15479,7 @@
         <v>80</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>89</v>
@@ -15511,10 +15514,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15540,10 +15543,10 @@
         <v>109</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" s="2"/>
@@ -15574,7 +15577,7 @@
       </c>
       <c r="Y109" s="2"/>
       <c r="Z109" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AA109" t="s" s="2">
         <v>80</v>
@@ -15592,7 +15595,7 @@
         <v>80</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>78</v>
@@ -15601,16 +15604,16 @@
         <v>89</v>
       </c>
       <c r="AI109" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AJ109" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AM109" t="s" s="2">
         <v>80</v>
@@ -15627,13 +15630,13 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C110" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="D110" t="s" s="2">
         <v>80</v>
@@ -15655,16 +15658,16 @@
         <v>80</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
@@ -15749,10 +15752,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15841,7 +15844,7 @@
         <v>89</v>
       </c>
       <c r="AI111" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AJ111" t="s" s="2">
         <v>80</v>
@@ -15867,10 +15870,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15896,10 +15899,10 @@
         <v>135</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" s="2"/>
@@ -15985,10 +15988,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16014,13 +16017,13 @@
         <v>103</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
@@ -16028,7 +16031,7 @@
       </c>
       <c r="Q113" s="2"/>
       <c r="R113" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="S113" t="s" s="2">
         <v>80</v>
@@ -16070,7 +16073,7 @@
         <v>80</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>89</v>
@@ -16105,10 +16108,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16131,13 +16134,13 @@
         <v>80</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
@@ -16149,7 +16152,7 @@
         <v>80</v>
       </c>
       <c r="S114" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="T114" t="s" s="2">
         <v>80</v>
@@ -16188,7 +16191,7 @@
         <v>80</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>78</v>
@@ -16197,7 +16200,7 @@
         <v>89</v>
       </c>
       <c r="AI114" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AJ114" t="s" s="2">
         <v>101</v>
@@ -16223,10 +16226,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16252,10 +16255,10 @@
         <v>159</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" s="2"/>
@@ -16279,7 +16282,7 @@
         <v>80</v>
       </c>
       <c r="W115" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="X115" t="s" s="2">
         <v>80</v>
@@ -16306,7 +16309,7 @@
         <v>80</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>78</v>
@@ -16341,7 +16344,7 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B116" t="s" s="2">
         <v>487</v>
@@ -16461,10 +16464,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16579,10 +16582,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16699,10 +16702,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16799,10 +16802,10 @@
         <v>101</v>
       </c>
       <c r="AK119" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="AL119" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="AM119" t="s" s="2">
         <v>253</v>
@@ -16819,10 +16822,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16921,10 +16924,10 @@
         <v>101</v>
       </c>
       <c r="AK120" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="AL120" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="AM120" t="s" s="2">
         <v>262</v>
@@ -16941,10 +16944,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16970,14 +16973,14 @@
         <v>109</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="P121" t="s" s="2">
         <v>80</v>
@@ -17006,7 +17009,7 @@
       </c>
       <c r="Y121" s="2"/>
       <c r="Z121" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="AA121" t="s" s="2">
         <v>80</v>
@@ -17024,7 +17027,7 @@
         <v>80</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>78</v>
@@ -17039,19 +17042,19 @@
         <v>101</v>
       </c>
       <c r="AK121" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="AL121" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AM121" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="AN121" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="AO121" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="AP121" t="s" s="2">
         <v>80</v>
@@ -17059,10 +17062,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -17085,17 +17088,17 @@
         <v>90</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>80</v>
@@ -17144,7 +17147,7 @@
         <v>80</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>78</v>
@@ -17159,19 +17162,19 @@
         <v>101</v>
       </c>
       <c r="AK122" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="AL122" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="AM122" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="AN122" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="AO122" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="AP122" t="s" s="2">
         <v>80</v>
@@ -17179,10 +17182,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -17205,17 +17208,17 @@
         <v>80</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="N123" s="2"/>
       <c r="O123" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>80</v>
@@ -17264,7 +17267,7 @@
         <v>80</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>78</v>
@@ -17288,10 +17291,10 @@
         <v>80</v>
       </c>
       <c r="AN123" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="AO123" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="AP123" t="s" s="2">
         <v>80</v>
@@ -17299,10 +17302,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17325,13 +17328,13 @@
         <v>80</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="N124" s="2"/>
       <c r="O124" s="2"/>
@@ -17382,7 +17385,7 @@
         <v>80</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>78</v>
@@ -17403,13 +17406,13 @@
         <v>80</v>
       </c>
       <c r="AM124" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="AN124" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="AO124" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="AP124" t="s" s="2">
         <v>80</v>
@@ -17417,10 +17420,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17535,10 +17538,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17655,14 +17658,14 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="E127" s="2"/>
       <c r="F127" t="s" s="2">
@@ -17684,10 +17687,10 @@
         <v>135</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="N127" t="s" s="2">
         <v>138</v>
@@ -17742,7 +17745,7 @@
         <v>80</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>78</v>
@@ -17777,10 +17780,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17806,14 +17809,14 @@
         <v>147</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="N128" s="2"/>
       <c r="O128" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>80</v>
@@ -17862,7 +17865,7 @@
         <v>80</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>78</v>
@@ -17886,7 +17889,7 @@
         <v>80</v>
       </c>
       <c r="AN128" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="AO128" t="s" s="2">
         <v>80</v>
@@ -17897,10 +17900,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17926,10 +17929,10 @@
         <v>180</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="N129" s="2"/>
       <c r="O129" s="2"/>
@@ -17956,13 +17959,13 @@
         <v>80</v>
       </c>
       <c r="X129" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="Y129" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="Z129" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="AA129" t="s" s="2">
         <v>80</v>
@@ -17980,7 +17983,7 @@
         <v>80</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>89</v>
@@ -18004,10 +18007,10 @@
         <v>80</v>
       </c>
       <c r="AN129" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="AO129" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="AP129" t="s" s="2">
         <v>80</v>
@@ -18015,10 +18018,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -18133,10 +18136,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -18253,10 +18256,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18279,19 +18282,19 @@
         <v>90</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="O132" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="P132" t="s" s="2">
         <v>80</v>
@@ -18340,7 +18343,7 @@
         <v>80</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>78</v>
@@ -18361,10 +18364,10 @@
         <v>80</v>
       </c>
       <c r="AM132" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="AN132" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="AO132" t="s" s="2">
         <v>80</v>
@@ -18375,10 +18378,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18404,16 +18407,16 @@
         <v>159</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="O133" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="P133" t="s" s="2">
         <v>80</v>
@@ -18462,7 +18465,7 @@
         <v>80</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>78</v>
@@ -18477,16 +18480,16 @@
         <v>101</v>
       </c>
       <c r="AK133" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="AL133" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="AM133" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="AN133" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="AO133" t="s" s="2">
         <v>80</v>
@@ -18497,10 +18500,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18526,14 +18529,14 @@
         <v>212</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="N134" s="2"/>
       <c r="O134" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>80</v>
@@ -18582,7 +18585,7 @@
         <v>80</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>78</v>
@@ -18606,10 +18609,10 @@
         <v>80</v>
       </c>
       <c r="AN134" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="AO134" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="AP134" t="s" s="2">
         <v>80</v>
@@ -18617,10 +18620,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18646,10 +18649,10 @@
         <v>220</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="N135" s="2"/>
       <c r="O135" s="2"/>
@@ -18700,7 +18703,7 @@
         <v>80</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>78</v>
@@ -18724,7 +18727,7 @@
         <v>80</v>
       </c>
       <c r="AN135" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="AO135" t="s" s="2">
         <v>80</v>
@@ -18735,10 +18738,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -18764,16 +18767,16 @@
         <v>180</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="O136" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="P136" t="s" s="2">
         <v>80</v>
@@ -18822,7 +18825,7 @@
         <v>80</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>78</v>
@@ -18843,13 +18846,13 @@
         <v>80</v>
       </c>
       <c r="AM136" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="AN136" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="AO136" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="AP136" t="s" s="2">
         <v>80</v>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.52.0</t>
+    <t>0.53.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-19T08:28:17+00:00</t>
+    <t>2024-05-22T14:44:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.53.0</t>
+    <t>0.54.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-22T14:44:53+00:00</t>
+    <t>2024-05-25T10:26:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1039,10 +1039,10 @@
     <t>Practitioner.identifier:va-IEN.system</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/identifiers/Sta3n&lt;stationNr&gt;/200</t>
-  </si>
-  <si>
-    <t>415-1: fixed value = http://va.gov/fhir/identifiers/Sta3n&lt;stationNr&gt;/200</t>
+    <t>http://va.gov/fhir/identifiers/Sta3n$stationNr/200</t>
+  </si>
+  <si>
+    <t>415-1: fixed value = http://va.gov/fhir/identifiers/Sta3n$stationNr/200</t>
   </si>
   <si>
     <t>Practitioner.identifier:va-IEN.value</t>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.54.0</t>
+    <t>0.57.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-25T10:26:15+00:00</t>
+    <t>2024-06-04T15:52:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1039,10 +1039,10 @@
     <t>Practitioner.identifier:va-IEN.system</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/identifiers/Sta3n$stationNr/200</t>
-  </si>
-  <si>
-    <t>415-1: fixed value = http://va.gov/fhir/identifiers/Sta3n$stationNr/200</t>
+    <t>http://va.gov/identifiers/$Sta3n/200</t>
+  </si>
+  <si>
+    <t>415-1: fixed value = http://va.gov/identifiers/$Sta3n/200</t>
   </si>
   <si>
     <t>Practitioner.identifier:va-IEN.value</t>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-04T15:52:07+00:00</t>
+    <t>2024-06-11T05:38:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T05:38:55+00:00</t>
+    <t>2024-06-12T18:51:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.57.0</t>
+    <t>0.58.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-12T18:51:20+00:00</t>
+    <t>2024-06-14T11:56:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.58.0</t>
+    <t>0.59.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-14T11:56:40+00:00</t>
+    <t>2024-06-21T15:05:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-21T15:05:18+00:00</t>
+    <t>2024-07-09T16:26:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.59.0</t>
+    <t>0.61.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-09T16:26:13+00:00</t>
+    <t>2024-07-24T18:59:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.61.0</t>
+    <t>0.62.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-24T18:59:55+00:00</t>
+    <t>2024-07-28T09:11:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.62.0</t>
+    <t>0.63.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-28T09:11:13+00:00</t>
+    <t>2024-07-31T09:58:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.63.0</t>
+    <t>0.64.311</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T09:58:27+00:00</t>
+    <t>2024-07-31T19:09:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.311</t>
+    <t>0.64.312</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T19:09:08+00:00</t>
+    <t>2024-08-02T13:01:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.312</t>
+    <t>0.64.316</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-02T13:01:18+00:00</t>
+    <t>2024-08-04T09:05:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.316</t>
+    <t>0.64.318</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-04T09:05:29+00:00</t>
+    <t>2024-08-05T15:01:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.318</t>
+    <t>0.65.329</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-05T15:01:43+00:00</t>
+    <t>2024-08-13T08:01:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.329</t>
+    <t>0.65.332</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T08:01:15+00:00</t>
+    <t>2024-08-13T15:06:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.332</t>
+    <t>0.65.334</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T15:06:38+00:00</t>
+    <t>2024-08-14T15:16:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-14T15:16:17+00:00</t>
+    <t>2024-08-17T06:29:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.334</t>
+    <t>0.65.339</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-17T06:29:49+00:00</t>
+    <t>2024-08-18T10:15:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.339</t>
+    <t>0.65.341</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-18T10:15:47+00:00</t>
+    <t>2024-08-20T15:42:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.341</t>
+    <t>0.65.343</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-20T15:42:57+00:00</t>
+    <t>2024-08-24T10:06:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.343</t>
+    <t>0.65.345</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-24T10:06:05+00:00</t>
+    <t>2024-08-26T15:27:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.345</t>
+    <t>0.65.348</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-26T15:27:18+00:00</t>
+    <t>2024-09-15T08:33:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.348</t>
+    <t>0.66.354</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-15T08:33:43+00:00</t>
+    <t>2024-09-19T08:45:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$164</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$108</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6262" uniqueCount="784">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4157" uniqueCount="656">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.354</t>
+    <t>0.66.364</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-19T08:45:12+00:00</t>
+    <t>2024-10-02T18:53:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1784,395 +1784,6 @@
   </si>
   <si>
     <t>XAD.12 / XAD.13 + XAD.14</t>
-  </si>
-  <si>
-    <t>Practitioner.address:va-home</t>
-  </si>
-  <si>
-    <t>va-home</t>
-  </si>
-  <si>
-    <t>Practitioner.address:va-home.id</t>
-  </si>
-  <si>
-    <t>Practitioner.address:va-home.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.address:va-home.use</t>
-  </si>
-  <si>
-    <t>396-1: fixed value = #home</t>
-  </si>
-  <si>
-    <t>Practitioner.address:va-home.type</t>
-  </si>
-  <si>
-    <t>Practitioner.address:va-home.text</t>
-  </si>
-  <si>
-    <t>Practitioner.address:va-home.line</t>
-  </si>
-  <si>
-    <t>398: source value from NEW PERSON - STREET ADDRESS 3 (200-.113)</t>
-  </si>
-  <si>
-    <t>SStaff.PrescribingProvider.StreetAddress3,SStaff.SStaff.StreetAddress3</t>
-  </si>
-  <si>
-    <t>Practitioner.address:va-home.city</t>
-  </si>
-  <si>
-    <t>399: source value from NEW PERSON - CITY (200-.114)</t>
-  </si>
-  <si>
-    <t>SStaff.PrescribingProvider.City,SStaff.SStaff.City</t>
-  </si>
-  <si>
-    <t>Practitioner.address:va-home.district</t>
-  </si>
-  <si>
-    <t>Practitioner.address:va-home.state</t>
-  </si>
-  <si>
-    <t>400: source value from NEW PERSON - STATE (200-.115)</t>
-  </si>
-  <si>
-    <t>SStaff.PrescribingProvider.StateIEN,SStaff.SStaff.StateName</t>
-  </si>
-  <si>
-    <t>Practitioner.address:va-home.postalCode</t>
-  </si>
-  <si>
-    <t>401: source value from NEW PERSON - ZIP CODE (200-.116)</t>
-  </si>
-  <si>
-    <t>SStaff.PrescribingProvider.ZipCode,SStaff.SStaff.ZipCode</t>
-  </si>
-  <si>
-    <t>Practitioner.address:va-home.country</t>
-  </si>
-  <si>
-    <t>1530: transform using VF_PractitionerCountry on NEW PERSON - STATE (200-.115) case not NULL</t>
-  </si>
-  <si>
-    <t>Practitioner.address:va-home.country.id</t>
-  </si>
-  <si>
-    <t>Practitioner.address.country.id</t>
-  </si>
-  <si>
-    <t>xml:id (or equivalent in JSON)</t>
-  </si>
-  <si>
-    <t>unique id for the element within a resource (for internal references)</t>
-  </si>
-  <si>
-    <t>Practitioner.address:va-home.country.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.address.country.extension</t>
-  </si>
-  <si>
-    <t>Extension</t>
-  </si>
-  <si>
-    <t>An Extension</t>
-  </si>
-  <si>
-    <t>Practitioner.address:va-home.country.extension:data-absent-reason</t>
-  </si>
-  <si>
-    <t>data-absent-reason</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {data-absent-reason}
-</t>
-  </si>
-  <si>
-    <t>unknown | asked | temp | notasked | masked | unsupported | astext | error</t>
-  </si>
-  <si>
-    <t>Provides a reason why the expected value or elements in the element that is extended are missing.</t>
-  </si>
-  <si>
-    <t>ANY.nullFlavor</t>
-  </si>
-  <si>
-    <t>Practitioner.address:va-home.country.extension:data-absent-reason.id</t>
-  </si>
-  <si>
-    <t>Practitioner.address.country.extension.id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
-    <t>Practitioner.address:va-home.country.extension:data-absent-reason.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.address.country.extension.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.address:va-home.country.extension:data-absent-reason.url</t>
-  </si>
-  <si>
-    <t>Practitioner.address.country.extension.url</t>
-  </si>
-  <si>
-    <t>identifies the meaning of the extension</t>
-  </si>
-  <si>
-    <t>Source of the definition for the extension code - a logical name or a URL.</t>
-  </si>
-  <si>
-    <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/StructureDefinition/data-absent-reason</t>
-  </si>
-  <si>
-    <t>Extension.url</t>
-  </si>
-  <si>
-    <t>Practitioner.address:va-home.country.extension:data-absent-reason.value[x]</t>
-  </si>
-  <si>
-    <t>Practitioner.address.country.extension.value[x]</t>
-  </si>
-  <si>
-    <t>Value of extension</t>
-  </si>
-  <si>
-    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R5/extensibility.html) for a list).</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
-  </si>
-  <si>
-    <t>Extension.value[x]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ext-1
-</t>
-  </si>
-  <si>
-    <t>1531: fixed value = #unknown when NEW PERSON - STATE (200-.115) case NULL</t>
-  </si>
-  <si>
-    <t>Practitioner.address:va-home.country.extension:11179-permitted-value-conceptmap</t>
-  </si>
-  <si>
-    <t>11179-permitted-value-conceptmap</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {11179-permitted-value-conceptmap}
-</t>
-  </si>
-  <si>
-    <t>Mapping from permitted to transmitted</t>
-  </si>
-  <si>
-    <t>Expresses the linkage between the internal codes used for storage and the codes used for exchange.</t>
-  </si>
-  <si>
-    <t>The permitted value set must have a 1..1 set of codes for each code in the value meaning value set.  The source for the concept map is the value set the extension appears on.  The target is the permitted-value-valueset.</t>
-  </si>
-  <si>
-    <t>Practitioner.address:va-home.country.extension:11179-permitted-value-conceptmap.id</t>
-  </si>
-  <si>
-    <t>Practitioner.address:va-home.country.extension:11179-permitted-value-conceptmap.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.address:va-home.country.extension:11179-permitted-value-conceptmap.url</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/StructureDefinition/11179-permitted-value-conceptmap</t>
-  </si>
-  <si>
-    <t>Practitioner.address:va-home.country.extension:11179-permitted-value-conceptmap.value[x]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canonical(ConceptMap)
-</t>
-  </si>
-  <si>
-    <t>http://va.gov/fhir/ConceptMap/CMVFPractitionerCountry</t>
-  </si>
-  <si>
-    <t>Practitioner.address:va-home.country.value</t>
-  </si>
-  <si>
-    <t>Practitioner.address.country.value</t>
-  </si>
-  <si>
-    <t>Primitive value for string</t>
-  </si>
-  <si>
-    <t>The actual value</t>
-  </si>
-  <si>
-    <t>1048576</t>
-  </si>
-  <si>
-    <t>string.value</t>
-  </si>
-  <si>
-    <t>Practitioner.address:va-home.period</t>
-  </si>
-  <si>
-    <t>Practitioner.address:va-temp</t>
-  </si>
-  <si>
-    <t>va-temp</t>
-  </si>
-  <si>
-    <t>Practitioner.address:va-temp.id</t>
-  </si>
-  <si>
-    <t>Practitioner.address:va-temp.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.address:va-temp.use</t>
-  </si>
-  <si>
-    <t>temp</t>
-  </si>
-  <si>
-    <t>402-1: fixed value = #temp</t>
-  </si>
-  <si>
-    <t>Practitioner.address:va-temp.type</t>
-  </si>
-  <si>
-    <t>Practitioner.address:va-temp.text</t>
-  </si>
-  <si>
-    <t>Practitioner.address:va-temp.line</t>
-  </si>
-  <si>
-    <t>404: source value from NEW PERSON - TEMPORARY ADDRESS 3 (200-.1213)</t>
-  </si>
-  <si>
-    <t>SStaff.SStaff.TemporaryAddress3</t>
-  </si>
-  <si>
-    <t>Practitioner.address:va-temp.city</t>
-  </si>
-  <si>
-    <t>405: source value from NEW PERSON - TEMPORARY CITY (200-.1214)</t>
-  </si>
-  <si>
-    <t>SStaff.SStaff.TemporaryCity</t>
-  </si>
-  <si>
-    <t>Practitioner.address:va-temp.district</t>
-  </si>
-  <si>
-    <t>Practitioner.address:va-temp.state</t>
-  </si>
-  <si>
-    <t>406: source value from NEW PERSON - TEMPORARY STATE (200-.1215)</t>
-  </si>
-  <si>
-    <t>SStaff.SStaff.TemporaryStateName</t>
-  </si>
-  <si>
-    <t>Practitioner.address:va-temp.postalCode</t>
-  </si>
-  <si>
-    <t>407: source value from NEW PERSON - TEMPORARY ZIP CODE (200-.1216)</t>
-  </si>
-  <si>
-    <t>SStaff.SStaff.TemporaryZipCode</t>
-  </si>
-  <si>
-    <t>Practitioner.address:va-temp.country</t>
-  </si>
-  <si>
-    <t>1532: transform using VF_PractitionerCountry on NEW PERSON - TEMPORARY STATE (200-.1215) case not NULL</t>
-  </si>
-  <si>
-    <t>Practitioner.address:va-temp.country.id</t>
-  </si>
-  <si>
-    <t>Practitioner.address:va-temp.country.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.address:va-temp.country.extension:data-absent-reason</t>
-  </si>
-  <si>
-    <t>Practitioner.address:va-temp.country.extension:data-absent-reason.id</t>
-  </si>
-  <si>
-    <t>Practitioner.address:va-temp.country.extension:data-absent-reason.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.address:va-temp.country.extension:data-absent-reason.url</t>
-  </si>
-  <si>
-    <t>Practitioner.address:va-temp.country.extension:data-absent-reason.value[x]</t>
-  </si>
-  <si>
-    <t>1533: fixed value = #unknown when NEW PERSON - TEMPORARY STATE (200-.1215) case NULL</t>
-  </si>
-  <si>
-    <t>Practitioner.address:va-temp.country.extension:11179-permitted-value-conceptmap</t>
-  </si>
-  <si>
-    <t>Practitioner.address:va-temp.country.extension:11179-permitted-value-conceptmap.id</t>
-  </si>
-  <si>
-    <t>Practitioner.address:va-temp.country.extension:11179-permitted-value-conceptmap.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.address:va-temp.country.extension:11179-permitted-value-conceptmap.url</t>
-  </si>
-  <si>
-    <t>Practitioner.address:va-temp.country.extension:11179-permitted-value-conceptmap.value[x]</t>
-  </si>
-  <si>
-    <t>Practitioner.address:va-temp.country.value</t>
-  </si>
-  <si>
-    <t>Practitioner.address:va-temp.period</t>
-  </si>
-  <si>
-    <t>Practitioner.address:va-temp.period.id</t>
-  </si>
-  <si>
-    <t>Practitioner.address.period.id</t>
-  </si>
-  <si>
-    <t>Practitioner.address:va-temp.period.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.address.period.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.address:va-temp.period.start</t>
-  </si>
-  <si>
-    <t>Practitioner.address.period.start</t>
-  </si>
-  <si>
-    <t>408: source value from NEW PERSON - START DATE OF TEMP ADDRES (200-.1217)</t>
-  </si>
-  <si>
-    <t>SStaff.SStaff.TemporaryAddressStartDateTime</t>
-  </si>
-  <si>
-    <t>Practitioner.address:va-temp.period.end</t>
-  </si>
-  <si>
-    <t>Practitioner.address.period.end</t>
-  </si>
-  <si>
-    <t>409: source value from NEW PERSON - END DATE OF TEMP ADDRESS (200-.1218)</t>
-  </si>
-  <si>
-    <t>SStaff.SStaff.TemporaryAddressEndDateTime</t>
   </si>
   <si>
     <t>Practitioner.gender</t>
@@ -2771,12 +2382,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP164"/>
+  <dimension ref="A1:AP108"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="88.76171875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="46.1796875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="34.3203125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="1" max="1" width="40.70703125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="40.70703125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -2784,7 +2395,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="46.23828125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="23.58203125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -12414,14 +12025,16 @@
         <v>80</v>
       </c>
       <c r="AB80" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="AC80" s="2"/>
+        <v>80</v>
+      </c>
+      <c r="AC80" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="AD80" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE80" t="s" s="2">
-        <v>153</v>
+        <v>80</v>
       </c>
       <c r="AF80" t="s" s="2">
         <v>467</v>
@@ -13896,11 +13509,9 @@
         <v>564</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="C93" t="s" s="2">
-        <v>565</v>
-      </c>
+        <v>564</v>
+      </c>
+      <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
         <v>80</v>
       </c>
@@ -13921,19 +13532,17 @@
         <v>90</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>468</v>
+        <v>109</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>469</v>
+        <v>565</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="N93" t="s" s="2">
-        <v>471</v>
-      </c>
+        <v>566</v>
+      </c>
+      <c r="N93" s="2"/>
       <c r="O93" t="s" s="2">
-        <v>472</v>
+        <v>567</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>80</v>
@@ -13958,13 +13567,11 @@
         <v>80</v>
       </c>
       <c r="X93" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y93" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="Y93" s="2"/>
       <c r="Z93" t="s" s="2">
-        <v>80</v>
+        <v>568</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>80</v>
@@ -13982,13 +13589,13 @@
         <v>80</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>467</v>
+        <v>564</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI93" t="s" s="2">
         <v>80</v>
@@ -13997,19 +13604,19 @@
         <v>101</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>80</v>
+        <v>569</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>80</v>
+        <v>570</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>473</v>
+        <v>571</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>474</v>
+        <v>572</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>167</v>
+        <v>573</v>
       </c>
       <c r="AP93" t="s" s="2">
         <v>80</v>
@@ -14017,10 +13624,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>566</v>
+        <v>574</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>475</v>
+        <v>574</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14034,25 +13641,27 @@
         <v>89</v>
       </c>
       <c r="H94" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="I94" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J94" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>163</v>
+        <v>575</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>164</v>
+        <v>576</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>165</v>
+        <v>577</v>
       </c>
       <c r="N94" s="2"/>
-      <c r="O94" s="2"/>
+      <c r="O94" t="s" s="2">
+        <v>578</v>
+      </c>
       <c r="P94" t="s" s="2">
         <v>80</v>
       </c>
@@ -14100,7 +13709,7 @@
         <v>80</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>166</v>
+        <v>574</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>78</v>
@@ -14112,22 +13721,22 @@
         <v>80</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="AK94" t="s" s="2">
-        <v>80</v>
+        <v>579</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>80</v>
+        <v>580</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>80</v>
+        <v>581</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>167</v>
+        <v>582</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>80</v>
+        <v>583</v>
       </c>
       <c r="AP94" t="s" s="2">
         <v>80</v>
@@ -14135,14 +13744,14 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>567</v>
+        <v>584</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>476</v>
+        <v>584</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
-        <v>134</v>
+        <v>80</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
@@ -14161,18 +13770,18 @@
         <v>80</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>135</v>
+        <v>585</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>136</v>
+        <v>586</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N95" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O95" s="2"/>
+        <v>587</v>
+      </c>
+      <c r="N95" s="2"/>
+      <c r="O95" t="s" s="2">
+        <v>588</v>
+      </c>
       <c r="P95" t="s" s="2">
         <v>80</v>
       </c>
@@ -14208,19 +13817,19 @@
         <v>80</v>
       </c>
       <c r="AB95" t="s" s="2">
-        <v>171</v>
+        <v>80</v>
       </c>
       <c r="AC95" t="s" s="2">
-        <v>172</v>
+        <v>80</v>
       </c>
       <c r="AD95" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE95" t="s" s="2">
-        <v>153</v>
+        <v>80</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>173</v>
+        <v>584</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>78</v>
@@ -14232,7 +13841,7 @@
         <v>80</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>80</v>
@@ -14244,10 +13853,10 @@
         <v>80</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>167</v>
+        <v>589</v>
       </c>
       <c r="AO95" t="s" s="2">
-        <v>80</v>
+        <v>590</v>
       </c>
       <c r="AP95" t="s" s="2">
         <v>80</v>
@@ -14255,10 +13864,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>568</v>
+        <v>591</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>477</v>
+        <v>591</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14269,32 +13878,28 @@
         <v>78</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H96" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="I96" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="J96" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>109</v>
+        <v>592</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>478</v>
+        <v>593</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="O96" t="s" s="2">
-        <v>481</v>
-      </c>
+        <v>594</v>
+      </c>
+      <c r="N96" s="2"/>
+      <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
         <v>80</v>
       </c>
@@ -14303,10 +13908,10 @@
         <v>80</v>
       </c>
       <c r="S96" t="s" s="2">
-        <v>450</v>
+        <v>80</v>
       </c>
       <c r="T96" t="s" s="2">
-        <v>450</v>
+        <v>80</v>
       </c>
       <c r="U96" t="s" s="2">
         <v>80</v>
@@ -14318,13 +13923,13 @@
         <v>80</v>
       </c>
       <c r="X96" t="s" s="2">
-        <v>180</v>
+        <v>80</v>
       </c>
       <c r="Y96" t="s" s="2">
-        <v>482</v>
+        <v>80</v>
       </c>
       <c r="Z96" t="s" s="2">
-        <v>483</v>
+        <v>80</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>80</v>
@@ -14342,13 +13947,13 @@
         <v>80</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>484</v>
+        <v>591</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH96" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI96" t="s" s="2">
         <v>80</v>
@@ -14357,19 +13962,19 @@
         <v>101</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>569</v>
+        <v>80</v>
       </c>
       <c r="AL96" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>485</v>
+        <v>595</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>358</v>
+        <v>596</v>
       </c>
       <c r="AO96" t="s" s="2">
-        <v>486</v>
+        <v>597</v>
       </c>
       <c r="AP96" t="s" s="2">
         <v>80</v>
@@ -14377,10 +13982,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>570</v>
+        <v>598</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>487</v>
+        <v>598</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14400,20 +14005,18 @@
         <v>80</v>
       </c>
       <c r="J97" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>109</v>
+        <v>163</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>488</v>
+        <v>164</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>490</v>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="N97" s="2"/>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
         <v>80</v>
@@ -14426,7 +14029,7 @@
         <v>80</v>
       </c>
       <c r="T97" t="s" s="2">
-        <v>491</v>
+        <v>80</v>
       </c>
       <c r="U97" t="s" s="2">
         <v>80</v>
@@ -14438,13 +14041,13 @@
         <v>80</v>
       </c>
       <c r="X97" t="s" s="2">
-        <v>180</v>
+        <v>80</v>
       </c>
       <c r="Y97" t="s" s="2">
-        <v>492</v>
+        <v>80</v>
       </c>
       <c r="Z97" t="s" s="2">
-        <v>493</v>
+        <v>80</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>80</v>
@@ -14462,7 +14065,7 @@
         <v>80</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>494</v>
+        <v>166</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>78</v>
@@ -14474,7 +14077,7 @@
         <v>80</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>80</v>
@@ -14483,10 +14086,10 @@
         <v>80</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>495</v>
+        <v>80</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>358</v>
+        <v>167</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>80</v>
@@ -14497,21 +14100,21 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>571</v>
+        <v>599</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>496</v>
+        <v>599</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
-        <v>80</v>
+        <v>134</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G98" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H98" t="s" s="2">
         <v>80</v>
@@ -14520,23 +14123,21 @@
         <v>80</v>
       </c>
       <c r="J98" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>163</v>
+        <v>135</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>497</v>
+        <v>136</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>498</v>
+        <v>170</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>499</v>
-      </c>
-      <c r="O98" t="s" s="2">
-        <v>364</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
         <v>80</v>
       </c>
@@ -14548,7 +14149,7 @@
         <v>80</v>
       </c>
       <c r="T98" t="s" s="2">
-        <v>500</v>
+        <v>80</v>
       </c>
       <c r="U98" t="s" s="2">
         <v>80</v>
@@ -14584,19 +14185,19 @@
         <v>80</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>501</v>
+        <v>173</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH98" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI98" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK98" t="s" s="2">
         <v>80</v>
@@ -14605,10 +14206,10 @@
         <v>80</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>502</v>
+        <v>80</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>369</v>
+        <v>167</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>80</v>
@@ -14619,42 +14220,46 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>572</v>
+        <v>600</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>503</v>
+        <v>600</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>80</v>
+        <v>601</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G99" t="s" s="2">
-        <v>504</v>
+        <v>79</v>
       </c>
       <c r="H99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I99" t="s" s="2">
         <v>90</v>
-      </c>
-      <c r="I99" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="J99" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>163</v>
+        <v>135</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>505</v>
+        <v>602</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>506</v>
-      </c>
-      <c r="N99" s="2"/>
-      <c r="O99" s="2"/>
+        <v>603</v>
+      </c>
+      <c r="N99" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="O99" t="s" s="2">
+        <v>144</v>
+      </c>
       <c r="P99" t="s" s="2">
         <v>80</v>
       </c>
@@ -14666,7 +14271,7 @@
         <v>80</v>
       </c>
       <c r="T99" t="s" s="2">
-        <v>507</v>
+        <v>80</v>
       </c>
       <c r="U99" t="s" s="2">
         <v>80</v>
@@ -14702,7 +14307,7 @@
         <v>80</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>508</v>
+        <v>604</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>78</v>
@@ -14714,22 +14319,22 @@
         <v>80</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK99" t="s" s="2">
-        <v>573</v>
+        <v>80</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>574</v>
+        <v>80</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>509</v>
+        <v>80</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>510</v>
+        <v>132</v>
       </c>
       <c r="AO99" t="s" s="2">
-        <v>511</v>
+        <v>80</v>
       </c>
       <c r="AP99" t="s" s="2">
         <v>80</v>
@@ -14737,42 +14342,44 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>575</v>
+        <v>605</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>512</v>
+        <v>605</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
-        <v>513</v>
+        <v>80</v>
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G100" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H100" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="I100" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J100" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>163</v>
+        <v>147</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>514</v>
+        <v>606</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>515</v>
+        <v>607</v>
       </c>
       <c r="N100" s="2"/>
-      <c r="O100" s="2"/>
+      <c r="O100" t="s" s="2">
+        <v>608</v>
+      </c>
       <c r="P100" t="s" s="2">
         <v>80</v>
       </c>
@@ -14784,7 +14391,7 @@
         <v>80</v>
       </c>
       <c r="T100" t="s" s="2">
-        <v>516</v>
+        <v>80</v>
       </c>
       <c r="U100" t="s" s="2">
         <v>80</v>
@@ -14820,13 +14427,13 @@
         <v>80</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>517</v>
+        <v>605</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH100" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI100" t="s" s="2">
         <v>80</v>
@@ -14835,19 +14442,19 @@
         <v>101</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>576</v>
+        <v>80</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>577</v>
+        <v>80</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>518</v>
+        <v>80</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>519</v>
+        <v>609</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>520</v>
+        <v>80</v>
       </c>
       <c r="AP100" t="s" s="2">
         <v>80</v>
@@ -14855,18 +14462,18 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>578</v>
+        <v>610</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>521</v>
+        <v>610</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>522</v>
+        <v>80</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G101" t="s" s="2">
         <v>89</v>
@@ -14878,20 +14485,18 @@
         <v>80</v>
       </c>
       <c r="J101" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>163</v>
+        <v>187</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>523</v>
+        <v>611</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>524</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>525</v>
-      </c>
+        <v>612</v>
+      </c>
+      <c r="N101" s="2"/>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
         <v>80</v>
@@ -14904,7 +14509,7 @@
         <v>80</v>
       </c>
       <c r="T101" t="s" s="2">
-        <v>526</v>
+        <v>80</v>
       </c>
       <c r="U101" t="s" s="2">
         <v>80</v>
@@ -14916,13 +14521,13 @@
         <v>80</v>
       </c>
       <c r="X101" t="s" s="2">
-        <v>80</v>
+        <v>613</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>80</v>
+        <v>614</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>80</v>
+        <v>615</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>80</v>
@@ -14940,10 +14545,10 @@
         <v>80</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>527</v>
+        <v>610</v>
       </c>
       <c r="AG101" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AH101" t="s" s="2">
         <v>89</v>
@@ -14961,13 +14566,13 @@
         <v>80</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>528</v>
+        <v>80</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>529</v>
+        <v>596</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>80</v>
+        <v>616</v>
       </c>
       <c r="AP101" t="s" s="2">
         <v>80</v>
@@ -14975,14 +14580,14 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>579</v>
+        <v>617</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>530</v>
+        <v>617</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
-        <v>531</v>
+        <v>80</v>
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
@@ -14992,22 +14597,22 @@
         <v>89</v>
       </c>
       <c r="H102" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="I102" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J102" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K102" t="s" s="2">
         <v>163</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>532</v>
+        <v>164</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>533</v>
+        <v>165</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -15034,13 +14639,13 @@
         <v>80</v>
       </c>
       <c r="X102" t="s" s="2">
-        <v>193</v>
+        <v>80</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>534</v>
+        <v>80</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>535</v>
+        <v>80</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>80</v>
@@ -15058,7 +14663,7 @@
         <v>80</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>536</v>
+        <v>166</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>78</v>
@@ -15070,22 +14675,22 @@
         <v>80</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>580</v>
+        <v>80</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>581</v>
+        <v>80</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>537</v>
+        <v>80</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>538</v>
+        <v>167</v>
       </c>
       <c r="AO102" t="s" s="2">
-        <v>539</v>
+        <v>80</v>
       </c>
       <c r="AP102" t="s" s="2">
         <v>80</v>
@@ -15093,41 +14698,43 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>582</v>
+        <v>618</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>540</v>
+        <v>618</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
-        <v>541</v>
+        <v>134</v>
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G103" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H103" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="I103" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J103" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>163</v>
+        <v>135</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>542</v>
+        <v>136</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="N103" s="2"/>
+        <v>170</v>
+      </c>
+      <c r="N103" t="s" s="2">
+        <v>138</v>
+      </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
         <v>80</v>
@@ -15140,7 +14747,7 @@
         <v>80</v>
       </c>
       <c r="T103" t="s" s="2">
-        <v>544</v>
+        <v>80</v>
       </c>
       <c r="U103" t="s" s="2">
         <v>80</v>
@@ -15164,46 +14771,46 @@
         <v>80</v>
       </c>
       <c r="AB103" t="s" s="2">
-        <v>80</v>
+        <v>171</v>
       </c>
       <c r="AC103" t="s" s="2">
-        <v>80</v>
+        <v>172</v>
       </c>
       <c r="AD103" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE103" t="s" s="2">
-        <v>80</v>
+        <v>153</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>545</v>
+        <v>173</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH103" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI103" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK103" t="s" s="2">
-        <v>583</v>
+        <v>80</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>584</v>
+        <v>80</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>546</v>
+        <v>80</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>547</v>
+        <v>167</v>
       </c>
       <c r="AO103" t="s" s="2">
-        <v>548</v>
+        <v>80</v>
       </c>
       <c r="AP103" t="s" s="2">
         <v>80</v>
@@ -15211,10 +14818,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>585</v>
+        <v>619</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>549</v>
+        <v>619</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15225,10 +14832,10 @@
         <v>78</v>
       </c>
       <c r="G104" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H104" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="I104" t="s" s="2">
         <v>80</v>
@@ -15237,18 +14844,20 @@
         <v>90</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>163</v>
+        <v>620</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>550</v>
+        <v>621</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>551</v>
+        <v>622</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="O104" s="2"/>
+        <v>623</v>
+      </c>
+      <c r="O104" t="s" s="2">
+        <v>624</v>
+      </c>
       <c r="P104" t="s" s="2">
         <v>80</v>
       </c>
@@ -15296,13 +14905,13 @@
         <v>80</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>553</v>
+        <v>625</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH104" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI104" t="s" s="2">
         <v>80</v>
@@ -15311,19 +14920,19 @@
         <v>101</v>
       </c>
       <c r="AK104" t="s" s="2">
-        <v>586</v>
+        <v>80</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>581</v>
+        <v>80</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>554</v>
+        <v>626</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>555</v>
+        <v>627</v>
       </c>
       <c r="AO104" t="s" s="2">
-        <v>556</v>
+        <v>80</v>
       </c>
       <c r="AP104" t="s" s="2">
         <v>80</v>
@@ -15331,10 +14940,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>587</v>
+        <v>628</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>588</v>
+        <v>628</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15348,25 +14957,29 @@
         <v>89</v>
       </c>
       <c r="H105" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="I105" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J105" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K105" t="s" s="2">
         <v>163</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>589</v>
+        <v>629</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>590</v>
-      </c>
-      <c r="N105" s="2"/>
-      <c r="O105" s="2"/>
+        <v>630</v>
+      </c>
+      <c r="N105" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="O105" t="s" s="2">
+        <v>632</v>
+      </c>
       <c r="P105" t="s" s="2">
         <v>80</v>
       </c>
@@ -15414,7 +15027,7 @@
         <v>80</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>166</v>
+        <v>633</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>78</v>
@@ -15426,19 +15039,19 @@
         <v>80</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="AK105" t="s" s="2">
-        <v>80</v>
+        <v>634</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>80</v>
+        <v>635</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>80</v>
+        <v>636</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>80</v>
+        <v>637</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>80</v>
@@ -15449,10 +15062,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>591</v>
+        <v>638</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>592</v>
+        <v>638</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15463,7 +15076,7 @@
         <v>78</v>
       </c>
       <c r="G106" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H106" t="s" s="2">
         <v>80</v>
@@ -15475,16 +15088,18 @@
         <v>80</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>135</v>
+        <v>226</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>593</v>
+        <v>639</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>594</v>
+        <v>640</v>
       </c>
       <c r="N106" s="2"/>
-      <c r="O106" s="2"/>
+      <c r="O106" t="s" s="2">
+        <v>641</v>
+      </c>
       <c r="P106" t="s" s="2">
         <v>80</v>
       </c>
@@ -15520,29 +15135,31 @@
         <v>80</v>
       </c>
       <c r="AB106" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="AC106" s="2"/>
+        <v>80</v>
+      </c>
+      <c r="AC106" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="AD106" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE106" t="s" s="2">
-        <v>153</v>
+        <v>80</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>173</v>
+        <v>638</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH106" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI106" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK106" t="s" s="2">
         <v>80</v>
@@ -15554,10 +15171,10 @@
         <v>80</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>80</v>
+        <v>642</v>
       </c>
       <c r="AO106" t="s" s="2">
-        <v>80</v>
+        <v>643</v>
       </c>
       <c r="AP106" t="s" s="2">
         <v>80</v>
@@ -15565,14 +15182,12 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>595</v>
+        <v>644</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>592</v>
-      </c>
-      <c r="C107" t="s" s="2">
-        <v>596</v>
-      </c>
+        <v>644</v>
+      </c>
+      <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
         <v>80</v>
       </c>
@@ -15593,13 +15208,13 @@
         <v>80</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>597</v>
+        <v>259</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>598</v>
+        <v>645</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>599</v>
+        <v>646</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -15650,19 +15265,19 @@
         <v>80</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>173</v>
+        <v>644</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH107" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI107" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK107" t="s" s="2">
         <v>80</v>
@@ -15674,7 +15289,7 @@
         <v>80</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>600</v>
+        <v>647</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>80</v>
@@ -15685,10 +15300,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>601</v>
+        <v>648</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>602</v>
+        <v>648</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15699,7 +15314,7 @@
         <v>78</v>
       </c>
       <c r="G108" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H108" t="s" s="2">
         <v>80</v>
@@ -15711,16 +15326,20 @@
         <v>80</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>91</v>
+        <v>187</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>164</v>
+        <v>649</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="N108" s="2"/>
-      <c r="O108" s="2"/>
+        <v>650</v>
+      </c>
+      <c r="N108" t="s" s="2">
+        <v>651</v>
+      </c>
+      <c r="O108" t="s" s="2">
+        <v>652</v>
+      </c>
       <c r="P108" t="s" s="2">
         <v>80</v>
       </c>
@@ -15744,13 +15363,13 @@
         <v>80</v>
       </c>
       <c r="X108" t="s" s="2">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="Y108" t="s" s="2">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="Z108" t="s" s="2">
-        <v>80</v>
+        <v>115</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>80</v>
@@ -15768,19 +15387,19 @@
         <v>80</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>166</v>
+        <v>648</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH108" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI108" t="s" s="2">
-        <v>603</v>
+        <v>80</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="AK108" t="s" s="2">
         <v>80</v>
@@ -15789,6702 +15408,20 @@
         <v>80</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>80</v>
+        <v>653</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>167</v>
+        <v>654</v>
       </c>
       <c r="AO108" t="s" s="2">
-        <v>80</v>
+        <v>655</v>
       </c>
       <c r="AP108" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="109" hidden="true">
-      <c r="A109" t="s" s="2">
-        <v>604</v>
-      </c>
-      <c r="B109" t="s" s="2">
-        <v>605</v>
-      </c>
-      <c r="C109" s="2"/>
-      <c r="D109" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E109" s="2"/>
-      <c r="F109" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G109" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H109" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I109" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J109" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K109" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="L109" t="s" s="2">
-        <v>593</v>
-      </c>
-      <c r="M109" t="s" s="2">
-        <v>594</v>
-      </c>
-      <c r="N109" s="2"/>
-      <c r="O109" s="2"/>
-      <c r="P109" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q109" s="2"/>
-      <c r="R109" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S109" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T109" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U109" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V109" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W109" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X109" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y109" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z109" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA109" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB109" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="AC109" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="AD109" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE109" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="AF109" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="AG109" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH109" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI109" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ109" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="AK109" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL109" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM109" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN109" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO109" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP109" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="110" hidden="true">
-      <c r="A110" t="s" s="2">
-        <v>606</v>
-      </c>
-      <c r="B110" t="s" s="2">
-        <v>607</v>
-      </c>
-      <c r="C110" s="2"/>
-      <c r="D110" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E110" s="2"/>
-      <c r="F110" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="G110" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H110" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I110" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J110" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K110" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="L110" t="s" s="2">
-        <v>608</v>
-      </c>
-      <c r="M110" t="s" s="2">
-        <v>609</v>
-      </c>
-      <c r="N110" t="s" s="2">
-        <v>610</v>
-      </c>
-      <c r="O110" s="2"/>
-      <c r="P110" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q110" s="2"/>
-      <c r="R110" t="s" s="2">
-        <v>611</v>
-      </c>
-      <c r="S110" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T110" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U110" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V110" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W110" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X110" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y110" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z110" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA110" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB110" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC110" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD110" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE110" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF110" t="s" s="2">
-        <v>612</v>
-      </c>
-      <c r="AG110" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AH110" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI110" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ110" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AK110" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL110" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM110" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN110" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="AO110" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP110" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="111" hidden="true">
-      <c r="A111" t="s" s="2">
-        <v>613</v>
-      </c>
-      <c r="B111" t="s" s="2">
-        <v>614</v>
-      </c>
-      <c r="C111" s="2"/>
-      <c r="D111" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E111" s="2"/>
-      <c r="F111" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="G111" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H111" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="I111" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J111" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K111" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="L111" t="s" s="2">
-        <v>615</v>
-      </c>
-      <c r="M111" t="s" s="2">
-        <v>616</v>
-      </c>
-      <c r="N111" s="2"/>
-      <c r="O111" s="2"/>
-      <c r="P111" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q111" s="2"/>
-      <c r="R111" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S111" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T111" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U111" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V111" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W111" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X111" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="Y111" s="2"/>
-      <c r="Z111" t="s" s="2">
-        <v>617</v>
-      </c>
-      <c r="AA111" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB111" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC111" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD111" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE111" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF111" t="s" s="2">
-        <v>618</v>
-      </c>
-      <c r="AG111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH111" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI111" t="s" s="2">
-        <v>619</v>
-      </c>
-      <c r="AJ111" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK111" t="s" s="2">
-        <v>620</v>
-      </c>
-      <c r="AL111" t="s" s="2">
-        <v>581</v>
-      </c>
-      <c r="AM111" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN111" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="AO111" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP111" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="112" hidden="true">
-      <c r="A112" t="s" s="2">
-        <v>621</v>
-      </c>
-      <c r="B112" t="s" s="2">
-        <v>592</v>
-      </c>
-      <c r="C112" t="s" s="2">
-        <v>622</v>
-      </c>
-      <c r="D112" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E112" s="2"/>
-      <c r="F112" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G112" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H112" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I112" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J112" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K112" t="s" s="2">
-        <v>623</v>
-      </c>
-      <c r="L112" t="s" s="2">
-        <v>624</v>
-      </c>
-      <c r="M112" t="s" s="2">
-        <v>625</v>
-      </c>
-      <c r="N112" t="s" s="2">
-        <v>626</v>
-      </c>
-      <c r="O112" s="2"/>
-      <c r="P112" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q112" s="2"/>
-      <c r="R112" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S112" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T112" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U112" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V112" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W112" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X112" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y112" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z112" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA112" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB112" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC112" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD112" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE112" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF112" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="AG112" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH112" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI112" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ112" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="AK112" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL112" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM112" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="AN112" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="AO112" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP112" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="113" hidden="true">
-      <c r="A113" t="s" s="2">
-        <v>627</v>
-      </c>
-      <c r="B113" t="s" s="2">
-        <v>602</v>
-      </c>
-      <c r="C113" s="2"/>
-      <c r="D113" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E113" s="2"/>
-      <c r="F113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G113" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H113" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I113" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J113" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K113" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="L113" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="M113" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="N113" s="2"/>
-      <c r="O113" s="2"/>
-      <c r="P113" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q113" s="2"/>
-      <c r="R113" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S113" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T113" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U113" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V113" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W113" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X113" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y113" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z113" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA113" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB113" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC113" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD113" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE113" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF113" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="AG113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH113" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI113" t="s" s="2">
-        <v>603</v>
-      </c>
-      <c r="AJ113" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AK113" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL113" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM113" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN113" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="AO113" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP113" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="114" hidden="true">
-      <c r="A114" t="s" s="2">
-        <v>628</v>
-      </c>
-      <c r="B114" t="s" s="2">
-        <v>605</v>
-      </c>
-      <c r="C114" s="2"/>
-      <c r="D114" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E114" s="2"/>
-      <c r="F114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H114" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I114" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J114" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K114" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="L114" t="s" s="2">
-        <v>593</v>
-      </c>
-      <c r="M114" t="s" s="2">
-        <v>594</v>
-      </c>
-      <c r="N114" s="2"/>
-      <c r="O114" s="2"/>
-      <c r="P114" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q114" s="2"/>
-      <c r="R114" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S114" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T114" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U114" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V114" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W114" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X114" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y114" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z114" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA114" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB114" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="AC114" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="AD114" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE114" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="AF114" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="AG114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH114" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI114" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ114" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="AK114" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL114" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM114" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN114" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO114" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP114" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="115" hidden="true">
-      <c r="A115" t="s" s="2">
-        <v>629</v>
-      </c>
-      <c r="B115" t="s" s="2">
-        <v>607</v>
-      </c>
-      <c r="C115" s="2"/>
-      <c r="D115" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E115" s="2"/>
-      <c r="F115" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="G115" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H115" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I115" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J115" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K115" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="L115" t="s" s="2">
-        <v>608</v>
-      </c>
-      <c r="M115" t="s" s="2">
-        <v>609</v>
-      </c>
-      <c r="N115" t="s" s="2">
-        <v>610</v>
-      </c>
-      <c r="O115" s="2"/>
-      <c r="P115" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q115" s="2"/>
-      <c r="R115" t="s" s="2">
-        <v>630</v>
-      </c>
-      <c r="S115" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T115" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U115" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V115" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W115" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X115" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y115" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z115" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA115" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB115" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC115" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD115" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE115" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF115" t="s" s="2">
-        <v>612</v>
-      </c>
-      <c r="AG115" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AH115" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI115" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ115" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AK115" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL115" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM115" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN115" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="AO115" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP115" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="116" hidden="true">
-      <c r="A116" t="s" s="2">
-        <v>631</v>
-      </c>
-      <c r="B116" t="s" s="2">
-        <v>614</v>
-      </c>
-      <c r="C116" s="2"/>
-      <c r="D116" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E116" s="2"/>
-      <c r="F116" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="G116" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H116" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I116" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J116" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K116" t="s" s="2">
-        <v>632</v>
-      </c>
-      <c r="L116" t="s" s="2">
-        <v>615</v>
-      </c>
-      <c r="M116" t="s" s="2">
-        <v>616</v>
-      </c>
-      <c r="N116" s="2"/>
-      <c r="O116" s="2"/>
-      <c r="P116" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q116" s="2"/>
-      <c r="R116" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S116" t="s" s="2">
-        <v>633</v>
-      </c>
-      <c r="T116" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U116" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V116" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W116" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X116" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y116" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z116" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA116" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB116" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC116" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD116" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE116" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF116" t="s" s="2">
-        <v>618</v>
-      </c>
-      <c r="AG116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH116" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI116" t="s" s="2">
-        <v>619</v>
-      </c>
-      <c r="AJ116" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK116" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL116" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM116" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN116" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="AO116" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP116" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="117" hidden="true">
-      <c r="A117" t="s" s="2">
-        <v>634</v>
-      </c>
-      <c r="B117" t="s" s="2">
-        <v>635</v>
-      </c>
-      <c r="C117" s="2"/>
-      <c r="D117" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E117" s="2"/>
-      <c r="F117" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G117" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H117" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I117" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J117" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K117" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="L117" t="s" s="2">
-        <v>636</v>
-      </c>
-      <c r="M117" t="s" s="2">
-        <v>637</v>
-      </c>
-      <c r="N117" s="2"/>
-      <c r="O117" s="2"/>
-      <c r="P117" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q117" s="2"/>
-      <c r="R117" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S117" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T117" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U117" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V117" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W117" t="s" s="2">
-        <v>638</v>
-      </c>
-      <c r="X117" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y117" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z117" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA117" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB117" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC117" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD117" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE117" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF117" t="s" s="2">
-        <v>639</v>
-      </c>
-      <c r="AG117" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH117" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI117" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ117" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AK117" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL117" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM117" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN117" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO117" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP117" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="118" hidden="true">
-      <c r="A118" t="s" s="2">
-        <v>640</v>
-      </c>
-      <c r="B118" t="s" s="2">
-        <v>557</v>
-      </c>
-      <c r="C118" s="2"/>
-      <c r="D118" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E118" s="2"/>
-      <c r="F118" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G118" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H118" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I118" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J118" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K118" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="L118" t="s" s="2">
-        <v>558</v>
-      </c>
-      <c r="M118" t="s" s="2">
-        <v>559</v>
-      </c>
-      <c r="N118" s="2"/>
-      <c r="O118" t="s" s="2">
-        <v>560</v>
-      </c>
-      <c r="P118" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q118" s="2"/>
-      <c r="R118" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S118" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T118" t="s" s="2">
-        <v>561</v>
-      </c>
-      <c r="U118" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V118" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W118" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X118" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y118" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z118" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA118" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB118" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC118" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD118" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE118" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF118" t="s" s="2">
-        <v>562</v>
-      </c>
-      <c r="AG118" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH118" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI118" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ118" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK118" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL118" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM118" t="s" s="2">
-        <v>563</v>
-      </c>
-      <c r="AN118" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="AO118" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="AP118" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="119" hidden="true">
-      <c r="A119" t="s" s="2">
-        <v>641</v>
-      </c>
-      <c r="B119" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="C119" t="s" s="2">
-        <v>642</v>
-      </c>
-      <c r="D119" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E119" s="2"/>
-      <c r="F119" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G119" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H119" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="I119" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J119" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K119" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="L119" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="M119" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="N119" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="O119" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="P119" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q119" s="2"/>
-      <c r="R119" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S119" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T119" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U119" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V119" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W119" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X119" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y119" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z119" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA119" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB119" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC119" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD119" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE119" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF119" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="AG119" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH119" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI119" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ119" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK119" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL119" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM119" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="AN119" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="AO119" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="AP119" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="120" hidden="true">
-      <c r="A120" t="s" s="2">
-        <v>643</v>
-      </c>
-      <c r="B120" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="C120" s="2"/>
-      <c r="D120" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E120" s="2"/>
-      <c r="F120" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G120" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H120" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I120" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J120" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K120" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="L120" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="M120" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="N120" s="2"/>
-      <c r="O120" s="2"/>
-      <c r="P120" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q120" s="2"/>
-      <c r="R120" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S120" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T120" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U120" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V120" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W120" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X120" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y120" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z120" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA120" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB120" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC120" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD120" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE120" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF120" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="AG120" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH120" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI120" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ120" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AK120" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL120" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM120" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN120" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="AO120" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP120" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="121" hidden="true">
-      <c r="A121" t="s" s="2">
-        <v>644</v>
-      </c>
-      <c r="B121" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="C121" s="2"/>
-      <c r="D121" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="E121" s="2"/>
-      <c r="F121" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G121" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H121" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I121" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J121" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K121" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="L121" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="M121" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N121" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O121" s="2"/>
-      <c r="P121" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q121" s="2"/>
-      <c r="R121" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S121" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T121" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U121" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V121" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W121" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X121" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y121" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z121" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA121" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB121" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="AC121" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="AD121" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE121" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="AF121" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="AG121" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH121" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI121" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ121" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="AK121" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL121" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM121" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN121" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="AO121" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP121" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="122" hidden="true">
-      <c r="A122" t="s" s="2">
-        <v>645</v>
-      </c>
-      <c r="B122" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="C122" s="2"/>
-      <c r="D122" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E122" s="2"/>
-      <c r="F122" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G122" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H122" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="I122" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="J122" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K122" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="L122" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="M122" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="N122" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="O122" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="P122" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q122" s="2"/>
-      <c r="R122" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S122" t="s" s="2">
-        <v>646</v>
-      </c>
-      <c r="T122" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="U122" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V122" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W122" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X122" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="Y122" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="Z122" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="AA122" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB122" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC122" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD122" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE122" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF122" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="AG122" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH122" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI122" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ122" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK122" t="s" s="2">
-        <v>647</v>
-      </c>
-      <c r="AL122" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM122" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="AN122" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="AO122" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="AP122" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="123" hidden="true">
-      <c r="A123" t="s" s="2">
-        <v>648</v>
-      </c>
-      <c r="B123" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="C123" s="2"/>
-      <c r="D123" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E123" s="2"/>
-      <c r="F123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G123" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H123" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I123" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J123" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K123" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="L123" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="M123" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="N123" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="O123" s="2"/>
-      <c r="P123" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q123" s="2"/>
-      <c r="R123" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S123" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T123" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="U123" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V123" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W123" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X123" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="Y123" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="Z123" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="AA123" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB123" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC123" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD123" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE123" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF123" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="AG123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH123" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI123" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ123" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK123" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL123" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM123" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="AN123" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="AO123" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP123" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="124" hidden="true">
-      <c r="A124" t="s" s="2">
-        <v>649</v>
-      </c>
-      <c r="B124" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="C124" s="2"/>
-      <c r="D124" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E124" s="2"/>
-      <c r="F124" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G124" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H124" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I124" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J124" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K124" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="L124" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="M124" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="N124" t="s" s="2">
-        <v>499</v>
-      </c>
-      <c r="O124" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="P124" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q124" s="2"/>
-      <c r="R124" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S124" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T124" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="U124" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V124" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W124" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X124" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y124" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z124" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA124" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB124" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC124" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD124" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE124" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF124" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="AG124" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH124" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI124" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ124" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK124" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL124" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM124" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="AN124" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="AO124" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP124" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="125" hidden="true">
-      <c r="A125" t="s" s="2">
-        <v>650</v>
-      </c>
-      <c r="B125" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="C125" s="2"/>
-      <c r="D125" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E125" s="2"/>
-      <c r="F125" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G125" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="H125" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="I125" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J125" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K125" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="L125" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="M125" t="s" s="2">
-        <v>506</v>
-      </c>
-      <c r="N125" s="2"/>
-      <c r="O125" s="2"/>
-      <c r="P125" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q125" s="2"/>
-      <c r="R125" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S125" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T125" t="s" s="2">
-        <v>507</v>
-      </c>
-      <c r="U125" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V125" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W125" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X125" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y125" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z125" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA125" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB125" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC125" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD125" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE125" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF125" t="s" s="2">
-        <v>508</v>
-      </c>
-      <c r="AG125" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH125" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI125" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ125" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK125" t="s" s="2">
-        <v>651</v>
-      </c>
-      <c r="AL125" t="s" s="2">
-        <v>652</v>
-      </c>
-      <c r="AM125" t="s" s="2">
-        <v>509</v>
-      </c>
-      <c r="AN125" t="s" s="2">
-        <v>510</v>
-      </c>
-      <c r="AO125" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="AP125" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="126" hidden="true">
-      <c r="A126" t="s" s="2">
-        <v>653</v>
-      </c>
-      <c r="B126" t="s" s="2">
-        <v>512</v>
-      </c>
-      <c r="C126" s="2"/>
-      <c r="D126" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="E126" s="2"/>
-      <c r="F126" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G126" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H126" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="I126" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J126" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K126" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="L126" t="s" s="2">
-        <v>514</v>
-      </c>
-      <c r="M126" t="s" s="2">
-        <v>515</v>
-      </c>
-      <c r="N126" s="2"/>
-      <c r="O126" s="2"/>
-      <c r="P126" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q126" s="2"/>
-      <c r="R126" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S126" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T126" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="U126" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V126" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W126" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X126" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y126" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z126" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA126" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB126" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC126" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD126" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE126" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF126" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="AG126" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH126" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI126" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ126" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK126" t="s" s="2">
-        <v>654</v>
-      </c>
-      <c r="AL126" t="s" s="2">
-        <v>655</v>
-      </c>
-      <c r="AM126" t="s" s="2">
-        <v>518</v>
-      </c>
-      <c r="AN126" t="s" s="2">
-        <v>519</v>
-      </c>
-      <c r="AO126" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="AP126" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="127" hidden="true">
-      <c r="A127" t="s" s="2">
-        <v>656</v>
-      </c>
-      <c r="B127" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="C127" s="2"/>
-      <c r="D127" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="E127" s="2"/>
-      <c r="F127" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G127" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J127" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K127" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="L127" t="s" s="2">
-        <v>523</v>
-      </c>
-      <c r="M127" t="s" s="2">
-        <v>524</v>
-      </c>
-      <c r="N127" t="s" s="2">
-        <v>525</v>
-      </c>
-      <c r="O127" s="2"/>
-      <c r="P127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q127" s="2"/>
-      <c r="R127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T127" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="U127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF127" t="s" s="2">
-        <v>527</v>
-      </c>
-      <c r="AG127" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH127" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ127" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM127" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="AN127" t="s" s="2">
-        <v>529</v>
-      </c>
-      <c r="AO127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP127" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="128" hidden="true">
-      <c r="A128" t="s" s="2">
-        <v>657</v>
-      </c>
-      <c r="B128" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="C128" s="2"/>
-      <c r="D128" t="s" s="2">
-        <v>531</v>
-      </c>
-      <c r="E128" s="2"/>
-      <c r="F128" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G128" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H128" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="I128" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J128" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K128" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="L128" t="s" s="2">
-        <v>532</v>
-      </c>
-      <c r="M128" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="N128" s="2"/>
-      <c r="O128" s="2"/>
-      <c r="P128" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q128" s="2"/>
-      <c r="R128" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S128" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T128" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U128" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V128" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W128" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X128" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="Y128" t="s" s="2">
-        <v>534</v>
-      </c>
-      <c r="Z128" t="s" s="2">
-        <v>535</v>
-      </c>
-      <c r="AA128" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB128" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC128" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD128" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE128" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF128" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="AG128" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH128" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI128" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ128" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK128" t="s" s="2">
-        <v>658</v>
-      </c>
-      <c r="AL128" t="s" s="2">
-        <v>659</v>
-      </c>
-      <c r="AM128" t="s" s="2">
-        <v>537</v>
-      </c>
-      <c r="AN128" t="s" s="2">
-        <v>538</v>
-      </c>
-      <c r="AO128" t="s" s="2">
-        <v>539</v>
-      </c>
-      <c r="AP128" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="129" hidden="true">
-      <c r="A129" t="s" s="2">
-        <v>660</v>
-      </c>
-      <c r="B129" t="s" s="2">
-        <v>540</v>
-      </c>
-      <c r="C129" s="2"/>
-      <c r="D129" t="s" s="2">
-        <v>541</v>
-      </c>
-      <c r="E129" s="2"/>
-      <c r="F129" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G129" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H129" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="I129" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J129" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K129" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="L129" t="s" s="2">
-        <v>542</v>
-      </c>
-      <c r="M129" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="N129" s="2"/>
-      <c r="O129" s="2"/>
-      <c r="P129" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q129" s="2"/>
-      <c r="R129" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S129" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T129" t="s" s="2">
-        <v>544</v>
-      </c>
-      <c r="U129" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V129" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W129" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X129" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y129" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z129" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA129" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB129" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC129" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD129" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE129" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF129" t="s" s="2">
-        <v>545</v>
-      </c>
-      <c r="AG129" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH129" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI129" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ129" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK129" t="s" s="2">
-        <v>661</v>
-      </c>
-      <c r="AL129" t="s" s="2">
-        <v>662</v>
-      </c>
-      <c r="AM129" t="s" s="2">
-        <v>546</v>
-      </c>
-      <c r="AN129" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="AO129" t="s" s="2">
-        <v>548</v>
-      </c>
-      <c r="AP129" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="130" hidden="true">
-      <c r="A130" t="s" s="2">
-        <v>663</v>
-      </c>
-      <c r="B130" t="s" s="2">
-        <v>549</v>
-      </c>
-      <c r="C130" s="2"/>
-      <c r="D130" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E130" s="2"/>
-      <c r="F130" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G130" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H130" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="I130" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J130" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K130" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="L130" t="s" s="2">
-        <v>550</v>
-      </c>
-      <c r="M130" t="s" s="2">
-        <v>551</v>
-      </c>
-      <c r="N130" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="O130" s="2"/>
-      <c r="P130" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q130" s="2"/>
-      <c r="R130" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S130" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T130" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U130" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V130" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W130" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X130" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y130" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z130" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA130" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB130" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC130" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD130" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE130" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF130" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="AG130" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH130" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI130" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ130" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK130" t="s" s="2">
-        <v>664</v>
-      </c>
-      <c r="AL130" t="s" s="2">
-        <v>659</v>
-      </c>
-      <c r="AM130" t="s" s="2">
-        <v>554</v>
-      </c>
-      <c r="AN130" t="s" s="2">
-        <v>555</v>
-      </c>
-      <c r="AO130" t="s" s="2">
-        <v>556</v>
-      </c>
-      <c r="AP130" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="131" hidden="true">
-      <c r="A131" t="s" s="2">
-        <v>665</v>
-      </c>
-      <c r="B131" t="s" s="2">
-        <v>588</v>
-      </c>
-      <c r="C131" s="2"/>
-      <c r="D131" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E131" s="2"/>
-      <c r="F131" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G131" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H131" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I131" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J131" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K131" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="L131" t="s" s="2">
-        <v>589</v>
-      </c>
-      <c r="M131" t="s" s="2">
-        <v>590</v>
-      </c>
-      <c r="N131" s="2"/>
-      <c r="O131" s="2"/>
-      <c r="P131" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q131" s="2"/>
-      <c r="R131" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S131" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T131" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U131" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V131" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W131" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X131" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y131" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z131" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA131" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB131" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC131" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD131" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE131" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF131" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="AG131" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH131" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI131" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ131" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AK131" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL131" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM131" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN131" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO131" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP131" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="132" hidden="true">
-      <c r="A132" t="s" s="2">
-        <v>666</v>
-      </c>
-      <c r="B132" t="s" s="2">
-        <v>592</v>
-      </c>
-      <c r="C132" s="2"/>
-      <c r="D132" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E132" s="2"/>
-      <c r="F132" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G132" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H132" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I132" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J132" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K132" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="L132" t="s" s="2">
-        <v>593</v>
-      </c>
-      <c r="M132" t="s" s="2">
-        <v>594</v>
-      </c>
-      <c r="N132" s="2"/>
-      <c r="O132" s="2"/>
-      <c r="P132" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q132" s="2"/>
-      <c r="R132" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S132" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T132" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U132" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V132" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W132" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X132" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y132" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z132" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA132" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB132" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="AC132" s="2"/>
-      <c r="AD132" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE132" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="AF132" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="AG132" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH132" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI132" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ132" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="AK132" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL132" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM132" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN132" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO132" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP132" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="133" hidden="true">
-      <c r="A133" t="s" s="2">
-        <v>667</v>
-      </c>
-      <c r="B133" t="s" s="2">
-        <v>592</v>
-      </c>
-      <c r="C133" t="s" s="2">
-        <v>596</v>
-      </c>
-      <c r="D133" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E133" s="2"/>
-      <c r="F133" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G133" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H133" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I133" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J133" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K133" t="s" s="2">
-        <v>597</v>
-      </c>
-      <c r="L133" t="s" s="2">
-        <v>598</v>
-      </c>
-      <c r="M133" t="s" s="2">
-        <v>599</v>
-      </c>
-      <c r="N133" s="2"/>
-      <c r="O133" s="2"/>
-      <c r="P133" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q133" s="2"/>
-      <c r="R133" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S133" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T133" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U133" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V133" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W133" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X133" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y133" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z133" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA133" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB133" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC133" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD133" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE133" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF133" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="AG133" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH133" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI133" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ133" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="AK133" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL133" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM133" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN133" t="s" s="2">
-        <v>600</v>
-      </c>
-      <c r="AO133" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP133" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="134" hidden="true">
-      <c r="A134" t="s" s="2">
-        <v>668</v>
-      </c>
-      <c r="B134" t="s" s="2">
-        <v>602</v>
-      </c>
-      <c r="C134" s="2"/>
-      <c r="D134" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E134" s="2"/>
-      <c r="F134" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G134" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H134" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I134" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J134" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K134" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="L134" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="M134" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="N134" s="2"/>
-      <c r="O134" s="2"/>
-      <c r="P134" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q134" s="2"/>
-      <c r="R134" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S134" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T134" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U134" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V134" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W134" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X134" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y134" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z134" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA134" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB134" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC134" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD134" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE134" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF134" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="AG134" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH134" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI134" t="s" s="2">
-        <v>603</v>
-      </c>
-      <c r="AJ134" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AK134" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL134" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM134" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN134" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="AO134" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP134" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="135" hidden="true">
-      <c r="A135" t="s" s="2">
-        <v>669</v>
-      </c>
-      <c r="B135" t="s" s="2">
-        <v>605</v>
-      </c>
-      <c r="C135" s="2"/>
-      <c r="D135" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E135" s="2"/>
-      <c r="F135" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G135" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H135" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I135" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J135" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K135" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="L135" t="s" s="2">
-        <v>593</v>
-      </c>
-      <c r="M135" t="s" s="2">
-        <v>594</v>
-      </c>
-      <c r="N135" s="2"/>
-      <c r="O135" s="2"/>
-      <c r="P135" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q135" s="2"/>
-      <c r="R135" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S135" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T135" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U135" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V135" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W135" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X135" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y135" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z135" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA135" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB135" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="AC135" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="AD135" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE135" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="AF135" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="AG135" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH135" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI135" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ135" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="AK135" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL135" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM135" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN135" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO135" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP135" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="136" hidden="true">
-      <c r="A136" t="s" s="2">
-        <v>670</v>
-      </c>
-      <c r="B136" t="s" s="2">
-        <v>607</v>
-      </c>
-      <c r="C136" s="2"/>
-      <c r="D136" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E136" s="2"/>
-      <c r="F136" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="G136" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H136" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I136" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J136" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K136" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="L136" t="s" s="2">
-        <v>608</v>
-      </c>
-      <c r="M136" t="s" s="2">
-        <v>609</v>
-      </c>
-      <c r="N136" t="s" s="2">
-        <v>610</v>
-      </c>
-      <c r="O136" s="2"/>
-      <c r="P136" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q136" s="2"/>
-      <c r="R136" t="s" s="2">
-        <v>611</v>
-      </c>
-      <c r="S136" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T136" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U136" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V136" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W136" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X136" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y136" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z136" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA136" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB136" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC136" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD136" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE136" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF136" t="s" s="2">
-        <v>612</v>
-      </c>
-      <c r="AG136" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AH136" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI136" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ136" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AK136" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL136" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM136" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN136" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="AO136" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP136" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="137" hidden="true">
-      <c r="A137" t="s" s="2">
-        <v>671</v>
-      </c>
-      <c r="B137" t="s" s="2">
-        <v>614</v>
-      </c>
-      <c r="C137" s="2"/>
-      <c r="D137" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E137" s="2"/>
-      <c r="F137" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="G137" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H137" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="I137" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J137" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K137" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="L137" t="s" s="2">
-        <v>615</v>
-      </c>
-      <c r="M137" t="s" s="2">
-        <v>616</v>
-      </c>
-      <c r="N137" s="2"/>
-      <c r="O137" s="2"/>
-      <c r="P137" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q137" s="2"/>
-      <c r="R137" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S137" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T137" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U137" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V137" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W137" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X137" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="Y137" s="2"/>
-      <c r="Z137" t="s" s="2">
-        <v>617</v>
-      </c>
-      <c r="AA137" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB137" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC137" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD137" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE137" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF137" t="s" s="2">
-        <v>618</v>
-      </c>
-      <c r="AG137" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH137" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI137" t="s" s="2">
-        <v>619</v>
-      </c>
-      <c r="AJ137" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK137" t="s" s="2">
-        <v>672</v>
-      </c>
-      <c r="AL137" t="s" s="2">
-        <v>659</v>
-      </c>
-      <c r="AM137" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN137" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="AO137" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP137" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="138" hidden="true">
-      <c r="A138" t="s" s="2">
-        <v>673</v>
-      </c>
-      <c r="B138" t="s" s="2">
-        <v>592</v>
-      </c>
-      <c r="C138" t="s" s="2">
-        <v>622</v>
-      </c>
-      <c r="D138" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E138" s="2"/>
-      <c r="F138" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G138" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H138" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I138" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J138" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K138" t="s" s="2">
-        <v>623</v>
-      </c>
-      <c r="L138" t="s" s="2">
-        <v>624</v>
-      </c>
-      <c r="M138" t="s" s="2">
-        <v>625</v>
-      </c>
-      <c r="N138" t="s" s="2">
-        <v>626</v>
-      </c>
-      <c r="O138" s="2"/>
-      <c r="P138" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q138" s="2"/>
-      <c r="R138" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S138" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T138" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U138" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V138" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W138" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X138" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y138" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z138" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA138" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB138" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC138" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD138" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE138" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF138" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="AG138" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH138" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI138" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ138" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="AK138" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL138" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM138" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="AN138" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="AO138" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP138" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="139" hidden="true">
-      <c r="A139" t="s" s="2">
-        <v>674</v>
-      </c>
-      <c r="B139" t="s" s="2">
-        <v>602</v>
-      </c>
-      <c r="C139" s="2"/>
-      <c r="D139" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E139" s="2"/>
-      <c r="F139" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G139" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H139" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I139" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J139" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K139" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="L139" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="M139" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="N139" s="2"/>
-      <c r="O139" s="2"/>
-      <c r="P139" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q139" s="2"/>
-      <c r="R139" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S139" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T139" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U139" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V139" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W139" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X139" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y139" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z139" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA139" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB139" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC139" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD139" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE139" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF139" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="AG139" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH139" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI139" t="s" s="2">
-        <v>603</v>
-      </c>
-      <c r="AJ139" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AK139" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL139" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM139" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN139" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="AO139" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP139" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="140" hidden="true">
-      <c r="A140" t="s" s="2">
-        <v>675</v>
-      </c>
-      <c r="B140" t="s" s="2">
-        <v>605</v>
-      </c>
-      <c r="C140" s="2"/>
-      <c r="D140" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E140" s="2"/>
-      <c r="F140" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G140" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H140" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I140" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J140" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K140" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="L140" t="s" s="2">
-        <v>593</v>
-      </c>
-      <c r="M140" t="s" s="2">
-        <v>594</v>
-      </c>
-      <c r="N140" s="2"/>
-      <c r="O140" s="2"/>
-      <c r="P140" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q140" s="2"/>
-      <c r="R140" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S140" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T140" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U140" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V140" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W140" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X140" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y140" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z140" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA140" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB140" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="AC140" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="AD140" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE140" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="AF140" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="AG140" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH140" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI140" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ140" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="AK140" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL140" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM140" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN140" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO140" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP140" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="141" hidden="true">
-      <c r="A141" t="s" s="2">
-        <v>676</v>
-      </c>
-      <c r="B141" t="s" s="2">
-        <v>607</v>
-      </c>
-      <c r="C141" s="2"/>
-      <c r="D141" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E141" s="2"/>
-      <c r="F141" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="G141" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H141" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I141" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J141" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K141" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="L141" t="s" s="2">
-        <v>608</v>
-      </c>
-      <c r="M141" t="s" s="2">
-        <v>609</v>
-      </c>
-      <c r="N141" t="s" s="2">
-        <v>610</v>
-      </c>
-      <c r="O141" s="2"/>
-      <c r="P141" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q141" s="2"/>
-      <c r="R141" t="s" s="2">
-        <v>630</v>
-      </c>
-      <c r="S141" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T141" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U141" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V141" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W141" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X141" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y141" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z141" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA141" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB141" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC141" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD141" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE141" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF141" t="s" s="2">
-        <v>612</v>
-      </c>
-      <c r="AG141" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AH141" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI141" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ141" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AK141" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL141" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM141" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN141" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="AO141" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP141" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="142" hidden="true">
-      <c r="A142" t="s" s="2">
-        <v>677</v>
-      </c>
-      <c r="B142" t="s" s="2">
-        <v>614</v>
-      </c>
-      <c r="C142" s="2"/>
-      <c r="D142" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E142" s="2"/>
-      <c r="F142" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="G142" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H142" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I142" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J142" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K142" t="s" s="2">
-        <v>632</v>
-      </c>
-      <c r="L142" t="s" s="2">
-        <v>615</v>
-      </c>
-      <c r="M142" t="s" s="2">
-        <v>616</v>
-      </c>
-      <c r="N142" s="2"/>
-      <c r="O142" s="2"/>
-      <c r="P142" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q142" s="2"/>
-      <c r="R142" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S142" t="s" s="2">
-        <v>633</v>
-      </c>
-      <c r="T142" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U142" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V142" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W142" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X142" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y142" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z142" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA142" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB142" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC142" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD142" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE142" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF142" t="s" s="2">
-        <v>618</v>
-      </c>
-      <c r="AG142" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH142" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI142" t="s" s="2">
-        <v>619</v>
-      </c>
-      <c r="AJ142" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK142" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL142" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM142" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN142" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="AO142" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP142" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="143" hidden="true">
-      <c r="A143" t="s" s="2">
-        <v>678</v>
-      </c>
-      <c r="B143" t="s" s="2">
-        <v>635</v>
-      </c>
-      <c r="C143" s="2"/>
-      <c r="D143" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E143" s="2"/>
-      <c r="F143" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G143" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H143" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I143" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J143" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K143" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="L143" t="s" s="2">
-        <v>636</v>
-      </c>
-      <c r="M143" t="s" s="2">
-        <v>637</v>
-      </c>
-      <c r="N143" s="2"/>
-      <c r="O143" s="2"/>
-      <c r="P143" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q143" s="2"/>
-      <c r="R143" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S143" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T143" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U143" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V143" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W143" t="s" s="2">
-        <v>638</v>
-      </c>
-      <c r="X143" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y143" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z143" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA143" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB143" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC143" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD143" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE143" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF143" t="s" s="2">
-        <v>639</v>
-      </c>
-      <c r="AG143" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH143" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI143" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ143" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AK143" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL143" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM143" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN143" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO143" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP143" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="144" hidden="true">
-      <c r="A144" t="s" s="2">
-        <v>679</v>
-      </c>
-      <c r="B144" t="s" s="2">
-        <v>557</v>
-      </c>
-      <c r="C144" s="2"/>
-      <c r="D144" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E144" s="2"/>
-      <c r="F144" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G144" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H144" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I144" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J144" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K144" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="L144" t="s" s="2">
-        <v>558</v>
-      </c>
-      <c r="M144" t="s" s="2">
-        <v>559</v>
-      </c>
-      <c r="N144" s="2"/>
-      <c r="O144" t="s" s="2">
-        <v>560</v>
-      </c>
-      <c r="P144" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q144" s="2"/>
-      <c r="R144" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S144" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T144" t="s" s="2">
-        <v>561</v>
-      </c>
-      <c r="U144" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V144" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W144" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X144" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y144" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z144" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA144" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB144" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC144" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD144" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE144" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF144" t="s" s="2">
-        <v>562</v>
-      </c>
-      <c r="AG144" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH144" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI144" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ144" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK144" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL144" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM144" t="s" s="2">
-        <v>563</v>
-      </c>
-      <c r="AN144" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="AO144" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="AP144" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="145" hidden="true">
-      <c r="A145" t="s" s="2">
-        <v>680</v>
-      </c>
-      <c r="B145" t="s" s="2">
-        <v>681</v>
-      </c>
-      <c r="C145" s="2"/>
-      <c r="D145" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E145" s="2"/>
-      <c r="F145" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G145" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H145" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I145" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J145" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K145" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="L145" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="M145" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="N145" s="2"/>
-      <c r="O145" s="2"/>
-      <c r="P145" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q145" s="2"/>
-      <c r="R145" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S145" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T145" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U145" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V145" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W145" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X145" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y145" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z145" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA145" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB145" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC145" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD145" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE145" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF145" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="AG145" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH145" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI145" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ145" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AK145" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL145" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM145" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN145" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="AO145" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP145" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="146" hidden="true">
-      <c r="A146" t="s" s="2">
-        <v>682</v>
-      </c>
-      <c r="B146" t="s" s="2">
-        <v>683</v>
-      </c>
-      <c r="C146" s="2"/>
-      <c r="D146" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="E146" s="2"/>
-      <c r="F146" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G146" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H146" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I146" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J146" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K146" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="L146" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="M146" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N146" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O146" s="2"/>
-      <c r="P146" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q146" s="2"/>
-      <c r="R146" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S146" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T146" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U146" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V146" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W146" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X146" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y146" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z146" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA146" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB146" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="AC146" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="AD146" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE146" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="AF146" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="AG146" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH146" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI146" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ146" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="AK146" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL146" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM146" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN146" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="AO146" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP146" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="147" hidden="true">
-      <c r="A147" t="s" s="2">
-        <v>684</v>
-      </c>
-      <c r="B147" t="s" s="2">
-        <v>685</v>
-      </c>
-      <c r="C147" s="2"/>
-      <c r="D147" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E147" s="2"/>
-      <c r="F147" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G147" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H147" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="I147" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J147" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K147" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="L147" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="M147" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="N147" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="O147" s="2"/>
-      <c r="P147" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q147" s="2"/>
-      <c r="R147" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S147" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T147" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U147" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V147" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W147" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X147" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y147" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z147" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA147" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB147" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC147" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD147" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE147" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF147" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="AG147" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH147" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI147" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="AJ147" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK147" t="s" s="2">
-        <v>686</v>
-      </c>
-      <c r="AL147" t="s" s="2">
-        <v>687</v>
-      </c>
-      <c r="AM147" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="AN147" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="AO147" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP147" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="148" hidden="true">
-      <c r="A148" t="s" s="2">
-        <v>688</v>
-      </c>
-      <c r="B148" t="s" s="2">
-        <v>689</v>
-      </c>
-      <c r="C148" s="2"/>
-      <c r="D148" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E148" s="2"/>
-      <c r="F148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G148" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H148" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="I148" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J148" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K148" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="L148" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="M148" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="N148" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="O148" s="2"/>
-      <c r="P148" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q148" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="R148" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S148" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T148" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U148" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V148" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W148" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X148" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y148" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z148" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA148" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB148" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC148" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD148" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE148" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF148" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="AG148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH148" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI148" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="AJ148" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK148" t="s" s="2">
-        <v>690</v>
-      </c>
-      <c r="AL148" t="s" s="2">
-        <v>691</v>
-      </c>
-      <c r="AM148" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="AN148" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="AO148" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP148" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="149" hidden="true">
-      <c r="A149" t="s" s="2">
-        <v>692</v>
-      </c>
-      <c r="B149" t="s" s="2">
-        <v>692</v>
-      </c>
-      <c r="C149" s="2"/>
-      <c r="D149" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E149" s="2"/>
-      <c r="F149" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G149" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H149" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="I149" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J149" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K149" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="L149" t="s" s="2">
-        <v>693</v>
-      </c>
-      <c r="M149" t="s" s="2">
-        <v>694</v>
-      </c>
-      <c r="N149" s="2"/>
-      <c r="O149" t="s" s="2">
-        <v>695</v>
-      </c>
-      <c r="P149" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q149" s="2"/>
-      <c r="R149" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S149" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T149" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U149" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V149" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W149" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X149" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="Y149" s="2"/>
-      <c r="Z149" t="s" s="2">
-        <v>696</v>
-      </c>
-      <c r="AA149" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB149" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC149" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD149" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE149" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF149" t="s" s="2">
-        <v>692</v>
-      </c>
-      <c r="AG149" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH149" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI149" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ149" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK149" t="s" s="2">
-        <v>697</v>
-      </c>
-      <c r="AL149" t="s" s="2">
-        <v>698</v>
-      </c>
-      <c r="AM149" t="s" s="2">
-        <v>699</v>
-      </c>
-      <c r="AN149" t="s" s="2">
-        <v>700</v>
-      </c>
-      <c r="AO149" t="s" s="2">
-        <v>701</v>
-      </c>
-      <c r="AP149" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="150" hidden="true">
-      <c r="A150" t="s" s="2">
-        <v>702</v>
-      </c>
-      <c r="B150" t="s" s="2">
-        <v>702</v>
-      </c>
-      <c r="C150" s="2"/>
-      <c r="D150" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E150" s="2"/>
-      <c r="F150" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G150" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H150" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="I150" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J150" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K150" t="s" s="2">
-        <v>703</v>
-      </c>
-      <c r="L150" t="s" s="2">
-        <v>704</v>
-      </c>
-      <c r="M150" t="s" s="2">
-        <v>705</v>
-      </c>
-      <c r="N150" s="2"/>
-      <c r="O150" t="s" s="2">
-        <v>706</v>
-      </c>
-      <c r="P150" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q150" s="2"/>
-      <c r="R150" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S150" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T150" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U150" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V150" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W150" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X150" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y150" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z150" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA150" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB150" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC150" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD150" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE150" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF150" t="s" s="2">
-        <v>702</v>
-      </c>
-      <c r="AG150" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH150" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI150" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ150" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK150" t="s" s="2">
-        <v>707</v>
-      </c>
-      <c r="AL150" t="s" s="2">
-        <v>708</v>
-      </c>
-      <c r="AM150" t="s" s="2">
-        <v>709</v>
-      </c>
-      <c r="AN150" t="s" s="2">
-        <v>710</v>
-      </c>
-      <c r="AO150" t="s" s="2">
-        <v>711</v>
-      </c>
-      <c r="AP150" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="151" hidden="true">
-      <c r="A151" t="s" s="2">
-        <v>712</v>
-      </c>
-      <c r="B151" t="s" s="2">
-        <v>712</v>
-      </c>
-      <c r="C151" s="2"/>
-      <c r="D151" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E151" s="2"/>
-      <c r="F151" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G151" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H151" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I151" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J151" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K151" t="s" s="2">
-        <v>713</v>
-      </c>
-      <c r="L151" t="s" s="2">
-        <v>714</v>
-      </c>
-      <c r="M151" t="s" s="2">
-        <v>715</v>
-      </c>
-      <c r="N151" s="2"/>
-      <c r="O151" t="s" s="2">
-        <v>716</v>
-      </c>
-      <c r="P151" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q151" s="2"/>
-      <c r="R151" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S151" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T151" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U151" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V151" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W151" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X151" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y151" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z151" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA151" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB151" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC151" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD151" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE151" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF151" t="s" s="2">
-        <v>712</v>
-      </c>
-      <c r="AG151" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH151" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI151" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ151" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK151" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL151" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM151" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN151" t="s" s="2">
-        <v>717</v>
-      </c>
-      <c r="AO151" t="s" s="2">
-        <v>718</v>
-      </c>
-      <c r="AP151" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="152" hidden="true">
-      <c r="A152" t="s" s="2">
-        <v>719</v>
-      </c>
-      <c r="B152" t="s" s="2">
-        <v>719</v>
-      </c>
-      <c r="C152" s="2"/>
-      <c r="D152" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E152" s="2"/>
-      <c r="F152" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G152" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H152" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I152" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J152" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K152" t="s" s="2">
-        <v>720</v>
-      </c>
-      <c r="L152" t="s" s="2">
-        <v>721</v>
-      </c>
-      <c r="M152" t="s" s="2">
-        <v>722</v>
-      </c>
-      <c r="N152" s="2"/>
-      <c r="O152" s="2"/>
-      <c r="P152" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q152" s="2"/>
-      <c r="R152" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S152" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T152" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U152" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V152" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W152" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X152" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y152" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z152" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA152" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB152" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC152" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD152" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE152" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF152" t="s" s="2">
-        <v>719</v>
-      </c>
-      <c r="AG152" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH152" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI152" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ152" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK152" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL152" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM152" t="s" s="2">
-        <v>723</v>
-      </c>
-      <c r="AN152" t="s" s="2">
-        <v>724</v>
-      </c>
-      <c r="AO152" t="s" s="2">
-        <v>725</v>
-      </c>
-      <c r="AP152" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="153" hidden="true">
-      <c r="A153" t="s" s="2">
-        <v>726</v>
-      </c>
-      <c r="B153" t="s" s="2">
-        <v>726</v>
-      </c>
-      <c r="C153" s="2"/>
-      <c r="D153" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E153" s="2"/>
-      <c r="F153" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G153" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H153" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I153" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J153" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K153" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="L153" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="M153" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="N153" s="2"/>
-      <c r="O153" s="2"/>
-      <c r="P153" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q153" s="2"/>
-      <c r="R153" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S153" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T153" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U153" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V153" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W153" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X153" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y153" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z153" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA153" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB153" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC153" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD153" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE153" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF153" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="AG153" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH153" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI153" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ153" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AK153" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL153" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM153" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN153" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="AO153" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP153" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="154" hidden="true">
-      <c r="A154" t="s" s="2">
-        <v>727</v>
-      </c>
-      <c r="B154" t="s" s="2">
-        <v>727</v>
-      </c>
-      <c r="C154" s="2"/>
-      <c r="D154" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="E154" s="2"/>
-      <c r="F154" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G154" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H154" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I154" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J154" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K154" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="L154" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="M154" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N154" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O154" s="2"/>
-      <c r="P154" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q154" s="2"/>
-      <c r="R154" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S154" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T154" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U154" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V154" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W154" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X154" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y154" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z154" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA154" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB154" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC154" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD154" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE154" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF154" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="AG154" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH154" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI154" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ154" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="AK154" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL154" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM154" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN154" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="AO154" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP154" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="155" hidden="true">
-      <c r="A155" t="s" s="2">
-        <v>728</v>
-      </c>
-      <c r="B155" t="s" s="2">
-        <v>728</v>
-      </c>
-      <c r="C155" s="2"/>
-      <c r="D155" t="s" s="2">
-        <v>729</v>
-      </c>
-      <c r="E155" s="2"/>
-      <c r="F155" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G155" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H155" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I155" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="J155" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K155" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="L155" t="s" s="2">
-        <v>730</v>
-      </c>
-      <c r="M155" t="s" s="2">
-        <v>731</v>
-      </c>
-      <c r="N155" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O155" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="P155" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q155" s="2"/>
-      <c r="R155" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S155" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T155" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U155" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V155" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W155" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X155" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y155" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z155" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA155" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB155" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC155" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD155" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE155" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF155" t="s" s="2">
-        <v>732</v>
-      </c>
-      <c r="AG155" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH155" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI155" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ155" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="AK155" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL155" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM155" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN155" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="AO155" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP155" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="156" hidden="true">
-      <c r="A156" t="s" s="2">
-        <v>733</v>
-      </c>
-      <c r="B156" t="s" s="2">
-        <v>733</v>
-      </c>
-      <c r="C156" s="2"/>
-      <c r="D156" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E156" s="2"/>
-      <c r="F156" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G156" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H156" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I156" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J156" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K156" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="L156" t="s" s="2">
-        <v>734</v>
-      </c>
-      <c r="M156" t="s" s="2">
-        <v>735</v>
-      </c>
-      <c r="N156" s="2"/>
-      <c r="O156" t="s" s="2">
-        <v>736</v>
-      </c>
-      <c r="P156" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q156" s="2"/>
-      <c r="R156" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S156" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T156" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U156" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V156" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W156" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X156" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y156" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z156" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA156" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB156" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC156" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD156" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE156" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF156" t="s" s="2">
-        <v>733</v>
-      </c>
-      <c r="AG156" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH156" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI156" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ156" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK156" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL156" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM156" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN156" t="s" s="2">
-        <v>737</v>
-      </c>
-      <c r="AO156" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP156" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="157" hidden="true">
-      <c r="A157" t="s" s="2">
-        <v>738</v>
-      </c>
-      <c r="B157" t="s" s="2">
-        <v>738</v>
-      </c>
-      <c r="C157" s="2"/>
-      <c r="D157" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E157" s="2"/>
-      <c r="F157" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="G157" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H157" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I157" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J157" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K157" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="L157" t="s" s="2">
-        <v>739</v>
-      </c>
-      <c r="M157" t="s" s="2">
-        <v>740</v>
-      </c>
-      <c r="N157" s="2"/>
-      <c r="O157" s="2"/>
-      <c r="P157" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q157" s="2"/>
-      <c r="R157" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S157" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T157" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U157" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V157" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W157" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X157" t="s" s="2">
-        <v>741</v>
-      </c>
-      <c r="Y157" t="s" s="2">
-        <v>742</v>
-      </c>
-      <c r="Z157" t="s" s="2">
-        <v>743</v>
-      </c>
-      <c r="AA157" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB157" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC157" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD157" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE157" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF157" t="s" s="2">
-        <v>738</v>
-      </c>
-      <c r="AG157" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AH157" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI157" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ157" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK157" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL157" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM157" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN157" t="s" s="2">
-        <v>724</v>
-      </c>
-      <c r="AO157" t="s" s="2">
-        <v>744</v>
-      </c>
-      <c r="AP157" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="158" hidden="true">
-      <c r="A158" t="s" s="2">
-        <v>745</v>
-      </c>
-      <c r="B158" t="s" s="2">
-        <v>745</v>
-      </c>
-      <c r="C158" s="2"/>
-      <c r="D158" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E158" s="2"/>
-      <c r="F158" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G158" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H158" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I158" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J158" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K158" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="L158" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="M158" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="N158" s="2"/>
-      <c r="O158" s="2"/>
-      <c r="P158" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q158" s="2"/>
-      <c r="R158" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S158" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T158" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U158" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V158" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W158" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X158" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y158" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z158" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA158" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB158" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC158" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD158" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE158" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF158" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="AG158" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH158" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI158" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ158" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AK158" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL158" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM158" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN158" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="AO158" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP158" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="159" hidden="true">
-      <c r="A159" t="s" s="2">
-        <v>746</v>
-      </c>
-      <c r="B159" t="s" s="2">
-        <v>746</v>
-      </c>
-      <c r="C159" s="2"/>
-      <c r="D159" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="E159" s="2"/>
-      <c r="F159" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G159" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H159" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I159" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J159" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K159" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="L159" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="M159" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N159" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O159" s="2"/>
-      <c r="P159" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q159" s="2"/>
-      <c r="R159" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S159" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T159" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U159" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V159" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W159" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X159" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y159" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z159" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA159" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB159" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="AC159" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="AD159" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE159" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="AF159" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="AG159" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH159" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI159" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ159" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="AK159" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL159" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM159" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN159" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="AO159" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP159" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="160" hidden="true">
-      <c r="A160" t="s" s="2">
-        <v>747</v>
-      </c>
-      <c r="B160" t="s" s="2">
-        <v>747</v>
-      </c>
-      <c r="C160" s="2"/>
-      <c r="D160" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E160" s="2"/>
-      <c r="F160" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G160" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H160" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I160" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J160" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K160" t="s" s="2">
-        <v>748</v>
-      </c>
-      <c r="L160" t="s" s="2">
-        <v>749</v>
-      </c>
-      <c r="M160" t="s" s="2">
-        <v>750</v>
-      </c>
-      <c r="N160" t="s" s="2">
-        <v>751</v>
-      </c>
-      <c r="O160" t="s" s="2">
-        <v>752</v>
-      </c>
-      <c r="P160" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q160" s="2"/>
-      <c r="R160" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S160" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T160" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U160" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V160" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W160" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X160" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y160" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z160" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA160" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB160" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC160" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD160" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE160" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF160" t="s" s="2">
-        <v>753</v>
-      </c>
-      <c r="AG160" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH160" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI160" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ160" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK160" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL160" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM160" t="s" s="2">
-        <v>754</v>
-      </c>
-      <c r="AN160" t="s" s="2">
-        <v>755</v>
-      </c>
-      <c r="AO160" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP160" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="161" hidden="true">
-      <c r="A161" t="s" s="2">
-        <v>756</v>
-      </c>
-      <c r="B161" t="s" s="2">
-        <v>756</v>
-      </c>
-      <c r="C161" s="2"/>
-      <c r="D161" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E161" s="2"/>
-      <c r="F161" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G161" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H161" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="I161" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J161" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K161" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="L161" t="s" s="2">
-        <v>757</v>
-      </c>
-      <c r="M161" t="s" s="2">
-        <v>758</v>
-      </c>
-      <c r="N161" t="s" s="2">
-        <v>759</v>
-      </c>
-      <c r="O161" t="s" s="2">
-        <v>760</v>
-      </c>
-      <c r="P161" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q161" s="2"/>
-      <c r="R161" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S161" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T161" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U161" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V161" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W161" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X161" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y161" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z161" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA161" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB161" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC161" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD161" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE161" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF161" t="s" s="2">
-        <v>761</v>
-      </c>
-      <c r="AG161" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH161" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI161" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ161" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK161" t="s" s="2">
-        <v>762</v>
-      </c>
-      <c r="AL161" t="s" s="2">
-        <v>763</v>
-      </c>
-      <c r="AM161" t="s" s="2">
-        <v>764</v>
-      </c>
-      <c r="AN161" t="s" s="2">
-        <v>765</v>
-      </c>
-      <c r="AO161" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP161" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="162" hidden="true">
-      <c r="A162" t="s" s="2">
-        <v>766</v>
-      </c>
-      <c r="B162" t="s" s="2">
-        <v>766</v>
-      </c>
-      <c r="C162" s="2"/>
-      <c r="D162" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E162" s="2"/>
-      <c r="F162" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G162" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H162" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I162" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J162" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K162" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="L162" t="s" s="2">
-        <v>767</v>
-      </c>
-      <c r="M162" t="s" s="2">
-        <v>768</v>
-      </c>
-      <c r="N162" s="2"/>
-      <c r="O162" t="s" s="2">
-        <v>769</v>
-      </c>
-      <c r="P162" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q162" s="2"/>
-      <c r="R162" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S162" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T162" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U162" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V162" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W162" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X162" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y162" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z162" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA162" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB162" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC162" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD162" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE162" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF162" t="s" s="2">
-        <v>766</v>
-      </c>
-      <c r="AG162" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH162" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI162" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ162" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK162" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL162" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM162" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN162" t="s" s="2">
-        <v>770</v>
-      </c>
-      <c r="AO162" t="s" s="2">
-        <v>771</v>
-      </c>
-      <c r="AP162" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="163" hidden="true">
-      <c r="A163" t="s" s="2">
-        <v>772</v>
-      </c>
-      <c r="B163" t="s" s="2">
-        <v>772</v>
-      </c>
-      <c r="C163" s="2"/>
-      <c r="D163" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E163" s="2"/>
-      <c r="F163" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G163" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H163" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I163" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J163" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K163" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="L163" t="s" s="2">
-        <v>773</v>
-      </c>
-      <c r="M163" t="s" s="2">
-        <v>774</v>
-      </c>
-      <c r="N163" s="2"/>
-      <c r="O163" s="2"/>
-      <c r="P163" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q163" s="2"/>
-      <c r="R163" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S163" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T163" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U163" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V163" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W163" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X163" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y163" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z163" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA163" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB163" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC163" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD163" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE163" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF163" t="s" s="2">
-        <v>772</v>
-      </c>
-      <c r="AG163" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH163" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI163" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ163" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK163" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL163" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM163" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN163" t="s" s="2">
-        <v>775</v>
-      </c>
-      <c r="AO163" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP163" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="164" hidden="true">
-      <c r="A164" t="s" s="2">
-        <v>776</v>
-      </c>
-      <c r="B164" t="s" s="2">
-        <v>776</v>
-      </c>
-      <c r="C164" s="2"/>
-      <c r="D164" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E164" s="2"/>
-      <c r="F164" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G164" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H164" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I164" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J164" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K164" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="L164" t="s" s="2">
-        <v>777</v>
-      </c>
-      <c r="M164" t="s" s="2">
-        <v>778</v>
-      </c>
-      <c r="N164" t="s" s="2">
-        <v>779</v>
-      </c>
-      <c r="O164" t="s" s="2">
-        <v>780</v>
-      </c>
-      <c r="P164" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q164" s="2"/>
-      <c r="R164" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S164" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T164" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U164" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V164" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W164" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X164" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="Y164" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="Z164" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="AA164" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB164" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC164" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD164" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE164" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF164" t="s" s="2">
-        <v>776</v>
-      </c>
-      <c r="AG164" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH164" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI164" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ164" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK164" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL164" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM164" t="s" s="2">
-        <v>781</v>
-      </c>
-      <c r="AN164" t="s" s="2">
-        <v>782</v>
-      </c>
-      <c r="AO164" t="s" s="2">
-        <v>783</v>
-      </c>
-      <c r="AP164" t="s" s="2">
         <v>80</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP164">
+  <autoFilter ref="A1:AP108">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -22494,7 +15431,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI163">
+  <conditionalFormatting sqref="A2:AI107">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.364</t>
+    <t>0.66.366</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-02T18:53:29+00:00</t>
+    <t>2024-10-11T07:57:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4157" uniqueCount="656">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4157" uniqueCount="657">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.366</t>
+    <t>0.66.367</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-11T07:57:28+00:00</t>
+    <t>2024-10-13T09:59:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1504,6 +1504,9 @@
   </si>
   <si>
     <t>The home/mailing address of the practitioner is often required for employee administration purposes, and also for some rostering services where the start point (practitioners home) can be used in calculations.</t>
+  </si>
+  <si>
+    <t>2012: target not supported</t>
   </si>
   <si>
     <t>ORC-24, STF-11, ROL-11, PRT-14</t>
@@ -12052,16 +12055,16 @@
         <v>101</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>80</v>
+        <v>473</v>
       </c>
       <c r="AL80" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>167</v>
@@ -12072,10 +12075,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12190,10 +12193,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12310,10 +12313,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12339,16 +12342,16 @@
         <v>109</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>80</v>
@@ -12376,10 +12379,10 @@
         <v>180</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>80</v>
@@ -12397,7 +12400,7 @@
         <v>80</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
@@ -12418,13 +12421,13 @@
         <v>80</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>358</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AP83" t="s" s="2">
         <v>80</v>
@@ -12432,10 +12435,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12461,13 +12464,13 @@
         <v>109</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -12481,7 +12484,7 @@
         <v>80</v>
       </c>
       <c r="T84" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="U84" t="s" s="2">
         <v>80</v>
@@ -12496,10 +12499,10 @@
         <v>180</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="Z84" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>80</v>
@@ -12517,7 +12520,7 @@
         <v>80</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>78</v>
@@ -12538,7 +12541,7 @@
         <v>80</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>358</v>
@@ -12552,10 +12555,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12581,13 +12584,13 @@
         <v>163</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="O85" t="s" s="2">
         <v>364</v>
@@ -12603,7 +12606,7 @@
         <v>80</v>
       </c>
       <c r="T85" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="U85" t="s" s="2">
         <v>80</v>
@@ -12639,7 +12642,7 @@
         <v>80</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>78</v>
@@ -12660,7 +12663,7 @@
         <v>80</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>369</v>
@@ -12674,10 +12677,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12688,7 +12691,7 @@
         <v>78</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>90</v>
@@ -12703,10 +12706,10 @@
         <v>163</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -12721,7 +12724,7 @@
         <v>80</v>
       </c>
       <c r="T86" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="U86" t="s" s="2">
         <v>80</v>
@@ -12757,7 +12760,7 @@
         <v>80</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>78</v>
@@ -12778,13 +12781,13 @@
         <v>80</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AO86" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AP86" t="s" s="2">
         <v>80</v>
@@ -12792,14 +12795,14 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
@@ -12821,10 +12824,10 @@
         <v>163</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -12839,7 +12842,7 @@
         <v>80</v>
       </c>
       <c r="T87" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="U87" t="s" s="2">
         <v>80</v>
@@ -12875,7 +12878,7 @@
         <v>80</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>78</v>
@@ -12896,13 +12899,13 @@
         <v>80</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AO87" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AP87" t="s" s="2">
         <v>80</v>
@@ -12910,14 +12913,14 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
@@ -12939,13 +12942,13 @@
         <v>163</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -12959,7 +12962,7 @@
         <v>80</v>
       </c>
       <c r="T88" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="U88" t="s" s="2">
         <v>80</v>
@@ -12995,7 +12998,7 @@
         <v>80</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>78</v>
@@ -13016,10 +13019,10 @@
         <v>80</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>80</v>
@@ -13030,14 +13033,14 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
@@ -13059,10 +13062,10 @@
         <v>163</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -13092,10 +13095,10 @@
         <v>193</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>80</v>
@@ -13113,7 +13116,7 @@
         <v>80</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>78</v>
@@ -13134,13 +13137,13 @@
         <v>80</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="AP89" t="s" s="2">
         <v>80</v>
@@ -13148,14 +13151,14 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
@@ -13177,10 +13180,10 @@
         <v>163</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -13195,7 +13198,7 @@
         <v>80</v>
       </c>
       <c r="T90" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="U90" t="s" s="2">
         <v>80</v>
@@ -13231,7 +13234,7 @@
         <v>80</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>78</v>
@@ -13252,13 +13255,13 @@
         <v>80</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AP90" t="s" s="2">
         <v>80</v>
@@ -13266,10 +13269,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13295,13 +13298,13 @@
         <v>163</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
@@ -13351,7 +13354,7 @@
         <v>80</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>78</v>
@@ -13372,13 +13375,13 @@
         <v>80</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="AP91" t="s" s="2">
         <v>80</v>
@@ -13386,10 +13389,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13415,14 +13418,14 @@
         <v>226</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>80</v>
@@ -13435,7 +13438,7 @@
         <v>80</v>
       </c>
       <c r="T92" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="U92" t="s" s="2">
         <v>80</v>
@@ -13471,7 +13474,7 @@
         <v>80</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>78</v>
@@ -13492,7 +13495,7 @@
         <v>80</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AN92" t="s" s="2">
         <v>411</v>
@@ -13506,10 +13509,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13535,14 +13538,14 @@
         <v>109</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>80</v>
@@ -13571,7 +13574,7 @@
       </c>
       <c r="Y93" s="2"/>
       <c r="Z93" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>80</v>
@@ -13589,7 +13592,7 @@
         <v>80</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>78</v>
@@ -13604,19 +13607,19 @@
         <v>101</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="AP93" t="s" s="2">
         <v>80</v>
@@ -13624,10 +13627,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13650,17 +13653,17 @@
         <v>90</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>80</v>
@@ -13709,7 +13712,7 @@
         <v>80</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>78</v>
@@ -13724,19 +13727,19 @@
         <v>101</v>
       </c>
       <c r="AK94" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AP94" t="s" s="2">
         <v>80</v>
@@ -13744,10 +13747,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13770,17 +13773,17 @@
         <v>80</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>80</v>
@@ -13829,7 +13832,7 @@
         <v>80</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>78</v>
@@ -13853,10 +13856,10 @@
         <v>80</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="AO95" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="AP95" t="s" s="2">
         <v>80</v>
@@ -13864,10 +13867,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13890,13 +13893,13 @@
         <v>80</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -13947,7 +13950,7 @@
         <v>80</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>78</v>
@@ -13968,13 +13971,13 @@
         <v>80</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="AO96" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AP96" t="s" s="2">
         <v>80</v>
@@ -13982,10 +13985,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14100,10 +14103,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14220,14 +14223,14 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
@@ -14249,10 +14252,10 @@
         <v>135</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="N99" t="s" s="2">
         <v>138</v>
@@ -14307,7 +14310,7 @@
         <v>80</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>78</v>
@@ -14342,10 +14345,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14371,14 +14374,14 @@
         <v>147</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>80</v>
@@ -14427,7 +14430,7 @@
         <v>80</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>78</v>
@@ -14451,7 +14454,7 @@
         <v>80</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>80</v>
@@ -14462,10 +14465,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14491,10 +14494,10 @@
         <v>187</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -14521,13 +14524,13 @@
         <v>80</v>
       </c>
       <c r="X101" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>80</v>
@@ -14545,7 +14548,7 @@
         <v>80</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>89</v>
@@ -14569,10 +14572,10 @@
         <v>80</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="AP101" t="s" s="2">
         <v>80</v>
@@ -14580,10 +14583,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14698,10 +14701,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14818,10 +14821,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14844,19 +14847,19 @@
         <v>90</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="O104" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>80</v>
@@ -14905,7 +14908,7 @@
         <v>80</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>78</v>
@@ -14926,10 +14929,10 @@
         <v>80</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>80</v>
@@ -14940,10 +14943,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14969,16 +14972,16 @@
         <v>163</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="O105" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>80</v>
@@ -15027,7 +15030,7 @@
         <v>80</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>78</v>
@@ -15042,16 +15045,16 @@
         <v>101</v>
       </c>
       <c r="AK105" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>80</v>
@@ -15062,10 +15065,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15091,14 +15094,14 @@
         <v>226</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>80</v>
@@ -15147,7 +15150,7 @@
         <v>80</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>78</v>
@@ -15171,10 +15174,10 @@
         <v>80</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="AO106" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="AP106" t="s" s="2">
         <v>80</v>
@@ -15182,10 +15185,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15211,10 +15214,10 @@
         <v>259</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -15265,7 +15268,7 @@
         <v>80</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>78</v>
@@ -15289,7 +15292,7 @@
         <v>80</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>80</v>
@@ -15300,10 +15303,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15329,16 +15332,16 @@
         <v>187</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="O108" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>80</v>
@@ -15387,7 +15390,7 @@
         <v>80</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>78</v>
@@ -15408,13 +15411,13 @@
         <v>80</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="AO108" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="AP108" t="s" s="2">
         <v>80</v>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.367</t>
+    <t>0.67.369</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-13T09:59:39+00:00</t>
+    <t>2024-10-18T16:05:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.369</t>
+    <t>0.67.370</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T16:05:33+00:00</t>
+    <t>2024-10-20T09:02:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.370</t>
+    <t>0.67.378</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-20T09:02:32+00:00</t>
+    <t>2024-10-30T12:26:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.378</t>
+    <t>0.67.381</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-30T12:26:51+00:00</t>
+    <t>2024-11-03T11:50:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4157" uniqueCount="657">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4157" uniqueCount="656">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.381</t>
+    <t>0.68.397</t>
   </si>
   <si>
     <t>Name</t>
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-03T11:50:46+00:00</t>
+    <t>2024-11-10T10:13:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1504,9 +1504,6 @@
   </si>
   <si>
     <t>The home/mailing address of the practitioner is often required for employee administration purposes, and also for some rostering services where the start point (practitioners home) can be used in calculations.</t>
-  </si>
-  <si>
-    <t>2012: target not supported</t>
   </si>
   <si>
     <t>ORC-24, STF-11, ROL-11, PRT-14</t>
@@ -12055,16 +12052,16 @@
         <v>101</v>
       </c>
       <c r="AK80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM80" t="s" s="2">
         <v>473</v>
       </c>
-      <c r="AL80" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM80" t="s" s="2">
+      <c r="AN80" t="s" s="2">
         <v>474</v>
-      </c>
-      <c r="AN80" t="s" s="2">
-        <v>475</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>167</v>
@@ -12075,10 +12072,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12193,10 +12190,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12313,10 +12310,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12342,16 +12339,16 @@
         <v>109</v>
       </c>
       <c r="L83" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="M83" t="s" s="2">
         <v>479</v>
       </c>
-      <c r="M83" t="s" s="2">
+      <c r="N83" t="s" s="2">
         <v>480</v>
       </c>
-      <c r="N83" t="s" s="2">
+      <c r="O83" t="s" s="2">
         <v>481</v>
-      </c>
-      <c r="O83" t="s" s="2">
-        <v>482</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>80</v>
@@ -12379,28 +12376,28 @@
         <v>180</v>
       </c>
       <c r="Y83" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="Z83" t="s" s="2">
         <v>483</v>
       </c>
-      <c r="Z83" t="s" s="2">
+      <c r="AA83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF83" t="s" s="2">
         <v>484</v>
-      </c>
-      <c r="AA83" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB83" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC83" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD83" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE83" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF83" t="s" s="2">
-        <v>485</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
@@ -12421,13 +12418,13 @@
         <v>80</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>358</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="AP83" t="s" s="2">
         <v>80</v>
@@ -12435,10 +12432,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12464,13 +12461,13 @@
         <v>109</v>
       </c>
       <c r="L84" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="M84" t="s" s="2">
         <v>489</v>
       </c>
-      <c r="M84" t="s" s="2">
+      <c r="N84" t="s" s="2">
         <v>490</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>491</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -12484,7 +12481,7 @@
         <v>80</v>
       </c>
       <c r="T84" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="U84" t="s" s="2">
         <v>80</v>
@@ -12499,28 +12496,28 @@
         <v>180</v>
       </c>
       <c r="Y84" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="Z84" t="s" s="2">
         <v>493</v>
       </c>
-      <c r="Z84" t="s" s="2">
+      <c r="AA84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF84" t="s" s="2">
         <v>494</v>
-      </c>
-      <c r="AA84" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB84" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC84" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD84" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE84" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF84" t="s" s="2">
-        <v>495</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>78</v>
@@ -12541,7 +12538,7 @@
         <v>80</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>358</v>
@@ -12555,10 +12552,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12584,13 +12581,13 @@
         <v>163</v>
       </c>
       <c r="L85" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="M85" t="s" s="2">
         <v>498</v>
       </c>
-      <c r="M85" t="s" s="2">
+      <c r="N85" t="s" s="2">
         <v>499</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>500</v>
       </c>
       <c r="O85" t="s" s="2">
         <v>364</v>
@@ -12606,43 +12603,43 @@
         <v>80</v>
       </c>
       <c r="T85" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="U85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF85" t="s" s="2">
         <v>501</v>
-      </c>
-      <c r="U85" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V85" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W85" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X85" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y85" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z85" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA85" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB85" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC85" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD85" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE85" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF85" t="s" s="2">
-        <v>502</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>78</v>
@@ -12663,7 +12660,7 @@
         <v>80</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>369</v>
@@ -12677,10 +12674,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12691,7 +12688,7 @@
         <v>78</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>90</v>
@@ -12706,10 +12703,10 @@
         <v>163</v>
       </c>
       <c r="L86" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="M86" t="s" s="2">
         <v>506</v>
-      </c>
-      <c r="M86" t="s" s="2">
-        <v>507</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -12724,43 +12721,43 @@
         <v>80</v>
       </c>
       <c r="T86" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="U86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF86" t="s" s="2">
         <v>508</v>
-      </c>
-      <c r="U86" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V86" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W86" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X86" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y86" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z86" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA86" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB86" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC86" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD86" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE86" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF86" t="s" s="2">
-        <v>509</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>78</v>
@@ -12781,13 +12778,13 @@
         <v>80</v>
       </c>
       <c r="AM86" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="AN86" t="s" s="2">
         <v>510</v>
       </c>
-      <c r="AN86" t="s" s="2">
+      <c r="AO86" t="s" s="2">
         <v>511</v>
-      </c>
-      <c r="AO86" t="s" s="2">
-        <v>512</v>
       </c>
       <c r="AP86" t="s" s="2">
         <v>80</v>
@@ -12795,14 +12792,14 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
@@ -12824,10 +12821,10 @@
         <v>163</v>
       </c>
       <c r="L87" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="M87" t="s" s="2">
         <v>515</v>
-      </c>
-      <c r="M87" t="s" s="2">
-        <v>516</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -12842,43 +12839,43 @@
         <v>80</v>
       </c>
       <c r="T87" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="U87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF87" t="s" s="2">
         <v>517</v>
-      </c>
-      <c r="U87" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V87" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W87" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X87" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y87" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z87" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA87" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB87" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC87" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD87" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE87" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF87" t="s" s="2">
-        <v>518</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>78</v>
@@ -12899,13 +12896,13 @@
         <v>80</v>
       </c>
       <c r="AM87" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="AN87" t="s" s="2">
         <v>519</v>
       </c>
-      <c r="AN87" t="s" s="2">
+      <c r="AO87" t="s" s="2">
         <v>520</v>
-      </c>
-      <c r="AO87" t="s" s="2">
-        <v>521</v>
       </c>
       <c r="AP87" t="s" s="2">
         <v>80</v>
@@ -12913,14 +12910,14 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
@@ -12942,13 +12939,13 @@
         <v>163</v>
       </c>
       <c r="L88" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="M88" t="s" s="2">
         <v>524</v>
       </c>
-      <c r="M88" t="s" s="2">
+      <c r="N88" t="s" s="2">
         <v>525</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>526</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -12962,43 +12959,43 @@
         <v>80</v>
       </c>
       <c r="T88" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="U88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF88" t="s" s="2">
         <v>527</v>
-      </c>
-      <c r="U88" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V88" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W88" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X88" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y88" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z88" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA88" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB88" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC88" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD88" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE88" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF88" t="s" s="2">
-        <v>528</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>78</v>
@@ -13019,10 +13016,10 @@
         <v>80</v>
       </c>
       <c r="AM88" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="AN88" t="s" s="2">
         <v>529</v>
-      </c>
-      <c r="AN88" t="s" s="2">
-        <v>530</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>80</v>
@@ -13033,14 +13030,14 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
@@ -13062,10 +13059,10 @@
         <v>163</v>
       </c>
       <c r="L89" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="M89" t="s" s="2">
         <v>533</v>
-      </c>
-      <c r="M89" t="s" s="2">
-        <v>534</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -13095,28 +13092,28 @@
         <v>193</v>
       </c>
       <c r="Y89" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="Z89" t="s" s="2">
         <v>535</v>
       </c>
-      <c r="Z89" t="s" s="2">
+      <c r="AA89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF89" t="s" s="2">
         <v>536</v>
-      </c>
-      <c r="AA89" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB89" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC89" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD89" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE89" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF89" t="s" s="2">
-        <v>537</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>78</v>
@@ -13137,13 +13134,13 @@
         <v>80</v>
       </c>
       <c r="AM89" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="AN89" t="s" s="2">
         <v>538</v>
       </c>
-      <c r="AN89" t="s" s="2">
+      <c r="AO89" t="s" s="2">
         <v>539</v>
-      </c>
-      <c r="AO89" t="s" s="2">
-        <v>540</v>
       </c>
       <c r="AP89" t="s" s="2">
         <v>80</v>
@@ -13151,14 +13148,14 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
@@ -13180,10 +13177,10 @@
         <v>163</v>
       </c>
       <c r="L90" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="M90" t="s" s="2">
         <v>543</v>
-      </c>
-      <c r="M90" t="s" s="2">
-        <v>544</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -13198,43 +13195,43 @@
         <v>80</v>
       </c>
       <c r="T90" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="U90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF90" t="s" s="2">
         <v>545</v>
-      </c>
-      <c r="U90" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V90" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W90" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X90" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y90" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z90" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA90" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB90" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC90" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD90" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE90" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF90" t="s" s="2">
-        <v>546</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>78</v>
@@ -13255,13 +13252,13 @@
         <v>80</v>
       </c>
       <c r="AM90" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="AN90" t="s" s="2">
         <v>547</v>
       </c>
-      <c r="AN90" t="s" s="2">
+      <c r="AO90" t="s" s="2">
         <v>548</v>
-      </c>
-      <c r="AO90" t="s" s="2">
-        <v>549</v>
       </c>
       <c r="AP90" t="s" s="2">
         <v>80</v>
@@ -13269,10 +13266,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13298,13 +13295,13 @@
         <v>163</v>
       </c>
       <c r="L91" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="M91" t="s" s="2">
         <v>551</v>
       </c>
-      <c r="M91" t="s" s="2">
+      <c r="N91" t="s" s="2">
         <v>552</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>553</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
@@ -13354,7 +13351,7 @@
         <v>80</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>78</v>
@@ -13375,13 +13372,13 @@
         <v>80</v>
       </c>
       <c r="AM91" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="AN91" t="s" s="2">
         <v>555</v>
       </c>
-      <c r="AN91" t="s" s="2">
+      <c r="AO91" t="s" s="2">
         <v>556</v>
-      </c>
-      <c r="AO91" t="s" s="2">
-        <v>557</v>
       </c>
       <c r="AP91" t="s" s="2">
         <v>80</v>
@@ -13389,10 +13386,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13418,14 +13415,14 @@
         <v>226</v>
       </c>
       <c r="L92" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="M92" t="s" s="2">
         <v>559</v>
-      </c>
-      <c r="M92" t="s" s="2">
-        <v>560</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>80</v>
@@ -13438,43 +13435,43 @@
         <v>80</v>
       </c>
       <c r="T92" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="U92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF92" t="s" s="2">
         <v>562</v>
-      </c>
-      <c r="U92" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V92" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W92" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X92" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y92" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z92" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA92" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB92" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC92" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD92" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE92" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF92" t="s" s="2">
-        <v>563</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>78</v>
@@ -13495,7 +13492,7 @@
         <v>80</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="AN92" t="s" s="2">
         <v>411</v>
@@ -13509,10 +13506,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13538,14 +13535,14 @@
         <v>109</v>
       </c>
       <c r="L93" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="M93" t="s" s="2">
         <v>566</v>
-      </c>
-      <c r="M93" t="s" s="2">
-        <v>567</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>80</v>
@@ -13574,7 +13571,7 @@
       </c>
       <c r="Y93" s="2"/>
       <c r="Z93" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>80</v>
@@ -13592,7 +13589,7 @@
         <v>80</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>78</v>
@@ -13607,19 +13604,19 @@
         <v>101</v>
       </c>
       <c r="AK93" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="AL93" t="s" s="2">
         <v>570</v>
       </c>
-      <c r="AL93" t="s" s="2">
+      <c r="AM93" t="s" s="2">
         <v>571</v>
       </c>
-      <c r="AM93" t="s" s="2">
+      <c r="AN93" t="s" s="2">
         <v>572</v>
       </c>
-      <c r="AN93" t="s" s="2">
+      <c r="AO93" t="s" s="2">
         <v>573</v>
-      </c>
-      <c r="AO93" t="s" s="2">
-        <v>574</v>
       </c>
       <c r="AP93" t="s" s="2">
         <v>80</v>
@@ -13627,10 +13624,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13653,17 +13650,17 @@
         <v>90</v>
       </c>
       <c r="K94" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="L94" t="s" s="2">
         <v>576</v>
       </c>
-      <c r="L94" t="s" s="2">
+      <c r="M94" t="s" s="2">
         <v>577</v>
-      </c>
-      <c r="M94" t="s" s="2">
-        <v>578</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" t="s" s="2">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>80</v>
@@ -13712,7 +13709,7 @@
         <v>80</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>78</v>
@@ -13727,19 +13724,19 @@
         <v>101</v>
       </c>
       <c r="AK94" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="AL94" t="s" s="2">
         <v>580</v>
       </c>
-      <c r="AL94" t="s" s="2">
+      <c r="AM94" t="s" s="2">
         <v>581</v>
       </c>
-      <c r="AM94" t="s" s="2">
+      <c r="AN94" t="s" s="2">
         <v>582</v>
       </c>
-      <c r="AN94" t="s" s="2">
+      <c r="AO94" t="s" s="2">
         <v>583</v>
-      </c>
-      <c r="AO94" t="s" s="2">
-        <v>584</v>
       </c>
       <c r="AP94" t="s" s="2">
         <v>80</v>
@@ -13747,10 +13744,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13773,17 +13770,17 @@
         <v>80</v>
       </c>
       <c r="K95" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="L95" t="s" s="2">
         <v>586</v>
       </c>
-      <c r="L95" t="s" s="2">
+      <c r="M95" t="s" s="2">
         <v>587</v>
-      </c>
-      <c r="M95" t="s" s="2">
-        <v>588</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" t="s" s="2">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>80</v>
@@ -13832,7 +13829,7 @@
         <v>80</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>78</v>
@@ -13856,10 +13853,10 @@
         <v>80</v>
       </c>
       <c r="AN95" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="AO95" t="s" s="2">
         <v>590</v>
-      </c>
-      <c r="AO95" t="s" s="2">
-        <v>591</v>
       </c>
       <c r="AP95" t="s" s="2">
         <v>80</v>
@@ -13867,10 +13864,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13893,13 +13890,13 @@
         <v>80</v>
       </c>
       <c r="K96" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="L96" t="s" s="2">
         <v>593</v>
       </c>
-      <c r="L96" t="s" s="2">
+      <c r="M96" t="s" s="2">
         <v>594</v>
-      </c>
-      <c r="M96" t="s" s="2">
-        <v>595</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -13950,7 +13947,7 @@
         <v>80</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>78</v>
@@ -13971,13 +13968,13 @@
         <v>80</v>
       </c>
       <c r="AM96" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="AN96" t="s" s="2">
         <v>596</v>
       </c>
-      <c r="AN96" t="s" s="2">
+      <c r="AO96" t="s" s="2">
         <v>597</v>
-      </c>
-      <c r="AO96" t="s" s="2">
-        <v>598</v>
       </c>
       <c r="AP96" t="s" s="2">
         <v>80</v>
@@ -13985,10 +13982,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14103,10 +14100,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14223,14 +14220,14 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
@@ -14252,10 +14249,10 @@
         <v>135</v>
       </c>
       <c r="L99" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="M99" t="s" s="2">
         <v>603</v>
-      </c>
-      <c r="M99" t="s" s="2">
-        <v>604</v>
       </c>
       <c r="N99" t="s" s="2">
         <v>138</v>
@@ -14310,7 +14307,7 @@
         <v>80</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>78</v>
@@ -14345,10 +14342,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14374,14 +14371,14 @@
         <v>147</v>
       </c>
       <c r="L100" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="M100" t="s" s="2">
         <v>607</v>
-      </c>
-      <c r="M100" t="s" s="2">
-        <v>608</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" t="s" s="2">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>80</v>
@@ -14430,7 +14427,7 @@
         <v>80</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>78</v>
@@ -14454,7 +14451,7 @@
         <v>80</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>80</v>
@@ -14465,10 +14462,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14494,10 +14491,10 @@
         <v>187</v>
       </c>
       <c r="L101" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="M101" t="s" s="2">
         <v>612</v>
-      </c>
-      <c r="M101" t="s" s="2">
-        <v>613</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -14524,14 +14521,14 @@
         <v>80</v>
       </c>
       <c r="X101" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="Y101" t="s" s="2">
         <v>614</v>
       </c>
-      <c r="Y101" t="s" s="2">
+      <c r="Z101" t="s" s="2">
         <v>615</v>
       </c>
-      <c r="Z101" t="s" s="2">
-        <v>616</v>
-      </c>
       <c r="AA101" t="s" s="2">
         <v>80</v>
       </c>
@@ -14548,7 +14545,7 @@
         <v>80</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>89</v>
@@ -14572,10 +14569,10 @@
         <v>80</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="AP101" t="s" s="2">
         <v>80</v>
@@ -14583,10 +14580,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14701,10 +14698,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14821,10 +14818,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14847,19 +14844,19 @@
         <v>90</v>
       </c>
       <c r="K104" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="L104" t="s" s="2">
         <v>621</v>
       </c>
-      <c r="L104" t="s" s="2">
+      <c r="M104" t="s" s="2">
         <v>622</v>
       </c>
-      <c r="M104" t="s" s="2">
+      <c r="N104" t="s" s="2">
         <v>623</v>
       </c>
-      <c r="N104" t="s" s="2">
+      <c r="O104" t="s" s="2">
         <v>624</v>
-      </c>
-      <c r="O104" t="s" s="2">
-        <v>625</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>80</v>
@@ -14908,7 +14905,7 @@
         <v>80</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>78</v>
@@ -14929,10 +14926,10 @@
         <v>80</v>
       </c>
       <c r="AM104" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="AN104" t="s" s="2">
         <v>627</v>
-      </c>
-      <c r="AN104" t="s" s="2">
-        <v>628</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>80</v>
@@ -14943,10 +14940,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14972,16 +14969,16 @@
         <v>163</v>
       </c>
       <c r="L105" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="M105" t="s" s="2">
         <v>630</v>
       </c>
-      <c r="M105" t="s" s="2">
+      <c r="N105" t="s" s="2">
         <v>631</v>
       </c>
-      <c r="N105" t="s" s="2">
+      <c r="O105" t="s" s="2">
         <v>632</v>
-      </c>
-      <c r="O105" t="s" s="2">
-        <v>633</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>80</v>
@@ -15030,7 +15027,7 @@
         <v>80</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>78</v>
@@ -15045,16 +15042,16 @@
         <v>101</v>
       </c>
       <c r="AK105" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="AL105" t="s" s="2">
         <v>635</v>
       </c>
-      <c r="AL105" t="s" s="2">
+      <c r="AM105" t="s" s="2">
         <v>636</v>
       </c>
-      <c r="AM105" t="s" s="2">
+      <c r="AN105" t="s" s="2">
         <v>637</v>
-      </c>
-      <c r="AN105" t="s" s="2">
-        <v>638</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>80</v>
@@ -15065,10 +15062,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15094,14 +15091,14 @@
         <v>226</v>
       </c>
       <c r="L106" t="s" s="2">
+        <v>639</v>
+      </c>
+      <c r="M106" t="s" s="2">
         <v>640</v>
-      </c>
-      <c r="M106" t="s" s="2">
-        <v>641</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>80</v>
@@ -15150,7 +15147,7 @@
         <v>80</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>78</v>
@@ -15174,10 +15171,10 @@
         <v>80</v>
       </c>
       <c r="AN106" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="AO106" t="s" s="2">
         <v>643</v>
-      </c>
-      <c r="AO106" t="s" s="2">
-        <v>644</v>
       </c>
       <c r="AP106" t="s" s="2">
         <v>80</v>
@@ -15185,10 +15182,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15214,10 +15211,10 @@
         <v>259</v>
       </c>
       <c r="L107" t="s" s="2">
+        <v>645</v>
+      </c>
+      <c r="M107" t="s" s="2">
         <v>646</v>
-      </c>
-      <c r="M107" t="s" s="2">
-        <v>647</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -15268,7 +15265,7 @@
         <v>80</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>78</v>
@@ -15292,7 +15289,7 @@
         <v>80</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>80</v>
@@ -15303,10 +15300,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15332,16 +15329,16 @@
         <v>187</v>
       </c>
       <c r="L108" t="s" s="2">
+        <v>649</v>
+      </c>
+      <c r="M108" t="s" s="2">
         <v>650</v>
       </c>
-      <c r="M108" t="s" s="2">
+      <c r="N108" t="s" s="2">
         <v>651</v>
       </c>
-      <c r="N108" t="s" s="2">
+      <c r="O108" t="s" s="2">
         <v>652</v>
-      </c>
-      <c r="O108" t="s" s="2">
-        <v>653</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>80</v>
@@ -15390,7 +15387,7 @@
         <v>80</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>78</v>
@@ -15411,13 +15408,13 @@
         <v>80</v>
       </c>
       <c r="AM108" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="AN108" t="s" s="2">
         <v>654</v>
       </c>
-      <c r="AN108" t="s" s="2">
+      <c r="AO108" t="s" s="2">
         <v>655</v>
-      </c>
-      <c r="AO108" t="s" s="2">
-        <v>656</v>
       </c>
       <c r="AP108" t="s" s="2">
         <v>80</v>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.397</t>
+    <t>0.68.401</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-10T10:13:24+00:00</t>
+    <t>2024-11-13T21:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.401</t>
+    <t>0.68.419</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-13T21:40:45+00:00</t>
+    <t>2024-11-25T07:50:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1798,7 +1798,7 @@
     <t>Needed to address the person correctly.</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFproviderGender</t>
+    <t>http://va.gov/fhir/ValueSet/providerGender</t>
   </si>
   <si>
     <t>1790: terminologyMaps using VF_providerGender on NEW PERSON - SEX (200-4)</t>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.419</t>
+    <t>0.68.424</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-25T07:50:24+00:00</t>
+    <t>2024-11-30T14:03:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.424</t>
+    <t>0.68.425</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T14:03:16+00:00</t>
+    <t>2024-11-30T15:07:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.425</t>
+    <t>0.69.436</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T15:07:22+00:00</t>
+    <t>2024-12-04T11:34:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.436</t>
+    <t>0.69.437</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T11:34:53+00:00</t>
+    <t>2024-12-04T16:25:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.437</t>
+    <t>0.69.438</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T16:25:11+00:00</t>
+    <t>2024-12-06T17:18:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.438</t>
+    <t>0.69.439</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-06T17:18:58+00:00</t>
+    <t>2024-12-07T11:18:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.439</t>
+    <t>0.69.440</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-07T11:18:15+00:00</t>
+    <t>2024-12-08T09:28:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.440</t>
+    <t>0.69.442</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-08T09:28:43+00:00</t>
+    <t>2024-12-11T20:06:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.442</t>
+    <t>0.69.448</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T20:06:32+00:00</t>
+    <t>2024-12-21T10:24:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file NEW PERSON (200) to us-core-practitioner</t>
+    <t>This StructureDefinition contains the maps for VistA file NEW PERSON (200) to us-core-practitioner.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4157" uniqueCount="656">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4157" uniqueCount="662">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.448</t>
+    <t>1.1.467</t>
   </si>
   <si>
     <t>Name</t>
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>active</t>
+    <t>draft</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-21T10:24:25+00:00</t>
+    <t>2025-01-04T09:38:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1506,6 +1506,9 @@
     <t>The home/mailing address of the practitioner is often required for employee administration purposes, and also for some rostering services where the start point (practitioners home) can be used in calculations.</t>
   </si>
   <si>
+    <t>2186: target not supported</t>
+  </si>
+  <si>
     <t>ORC-24, STF-11, ROL-11, PRT-14</t>
   </si>
   <si>
@@ -1612,6 +1615,9 @@
   </si>
   <si>
     <t>Address.line</t>
+  </si>
+  <si>
+    <t>2187: target not supported</t>
   </si>
   <si>
     <t>XAD.1 + XAD.2 (note: XAD.1 and XAD.2 have different meanings for a company address than for a person address)</t>
@@ -1642,6 +1648,9 @@
     <t>Address.city</t>
   </si>
   <si>
+    <t>2188: target not supported</t>
+  </si>
+  <si>
     <t>XAD.3</t>
   </si>
   <si>
@@ -1701,6 +1710,9 @@
     <t>Address.state</t>
   </si>
   <si>
+    <t>2189: target not supported</t>
+  </si>
+  <si>
     <t>XAD.4</t>
   </si>
   <si>
@@ -1729,6 +1741,9 @@
     <t>Address.postalCode</t>
   </si>
   <si>
+    <t>2190: target not supported</t>
+  </si>
+  <si>
     <t>XAD.5</t>
   </si>
   <si>
@@ -1751,6 +1766,9 @@
   </si>
   <si>
     <t>Address.country</t>
+  </si>
+  <si>
+    <t>2191: target not supported</t>
   </si>
   <si>
     <t>XAD.6</t>
@@ -12052,16 +12070,16 @@
         <v>101</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>80</v>
+        <v>473</v>
       </c>
       <c r="AL80" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>167</v>
@@ -12072,10 +12090,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12190,10 +12208,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12310,10 +12328,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12339,16 +12357,16 @@
         <v>109</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>80</v>
@@ -12376,10 +12394,10 @@
         <v>180</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>80</v>
@@ -12397,7 +12415,7 @@
         <v>80</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
@@ -12418,13 +12436,13 @@
         <v>80</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>358</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AP83" t="s" s="2">
         <v>80</v>
@@ -12432,10 +12450,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12461,13 +12479,13 @@
         <v>109</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -12481,7 +12499,7 @@
         <v>80</v>
       </c>
       <c r="T84" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="U84" t="s" s="2">
         <v>80</v>
@@ -12496,10 +12514,10 @@
         <v>180</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="Z84" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>80</v>
@@ -12517,7 +12535,7 @@
         <v>80</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>78</v>
@@ -12538,7 +12556,7 @@
         <v>80</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>358</v>
@@ -12552,10 +12570,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12581,13 +12599,13 @@
         <v>163</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="O85" t="s" s="2">
         <v>364</v>
@@ -12603,7 +12621,7 @@
         <v>80</v>
       </c>
       <c r="T85" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="U85" t="s" s="2">
         <v>80</v>
@@ -12639,7 +12657,7 @@
         <v>80</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>78</v>
@@ -12660,7 +12678,7 @@
         <v>80</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>369</v>
@@ -12674,10 +12692,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12688,7 +12706,7 @@
         <v>78</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>90</v>
@@ -12703,10 +12721,10 @@
         <v>163</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -12721,7 +12739,7 @@
         <v>80</v>
       </c>
       <c r="T86" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="U86" t="s" s="2">
         <v>80</v>
@@ -12757,7 +12775,7 @@
         <v>80</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>78</v>
@@ -12772,19 +12790,19 @@
         <v>101</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>80</v>
+        <v>510</v>
       </c>
       <c r="AL86" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="AO86" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="AP86" t="s" s="2">
         <v>80</v>
@@ -12792,14 +12810,14 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
@@ -12821,10 +12839,10 @@
         <v>163</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -12839,7 +12857,7 @@
         <v>80</v>
       </c>
       <c r="T87" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="U87" t="s" s="2">
         <v>80</v>
@@ -12875,7 +12893,7 @@
         <v>80</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>78</v>
@@ -12890,19 +12908,19 @@
         <v>101</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>80</v>
+        <v>520</v>
       </c>
       <c r="AL87" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="AO87" t="s" s="2">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="AP87" t="s" s="2">
         <v>80</v>
@@ -12910,14 +12928,14 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
@@ -12939,13 +12957,13 @@
         <v>163</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -12959,7 +12977,7 @@
         <v>80</v>
       </c>
       <c r="T88" t="s" s="2">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="U88" t="s" s="2">
         <v>80</v>
@@ -12995,7 +13013,7 @@
         <v>80</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>78</v>
@@ -13016,10 +13034,10 @@
         <v>80</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>80</v>
@@ -13030,14 +13048,14 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
@@ -13059,10 +13077,10 @@
         <v>163</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -13092,10 +13110,10 @@
         <v>193</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>80</v>
@@ -13113,7 +13131,7 @@
         <v>80</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>78</v>
@@ -13128,19 +13146,19 @@
         <v>101</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>80</v>
+        <v>540</v>
       </c>
       <c r="AL89" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="AP89" t="s" s="2">
         <v>80</v>
@@ -13148,14 +13166,14 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
@@ -13177,10 +13195,10 @@
         <v>163</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -13195,7 +13213,7 @@
         <v>80</v>
       </c>
       <c r="T90" t="s" s="2">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="U90" t="s" s="2">
         <v>80</v>
@@ -13231,7 +13249,7 @@
         <v>80</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>78</v>
@@ -13246,19 +13264,19 @@
         <v>101</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>80</v>
+        <v>550</v>
       </c>
       <c r="AL90" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="AP90" t="s" s="2">
         <v>80</v>
@@ -13266,10 +13284,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>549</v>
+        <v>554</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>549</v>
+        <v>554</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13295,13 +13313,13 @@
         <v>163</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>550</v>
+        <v>555</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>551</v>
+        <v>556</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>552</v>
+        <v>557</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
@@ -13351,7 +13369,7 @@
         <v>80</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>78</v>
@@ -13366,19 +13384,19 @@
         <v>101</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>80</v>
+        <v>559</v>
       </c>
       <c r="AL91" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>554</v>
+        <v>560</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>555</v>
+        <v>561</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>556</v>
+        <v>562</v>
       </c>
       <c r="AP91" t="s" s="2">
         <v>80</v>
@@ -13386,10 +13404,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>557</v>
+        <v>563</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>557</v>
+        <v>563</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13415,14 +13433,14 @@
         <v>226</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>558</v>
+        <v>564</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>559</v>
+        <v>565</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" t="s" s="2">
-        <v>560</v>
+        <v>566</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>80</v>
@@ -13435,7 +13453,7 @@
         <v>80</v>
       </c>
       <c r="T92" t="s" s="2">
-        <v>561</v>
+        <v>567</v>
       </c>
       <c r="U92" t="s" s="2">
         <v>80</v>
@@ -13471,7 +13489,7 @@
         <v>80</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>562</v>
+        <v>568</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>78</v>
@@ -13492,7 +13510,7 @@
         <v>80</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="AN92" t="s" s="2">
         <v>411</v>
@@ -13506,10 +13524,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>564</v>
+        <v>570</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>564</v>
+        <v>570</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13535,14 +13553,14 @@
         <v>109</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>566</v>
+        <v>572</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" t="s" s="2">
-        <v>567</v>
+        <v>573</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>80</v>
@@ -13571,7 +13589,7 @@
       </c>
       <c r="Y93" s="2"/>
       <c r="Z93" t="s" s="2">
-        <v>568</v>
+        <v>574</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>80</v>
@@ -13589,7 +13607,7 @@
         <v>80</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>564</v>
+        <v>570</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>78</v>
@@ -13604,19 +13622,19 @@
         <v>101</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>570</v>
+        <v>576</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>571</v>
+        <v>577</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>572</v>
+        <v>578</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>573</v>
+        <v>579</v>
       </c>
       <c r="AP93" t="s" s="2">
         <v>80</v>
@@ -13624,10 +13642,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>574</v>
+        <v>580</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>574</v>
+        <v>580</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13650,17 +13668,17 @@
         <v>90</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>575</v>
+        <v>581</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>576</v>
+        <v>582</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>577</v>
+        <v>583</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" t="s" s="2">
-        <v>578</v>
+        <v>584</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>80</v>
@@ -13709,7 +13727,7 @@
         <v>80</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>574</v>
+        <v>580</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>78</v>
@@ -13724,19 +13742,19 @@
         <v>101</v>
       </c>
       <c r="AK94" t="s" s="2">
-        <v>579</v>
+        <v>585</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>580</v>
+        <v>586</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>581</v>
+        <v>587</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>582</v>
+        <v>588</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>583</v>
+        <v>589</v>
       </c>
       <c r="AP94" t="s" s="2">
         <v>80</v>
@@ -13744,10 +13762,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>584</v>
+        <v>590</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>584</v>
+        <v>590</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13770,17 +13788,17 @@
         <v>80</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>585</v>
+        <v>591</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>586</v>
+        <v>592</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>587</v>
+        <v>593</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" t="s" s="2">
-        <v>588</v>
+        <v>594</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>80</v>
@@ -13829,7 +13847,7 @@
         <v>80</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>584</v>
+        <v>590</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>78</v>
@@ -13853,10 +13871,10 @@
         <v>80</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>589</v>
+        <v>595</v>
       </c>
       <c r="AO95" t="s" s="2">
-        <v>590</v>
+        <v>596</v>
       </c>
       <c r="AP95" t="s" s="2">
         <v>80</v>
@@ -13864,10 +13882,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>591</v>
+        <v>597</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>591</v>
+        <v>597</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13890,13 +13908,13 @@
         <v>80</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>592</v>
+        <v>598</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>593</v>
+        <v>599</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>594</v>
+        <v>600</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -13947,7 +13965,7 @@
         <v>80</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>591</v>
+        <v>597</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>78</v>
@@ -13968,13 +13986,13 @@
         <v>80</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>595</v>
+        <v>601</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="AO96" t="s" s="2">
-        <v>597</v>
+        <v>603</v>
       </c>
       <c r="AP96" t="s" s="2">
         <v>80</v>
@@ -13982,10 +14000,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>598</v>
+        <v>604</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>598</v>
+        <v>604</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14100,10 +14118,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>599</v>
+        <v>605</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>599</v>
+        <v>605</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14220,14 +14238,14 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>600</v>
+        <v>606</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>600</v>
+        <v>606</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>601</v>
+        <v>607</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
@@ -14249,10 +14267,10 @@
         <v>135</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>602</v>
+        <v>608</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>603</v>
+        <v>609</v>
       </c>
       <c r="N99" t="s" s="2">
         <v>138</v>
@@ -14307,7 +14325,7 @@
         <v>80</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>604</v>
+        <v>610</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>78</v>
@@ -14342,10 +14360,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>605</v>
+        <v>611</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>605</v>
+        <v>611</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14371,14 +14389,14 @@
         <v>147</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>606</v>
+        <v>612</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>607</v>
+        <v>613</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" t="s" s="2">
-        <v>608</v>
+        <v>614</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>80</v>
@@ -14427,7 +14445,7 @@
         <v>80</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>605</v>
+        <v>611</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>78</v>
@@ -14451,7 +14469,7 @@
         <v>80</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>609</v>
+        <v>615</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>80</v>
@@ -14462,10 +14480,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>610</v>
+        <v>616</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>610</v>
+        <v>616</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14491,10 +14509,10 @@
         <v>187</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>611</v>
+        <v>617</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>612</v>
+        <v>618</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -14521,13 +14539,13 @@
         <v>80</v>
       </c>
       <c r="X101" t="s" s="2">
-        <v>613</v>
+        <v>619</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>614</v>
+        <v>620</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>615</v>
+        <v>621</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>80</v>
@@ -14545,7 +14563,7 @@
         <v>80</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>610</v>
+        <v>616</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>89</v>
@@ -14569,10 +14587,10 @@
         <v>80</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>616</v>
+        <v>622</v>
       </c>
       <c r="AP101" t="s" s="2">
         <v>80</v>
@@ -14580,10 +14598,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>617</v>
+        <v>623</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>617</v>
+        <v>623</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14698,10 +14716,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>618</v>
+        <v>624</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>618</v>
+        <v>624</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14818,10 +14836,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>619</v>
+        <v>625</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>619</v>
+        <v>625</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14844,19 +14862,19 @@
         <v>90</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>620</v>
+        <v>626</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>621</v>
+        <v>627</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>622</v>
+        <v>628</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>623</v>
+        <v>629</v>
       </c>
       <c r="O104" t="s" s="2">
-        <v>624</v>
+        <v>630</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>80</v>
@@ -14905,7 +14923,7 @@
         <v>80</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>625</v>
+        <v>631</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>78</v>
@@ -14926,10 +14944,10 @@
         <v>80</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>626</v>
+        <v>632</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>627</v>
+        <v>633</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>80</v>
@@ -14940,10 +14958,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>628</v>
+        <v>634</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>628</v>
+        <v>634</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14969,16 +14987,16 @@
         <v>163</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>629</v>
+        <v>635</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>630</v>
+        <v>636</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>631</v>
+        <v>637</v>
       </c>
       <c r="O105" t="s" s="2">
-        <v>632</v>
+        <v>638</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>80</v>
@@ -15027,7 +15045,7 @@
         <v>80</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>633</v>
+        <v>639</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>78</v>
@@ -15042,16 +15060,16 @@
         <v>101</v>
       </c>
       <c r="AK105" t="s" s="2">
-        <v>634</v>
+        <v>640</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>635</v>
+        <v>641</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>636</v>
+        <v>642</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>637</v>
+        <v>643</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>80</v>
@@ -15062,10 +15080,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>638</v>
+        <v>644</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>638</v>
+        <v>644</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15091,14 +15109,14 @@
         <v>226</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>639</v>
+        <v>645</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>640</v>
+        <v>646</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" t="s" s="2">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>80</v>
@@ -15147,7 +15165,7 @@
         <v>80</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>638</v>
+        <v>644</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>78</v>
@@ -15171,10 +15189,10 @@
         <v>80</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>642</v>
+        <v>648</v>
       </c>
       <c r="AO106" t="s" s="2">
-        <v>643</v>
+        <v>649</v>
       </c>
       <c r="AP106" t="s" s="2">
         <v>80</v>
@@ -15182,10 +15200,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>644</v>
+        <v>650</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>644</v>
+        <v>650</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15211,10 +15229,10 @@
         <v>259</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>645</v>
+        <v>651</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>646</v>
+        <v>652</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -15265,7 +15283,7 @@
         <v>80</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>644</v>
+        <v>650</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>78</v>
@@ -15289,7 +15307,7 @@
         <v>80</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>80</v>
@@ -15300,10 +15318,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15329,16 +15347,16 @@
         <v>187</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>649</v>
+        <v>655</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>650</v>
+        <v>656</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>651</v>
+        <v>657</v>
       </c>
       <c r="O108" t="s" s="2">
-        <v>652</v>
+        <v>658</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>80</v>
@@ -15387,7 +15405,7 @@
         <v>80</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>78</v>
@@ -15408,13 +15426,13 @@
         <v>80</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>653</v>
+        <v>659</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>654</v>
+        <v>660</v>
       </c>
       <c r="AO108" t="s" s="2">
-        <v>655</v>
+        <v>661</v>
       </c>
       <c r="AP108" t="s" s="2">
         <v>80</v>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.467</t>
+    <t>1.1.468</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T09:38:39+00:00</t>
+    <t>2025-01-04T15:04:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.468</t>
+    <t>1.1.477</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T15:04:27+00:00</t>
+    <t>2025-01-07T16:27:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.477</t>
+    <t>1.1.478</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-07T16:27:08+00:00</t>
+    <t>2025-01-13T09:39:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.478</t>
+    <t>1.1.487</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-13T09:39:57+00:00</t>
+    <t>2025-01-17T12:09:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -703,7 +703,7 @@
     <t>Identifier.value</t>
   </si>
   <si>
-    <t>376: source value from NEW PERSON - NPI (200-41.99)</t>
+    <t>376: source value based on NEW PERSON - NPI (200-41.99)</t>
   </si>
   <si>
     <t>SStaff.PrescribingProvider.NPI,SStaff.SStaff.NPI</t>
@@ -784,7 +784,7 @@
 </t>
   </si>
   <si>
-    <t>380: source value from NEW PERSON - EFFECTIVE DATE/TIME (200-42)</t>
+    <t>380: source value based on NEW PERSON - EFFECTIVE DATE/TIME (200-42)</t>
   </si>
   <si>
     <t>DR.1</t>
@@ -892,7 +892,7 @@
     <t>Practitioner.identifier:va-DEA.value</t>
   </si>
   <si>
-    <t>377: source value from NEW PERSON - DEA# (200-53.2)</t>
+    <t>377: source value based on NEW PERSON - DEA# (200-53.2)</t>
   </si>
   <si>
     <t>SStaff.PrescribingProvider.DEA,SStaff.SStaff.DEA</t>
@@ -945,7 +945,7 @@
     <t>Practitioner.identifier:va-nr.value</t>
   </si>
   <si>
-    <t>378: source value from NEW PERSON - VA# (200-53.3)</t>
+    <t>378: source value based on NEW PERSON - VA# (200-53.3)</t>
   </si>
   <si>
     <t>SStaff.PrescribingProvider.VANumber,SStaff.SStaff.VANumber</t>
@@ -995,7 +995,7 @@
     <t>Practitioner.identifier:va-VPID.value</t>
   </si>
   <si>
-    <t>379: source value from NEW PERSON - VPID (200-9000)</t>
+    <t>379: source value based on NEW PERSON - VPID (200-9000)</t>
   </si>
   <si>
     <t>SStaff.PrescribingProvider.VPID,SStaff.SStaff.VAPersonIdentificationNumber</t>
@@ -1048,7 +1048,7 @@
     <t>Practitioner.identifier:va-IEN.value</t>
   </si>
   <si>
-    <t>415: source value from NEW PERSON - IEN (200-.001)</t>
+    <t>415: source value based on NEW PERSON - IEN (200-.001)</t>
   </si>
   <si>
     <t>Practitioner.identifier:va-IEN.period</t>
@@ -1178,7 +1178,7 @@
     <t>HumanName.text</t>
   </si>
   <si>
-    <t>382: source value from NEW PERSON - NAME COMPONENTS &gt; NAME COMPONENTS - (200-10.1 &gt; 20-)</t>
+    <t>382: source value based on NEW PERSON - NAME COMPONENTS &gt; NAME COMPONENTS - (200-10.1 &gt; 20-)</t>
   </si>
   <si>
     <t>SStaff.SStaff.FirstName,SStaff.SStaff.LastName,SStaff.SStaff.MiddleName,SStaff.SStaff.StaffNamePrefix,SStaff.SStaff.StaffNameSuffix</t>
@@ -1209,7 +1209,7 @@
     <t>HumanName.family</t>
   </si>
   <si>
-    <t>382-1: source value from NEW PERSON - NAME COMPONENTS &gt; NAME COMPONENTS - FAMILY (LAST) NAME (200-10.1 &gt; 20-1)</t>
+    <t>382-1: source value based on NEW PERSON - NAME COMPONENTS &gt; NAME COMPONENTS - FAMILY (LAST) NAME (200-10.1 &gt; 20-1)</t>
   </si>
   <si>
     <t>XPN.1/FN.1</t>
@@ -1240,7 +1240,7 @@
     <t>HumanName.given</t>
   </si>
   <si>
-    <t>382-2: source value from NEW PERSON - NAME COMPONENTS &gt; NAME COMPONENTS - GIVEN (FIRST) NAME (200-10.1 &gt; 20-2)</t>
+    <t>382-2: source value based on NEW PERSON - NAME COMPONENTS &gt; NAME COMPONENTS - GIVEN (FIRST) NAME (200-10.1 &gt; 20-2)</t>
   </si>
   <si>
     <t>XPN.2 + XPN.3</t>
@@ -1264,7 +1264,7 @@
     <t>HumanName.prefix</t>
   </si>
   <si>
-    <t>382-3: source value from NEW PERSON - NAME COMPONENTS &gt; NAME COMPONENTS - PREFIX (200-10.1 &gt; 20-4)</t>
+    <t>382-3: source value based on NEW PERSON - NAME COMPONENTS &gt; NAME COMPONENTS - PREFIX (200-10.1 &gt; 20-4)</t>
   </si>
   <si>
     <t>XPN.5</t>
@@ -1288,7 +1288,7 @@
     <t>HumanName.suffix</t>
   </si>
   <si>
-    <t>382-4: source value from NEW PERSON - NAME COMPONENTS &gt; NAME COMPONENTS - SUFFIX (200-10.1 &gt; 20-5)</t>
+    <t>382-4: source value based on NEW PERSON - NAME COMPONENTS &gt; NAME COMPONENTS - SUFFIX (200-10.1 &gt; 20-5)</t>
   </si>
   <si>
     <t>XPN/4</t>
@@ -1407,7 +1407,7 @@
     <t>ContactPoint.value</t>
   </si>
   <si>
-    <t>383: source value from NEW PERSON - PHONE (HOME) (200-.131)</t>
+    <t>383: source value based on NEW PERSON - PHONE (HOME) (200-.131)</t>
   </si>
   <si>
     <t>SStaff.PrescribingProvider.HomePhone,SStaff.SStaff.HomePhone</t>
@@ -1850,7 +1850,7 @@
     <t>Needed for identification.</t>
   </si>
   <si>
-    <t>394: source value from NEW PERSON - DOB (200-5)</t>
+    <t>394: source value based on NEW PERSON - DOB (200-5)</t>
   </si>
   <si>
     <t>SStaff.SStaff.BirthDateTime,Staff.Staff.BirthDateTime</t>
@@ -2020,7 +2020,7 @@
     <t>CodeableConcept.text</t>
   </si>
   <si>
-    <t>395: source value from NEW PERSON - DEGREE (200-10.6)</t>
+    <t>395: source value based on NEW PERSON - DEGREE (200-10.6)</t>
   </si>
   <si>
     <t>SStaff.SStaff.Degree,Staff.Staff.Degree</t>
@@ -2438,7 +2438,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="117.74609375" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="121.83984375" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="123.75" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="107.3984375" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="102.6171875" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.487</t>
+    <t>1.1.491</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T12:09:20+00:00</t>
+    <t>2025-01-17T13:37:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.491</t>
+    <t>1.1.494</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T13:37:46+00:00</t>
+    <t>2025-01-25T09:28:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.494</t>
+    <t>1.1.500</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-25T09:28:03+00:00</t>
+    <t>2025-02-01T09:13:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4157" uniqueCount="662">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4158" uniqueCount="663">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.500</t>
+    <t>1.2.512</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-01T09:13:38+00:00</t>
+    <t>2025-02-05T16:47:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1814,6 +1814,9 @@
   </si>
   <si>
     <t>Needed to address the person correctly.</t>
+  </si>
+  <si>
+    <t>see mapping [VF_providerGender](ConceptMap-VF-providerGender.html)</t>
   </si>
   <si>
     <t>http://va.gov/fhir/ValueSet/providerGender</t>
@@ -13587,9 +13590,11 @@
       <c r="X93" t="s" s="2">
         <v>180</v>
       </c>
-      <c r="Y93" s="2"/>
+      <c r="Y93" t="s" s="2">
+        <v>574</v>
+      </c>
       <c r="Z93" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>80</v>
@@ -13622,19 +13627,19 @@
         <v>101</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AP93" t="s" s="2">
         <v>80</v>
@@ -13642,10 +13647,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13668,17 +13673,17 @@
         <v>90</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>80</v>
@@ -13727,7 +13732,7 @@
         <v>80</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>78</v>
@@ -13742,19 +13747,19 @@
         <v>101</v>
       </c>
       <c r="AK94" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="AP94" t="s" s="2">
         <v>80</v>
@@ -13762,10 +13767,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13788,17 +13793,17 @@
         <v>80</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>80</v>
@@ -13847,7 +13852,7 @@
         <v>80</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>78</v>
@@ -13871,10 +13876,10 @@
         <v>80</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AO95" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="AP95" t="s" s="2">
         <v>80</v>
@@ -13882,10 +13887,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13908,13 +13913,13 @@
         <v>80</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -13965,7 +13970,7 @@
         <v>80</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>78</v>
@@ -13986,13 +13991,13 @@
         <v>80</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="AO96" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="AP96" t="s" s="2">
         <v>80</v>
@@ -14000,10 +14005,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14118,10 +14123,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14238,14 +14243,14 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
@@ -14267,10 +14272,10 @@
         <v>135</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="N99" t="s" s="2">
         <v>138</v>
@@ -14325,7 +14330,7 @@
         <v>80</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>78</v>
@@ -14360,10 +14365,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14389,14 +14394,14 @@
         <v>147</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>80</v>
@@ -14445,7 +14450,7 @@
         <v>80</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>78</v>
@@ -14469,7 +14474,7 @@
         <v>80</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>80</v>
@@ -14480,10 +14485,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14509,10 +14514,10 @@
         <v>187</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -14539,13 +14544,13 @@
         <v>80</v>
       </c>
       <c r="X101" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>80</v>
@@ -14563,7 +14568,7 @@
         <v>80</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>89</v>
@@ -14587,10 +14592,10 @@
         <v>80</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="AP101" t="s" s="2">
         <v>80</v>
@@ -14598,10 +14603,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14716,10 +14721,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14836,10 +14841,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14862,19 +14867,19 @@
         <v>90</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="O104" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>80</v>
@@ -14923,7 +14928,7 @@
         <v>80</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>78</v>
@@ -14944,10 +14949,10 @@
         <v>80</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>80</v>
@@ -14958,10 +14963,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14987,16 +14992,16 @@
         <v>163</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="O105" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>80</v>
@@ -15045,7 +15050,7 @@
         <v>80</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>78</v>
@@ -15060,16 +15065,16 @@
         <v>101</v>
       </c>
       <c r="AK105" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>80</v>
@@ -15080,10 +15085,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15109,14 +15114,14 @@
         <v>226</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>80</v>
@@ -15165,7 +15170,7 @@
         <v>80</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>78</v>
@@ -15189,10 +15194,10 @@
         <v>80</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="AO106" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="AP106" t="s" s="2">
         <v>80</v>
@@ -15200,10 +15205,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15229,10 +15234,10 @@
         <v>259</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -15283,7 +15288,7 @@
         <v>80</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>78</v>
@@ -15307,7 +15312,7 @@
         <v>80</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>80</v>
@@ -15318,10 +15323,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15347,16 +15352,16 @@
         <v>187</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="O108" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>80</v>
@@ -15405,7 +15410,7 @@
         <v>80</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>78</v>
@@ -15426,13 +15431,13 @@
         <v>80</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="AO108" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="AP108" t="s" s="2">
         <v>80</v>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T16:47:13+00:00</t>
+    <t>2025-02-05T17:20:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.512</t>
+    <t>1.2.520</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T17:20:26+00:00</t>
+    <t>2025-02-08T12:00:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.520</t>
+    <t>1.2.529</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-08T12:00:09+00:00</t>
+    <t>2025-02-20T14:56:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.529</t>
+    <t>1.2.531</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:56:35+00:00</t>
+    <t>2025-02-22T09:54:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.531</t>
+    <t>1.2.537</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-22T09:54:59+00:00</t>
+    <t>2025-02-24T13:20:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T13:20:37+00:00</t>
+    <t>2025-02-25T20:49:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.537</t>
+    <t>1.2.540</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-25T20:49:13+00:00</t>
+    <t>2025-03-11T10:08:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.540</t>
+    <t>1.3.557</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T10:08:33+00:00</t>
+    <t>2025-03-15T09:48:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.557</t>
+    <t>1.3.574</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-15T09:48:09+00:00</t>
+    <t>2025-03-22T10:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.574</t>
+    <t>1.3.575</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:33:38+00:00</t>
+    <t>2025-03-22T10:56:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.575</t>
+    <t>1.3.578</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:56:07+00:00</t>
+    <t>2025-03-23T10:22:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.578</t>
+    <t>1.3.580</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T10:22:17+00:00</t>
+    <t>2025-03-23T13:19:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Practitioner.xlsx
+++ b/docs/StructureDefinition-Practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.580</t>
+    <t>1.4.588</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T13:19:29+00:00</t>
+    <t>2025-04-01T14:43:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
